--- a/시간표.xlsx
+++ b/시간표.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="103">
   <si>
     <r>
       <rPr>
@@ -390,6 +390,117 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">미술학원
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF9C4A16"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">15:00–16:00
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF9C4A16"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">새로 추가</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">15:30</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF9C4A16"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">한글수업
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF9C4A16"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">15:50–16:20
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF9C4A16"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">한글교실</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">16:00</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF9C4A16"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">피아노
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF9C4A16"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">16:00–16:30
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF9C4A16"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">피아노학원</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF9C4A16"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">태권도
 </t>
     </r>
@@ -402,7 +513,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">15:00–16:00
+      <t xml:space="preserve">16:00–17:00
 </t>
     </r>
     <r>
@@ -414,82 +525,6 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">둘째와 함께</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">15:30</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF9C4A16"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">한글수업
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF9C4A16"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">15:50–16:20
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF9C4A16"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">한글교실</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">16:00</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF9C4A16"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">피아노
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF9C4A16"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">16:00–16:30
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF9C4A16"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">피아노학원</t>
     </r>
   </si>
   <si>
@@ -815,6 +850,41 @@
       <rPr>
         <b val="true"/>
         <sz val="10"/>
+        <color rgb="FF1F4E79"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">어린이집
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F4E79"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">09:10–15:30
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F4E79"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">하원 시간 늘림</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
         <color rgb="FF9C4A16"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
@@ -866,7 +936,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">15:00–16:00
+      <t xml:space="preserve">16:00–17:00
 </t>
     </r>
     <r>
@@ -1223,6 +1293,12 @@
     <t xml:space="preserve">방과후 종이접기</t>
   </si>
   <si>
+    <t xml:space="preserve">미술학원</t>
+  </si>
+  <si>
+    <t xml:space="preserve">새로 추가</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -1246,7 +1322,29 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">이모님</t>
+      <t xml:space="preserve">이모님 픽업</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">둘째</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09:10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">어린이집</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16:50</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">태권도 위해 일찍 하원 </t>
     </r>
     <r>
       <rPr>
@@ -1263,7 +1361,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">둘째 하원→첫째 하교→태권도</t>
+      <t xml:space="preserve">확인 필요</t>
     </r>
     <r>
       <rPr>
@@ -1276,54 +1374,6 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">둘째</t>
-  </si>
-  <si>
-    <t xml:space="preserve">09:10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">어린이집</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16:50</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">태권도 위해 일찍 하원 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">확인 필요</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -1349,6 +1399,9 @@
       </rPr>
       <t xml:space="preserve">이모님 픽업</t>
     </r>
+  </si>
+  <si>
+    <t xml:space="preserve">하원 시간 늘림</t>
   </si>
 </sst>
 </file>
@@ -2470,7 +2523,9 @@
       </c>
       <c r="D35" s="5"/>
       <c r="E35" s="5"/>
-      <c r="F35" s="5"/>
+      <c r="F35" s="9" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="6"/>
@@ -2478,17 +2533,17 @@
       <c r="C36" s="9"/>
       <c r="D36" s="5"/>
       <c r="E36" s="5"/>
-      <c r="F36" s="5"/>
+      <c r="F36" s="9"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5"/>
       <c r="D37" s="5"/>
       <c r="E37" s="5"/>
-      <c r="F37" s="5"/>
+      <c r="F37" s="9"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="6"/>
@@ -2496,17 +2551,17 @@
       <c r="C38" s="5"/>
       <c r="D38" s="5"/>
       <c r="E38" s="5"/>
-      <c r="F38" s="5"/>
+      <c r="F38" s="9"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5"/>
       <c r="D39" s="5"/>
       <c r="E39" s="9" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F39" s="5"/>
     </row>
@@ -2520,7 +2575,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5"/>
@@ -2538,31 +2593,31 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="11" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B44" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C44" s="13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D44" s="14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E44" s="15" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F44" s="16" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="17" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="21">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="B4:B5"/>
     <mergeCell ref="C4:C5"/>
@@ -2582,6 +2637,7 @@
     <mergeCell ref="F31:F34"/>
     <mergeCell ref="B34:B36"/>
     <mergeCell ref="C35:C36"/>
+    <mergeCell ref="F35:F38"/>
     <mergeCell ref="E39:E41"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -2608,7 +2664,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="18" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -2677,19 +2733,19 @@
         <v>12</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C7" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="D7" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D7" s="8" t="s">
-        <v>47</v>
-      </c>
       <c r="E7" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2868,11 +2924,11 @@
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="9" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D27" s="5"/>
       <c r="E27" s="5"/>
-      <c r="F27" s="5"/>
+      <c r="F27" s="8"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="6"/>
@@ -2880,7 +2936,7 @@
       <c r="C28" s="9"/>
       <c r="D28" s="5"/>
       <c r="E28" s="5"/>
-      <c r="F28" s="5"/>
+      <c r="F28" s="8"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
@@ -2890,7 +2946,7 @@
       <c r="C29" s="9"/>
       <c r="D29" s="5"/>
       <c r="E29" s="5"/>
-      <c r="F29" s="5"/>
+      <c r="F29" s="8"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="6"/>
@@ -2898,7 +2954,7 @@
       <c r="C30" s="9"/>
       <c r="D30" s="5"/>
       <c r="E30" s="5"/>
-      <c r="F30" s="5"/>
+      <c r="F30" s="8"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
@@ -2908,9 +2964,7 @@
       <c r="C31" s="5"/>
       <c r="D31" s="5"/>
       <c r="E31" s="5"/>
-      <c r="F31" s="9" t="s">
-        <v>50</v>
-      </c>
+      <c r="F31" s="8"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="6"/>
@@ -2918,7 +2972,7 @@
       <c r="C32" s="5"/>
       <c r="D32" s="5"/>
       <c r="E32" s="5"/>
-      <c r="F32" s="9"/>
+      <c r="F32" s="8"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="6" t="s">
@@ -2928,7 +2982,7 @@
       <c r="C33" s="5"/>
       <c r="D33" s="5"/>
       <c r="E33" s="5"/>
-      <c r="F33" s="9"/>
+      <c r="F33" s="5"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="6"/>
@@ -2936,7 +2990,7 @@
       <c r="C34" s="5"/>
       <c r="D34" s="5"/>
       <c r="E34" s="5"/>
-      <c r="F34" s="9"/>
+      <c r="F34" s="5"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="4" t="s">
@@ -2946,29 +3000,31 @@
       <c r="C35" s="5"/>
       <c r="D35" s="5"/>
       <c r="E35" s="5"/>
-      <c r="F35" s="5"/>
+      <c r="F35" s="9" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="6"/>
       <c r="B36" s="9" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C36" s="5"/>
       <c r="D36" s="5"/>
       <c r="E36" s="5"/>
-      <c r="F36" s="5"/>
+      <c r="F36" s="9"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B37" s="9"/>
       <c r="C37" s="5"/>
       <c r="D37" s="9" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E37" s="5"/>
-      <c r="F37" s="5"/>
+      <c r="F37" s="9"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="6"/>
@@ -2976,11 +3032,11 @@
       <c r="C38" s="5"/>
       <c r="D38" s="9"/>
       <c r="E38" s="5"/>
-      <c r="F38" s="5"/>
+      <c r="F38" s="9"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5"/>
@@ -2998,7 +3054,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5"/>
@@ -3016,27 +3072,27 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="11" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B44" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C44" s="13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D44" s="14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E44" s="15" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F44" s="16" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="17" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -3046,9 +3102,9 @@
     <mergeCell ref="C7:C26"/>
     <mergeCell ref="D7:D26"/>
     <mergeCell ref="E7:E26"/>
-    <mergeCell ref="F7:F26"/>
+    <mergeCell ref="F7:F32"/>
     <mergeCell ref="C27:C30"/>
-    <mergeCell ref="F31:F34"/>
+    <mergeCell ref="F35:F38"/>
     <mergeCell ref="B36:B38"/>
     <mergeCell ref="D37:D38"/>
   </mergeCells>
@@ -3067,7 +3123,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="7"/>
@@ -3081,7 +3137,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="19" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -3093,177 +3149,177 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="20" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B2" s="20" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C2" s="20" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D2" s="20" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F2" s="20" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G2" s="20" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H2" s="20" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="21" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B3" s="22" t="s">
         <v>2</v>
       </c>
       <c r="C3" s="23" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D3" s="23" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E3" s="24" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F3" s="25" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G3" s="24" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H3" s="24"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="21" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B4" s="22" t="s">
         <v>2</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D4" s="23" t="s">
         <v>23</v>
       </c>
       <c r="E4" s="24" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F4" s="26" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G4" s="24" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H4" s="24"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="21" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B5" s="22" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="23" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D5" s="23" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E5" s="24" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F5" s="27" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G5" s="24" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H5" s="24"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="21" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B6" s="22" t="s">
         <v>2</v>
       </c>
       <c r="C6" s="23" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D6" s="23" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E6" s="24" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F6" s="28" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G6" s="24" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H6" s="24"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="21" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B7" s="22" t="s">
         <v>3</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D7" s="23" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E7" s="24" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F7" s="25" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G7" s="24" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H7" s="24"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="21" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B8" s="22" t="s">
         <v>3</v>
       </c>
       <c r="C8" s="23" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D8" s="23" t="s">
         <v>23</v>
       </c>
       <c r="E8" s="24" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F8" s="26" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G8" s="24" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H8" s="24"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="21" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B9" s="22" t="s">
         <v>3</v>
@@ -3275,21 +3331,21 @@
         <v>29</v>
       </c>
       <c r="E9" s="24" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F9" s="28" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G9" s="24" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H9" s="24" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="21" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B10" s="22" t="s">
         <v>3</v>
@@ -3298,70 +3354,70 @@
         <v>33</v>
       </c>
       <c r="D10" s="23" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E10" s="24" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F10" s="28" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G10" s="24" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H10" s="24"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="21" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B11" s="22" t="s">
         <v>4</v>
       </c>
       <c r="C11" s="23" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D11" s="23" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E11" s="24" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F11" s="25" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G11" s="24" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H11" s="24"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="21" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B12" s="22" t="s">
         <v>4</v>
       </c>
       <c r="C12" s="23" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D12" s="23" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E12" s="24" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F12" s="26" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G12" s="24" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H12" s="24"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="21" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B13" s="22" t="s">
         <v>4</v>
@@ -3373,187 +3429,187 @@
         <v>26</v>
       </c>
       <c r="E13" s="24" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F13" s="28" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G13" s="24" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H13" s="24"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="21" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B14" s="22" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="23" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D14" s="23" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E14" s="24" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F14" s="25" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G14" s="24" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H14" s="24"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="21" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B15" s="22" t="s">
         <v>5</v>
       </c>
       <c r="C15" s="23" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D15" s="23" t="s">
         <v>23</v>
       </c>
       <c r="E15" s="24" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F15" s="26" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G15" s="24" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H15" s="24"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="21" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B16" s="22" t="s">
         <v>5</v>
       </c>
       <c r="C16" s="23" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D16" s="23" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E16" s="24" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F16" s="27" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G16" s="24" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H16" s="24"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="21" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B17" s="22" t="s">
         <v>5</v>
       </c>
       <c r="C17" s="23" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D17" s="23" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E17" s="24" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F17" s="28" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G17" s="24" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H17" s="24"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="21" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B18" s="22" t="s">
         <v>6</v>
       </c>
       <c r="C18" s="23" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D18" s="23" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E18" s="24" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F18" s="25" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G18" s="24" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H18" s="24"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="21" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B19" s="22" t="s">
         <v>6</v>
       </c>
       <c r="C19" s="23" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D19" s="23" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E19" s="24" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F19" s="26" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G19" s="24" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H19" s="24"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="21" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B20" s="22" t="s">
         <v>6</v>
       </c>
       <c r="C20" s="23" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D20" s="23" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E20" s="24" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F20" s="27" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G20" s="24" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H20" s="24"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="21" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B21" s="22" t="s">
         <v>6</v>
@@ -3565,238 +3621,266 @@
         <v>33</v>
       </c>
       <c r="E21" s="24" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="F21" s="28" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G21" s="24" t="s">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="H21" s="24" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="29" t="s">
-        <v>92</v>
+      <c r="A22" s="21" t="s">
+        <v>64</v>
       </c>
       <c r="B22" s="22" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C22" s="23" t="s">
-        <v>93</v>
+        <v>33</v>
       </c>
       <c r="D22" s="23" t="s">
-        <v>69</v>
+        <v>37</v>
       </c>
       <c r="E22" s="24" t="s">
-        <v>94</v>
-      </c>
-      <c r="F22" s="26" t="s">
-        <v>40</v>
+        <v>79</v>
+      </c>
+      <c r="F22" s="28" t="s">
+        <v>43</v>
       </c>
       <c r="G22" s="24" t="s">
-        <v>94</v>
-      </c>
-      <c r="H22" s="24"/>
+        <v>80</v>
+      </c>
+      <c r="H22" s="24" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="29" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B23" s="22" t="s">
         <v>2</v>
       </c>
       <c r="C23" s="23" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="D23" s="23" t="s">
-        <v>95</v>
+        <v>71</v>
       </c>
       <c r="E23" s="24" t="s">
-        <v>75</v>
-      </c>
-      <c r="F23" s="28" t="s">
-        <v>42</v>
+        <v>98</v>
+      </c>
+      <c r="F23" s="26" t="s">
+        <v>41</v>
       </c>
       <c r="G23" s="24" t="s">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="H23" s="24"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="29" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B24" s="22" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C24" s="23" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="D24" s="23" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="E24" s="24" t="s">
-        <v>94</v>
-      </c>
-      <c r="F24" s="26" t="s">
-        <v>40</v>
+        <v>77</v>
+      </c>
+      <c r="F24" s="28" t="s">
+        <v>43</v>
       </c>
       <c r="G24" s="24" t="s">
-        <v>94</v>
-      </c>
-      <c r="H24" s="24" t="s">
-        <v>96</v>
-      </c>
+        <v>78</v>
+      </c>
+      <c r="H24" s="24"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="29" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B25" s="22" t="s">
         <v>3</v>
       </c>
       <c r="C25" s="23" t="s">
-        <v>26</v>
+        <v>97</v>
       </c>
       <c r="D25" s="23" t="s">
-        <v>29</v>
+        <v>71</v>
       </c>
       <c r="E25" s="24" t="s">
-        <v>77</v>
-      </c>
-      <c r="F25" s="28" t="s">
-        <v>42</v>
+        <v>98</v>
+      </c>
+      <c r="F25" s="26" t="s">
+        <v>41</v>
       </c>
       <c r="G25" s="24" t="s">
-        <v>78</v>
+        <v>98</v>
       </c>
       <c r="H25" s="24" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="29" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B26" s="22" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C26" s="23" t="s">
-        <v>93</v>
+        <v>26</v>
       </c>
       <c r="D26" s="23" t="s">
-        <v>69</v>
+        <v>29</v>
       </c>
       <c r="E26" s="24" t="s">
-        <v>94</v>
-      </c>
-      <c r="F26" s="26" t="s">
-        <v>40</v>
+        <v>79</v>
+      </c>
+      <c r="F26" s="28" t="s">
+        <v>43</v>
       </c>
       <c r="G26" s="24" t="s">
-        <v>94</v>
-      </c>
-      <c r="H26" s="24"/>
+        <v>80</v>
+      </c>
+      <c r="H26" s="24" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="29" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B27" s="22" t="s">
         <v>4</v>
       </c>
       <c r="C27" s="23" t="s">
-        <v>35</v>
+        <v>97</v>
       </c>
       <c r="D27" s="23" t="s">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="E27" s="24" t="s">
-        <v>75</v>
-      </c>
-      <c r="F27" s="28" t="s">
-        <v>42</v>
+        <v>98</v>
+      </c>
+      <c r="F27" s="26" t="s">
+        <v>41</v>
       </c>
       <c r="G27" s="24" t="s">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="H27" s="24"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="29" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B28" s="22" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C28" s="23" t="s">
-        <v>93</v>
+        <v>36</v>
       </c>
       <c r="D28" s="23" t="s">
-        <v>69</v>
+        <v>37</v>
       </c>
       <c r="E28" s="24" t="s">
-        <v>94</v>
-      </c>
-      <c r="F28" s="26" t="s">
-        <v>40</v>
+        <v>77</v>
+      </c>
+      <c r="F28" s="28" t="s">
+        <v>43</v>
       </c>
       <c r="G28" s="24" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="H28" s="24"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="29" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B29" s="22" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C29" s="23" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="D29" s="23" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E29" s="24" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F29" s="26" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G29" s="24" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="H29" s="24"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="29" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B30" s="22" t="s">
         <v>6</v>
       </c>
       <c r="C30" s="23" t="s">
-        <v>29</v>
+        <v>97</v>
       </c>
       <c r="D30" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="E30" s="24" t="s">
+        <v>98</v>
+      </c>
+      <c r="F30" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="G30" s="24" t="s">
+        <v>98</v>
+      </c>
+      <c r="H30" s="24" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="29" t="s">
+        <v>96</v>
+      </c>
+      <c r="B31" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="E30" s="24" t="s">
-        <v>77</v>
-      </c>
-      <c r="F30" s="28" t="s">
-        <v>42</v>
-      </c>
-      <c r="G30" s="24" t="s">
-        <v>78</v>
-      </c>
-      <c r="H30" s="24" t="s">
-        <v>97</v>
+      <c r="D31" s="23" t="s">
+        <v>37</v>
+      </c>
+      <c r="E31" s="24" t="s">
+        <v>79</v>
+      </c>
+      <c r="F31" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="G31" s="24" t="s">
+        <v>80</v>
+      </c>
+      <c r="H31" s="24" t="s">
+        <v>101</v>
       </c>
     </row>
   </sheetData>

--- a/시간표.xlsx
+++ b/시간표.xlsx
@@ -13,8 +13,8 @@
     <sheet name="일정(편집용)" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Area" vbProcedure="false">'둘째 주간표'!$A$1:$F$42</definedName>
-    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">'첫째 주간표'!$A$1:$F$42</definedName>
+    <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Area" vbProcedure="false">'둘째 주간표'!$A$1:$H$52</definedName>
+    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">'첫째 주간표'!$A$1:$H$52</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="125">
   <si>
     <r>
       <rPr>
@@ -69,6 +69,12 @@
     <t xml:space="preserve">금</t>
   </si>
   <si>
+    <t xml:space="preserve">토</t>
+  </si>
+  <si>
+    <t xml:space="preserve">일</t>
+  </si>
+  <si>
     <t xml:space="preserve">08:00</t>
   </si>
   <si>
@@ -174,6 +180,94 @@
     <t xml:space="preserve">09:30</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF9C4A16"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">첼로
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF9C4A16"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">09:30–10:10*
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF9C4A16"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">수</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF9C4A16"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF9C4A16"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">토 중 하나 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF9C4A16"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF9C4A16"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">주말 일정에 따라 변동</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF9C4A16"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">10:00</t>
   </si>
   <si>
@@ -417,6 +511,41 @@
     </r>
   </si>
   <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF9C4A16"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">수영
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF9C4A16"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">15:00–15:50*
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF9C4A16"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">수영장</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">15:30</t>
   </si>
   <si>
@@ -570,6 +699,109 @@
   </si>
   <si>
     <t xml:space="preserve">17:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19:30</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF9C4A16"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">첼로
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF9C4A16"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">19:40–20:20*
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF9C4A16"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">수</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF9C4A16"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF9C4A16"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">토 중 하나 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF9C4A16"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF9C4A16"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">주말 일정에 따라 변동</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF9C4A16"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">20:00</t>
   </si>
   <si>
     <r>
@@ -924,6 +1156,41 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">축구
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF9C4A16"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">14:30–15:30*
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF9C4A16"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">축구교실</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF9C4A16"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">태권도
 </t>
     </r>
@@ -1402,6 +1669,97 @@
   </si>
   <si>
     <t xml:space="preserve">하원 시간 늘림</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19:40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20:20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">첼로</t>
+  </si>
+  <si>
+    <t xml:space="preserve">첼로교실</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">수</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">토 중 하나 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">주말 일정에 따라 변동</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">) / ※ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">종료시간 추정</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">10:10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">수영</t>
+  </si>
+  <si>
+    <t xml:space="preserve">수영장</t>
+  </si>
+  <si>
+    <t xml:space="preserve">※ 종료시간 추정</t>
+  </si>
+  <si>
+    <t xml:space="preserve">축구</t>
+  </si>
+  <si>
+    <t xml:space="preserve">축구교실</t>
   </si>
 </sst>
 </file>
@@ -2154,11 +2512,11 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:F45"/>
+  <dimension ref="A1:H55"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="2" style="0" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="2" style="0" width="17"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2170,6 +2528,8 @@
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
@@ -2190,72 +2550,88 @@
       <c r="F2" s="3" t="s">
         <v>6</v>
       </c>
+      <c r="G2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B3" s="5"/>
       <c r="C3" s="5"/>
       <c r="D3" s="5"/>
       <c r="E3" s="5"/>
       <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="5"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6"/>
       <c r="B4" s="7" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>8</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="G4" s="5"/>
+      <c r="H4" s="5"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
       <c r="D5" s="7"/>
       <c r="E5" s="7"/>
       <c r="F5" s="7"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6"/>
       <c r="B6" s="8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>11</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B7" s="8"/>
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
       <c r="E7" s="8"/>
       <c r="F7" s="8"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="6"/>
@@ -2264,16 +2640,22 @@
       <c r="D8" s="8"/>
       <c r="E8" s="8"/>
       <c r="F8" s="8"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="5"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B9" s="8"/>
       <c r="C9" s="8"/>
       <c r="D9" s="8"/>
       <c r="E9" s="8"/>
       <c r="F9" s="8"/>
+      <c r="G9" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H9" s="5"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="6"/>
@@ -2282,16 +2664,20 @@
       <c r="D10" s="8"/>
       <c r="E10" s="8"/>
       <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="5"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B11" s="8"/>
       <c r="C11" s="8"/>
       <c r="D11" s="8"/>
       <c r="E11" s="8"/>
       <c r="F11" s="8"/>
+      <c r="G11" s="9"/>
+      <c r="H11" s="5"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="6"/>
@@ -2300,16 +2686,20 @@
       <c r="D12" s="8"/>
       <c r="E12" s="8"/>
       <c r="F12" s="8"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B13" s="8"/>
       <c r="C13" s="8"/>
       <c r="D13" s="8"/>
       <c r="E13" s="8"/>
       <c r="F13" s="8"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="6"/>
@@ -2318,16 +2708,20 @@
       <c r="D14" s="8"/>
       <c r="E14" s="8"/>
       <c r="F14" s="8"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B15" s="8"/>
       <c r="C15" s="8"/>
       <c r="D15" s="8"/>
       <c r="E15" s="8"/>
       <c r="F15" s="8"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="6"/>
@@ -2336,16 +2730,20 @@
       <c r="D16" s="8"/>
       <c r="E16" s="8"/>
       <c r="F16" s="8"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B17" s="8"/>
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
       <c r="E17" s="8"/>
       <c r="F17" s="8"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="6"/>
@@ -2354,16 +2752,20 @@
       <c r="D18" s="8"/>
       <c r="E18" s="8"/>
       <c r="F18" s="8"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B19" s="8"/>
       <c r="C19" s="8"/>
       <c r="D19" s="8"/>
       <c r="E19" s="8"/>
       <c r="F19" s="8"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="6"/>
@@ -2372,16 +2774,20 @@
       <c r="D20" s="8"/>
       <c r="E20" s="8"/>
       <c r="F20" s="8"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B21" s="8"/>
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
       <c r="F21" s="8"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="6"/>
@@ -2390,20 +2796,24 @@
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
       <c r="F22" s="8"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B23" s="8"/>
       <c r="C23" s="8"/>
       <c r="D23" s="9" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E23" s="8"/>
       <c r="F23" s="10" t="s">
-        <v>22</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="G23" s="5"/>
+      <c r="H23" s="5"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="6"/>
@@ -2412,40 +2822,48 @@
       <c r="D24" s="9"/>
       <c r="E24" s="8"/>
       <c r="F24" s="10"/>
+      <c r="G24" s="5"/>
+      <c r="H24" s="5"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
       <c r="D25" s="9"/>
       <c r="E25" s="10" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F25" s="10"/>
+      <c r="G25" s="5"/>
+      <c r="H25" s="5"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="6"/>
       <c r="B26" s="10" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C26" s="5"/>
       <c r="D26" s="9"/>
       <c r="E26" s="10"/>
       <c r="F26" s="10"/>
+      <c r="G26" s="5"/>
+      <c r="H26" s="5"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B27" s="10"/>
       <c r="C27" s="9" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D27" s="5"/>
       <c r="E27" s="10"/>
       <c r="F27" s="10"/>
+      <c r="G27" s="5"/>
+      <c r="H27" s="5"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="6"/>
@@ -2454,16 +2872,20 @@
       <c r="D28" s="5"/>
       <c r="E28" s="10"/>
       <c r="F28" s="10"/>
+      <c r="G28" s="5"/>
+      <c r="H28" s="5"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B29" s="10"/>
       <c r="C29" s="10"/>
       <c r="D29" s="5"/>
       <c r="E29" s="10"/>
       <c r="F29" s="5"/>
+      <c r="G29" s="5"/>
+      <c r="H29" s="5"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="6"/>
@@ -2472,17 +2894,23 @@
       <c r="D30" s="5"/>
       <c r="E30" s="10"/>
       <c r="F30" s="5"/>
+      <c r="G30" s="5"/>
+      <c r="H30" s="5"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B31" s="10"/>
       <c r="C31" s="5"/>
       <c r="D31" s="5"/>
       <c r="E31" s="10"/>
       <c r="F31" s="9" t="s">
-        <v>30</v>
+        <v>33</v>
+      </c>
+      <c r="G31" s="5"/>
+      <c r="H31" s="9" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2492,40 +2920,48 @@
       <c r="D32" s="5"/>
       <c r="E32" s="5"/>
       <c r="F32" s="9"/>
+      <c r="G32" s="5"/>
+      <c r="H32" s="9"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="6" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5"/>
       <c r="D33" s="5"/>
       <c r="E33" s="5"/>
       <c r="F33" s="9"/>
+      <c r="G33" s="5"/>
+      <c r="H33" s="9"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="6"/>
       <c r="B34" s="9" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C34" s="5"/>
       <c r="D34" s="5"/>
       <c r="E34" s="5"/>
       <c r="F34" s="9"/>
+      <c r="G34" s="5"/>
+      <c r="H34" s="9"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="4" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B35" s="9"/>
       <c r="C35" s="9" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D35" s="5"/>
       <c r="E35" s="5"/>
       <c r="F35" s="9" t="s">
-        <v>35</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="G35" s="5"/>
+      <c r="H35" s="5"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="6"/>
@@ -2534,16 +2970,20 @@
       <c r="D36" s="5"/>
       <c r="E36" s="5"/>
       <c r="F36" s="9"/>
+      <c r="G36" s="5"/>
+      <c r="H36" s="5"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="6" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5"/>
       <c r="D37" s="5"/>
       <c r="E37" s="5"/>
       <c r="F37" s="9"/>
+      <c r="G37" s="5"/>
+      <c r="H37" s="5"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="6"/>
@@ -2552,18 +2992,22 @@
       <c r="D38" s="5"/>
       <c r="E38" s="5"/>
       <c r="F38" s="9"/>
+      <c r="G38" s="5"/>
+      <c r="H38" s="5"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="4" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5"/>
       <c r="D39" s="5"/>
       <c r="E39" s="9" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F39" s="5"/>
+      <c r="G39" s="5"/>
+      <c r="H39" s="5"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="6"/>
@@ -2572,16 +3016,20 @@
       <c r="D40" s="5"/>
       <c r="E40" s="9"/>
       <c r="F40" s="5"/>
+      <c r="G40" s="5"/>
+      <c r="H40" s="5"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="6" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5"/>
       <c r="D41" s="5"/>
       <c r="E41" s="9"/>
       <c r="F41" s="5"/>
+      <c r="G41" s="5"/>
+      <c r="H41" s="5"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="6"/>
@@ -2590,35 +3038,149 @@
       <c r="D42" s="5"/>
       <c r="E42" s="5"/>
       <c r="F42" s="5"/>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="B44" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="C44" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="D44" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="E44" s="15" t="s">
+      <c r="G42" s="5"/>
+      <c r="H42" s="5"/>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="F44" s="16" t="s">
+      <c r="B43" s="5"/>
+      <c r="C43" s="5"/>
+      <c r="D43" s="5"/>
+      <c r="E43" s="5"/>
+      <c r="F43" s="5"/>
+      <c r="G43" s="5"/>
+      <c r="H43" s="5"/>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="6"/>
+      <c r="B44" s="5"/>
+      <c r="C44" s="5"/>
+      <c r="D44" s="5"/>
+      <c r="E44" s="5"/>
+      <c r="F44" s="5"/>
+      <c r="G44" s="5"/>
+      <c r="H44" s="5"/>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="6" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="17" t="s">
+      <c r="B45" s="5"/>
+      <c r="C45" s="5"/>
+      <c r="D45" s="5"/>
+      <c r="E45" s="5"/>
+      <c r="F45" s="5"/>
+      <c r="G45" s="5"/>
+      <c r="H45" s="5"/>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="6"/>
+      <c r="B46" s="5"/>
+      <c r="C46" s="5"/>
+      <c r="D46" s="5"/>
+      <c r="E46" s="5"/>
+      <c r="F46" s="5"/>
+      <c r="G46" s="5"/>
+      <c r="H46" s="5"/>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="4" t="s">
         <v>46</v>
       </c>
+      <c r="B47" s="5"/>
+      <c r="C47" s="5"/>
+      <c r="D47" s="5"/>
+      <c r="E47" s="5"/>
+      <c r="F47" s="5"/>
+      <c r="G47" s="5"/>
+      <c r="H47" s="5"/>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="6"/>
+      <c r="B48" s="5"/>
+      <c r="C48" s="5"/>
+      <c r="D48" s="5"/>
+      <c r="E48" s="5"/>
+      <c r="F48" s="5"/>
+      <c r="G48" s="5"/>
+      <c r="H48" s="5"/>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B49" s="5"/>
+      <c r="C49" s="5"/>
+      <c r="D49" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="E49" s="5"/>
+      <c r="F49" s="5"/>
+      <c r="G49" s="5"/>
+      <c r="H49" s="5"/>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="6"/>
+      <c r="B50" s="5"/>
+      <c r="C50" s="5"/>
+      <c r="D50" s="9"/>
+      <c r="E50" s="5"/>
+      <c r="F50" s="5"/>
+      <c r="G50" s="5"/>
+      <c r="H50" s="5"/>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B51" s="5"/>
+      <c r="C51" s="5"/>
+      <c r="D51" s="9"/>
+      <c r="E51" s="5"/>
+      <c r="F51" s="5"/>
+      <c r="G51" s="5"/>
+      <c r="H51" s="5"/>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="6"/>
+      <c r="B52" s="5"/>
+      <c r="C52" s="5"/>
+      <c r="D52" s="9"/>
+      <c r="E52" s="5"/>
+      <c r="F52" s="5"/>
+      <c r="G52" s="5"/>
+      <c r="H52" s="5"/>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="B54" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C54" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="D54" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="E54" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="F54" s="16" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="17" t="s">
+        <v>56</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="21">
-    <mergeCell ref="A1:F1"/>
+  <mergeCells count="24">
+    <mergeCell ref="A1:H1"/>
     <mergeCell ref="B4:B5"/>
     <mergeCell ref="C4:C5"/>
     <mergeCell ref="D4:D5"/>
@@ -2629,16 +3191,19 @@
     <mergeCell ref="D6:D22"/>
     <mergeCell ref="E6:E24"/>
     <mergeCell ref="F6:F22"/>
+    <mergeCell ref="G9:G11"/>
     <mergeCell ref="D23:D26"/>
     <mergeCell ref="F23:F28"/>
     <mergeCell ref="E25:E31"/>
     <mergeCell ref="B26:B32"/>
     <mergeCell ref="C27:C30"/>
     <mergeCell ref="F31:F34"/>
+    <mergeCell ref="H31:H34"/>
     <mergeCell ref="B34:B36"/>
     <mergeCell ref="C35:C36"/>
     <mergeCell ref="F35:F38"/>
     <mergeCell ref="E39:E41"/>
+    <mergeCell ref="D49:D52"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2655,22 +3220,24 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:F45"/>
+  <dimension ref="A1:H55"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="2" style="0" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="2" style="0" width="17"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="18" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
       <c r="D1" s="18"/>
       <c r="E1" s="18"/>
       <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
@@ -2691,16 +3258,24 @@
       <c r="F2" s="3" t="s">
         <v>6</v>
       </c>
+      <c r="G2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B3" s="5"/>
       <c r="C3" s="5"/>
       <c r="D3" s="5"/>
       <c r="E3" s="5"/>
       <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="5"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6"/>
@@ -2709,16 +3284,20 @@
       <c r="D4" s="5"/>
       <c r="E4" s="5"/>
       <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="5"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
       <c r="E5" s="5"/>
       <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6"/>
@@ -2727,26 +3306,30 @@
       <c r="D6" s="5"/>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>50</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="6"/>
@@ -2755,16 +3338,20 @@
       <c r="D8" s="8"/>
       <c r="E8" s="8"/>
       <c r="F8" s="8"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="5"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B9" s="8"/>
       <c r="C9" s="8"/>
       <c r="D9" s="8"/>
       <c r="E9" s="8"/>
       <c r="F9" s="8"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="6"/>
@@ -2773,16 +3360,20 @@
       <c r="D10" s="8"/>
       <c r="E10" s="8"/>
       <c r="F10" s="8"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B11" s="8"/>
       <c r="C11" s="8"/>
       <c r="D11" s="8"/>
       <c r="E11" s="8"/>
       <c r="F11" s="8"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="6"/>
@@ -2791,16 +3382,20 @@
       <c r="D12" s="8"/>
       <c r="E12" s="8"/>
       <c r="F12" s="8"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B13" s="8"/>
       <c r="C13" s="8"/>
       <c r="D13" s="8"/>
       <c r="E13" s="8"/>
       <c r="F13" s="8"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="6"/>
@@ -2809,16 +3404,20 @@
       <c r="D14" s="8"/>
       <c r="E14" s="8"/>
       <c r="F14" s="8"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B15" s="8"/>
       <c r="C15" s="8"/>
       <c r="D15" s="8"/>
       <c r="E15" s="8"/>
       <c r="F15" s="8"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="6"/>
@@ -2827,16 +3426,20 @@
       <c r="D16" s="8"/>
       <c r="E16" s="8"/>
       <c r="F16" s="8"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B17" s="8"/>
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
       <c r="E17" s="8"/>
       <c r="F17" s="8"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="6"/>
@@ -2845,16 +3448,20 @@
       <c r="D18" s="8"/>
       <c r="E18" s="8"/>
       <c r="F18" s="8"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B19" s="8"/>
       <c r="C19" s="8"/>
       <c r="D19" s="8"/>
       <c r="E19" s="8"/>
       <c r="F19" s="8"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="6"/>
@@ -2863,16 +3470,20 @@
       <c r="D20" s="8"/>
       <c r="E20" s="8"/>
       <c r="F20" s="8"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B21" s="8"/>
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
       <c r="F21" s="8"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="6"/>
@@ -2881,16 +3492,20 @@
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
       <c r="F22" s="8"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B23" s="8"/>
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
       <c r="F23" s="8"/>
+      <c r="G23" s="5"/>
+      <c r="H23" s="5"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="6"/>
@@ -2899,16 +3514,20 @@
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
       <c r="F24" s="8"/>
+      <c r="G24" s="5"/>
+      <c r="H24" s="5"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B25" s="8"/>
       <c r="C25" s="8"/>
       <c r="D25" s="8"/>
       <c r="E25" s="8"/>
       <c r="F25" s="8"/>
+      <c r="G25" s="5"/>
+      <c r="H25" s="5"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="6"/>
@@ -2917,18 +3536,22 @@
       <c r="D26" s="8"/>
       <c r="E26" s="8"/>
       <c r="F26" s="8"/>
+      <c r="G26" s="5"/>
+      <c r="H26" s="5"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="9" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="D27" s="5"/>
       <c r="E27" s="5"/>
       <c r="F27" s="8"/>
+      <c r="G27" s="5"/>
+      <c r="H27" s="5"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="6"/>
@@ -2937,52 +3560,66 @@
       <c r="D28" s="5"/>
       <c r="E28" s="5"/>
       <c r="F28" s="8"/>
+      <c r="G28" s="5"/>
+      <c r="H28" s="5"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="9"/>
       <c r="D29" s="5"/>
-      <c r="E29" s="5"/>
+      <c r="E29" s="9" t="s">
+        <v>62</v>
+      </c>
       <c r="F29" s="8"/>
+      <c r="G29" s="5"/>
+      <c r="H29" s="5"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="6"/>
       <c r="B30" s="5"/>
       <c r="C30" s="9"/>
       <c r="D30" s="5"/>
-      <c r="E30" s="5"/>
-      <c r="F30" s="8"/>
+      <c r="E30" s="9"/>
+      <c r="F30" s="9"/>
+      <c r="G30" s="5"/>
+      <c r="H30" s="5"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5"/>
       <c r="D31" s="5"/>
-      <c r="E31" s="5"/>
-      <c r="F31" s="8"/>
+      <c r="E31" s="9"/>
+      <c r="F31" s="9"/>
+      <c r="G31" s="5"/>
+      <c r="H31" s="5"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="6"/>
       <c r="B32" s="5"/>
       <c r="C32" s="5"/>
       <c r="D32" s="5"/>
-      <c r="E32" s="5"/>
-      <c r="F32" s="8"/>
+      <c r="E32" s="9"/>
+      <c r="F32" s="9"/>
+      <c r="G32" s="5"/>
+      <c r="H32" s="5"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="6" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5"/>
       <c r="D33" s="5"/>
       <c r="E33" s="5"/>
       <c r="F33" s="5"/>
+      <c r="G33" s="5"/>
+      <c r="H33" s="5"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="6"/>
@@ -2991,40 +3628,48 @@
       <c r="D34" s="5"/>
       <c r="E34" s="5"/>
       <c r="F34" s="5"/>
+      <c r="G34" s="5"/>
+      <c r="H34" s="5"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="4" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5"/>
       <c r="D35" s="5"/>
       <c r="E35" s="5"/>
       <c r="F35" s="9" t="s">
-        <v>52</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="G35" s="5"/>
+      <c r="H35" s="5"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="6"/>
       <c r="B36" s="9" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="C36" s="5"/>
       <c r="D36" s="5"/>
       <c r="E36" s="5"/>
       <c r="F36" s="9"/>
+      <c r="G36" s="5"/>
+      <c r="H36" s="5"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="6" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B37" s="9"/>
       <c r="C37" s="5"/>
       <c r="D37" s="9" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="E37" s="5"/>
       <c r="F37" s="9"/>
+      <c r="G37" s="5"/>
+      <c r="H37" s="5"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="6"/>
@@ -3033,16 +3678,20 @@
       <c r="D38" s="9"/>
       <c r="E38" s="5"/>
       <c r="F38" s="9"/>
+      <c r="G38" s="5"/>
+      <c r="H38" s="5"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="4" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5"/>
       <c r="D39" s="5"/>
       <c r="E39" s="5"/>
       <c r="F39" s="5"/>
+      <c r="G39" s="5"/>
+      <c r="H39" s="5"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="6"/>
@@ -3051,16 +3700,20 @@
       <c r="D40" s="5"/>
       <c r="E40" s="5"/>
       <c r="F40" s="5"/>
+      <c r="G40" s="5"/>
+      <c r="H40" s="5"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="6" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5"/>
       <c r="D41" s="5"/>
       <c r="E41" s="5"/>
       <c r="F41" s="5"/>
+      <c r="G41" s="5"/>
+      <c r="H41" s="5"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="6"/>
@@ -3069,41 +3722,154 @@
       <c r="D42" s="5"/>
       <c r="E42" s="5"/>
       <c r="F42" s="5"/>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="B44" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="C44" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="D44" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="E44" s="15" t="s">
+      <c r="G42" s="5"/>
+      <c r="H42" s="5"/>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="F44" s="16" t="s">
+      <c r="B43" s="5"/>
+      <c r="C43" s="5"/>
+      <c r="D43" s="5"/>
+      <c r="E43" s="5"/>
+      <c r="F43" s="5"/>
+      <c r="G43" s="5"/>
+      <c r="H43" s="5"/>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="6"/>
+      <c r="B44" s="5"/>
+      <c r="C44" s="5"/>
+      <c r="D44" s="5"/>
+      <c r="E44" s="5"/>
+      <c r="F44" s="5"/>
+      <c r="G44" s="5"/>
+      <c r="H44" s="5"/>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="6" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="17" t="s">
+      <c r="B45" s="5"/>
+      <c r="C45" s="5"/>
+      <c r="D45" s="5"/>
+      <c r="E45" s="5"/>
+      <c r="F45" s="5"/>
+      <c r="G45" s="5"/>
+      <c r="H45" s="5"/>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="6"/>
+      <c r="B46" s="5"/>
+      <c r="C46" s="5"/>
+      <c r="D46" s="5"/>
+      <c r="E46" s="5"/>
+      <c r="F46" s="5"/>
+      <c r="G46" s="5"/>
+      <c r="H46" s="5"/>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="4" t="s">
         <v>46</v>
       </c>
+      <c r="B47" s="5"/>
+      <c r="C47" s="5"/>
+      <c r="D47" s="5"/>
+      <c r="E47" s="5"/>
+      <c r="F47" s="5"/>
+      <c r="G47" s="5"/>
+      <c r="H47" s="5"/>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="6"/>
+      <c r="B48" s="5"/>
+      <c r="C48" s="5"/>
+      <c r="D48" s="5"/>
+      <c r="E48" s="5"/>
+      <c r="F48" s="5"/>
+      <c r="G48" s="5"/>
+      <c r="H48" s="5"/>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B49" s="5"/>
+      <c r="C49" s="5"/>
+      <c r="D49" s="5"/>
+      <c r="E49" s="5"/>
+      <c r="F49" s="5"/>
+      <c r="G49" s="5"/>
+      <c r="H49" s="5"/>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="6"/>
+      <c r="B50" s="5"/>
+      <c r="C50" s="5"/>
+      <c r="D50" s="5"/>
+      <c r="E50" s="5"/>
+      <c r="F50" s="5"/>
+      <c r="G50" s="5"/>
+      <c r="H50" s="5"/>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B51" s="5"/>
+      <c r="C51" s="5"/>
+      <c r="D51" s="5"/>
+      <c r="E51" s="5"/>
+      <c r="F51" s="5"/>
+      <c r="G51" s="5"/>
+      <c r="H51" s="5"/>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="6"/>
+      <c r="B52" s="5"/>
+      <c r="C52" s="5"/>
+      <c r="D52" s="5"/>
+      <c r="E52" s="5"/>
+      <c r="F52" s="5"/>
+      <c r="G52" s="5"/>
+      <c r="H52" s="5"/>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="B54" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C54" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="D54" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="E54" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="F54" s="16" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="17" t="s">
+        <v>56</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:F1"/>
+  <mergeCells count="11">
+    <mergeCell ref="A1:H1"/>
     <mergeCell ref="B7:B26"/>
     <mergeCell ref="C7:C26"/>
     <mergeCell ref="D7:D26"/>
     <mergeCell ref="E7:E26"/>
     <mergeCell ref="F7:F32"/>
     <mergeCell ref="C27:C30"/>
+    <mergeCell ref="E29:E32"/>
     <mergeCell ref="F35:F38"/>
     <mergeCell ref="B36:B38"/>
     <mergeCell ref="D37:D38"/>
@@ -3123,7 +3889,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="7"/>
@@ -3137,7 +3903,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="19" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -3149,738 +3915,842 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="20" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="B2" s="20" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="C2" s="20" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="D2" s="20" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="F2" s="20" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="G2" s="20" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="H2" s="20" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="21" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="B3" s="22" t="s">
         <v>2</v>
       </c>
       <c r="C3" s="23" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="D3" s="23" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="E3" s="24" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="F3" s="25" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="G3" s="24" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="H3" s="24"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="21" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="B4" s="22" t="s">
         <v>2</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="D4" s="23" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E4" s="24" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="F4" s="26" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="G4" s="24" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="H4" s="24"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="21" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="B5" s="22" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="23" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="D5" s="23" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="E5" s="24" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="F5" s="27" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="G5" s="24" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="H5" s="24"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="21" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="B6" s="22" t="s">
         <v>2</v>
       </c>
       <c r="C6" s="23" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="D6" s="23" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="E6" s="24" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="F6" s="28" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="G6" s="24" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H6" s="24"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="21" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="B7" s="22" t="s">
         <v>3</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="D7" s="23" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="E7" s="24" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="F7" s="25" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="G7" s="24" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="H7" s="24"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="21" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="B8" s="22" t="s">
         <v>3</v>
       </c>
       <c r="C8" s="23" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="D8" s="23" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E8" s="24" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="F8" s="26" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="G8" s="24" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="H8" s="24"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="21" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="B9" s="22" t="s">
         <v>3</v>
       </c>
       <c r="C9" s="23" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D9" s="23" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E9" s="24" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="F9" s="28" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="G9" s="24" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H9" s="24" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="21" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="B10" s="22" t="s">
         <v>3</v>
       </c>
       <c r="C10" s="23" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D10" s="23" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E10" s="24" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="F10" s="28" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="G10" s="24" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H10" s="24"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="21" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="B11" s="22" t="s">
         <v>4</v>
       </c>
       <c r="C11" s="23" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="D11" s="23" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="E11" s="24" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="F11" s="25" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="G11" s="24" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="H11" s="24"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="21" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="B12" s="22" t="s">
         <v>4</v>
       </c>
       <c r="C12" s="23" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="D12" s="23" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="E12" s="24" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="F12" s="26" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="G12" s="24" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="H12" s="24"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="21" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="B13" s="22" t="s">
         <v>4</v>
       </c>
       <c r="C13" s="23" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D13" s="23" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E13" s="24" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="F13" s="28" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="G13" s="24" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H13" s="24"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="21" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="B14" s="22" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="23" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="D14" s="23" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="E14" s="24" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="F14" s="25" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="G14" s="24" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="H14" s="24"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="21" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="B15" s="22" t="s">
         <v>5</v>
       </c>
       <c r="C15" s="23" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="D15" s="23" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E15" s="24" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="F15" s="26" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="G15" s="24" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="H15" s="24"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="21" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="B16" s="22" t="s">
         <v>5</v>
       </c>
       <c r="C16" s="23" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="D16" s="23" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="E16" s="24" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="F16" s="27" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="G16" s="24" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="H16" s="24"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="21" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="B17" s="22" t="s">
         <v>5</v>
       </c>
       <c r="C17" s="23" t="s">
+        <v>100</v>
+      </c>
+      <c r="D17" s="23" t="s">
+        <v>101</v>
+      </c>
+      <c r="E17" s="24" t="s">
+        <v>88</v>
+      </c>
+      <c r="F17" s="28" t="s">
+        <v>53</v>
+      </c>
+      <c r="G17" s="24" t="s">
         <v>89</v>
-      </c>
-      <c r="D17" s="23" t="s">
-        <v>90</v>
-      </c>
-      <c r="E17" s="24" t="s">
-        <v>77</v>
-      </c>
-      <c r="F17" s="28" t="s">
-        <v>43</v>
-      </c>
-      <c r="G17" s="24" t="s">
-        <v>78</v>
       </c>
       <c r="H17" s="24"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="21" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="B18" s="22" t="s">
         <v>6</v>
       </c>
       <c r="C18" s="23" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="D18" s="23" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="E18" s="24" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="F18" s="25" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="G18" s="24" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="H18" s="24"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="21" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="B19" s="22" t="s">
         <v>6</v>
       </c>
       <c r="C19" s="23" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="D19" s="23" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="E19" s="24" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="F19" s="26" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="G19" s="24" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="H19" s="24"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="21" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="B20" s="22" t="s">
         <v>6</v>
       </c>
       <c r="C20" s="23" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="D20" s="23" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="E20" s="24" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="F20" s="27" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="G20" s="24" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="H20" s="24"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="21" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="B21" s="22" t="s">
         <v>6</v>
       </c>
       <c r="C21" s="23" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D21" s="23" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E21" s="24" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="F21" s="28" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="G21" s="24" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="H21" s="24" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="21" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="B22" s="22" t="s">
         <v>6</v>
       </c>
       <c r="C22" s="23" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D22" s="23" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E22" s="24" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="F22" s="28" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="G22" s="24" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H22" s="24" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="29" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="B23" s="22" t="s">
         <v>2</v>
       </c>
       <c r="C23" s="23" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="D23" s="23" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="E23" s="24" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="F23" s="26" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="G23" s="24" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="H23" s="24"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="29" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="B24" s="22" t="s">
         <v>2</v>
       </c>
       <c r="C24" s="23" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="D24" s="23" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="E24" s="24" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="F24" s="28" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="G24" s="24" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H24" s="24"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="29" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="B25" s="22" t="s">
         <v>3</v>
       </c>
       <c r="C25" s="23" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="D25" s="23" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="E25" s="24" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="F25" s="26" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="G25" s="24" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="H25" s="24" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="29" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="B26" s="22" t="s">
         <v>3</v>
       </c>
       <c r="C26" s="23" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D26" s="23" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E26" s="24" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="F26" s="28" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="G26" s="24" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H26" s="24" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="29" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="B27" s="22" t="s">
         <v>4</v>
       </c>
       <c r="C27" s="23" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="D27" s="23" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="E27" s="24" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="F27" s="26" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="G27" s="24" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="H27" s="24"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="29" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="B28" s="22" t="s">
         <v>4</v>
       </c>
       <c r="C28" s="23" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D28" s="23" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E28" s="24" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="F28" s="28" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="G28" s="24" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H28" s="24"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="29" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="B29" s="22" t="s">
         <v>5</v>
       </c>
       <c r="C29" s="23" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="D29" s="23" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="E29" s="24" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="F29" s="26" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="G29" s="24" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="H29" s="24"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="29" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="B30" s="22" t="s">
         <v>6</v>
       </c>
       <c r="C30" s="23" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="D30" s="23" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="E30" s="24" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="F30" s="26" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="G30" s="24" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="H30" s="24" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="29" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="B31" s="22" t="s">
         <v>6</v>
       </c>
       <c r="C31" s="23" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D31" s="23" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E31" s="24" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="F31" s="28" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="G31" s="24" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H31" s="24" t="s">
-        <v>101</v>
+        <v>112</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="21" t="s">
+        <v>75</v>
+      </c>
+      <c r="B32" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="C32" s="23" t="s">
+        <v>114</v>
+      </c>
+      <c r="D32" s="23" t="s">
+        <v>115</v>
+      </c>
+      <c r="E32" s="24" t="s">
+        <v>116</v>
+      </c>
+      <c r="F32" s="28" t="s">
+        <v>53</v>
+      </c>
+      <c r="G32" s="24" t="s">
+        <v>117</v>
+      </c>
+      <c r="H32" s="24" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="21" t="s">
+        <v>75</v>
+      </c>
+      <c r="B33" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="D33" s="23" t="s">
+        <v>119</v>
+      </c>
+      <c r="E33" s="24" t="s">
+        <v>116</v>
+      </c>
+      <c r="F33" s="28" t="s">
+        <v>53</v>
+      </c>
+      <c r="G33" s="24" t="s">
+        <v>117</v>
+      </c>
+      <c r="H33" s="24" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="21" t="s">
+        <v>75</v>
+      </c>
+      <c r="B34" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="C34" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="D34" s="23" t="s">
+        <v>86</v>
+      </c>
+      <c r="E34" s="24" t="s">
+        <v>120</v>
+      </c>
+      <c r="F34" s="28" t="s">
+        <v>53</v>
+      </c>
+      <c r="G34" s="24" t="s">
+        <v>121</v>
+      </c>
+      <c r="H34" s="24" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="29" t="s">
+        <v>107</v>
+      </c>
+      <c r="B35" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="C35" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="D35" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="E35" s="24" t="s">
+        <v>123</v>
+      </c>
+      <c r="F35" s="28" t="s">
+        <v>53</v>
+      </c>
+      <c r="G35" s="24" t="s">
+        <v>124</v>
+      </c>
+      <c r="H35" s="24" t="s">
+        <v>122</v>
       </c>
     </row>
   </sheetData>

--- a/시간표.xlsx
+++ b/시간표.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="123">
   <si>
     <r>
       <rPr>
@@ -200,7 +200,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">09:30–10:10*
+      <t xml:space="preserve">09:30–10:00
 </t>
     </r>
     <r>
@@ -531,7 +531,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">15:00–15:50*
+      <t xml:space="preserve">15:00–16:00
 </t>
     </r>
     <r>
@@ -733,7 +733,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">19:40–20:20*
+      <t xml:space="preserve">19:40–20:10
 </t>
     </r>
     <r>
@@ -1168,7 +1168,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">14:30–15:30*
+      <t xml:space="preserve">14:30–15:00
 </t>
     </r>
     <r>
@@ -1674,7 +1674,7 @@
     <t xml:space="preserve">19:40</t>
   </si>
   <si>
-    <t xml:space="preserve">20:20</t>
+    <t xml:space="preserve">20:10</t>
   </si>
   <si>
     <t xml:space="preserve">첼로</t>
@@ -1732,28 +1732,14 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">) / ※ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">종료시간 추정</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">10:10</t>
+      <t xml:space="preserve">)</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">수영</t>
   </si>
   <si>
     <t xml:space="preserve">수영장</t>
-  </si>
-  <si>
-    <t xml:space="preserve">※ 종료시간 추정</t>
   </si>
   <si>
     <t xml:space="preserve">축구</t>
@@ -2664,7 +2650,7 @@
       <c r="D10" s="8"/>
       <c r="E10" s="8"/>
       <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
+      <c r="G10" s="9"/>
       <c r="H10" s="5"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2676,7 +2662,7 @@
       <c r="D11" s="8"/>
       <c r="E11" s="8"/>
       <c r="F11" s="8"/>
-      <c r="G11" s="9"/>
+      <c r="G11" s="5"/>
       <c r="H11" s="5"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3147,7 +3133,7 @@
       <c r="A52" s="6"/>
       <c r="B52" s="5"/>
       <c r="C52" s="5"/>
-      <c r="D52" s="9"/>
+      <c r="D52" s="5"/>
       <c r="E52" s="5"/>
       <c r="F52" s="5"/>
       <c r="G52" s="5"/>
@@ -3191,7 +3177,7 @@
     <mergeCell ref="D6:D22"/>
     <mergeCell ref="E6:E24"/>
     <mergeCell ref="F6:F22"/>
-    <mergeCell ref="G9:G11"/>
+    <mergeCell ref="G9:G10"/>
     <mergeCell ref="D23:D26"/>
     <mergeCell ref="F23:F28"/>
     <mergeCell ref="E25:E31"/>
@@ -3203,7 +3189,7 @@
     <mergeCell ref="C35:C36"/>
     <mergeCell ref="F35:F38"/>
     <mergeCell ref="E39:E41"/>
-    <mergeCell ref="D49:D52"/>
+    <mergeCell ref="D49:D51"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3583,7 +3569,7 @@
       <c r="C30" s="9"/>
       <c r="D30" s="5"/>
       <c r="E30" s="9"/>
-      <c r="F30" s="9"/>
+      <c r="F30" s="8"/>
       <c r="G30" s="5"/>
       <c r="H30" s="5"/>
     </row>
@@ -3594,8 +3580,8 @@
       <c r="B31" s="5"/>
       <c r="C31" s="5"/>
       <c r="D31" s="5"/>
-      <c r="E31" s="9"/>
-      <c r="F31" s="9"/>
+      <c r="E31" s="5"/>
+      <c r="F31" s="8"/>
       <c r="G31" s="5"/>
       <c r="H31" s="5"/>
     </row>
@@ -3604,8 +3590,8 @@
       <c r="B32" s="5"/>
       <c r="C32" s="5"/>
       <c r="D32" s="5"/>
-      <c r="E32" s="9"/>
-      <c r="F32" s="9"/>
+      <c r="E32" s="5"/>
+      <c r="F32" s="8"/>
       <c r="G32" s="5"/>
       <c r="H32" s="5"/>
     </row>
@@ -3869,7 +3855,7 @@
     <mergeCell ref="E7:E26"/>
     <mergeCell ref="F7:F32"/>
     <mergeCell ref="C27:C30"/>
-    <mergeCell ref="E29:E32"/>
+    <mergeCell ref="E29:E30"/>
     <mergeCell ref="F35:F38"/>
     <mergeCell ref="B36:B38"/>
     <mergeCell ref="D37:D38"/>
@@ -4686,7 +4672,7 @@
         <v>15</v>
       </c>
       <c r="D33" s="23" t="s">
-        <v>119</v>
+        <v>17</v>
       </c>
       <c r="E33" s="24" t="s">
         <v>116</v>
@@ -4712,20 +4698,18 @@
         <v>32</v>
       </c>
       <c r="D34" s="23" t="s">
-        <v>86</v>
+        <v>37</v>
       </c>
       <c r="E34" s="24" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F34" s="28" t="s">
         <v>53</v>
       </c>
       <c r="G34" s="24" t="s">
-        <v>121</v>
-      </c>
-      <c r="H34" s="24" t="s">
-        <v>122</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="H34" s="24"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="29" t="s">
@@ -4738,20 +4722,18 @@
         <v>31</v>
       </c>
       <c r="D35" s="23" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E35" s="24" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F35" s="28" t="s">
         <v>53</v>
       </c>
       <c r="G35" s="24" t="s">
-        <v>124</v>
-      </c>
-      <c r="H35" s="24" t="s">
         <v>122</v>
       </c>
+      <c r="H35" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/시간표.xlsx
+++ b/시간표.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="126">
   <si>
     <r>
       <rPr>
@@ -705,6 +705,41 @@
   </si>
   <si>
     <t xml:space="preserve">18:30</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF9C4A16"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">화상영어
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF9C4A16"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">18:30–19:00
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF9C4A16"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">온라인</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">19:00</t>
@@ -1746,6 +1781,12 @@
   </si>
   <si>
     <t xml:space="preserve">축구교실</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화상영어</t>
+  </si>
+  <si>
+    <t xml:space="preserve">온라인</t>
   </si>
 </sst>
 </file>
@@ -3054,26 +3095,30 @@
         <v>45</v>
       </c>
       <c r="B45" s="5"/>
-      <c r="C45" s="5"/>
+      <c r="C45" s="9" t="s">
+        <v>46</v>
+      </c>
       <c r="D45" s="5"/>
       <c r="E45" s="5"/>
-      <c r="F45" s="5"/>
+      <c r="F45" s="9" t="s">
+        <v>46</v>
+      </c>
       <c r="G45" s="5"/>
       <c r="H45" s="5"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="6"/>
       <c r="B46" s="5"/>
-      <c r="C46" s="5"/>
+      <c r="C46" s="9"/>
       <c r="D46" s="5"/>
       <c r="E46" s="5"/>
-      <c r="F46" s="5"/>
+      <c r="F46" s="9"/>
       <c r="G46" s="5"/>
       <c r="H46" s="5"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5"/>
@@ -3095,12 +3140,12 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5"/>
       <c r="D49" s="9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E49" s="5"/>
       <c r="F49" s="5"/>
@@ -3119,7 +3164,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5"/>
@@ -3141,31 +3186,31 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="11" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B54" s="12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C54" s="13" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D54" s="14" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E54" s="15" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F54" s="16" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="17" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="24">
+  <mergeCells count="26">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="B4:B5"/>
     <mergeCell ref="C4:C5"/>
@@ -3189,6 +3234,8 @@
     <mergeCell ref="C35:C36"/>
     <mergeCell ref="F35:F38"/>
     <mergeCell ref="E39:E41"/>
+    <mergeCell ref="C45:C46"/>
+    <mergeCell ref="F45:F46"/>
     <mergeCell ref="D49:D51"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -3215,7 +3262,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="18" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -3300,19 +3347,19 @@
         <v>14</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C7" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="D7" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="D7" s="8" t="s">
-        <v>58</v>
-      </c>
       <c r="E7" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G7" s="5"/>
       <c r="H7" s="5"/>
@@ -3531,7 +3578,7 @@
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D27" s="5"/>
       <c r="E27" s="5"/>
@@ -3557,7 +3604,7 @@
       <c r="C29" s="9"/>
       <c r="D29" s="5"/>
       <c r="E29" s="9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F29" s="8"/>
       <c r="G29" s="5"/>
@@ -3626,7 +3673,7 @@
       <c r="D35" s="5"/>
       <c r="E35" s="5"/>
       <c r="F35" s="9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G35" s="5"/>
       <c r="H35" s="5"/>
@@ -3634,7 +3681,7 @@
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="6"/>
       <c r="B36" s="9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C36" s="5"/>
       <c r="D36" s="5"/>
@@ -3650,7 +3697,7 @@
       <c r="B37" s="9"/>
       <c r="C37" s="5"/>
       <c r="D37" s="9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E37" s="5"/>
       <c r="F37" s="9"/>
@@ -3757,7 +3804,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5"/>
@@ -3779,7 +3826,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5"/>
@@ -3801,7 +3848,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5"/>
@@ -3823,27 +3870,27 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="11" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B54" s="12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C54" s="13" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D54" s="14" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E54" s="15" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F54" s="16" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="17" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -3875,7 +3922,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H35"/>
+  <dimension ref="A1:H37"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="7"/>
@@ -3889,7 +3936,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="19" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -3901,177 +3948,177 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="20" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B2" s="20" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C2" s="20" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D2" s="20" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F2" s="20" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G2" s="20" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H2" s="20" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="21" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B3" s="22" t="s">
         <v>2</v>
       </c>
       <c r="C3" s="23" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D3" s="23" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E3" s="24" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F3" s="25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G3" s="24" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H3" s="24"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="21" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B4" s="22" t="s">
         <v>2</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D4" s="23" t="s">
         <v>26</v>
       </c>
       <c r="E4" s="24" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F4" s="26" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G4" s="24" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H4" s="24"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="21" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B5" s="22" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="23" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D5" s="23" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E5" s="24" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F5" s="27" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G5" s="24" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H5" s="24"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="21" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B6" s="22" t="s">
         <v>2</v>
       </c>
       <c r="C6" s="23" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D6" s="23" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E6" s="24" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F6" s="28" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G6" s="24" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H6" s="24"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="21" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B7" s="22" t="s">
         <v>3</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D7" s="23" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E7" s="24" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F7" s="25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G7" s="24" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H7" s="24"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="21" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B8" s="22" t="s">
         <v>3</v>
       </c>
       <c r="C8" s="23" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D8" s="23" t="s">
         <v>26</v>
       </c>
       <c r="E8" s="24" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F8" s="26" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G8" s="24" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H8" s="24"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="21" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B9" s="22" t="s">
         <v>3</v>
@@ -4083,21 +4130,21 @@
         <v>32</v>
       </c>
       <c r="E9" s="24" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F9" s="28" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G9" s="24" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H9" s="24" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="21" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B10" s="22" t="s">
         <v>3</v>
@@ -4109,67 +4156,67 @@
         <v>40</v>
       </c>
       <c r="E10" s="24" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F10" s="28" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G10" s="24" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H10" s="24"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="21" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B11" s="22" t="s">
         <v>4</v>
       </c>
       <c r="C11" s="23" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D11" s="23" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E11" s="24" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F11" s="25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G11" s="24" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H11" s="24"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="21" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B12" s="22" t="s">
         <v>4</v>
       </c>
       <c r="C12" s="23" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D12" s="23" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E12" s="24" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F12" s="26" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G12" s="24" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H12" s="24"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="21" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B13" s="22" t="s">
         <v>4</v>
@@ -4181,187 +4228,187 @@
         <v>29</v>
       </c>
       <c r="E13" s="24" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F13" s="28" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G13" s="24" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H13" s="24"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="21" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B14" s="22" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="23" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D14" s="23" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E14" s="24" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F14" s="25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G14" s="24" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H14" s="24"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="21" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B15" s="22" t="s">
         <v>5</v>
       </c>
       <c r="C15" s="23" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D15" s="23" t="s">
         <v>26</v>
       </c>
       <c r="E15" s="24" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F15" s="26" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G15" s="24" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H15" s="24"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="21" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B16" s="22" t="s">
         <v>5</v>
       </c>
       <c r="C16" s="23" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D16" s="23" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E16" s="24" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F16" s="27" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G16" s="24" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H16" s="24"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="21" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B17" s="22" t="s">
         <v>5</v>
       </c>
       <c r="C17" s="23" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D17" s="23" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E17" s="24" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F17" s="28" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G17" s="24" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H17" s="24"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="21" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B18" s="22" t="s">
         <v>6</v>
       </c>
       <c r="C18" s="23" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D18" s="23" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E18" s="24" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F18" s="25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G18" s="24" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H18" s="24"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="21" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B19" s="22" t="s">
         <v>6</v>
       </c>
       <c r="C19" s="23" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D19" s="23" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E19" s="24" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F19" s="26" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G19" s="24" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H19" s="24"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="21" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B20" s="22" t="s">
         <v>6</v>
       </c>
       <c r="C20" s="23" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D20" s="23" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E20" s="24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F20" s="27" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G20" s="24" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H20" s="24"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="21" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B21" s="22" t="s">
         <v>6</v>
@@ -4373,21 +4420,21 @@
         <v>37</v>
       </c>
       <c r="E21" s="24" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F21" s="28" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G21" s="24" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H21" s="24" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="21" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B22" s="22" t="s">
         <v>6</v>
@@ -4399,95 +4446,95 @@
         <v>41</v>
       </c>
       <c r="E22" s="24" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F22" s="28" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G22" s="24" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H22" s="24" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="29" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B23" s="22" t="s">
         <v>2</v>
       </c>
       <c r="C23" s="23" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D23" s="23" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E23" s="24" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F23" s="26" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G23" s="24" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H23" s="24"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="29" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B24" s="22" t="s">
         <v>2</v>
       </c>
       <c r="C24" s="23" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D24" s="23" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E24" s="24" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F24" s="28" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G24" s="24" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H24" s="24"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="29" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B25" s="22" t="s">
         <v>3</v>
       </c>
       <c r="C25" s="23" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D25" s="23" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E25" s="24" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F25" s="26" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G25" s="24" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H25" s="24" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="29" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B26" s="22" t="s">
         <v>3</v>
@@ -4499,45 +4546,45 @@
         <v>32</v>
       </c>
       <c r="E26" s="24" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F26" s="28" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G26" s="24" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H26" s="24" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="29" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B27" s="22" t="s">
         <v>4</v>
       </c>
       <c r="C27" s="23" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D27" s="23" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E27" s="24" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F27" s="26" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G27" s="24" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H27" s="24"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="29" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B28" s="22" t="s">
         <v>4</v>
@@ -4549,69 +4596,69 @@
         <v>41</v>
       </c>
       <c r="E28" s="24" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F28" s="28" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G28" s="24" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H28" s="24"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="29" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B29" s="22" t="s">
         <v>5</v>
       </c>
       <c r="C29" s="23" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D29" s="23" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E29" s="24" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F29" s="26" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G29" s="24" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H29" s="24"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="29" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B30" s="22" t="s">
         <v>6</v>
       </c>
       <c r="C30" s="23" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D30" s="23" t="s">
         <v>35</v>
       </c>
       <c r="E30" s="24" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F30" s="26" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G30" s="24" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H30" s="24" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="29" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B31" s="22" t="s">
         <v>6</v>
@@ -4623,47 +4670,47 @@
         <v>41</v>
       </c>
       <c r="E31" s="24" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F31" s="28" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G31" s="24" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H31" s="24" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="21" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B32" s="22" t="s">
         <v>4</v>
       </c>
       <c r="C32" s="23" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D32" s="23" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E32" s="24" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F32" s="28" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G32" s="24" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H32" s="24" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="21" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B33" s="22" t="s">
         <v>7</v>
@@ -4675,21 +4722,21 @@
         <v>17</v>
       </c>
       <c r="E33" s="24" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F33" s="28" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G33" s="24" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H33" s="24" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="21" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B34" s="22" t="s">
         <v>8</v>
@@ -4701,19 +4748,19 @@
         <v>37</v>
       </c>
       <c r="E34" s="24" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F34" s="28" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G34" s="24" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H34" s="24"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="29" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B35" s="22" t="s">
         <v>5</v>
@@ -4725,15 +4772,63 @@
         <v>32</v>
       </c>
       <c r="E35" s="24" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F35" s="28" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G35" s="24" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H35" s="24"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="B36" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="C36" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="D36" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="E36" s="24" t="s">
+        <v>124</v>
+      </c>
+      <c r="F36" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="G36" s="24" t="s">
+        <v>125</v>
+      </c>
+      <c r="H36" s="24"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="B37" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="D37" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="E37" s="24" t="s">
+        <v>124</v>
+      </c>
+      <c r="F37" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="G37" s="24" t="s">
+        <v>125</v>
+      </c>
+      <c r="H37" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/시간표.xlsx
+++ b/시간표.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="123">
   <si>
     <r>
       <rPr>
@@ -466,14 +466,11 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">둘째와 함께</t>
+      <t xml:space="preserve">태권도장</t>
     </r>
   </si>
   <si>
     <t xml:space="preserve">14:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15:00</t>
   </si>
   <si>
     <r>
@@ -496,7 +493,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">15:00–16:00
+      <t xml:space="preserve">14:40–16:00
 </t>
     </r>
     <r>
@@ -507,8 +504,11 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">새로 추가</t>
-    </r>
+      <t xml:space="preserve">미술학원</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">15:00</t>
   </si>
   <si>
     <r>
@@ -1066,50 +1066,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">09:10–13:50
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF1F4E79"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">태권도 위해 일찍 하원 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF1F4E79"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF1F4E79"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">확인 필요</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF1F4E79"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
+      <t xml:space="preserve">09:10–15:20</t>
     </r>
   </si>
   <si>
@@ -1156,6 +1113,41 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">축구
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF9C4A16"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">14:30–15:00
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF9C4A16"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">축구교실</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF9C4A16"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">태권도
 </t>
     </r>
@@ -1168,76 +1160,6 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">14:00–15:00
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF9C4A16"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">첫째와 함께</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF9C4A16"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">축구
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF9C4A16"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">14:30–15:00
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF9C4A16"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">축구교실</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF9C4A16"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">태권도
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF9C4A16"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
       <t xml:space="preserve">16:00–17:00
 </t>
     </r>
@@ -1476,6 +1398,78 @@
     <t xml:space="preserve">태권도장</t>
   </si>
   <si>
+    <t xml:space="preserve">피아노</t>
+  </si>
+  <si>
+    <t xml:space="preserve">피아노학원</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12:50</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">정규수업</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">단축</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">13:40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15:10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">방과후 메이키메이커</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17:10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17:40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14:20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">방과후 종이접기</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14:40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">미술학원</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -1499,115 +1493,32 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">이모님</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">첫째 하교→둘째 하원→태권도</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">피아노</t>
-  </si>
-  <si>
-    <t xml:space="preserve">피아노학원</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12:50</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">정규수업</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">단축</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">13:40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15:10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">방과후 메이키메이커</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17:10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17:40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14:20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">방과후 종이접기</t>
-  </si>
-  <si>
-    <t xml:space="preserve">미술학원</t>
-  </si>
-  <si>
-    <t xml:space="preserve">새로 추가</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">둘째와 함께 </t>
+      <t xml:space="preserve">이모님 픽업</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">둘째</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09:10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">어린이집</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16:50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">하원 시간 늘림</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">첫째와 함께 </t>
     </r>
     <r>
       <rPr>
@@ -1626,84 +1537,6 @@
       </rPr>
       <t xml:space="preserve">이모님 픽업</t>
     </r>
-  </si>
-  <si>
-    <t xml:space="preserve">둘째</t>
-  </si>
-  <si>
-    <t xml:space="preserve">09:10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">어린이집</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16:50</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">태권도 위해 일찍 하원 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">확인 필요</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">첫째와 함께 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">· </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">이모님 픽업</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">하원 시간 늘림</t>
   </si>
   <si>
     <t xml:space="preserve">19:40</t>
@@ -2910,7 +2743,9 @@
       <c r="C29" s="10"/>
       <c r="D29" s="5"/>
       <c r="E29" s="10"/>
-      <c r="F29" s="5"/>
+      <c r="F29" s="9" t="s">
+        <v>32</v>
+      </c>
       <c r="G29" s="5"/>
       <c r="H29" s="5"/>
     </row>
@@ -2920,21 +2755,19 @@
       <c r="C30" s="9"/>
       <c r="D30" s="5"/>
       <c r="E30" s="10"/>
-      <c r="F30" s="5"/>
+      <c r="F30" s="10"/>
       <c r="G30" s="5"/>
       <c r="H30" s="5"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B31" s="10"/>
       <c r="C31" s="5"/>
       <c r="D31" s="5"/>
       <c r="E31" s="10"/>
-      <c r="F31" s="9" t="s">
-        <v>33</v>
-      </c>
+      <c r="F31" s="9"/>
       <c r="G31" s="5"/>
       <c r="H31" s="9" t="s">
         <v>34</v>
@@ -3228,7 +3061,7 @@
     <mergeCell ref="E25:E31"/>
     <mergeCell ref="B26:B32"/>
     <mergeCell ref="C27:C30"/>
-    <mergeCell ref="F31:F34"/>
+    <mergeCell ref="F29:F34"/>
     <mergeCell ref="H31:H34"/>
     <mergeCell ref="B34:B36"/>
     <mergeCell ref="C35:C36"/>
@@ -3577,9 +3410,7 @@
         <v>29</v>
       </c>
       <c r="B27" s="5"/>
-      <c r="C27" s="9" t="s">
-        <v>62</v>
-      </c>
+      <c r="C27" s="8"/>
       <c r="D27" s="5"/>
       <c r="E27" s="5"/>
       <c r="F27" s="8"/>
@@ -3589,7 +3420,7 @@
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="6"/>
       <c r="B28" s="5"/>
-      <c r="C28" s="9"/>
+      <c r="C28" s="8"/>
       <c r="D28" s="5"/>
       <c r="E28" s="5"/>
       <c r="F28" s="8"/>
@@ -3601,10 +3432,10 @@
         <v>31</v>
       </c>
       <c r="B29" s="5"/>
-      <c r="C29" s="9"/>
+      <c r="C29" s="8"/>
       <c r="D29" s="5"/>
       <c r="E29" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F29" s="8"/>
       <c r="G29" s="5"/>
@@ -3613,7 +3444,7 @@
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="6"/>
       <c r="B30" s="5"/>
-      <c r="C30" s="9"/>
+      <c r="C30" s="8"/>
       <c r="D30" s="5"/>
       <c r="E30" s="9"/>
       <c r="F30" s="8"/>
@@ -3622,10 +3453,10 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B31" s="5"/>
-      <c r="C31" s="5"/>
+      <c r="C31" s="8"/>
       <c r="D31" s="5"/>
       <c r="E31" s="5"/>
       <c r="F31" s="8"/>
@@ -3635,7 +3466,7 @@
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="6"/>
       <c r="B32" s="5"/>
-      <c r="C32" s="5"/>
+      <c r="C32" s="8"/>
       <c r="D32" s="5"/>
       <c r="E32" s="5"/>
       <c r="F32" s="8"/>
@@ -3673,7 +3504,7 @@
       <c r="D35" s="5"/>
       <c r="E35" s="5"/>
       <c r="F35" s="9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G35" s="5"/>
       <c r="H35" s="5"/>
@@ -3681,7 +3512,7 @@
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="6"/>
       <c r="B36" s="9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C36" s="5"/>
       <c r="D36" s="5"/>
@@ -3697,7 +3528,7 @@
       <c r="B37" s="9"/>
       <c r="C37" s="5"/>
       <c r="D37" s="9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E37" s="5"/>
       <c r="F37" s="9"/>
@@ -3894,14 +3725,13 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="B7:B26"/>
-    <mergeCell ref="C7:C26"/>
+    <mergeCell ref="C7:C32"/>
     <mergeCell ref="D7:D26"/>
     <mergeCell ref="E7:E26"/>
     <mergeCell ref="F7:F32"/>
-    <mergeCell ref="C27:C30"/>
     <mergeCell ref="E29:E30"/>
     <mergeCell ref="F35:F38"/>
     <mergeCell ref="B36:B38"/>
@@ -3922,7 +3752,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H37"/>
+  <dimension ref="A1:H36"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="7"/>
@@ -3936,7 +3766,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="19" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -3948,63 +3778,63 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="B2" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="C2" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="C2" s="20" t="s">
+      <c r="D2" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="D2" s="20" t="s">
+      <c r="E2" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="E2" s="20" t="s">
+      <c r="F2" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="F2" s="20" t="s">
+      <c r="G2" s="20" t="s">
         <v>73</v>
       </c>
-      <c r="G2" s="20" t="s">
+      <c r="H2" s="20" t="s">
         <v>74</v>
-      </c>
-      <c r="H2" s="20" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="21" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B3" s="22" t="s">
         <v>2</v>
       </c>
       <c r="C3" s="23" t="s">
+        <v>76</v>
+      </c>
+      <c r="D3" s="23" t="s">
         <v>77</v>
       </c>
-      <c r="D3" s="23" t="s">
+      <c r="E3" s="24" t="s">
         <v>78</v>
       </c>
-      <c r="E3" s="24" t="s">
+      <c r="F3" s="25" t="s">
         <v>79</v>
       </c>
-      <c r="F3" s="25" t="s">
+      <c r="G3" s="24" t="s">
         <v>80</v>
-      </c>
-      <c r="G3" s="24" t="s">
-        <v>81</v>
       </c>
       <c r="H3" s="24"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="21" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B4" s="22" t="s">
         <v>2</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D4" s="23" t="s">
         <v>26</v>
@@ -4016,91 +3846,91 @@
         <v>52</v>
       </c>
       <c r="G4" s="24" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H4" s="24"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="21" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B5" s="22" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="23" t="s">
+        <v>82</v>
+      </c>
+      <c r="D5" s="23" t="s">
         <v>83</v>
       </c>
-      <c r="D5" s="23" t="s">
+      <c r="E5" s="24" t="s">
         <v>84</v>
-      </c>
-      <c r="E5" s="24" t="s">
-        <v>85</v>
       </c>
       <c r="F5" s="27" t="s">
         <v>53</v>
       </c>
       <c r="G5" s="24" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H5" s="24"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="21" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B6" s="22" t="s">
         <v>2</v>
       </c>
       <c r="C6" s="23" t="s">
+        <v>86</v>
+      </c>
+      <c r="D6" s="23" t="s">
         <v>87</v>
       </c>
-      <c r="D6" s="23" t="s">
+      <c r="E6" s="24" t="s">
         <v>88</v>
-      </c>
-      <c r="E6" s="24" t="s">
-        <v>89</v>
       </c>
       <c r="F6" s="28" t="s">
         <v>54</v>
       </c>
       <c r="G6" s="24" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H6" s="24"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="21" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B7" s="22" t="s">
         <v>3</v>
       </c>
       <c r="C7" s="23" t="s">
+        <v>76</v>
+      </c>
+      <c r="D7" s="23" t="s">
         <v>77</v>
       </c>
-      <c r="D7" s="23" t="s">
+      <c r="E7" s="24" t="s">
         <v>78</v>
       </c>
-      <c r="E7" s="24" t="s">
+      <c r="F7" s="25" t="s">
         <v>79</v>
       </c>
-      <c r="F7" s="25" t="s">
+      <c r="G7" s="24" t="s">
         <v>80</v>
-      </c>
-      <c r="G7" s="24" t="s">
-        <v>81</v>
       </c>
       <c r="H7" s="24"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="21" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B8" s="22" t="s">
         <v>3</v>
       </c>
       <c r="C8" s="23" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D8" s="23" t="s">
         <v>26</v>
@@ -4112,13 +3942,13 @@
         <v>52</v>
       </c>
       <c r="G8" s="24" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H8" s="24"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="21" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B9" s="22" t="s">
         <v>3</v>
@@ -4127,24 +3957,22 @@
         <v>29</v>
       </c>
       <c r="D9" s="23" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E9" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F9" s="28" t="s">
         <v>54</v>
       </c>
       <c r="G9" s="24" t="s">
-        <v>92</v>
-      </c>
-      <c r="H9" s="24" t="s">
-        <v>93</v>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="H9" s="24"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="21" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B10" s="22" t="s">
         <v>3</v>
@@ -4156,67 +3984,67 @@
         <v>40</v>
       </c>
       <c r="E10" s="24" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F10" s="28" t="s">
         <v>54</v>
       </c>
       <c r="G10" s="24" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="H10" s="24"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="21" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B11" s="22" t="s">
         <v>4</v>
       </c>
       <c r="C11" s="23" t="s">
+        <v>76</v>
+      </c>
+      <c r="D11" s="23" t="s">
         <v>77</v>
       </c>
-      <c r="D11" s="23" t="s">
+      <c r="E11" s="24" t="s">
         <v>78</v>
       </c>
-      <c r="E11" s="24" t="s">
+      <c r="F11" s="25" t="s">
         <v>79</v>
       </c>
-      <c r="F11" s="25" t="s">
+      <c r="G11" s="24" t="s">
         <v>80</v>
-      </c>
-      <c r="G11" s="24" t="s">
-        <v>81</v>
       </c>
       <c r="H11" s="24"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="21" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B12" s="22" t="s">
         <v>4</v>
       </c>
       <c r="C12" s="23" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D12" s="23" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E12" s="24" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F12" s="26" t="s">
         <v>52</v>
       </c>
       <c r="G12" s="24" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H12" s="24"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="21" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B13" s="22" t="s">
         <v>4</v>
@@ -4228,49 +4056,49 @@
         <v>29</v>
       </c>
       <c r="E13" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F13" s="28" t="s">
         <v>54</v>
       </c>
       <c r="G13" s="24" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H13" s="24"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="21" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B14" s="22" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="23" t="s">
+        <v>76</v>
+      </c>
+      <c r="D14" s="23" t="s">
         <v>77</v>
       </c>
-      <c r="D14" s="23" t="s">
+      <c r="E14" s="24" t="s">
         <v>78</v>
       </c>
-      <c r="E14" s="24" t="s">
+      <c r="F14" s="25" t="s">
         <v>79</v>
       </c>
-      <c r="F14" s="25" t="s">
+      <c r="G14" s="24" t="s">
         <v>80</v>
-      </c>
-      <c r="G14" s="24" t="s">
-        <v>81</v>
       </c>
       <c r="H14" s="24"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="21" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B15" s="22" t="s">
         <v>5</v>
       </c>
       <c r="C15" s="23" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D15" s="23" t="s">
         <v>26</v>
@@ -4282,159 +4110,157 @@
         <v>52</v>
       </c>
       <c r="G15" s="24" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H15" s="24"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="21" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B16" s="22" t="s">
         <v>5</v>
       </c>
       <c r="C16" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="D16" s="23" t="s">
+        <v>97</v>
+      </c>
+      <c r="E16" s="24" t="s">
         <v>98</v>
-      </c>
-      <c r="D16" s="23" t="s">
-        <v>99</v>
-      </c>
-      <c r="E16" s="24" t="s">
-        <v>100</v>
       </c>
       <c r="F16" s="27" t="s">
         <v>53</v>
       </c>
       <c r="G16" s="24" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H16" s="24"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="21" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B17" s="22" t="s">
         <v>5</v>
       </c>
       <c r="C17" s="23" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D17" s="23" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E17" s="24" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F17" s="28" t="s">
         <v>54</v>
       </c>
       <c r="G17" s="24" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H17" s="24"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="21" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B18" s="22" t="s">
         <v>6</v>
       </c>
       <c r="C18" s="23" t="s">
+        <v>76</v>
+      </c>
+      <c r="D18" s="23" t="s">
         <v>77</v>
       </c>
-      <c r="D18" s="23" t="s">
+      <c r="E18" s="24" t="s">
         <v>78</v>
       </c>
-      <c r="E18" s="24" t="s">
+      <c r="F18" s="25" t="s">
         <v>79</v>
       </c>
-      <c r="F18" s="25" t="s">
+      <c r="G18" s="24" t="s">
         <v>80</v>
-      </c>
-      <c r="G18" s="24" t="s">
-        <v>81</v>
       </c>
       <c r="H18" s="24"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="21" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B19" s="22" t="s">
         <v>6</v>
       </c>
       <c r="C19" s="23" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D19" s="23" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E19" s="24" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F19" s="26" t="s">
         <v>52</v>
       </c>
       <c r="G19" s="24" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H19" s="24"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="21" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B20" s="22" t="s">
         <v>6</v>
       </c>
       <c r="C20" s="23" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D20" s="23" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E20" s="24" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F20" s="27" t="s">
         <v>53</v>
       </c>
       <c r="G20" s="24" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H20" s="24"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="21" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B21" s="22" t="s">
         <v>6</v>
       </c>
       <c r="C21" s="23" t="s">
-        <v>32</v>
+        <v>103</v>
       </c>
       <c r="D21" s="23" t="s">
         <v>37</v>
       </c>
       <c r="E21" s="24" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F21" s="28" t="s">
         <v>54</v>
       </c>
       <c r="G21" s="24" t="s">
-        <v>105</v>
-      </c>
-      <c r="H21" s="24" t="s">
-        <v>106</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="H21" s="24"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="21" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B22" s="22" t="s">
         <v>6</v>
@@ -4446,280 +4272,278 @@
         <v>41</v>
       </c>
       <c r="E22" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F22" s="28" t="s">
         <v>54</v>
       </c>
       <c r="G22" s="24" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H22" s="24" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="29" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B23" s="22" t="s">
         <v>2</v>
       </c>
       <c r="C23" s="23" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D23" s="23" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E23" s="24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F23" s="26" t="s">
         <v>52</v>
       </c>
       <c r="G23" s="24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H23" s="24"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="29" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B24" s="22" t="s">
         <v>2</v>
       </c>
       <c r="C24" s="23" t="s">
+        <v>87</v>
+      </c>
+      <c r="D24" s="23" t="s">
+        <v>109</v>
+      </c>
+      <c r="E24" s="24" t="s">
         <v>88</v>
-      </c>
-      <c r="D24" s="23" t="s">
-        <v>111</v>
-      </c>
-      <c r="E24" s="24" t="s">
-        <v>89</v>
       </c>
       <c r="F24" s="28" t="s">
         <v>54</v>
       </c>
       <c r="G24" s="24" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H24" s="24"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="29" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B25" s="22" t="s">
         <v>3</v>
       </c>
       <c r="C25" s="23" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D25" s="23" t="s">
         <v>83</v>
       </c>
       <c r="E25" s="24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F25" s="26" t="s">
         <v>52</v>
       </c>
       <c r="G25" s="24" t="s">
-        <v>110</v>
-      </c>
-      <c r="H25" s="24" t="s">
-        <v>112</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="H25" s="24"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="29" t="s">
+        <v>106</v>
+      </c>
+      <c r="B26" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="C26" s="23" t="s">
+        <v>107</v>
+      </c>
+      <c r="D26" s="23" t="s">
+        <v>82</v>
+      </c>
+      <c r="E26" s="24" t="s">
         <v>108</v>
       </c>
-      <c r="B26" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="C26" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="D26" s="23" t="s">
-        <v>32</v>
-      </c>
-      <c r="E26" s="24" t="s">
-        <v>91</v>
-      </c>
-      <c r="F26" s="28" t="s">
-        <v>54</v>
+      <c r="F26" s="26" t="s">
+        <v>52</v>
       </c>
       <c r="G26" s="24" t="s">
-        <v>92</v>
-      </c>
-      <c r="H26" s="24" t="s">
-        <v>113</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="H26" s="24"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="29" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B27" s="22" t="s">
         <v>4</v>
       </c>
       <c r="C27" s="23" t="s">
-        <v>109</v>
+        <v>40</v>
       </c>
       <c r="D27" s="23" t="s">
-        <v>83</v>
+        <v>41</v>
       </c>
       <c r="E27" s="24" t="s">
-        <v>110</v>
-      </c>
-      <c r="F27" s="26" t="s">
-        <v>52</v>
+        <v>88</v>
+      </c>
+      <c r="F27" s="28" t="s">
+        <v>54</v>
       </c>
       <c r="G27" s="24" t="s">
-        <v>110</v>
+        <v>89</v>
       </c>
       <c r="H27" s="24"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="29" t="s">
+        <v>106</v>
+      </c>
+      <c r="B28" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="C28" s="23" t="s">
+        <v>107</v>
+      </c>
+      <c r="D28" s="23" t="s">
+        <v>82</v>
+      </c>
+      <c r="E28" s="24" t="s">
         <v>108</v>
       </c>
-      <c r="B28" s="22" t="s">
-        <v>4</v>
-      </c>
-      <c r="C28" s="23" t="s">
-        <v>40</v>
-      </c>
-      <c r="D28" s="23" t="s">
-        <v>41</v>
-      </c>
-      <c r="E28" s="24" t="s">
-        <v>89</v>
-      </c>
-      <c r="F28" s="28" t="s">
-        <v>54</v>
+      <c r="F28" s="26" t="s">
+        <v>52</v>
       </c>
       <c r="G28" s="24" t="s">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="H28" s="24"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="29" t="s">
+        <v>106</v>
+      </c>
+      <c r="B29" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" s="23" t="s">
+        <v>107</v>
+      </c>
+      <c r="D29" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="E29" s="24" t="s">
         <v>108</v>
-      </c>
-      <c r="B29" s="22" t="s">
-        <v>5</v>
-      </c>
-      <c r="C29" s="23" t="s">
-        <v>109</v>
-      </c>
-      <c r="D29" s="23" t="s">
-        <v>83</v>
-      </c>
-      <c r="E29" s="24" t="s">
-        <v>110</v>
       </c>
       <c r="F29" s="26" t="s">
         <v>52</v>
       </c>
       <c r="G29" s="24" t="s">
+        <v>108</v>
+      </c>
+      <c r="H29" s="24" t="s">
         <v>110</v>
       </c>
-      <c r="H29" s="24"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="29" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B30" s="22" t="s">
         <v>6</v>
       </c>
       <c r="C30" s="23" t="s">
-        <v>109</v>
+        <v>37</v>
       </c>
       <c r="D30" s="23" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="E30" s="24" t="s">
-        <v>110</v>
-      </c>
-      <c r="F30" s="26" t="s">
-        <v>52</v>
+        <v>90</v>
+      </c>
+      <c r="F30" s="28" t="s">
+        <v>54</v>
       </c>
       <c r="G30" s="24" t="s">
-        <v>110</v>
+        <v>91</v>
       </c>
       <c r="H30" s="24" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="21" t="s">
+        <v>75</v>
+      </c>
+      <c r="B31" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="C31" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="D31" s="23" t="s">
+        <v>113</v>
+      </c>
+      <c r="E31" s="24" t="s">
         <v>114</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="29" t="s">
-        <v>108</v>
-      </c>
-      <c r="B31" s="22" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31" s="23" t="s">
-        <v>37</v>
-      </c>
-      <c r="D31" s="23" t="s">
-        <v>41</v>
-      </c>
-      <c r="E31" s="24" t="s">
-        <v>91</v>
       </c>
       <c r="F31" s="28" t="s">
         <v>54</v>
       </c>
       <c r="G31" s="24" t="s">
-        <v>92</v>
+        <v>115</v>
       </c>
       <c r="H31" s="24" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="21" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B32" s="22" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C32" s="23" t="s">
-        <v>115</v>
+        <v>15</v>
       </c>
       <c r="D32" s="23" t="s">
-        <v>116</v>
+        <v>17</v>
       </c>
       <c r="E32" s="24" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="F32" s="28" t="s">
         <v>54</v>
       </c>
       <c r="G32" s="24" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="H32" s="24" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="21" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B33" s="22" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C33" s="23" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="D33" s="23" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="E33" s="24" t="s">
         <v>117</v>
@@ -4730,64 +4554,62 @@
       <c r="G33" s="24" t="s">
         <v>118</v>
       </c>
-      <c r="H33" s="24" t="s">
+      <c r="H33" s="24"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="29" t="s">
+        <v>106</v>
+      </c>
+      <c r="B34" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="C34" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="D34" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="E34" s="24" t="s">
         <v>119</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="21" t="s">
-        <v>76</v>
-      </c>
-      <c r="B34" s="22" t="s">
-        <v>8</v>
-      </c>
-      <c r="C34" s="23" t="s">
-        <v>32</v>
-      </c>
-      <c r="D34" s="23" t="s">
-        <v>37</v>
-      </c>
-      <c r="E34" s="24" t="s">
-        <v>120</v>
       </c>
       <c r="F34" s="28" t="s">
         <v>54</v>
       </c>
       <c r="G34" s="24" t="s">
+        <v>120</v>
+      </c>
+      <c r="H34" s="24"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="21" t="s">
+        <v>75</v>
+      </c>
+      <c r="B35" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="C35" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="D35" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="E35" s="24" t="s">
         <v>121</v>
-      </c>
-      <c r="H34" s="24"/>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="29" t="s">
-        <v>108</v>
-      </c>
-      <c r="B35" s="22" t="s">
-        <v>5</v>
-      </c>
-      <c r="C35" s="23" t="s">
-        <v>31</v>
-      </c>
-      <c r="D35" s="23" t="s">
-        <v>32</v>
-      </c>
-      <c r="E35" s="24" t="s">
-        <v>122</v>
       </c>
       <c r="F35" s="28" t="s">
         <v>54</v>
       </c>
       <c r="G35" s="24" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H35" s="24"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="21" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B36" s="22" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C36" s="23" t="s">
         <v>45</v>
@@ -4796,39 +4618,15 @@
         <v>47</v>
       </c>
       <c r="E36" s="24" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F36" s="28" t="s">
         <v>54</v>
       </c>
       <c r="G36" s="24" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="H36" s="24"/>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="21" t="s">
-        <v>76</v>
-      </c>
-      <c r="B37" s="22" t="s">
-        <v>6</v>
-      </c>
-      <c r="C37" s="23" t="s">
-        <v>45</v>
-      </c>
-      <c r="D37" s="23" t="s">
-        <v>47</v>
-      </c>
-      <c r="E37" s="24" t="s">
-        <v>124</v>
-      </c>
-      <c r="F37" s="28" t="s">
-        <v>54</v>
-      </c>
-      <c r="G37" s="24" t="s">
-        <v>125</v>
-      </c>
-      <c r="H37" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/시간표.xlsx
+++ b/시간표.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="126">
   <si>
     <r>
       <rPr>
@@ -1042,7 +1042,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">09:10–13:50</t>
+      <t xml:space="preserve">09:10–15:30</t>
     </r>
   </si>
   <si>
@@ -1090,6 +1090,54 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">09:10–14:10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F4E79"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">어린이집
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F4E79"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">09:10–13:50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F4E79"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">어린이집
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF1F4E79"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">09:10–15:30
 </t>
     </r>
@@ -1507,6 +1555,9 @@
   </si>
   <si>
     <t xml:space="preserve">16:50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14:10</t>
   </si>
   <si>
     <t xml:space="preserve">하원 시간 늘림</t>
@@ -3186,13 +3237,13 @@
         <v>60</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G7" s="5"/>
       <c r="H7" s="5"/>
@@ -3409,9 +3460,9 @@
       <c r="A27" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B27" s="5"/>
+      <c r="B27" s="8"/>
       <c r="C27" s="8"/>
-      <c r="D27" s="5"/>
+      <c r="D27" s="8"/>
       <c r="E27" s="5"/>
       <c r="F27" s="8"/>
       <c r="G27" s="5"/>
@@ -3419,7 +3470,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="6"/>
-      <c r="B28" s="5"/>
+      <c r="B28" s="8"/>
       <c r="C28" s="8"/>
       <c r="D28" s="5"/>
       <c r="E28" s="5"/>
@@ -3431,11 +3482,11 @@
       <c r="A29" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B29" s="5"/>
+      <c r="B29" s="8"/>
       <c r="C29" s="8"/>
       <c r="D29" s="5"/>
       <c r="E29" s="9" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F29" s="8"/>
       <c r="G29" s="5"/>
@@ -3443,7 +3494,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="6"/>
-      <c r="B30" s="5"/>
+      <c r="B30" s="8"/>
       <c r="C30" s="8"/>
       <c r="D30" s="5"/>
       <c r="E30" s="9"/>
@@ -3455,7 +3506,7 @@
       <c r="A31" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B31" s="5"/>
+      <c r="B31" s="8"/>
       <c r="C31" s="8"/>
       <c r="D31" s="5"/>
       <c r="E31" s="5"/>
@@ -3465,7 +3516,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="6"/>
-      <c r="B32" s="5"/>
+      <c r="B32" s="8"/>
       <c r="C32" s="8"/>
       <c r="D32" s="5"/>
       <c r="E32" s="5"/>
@@ -3504,7 +3555,7 @@
       <c r="D35" s="5"/>
       <c r="E35" s="5"/>
       <c r="F35" s="9" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G35" s="5"/>
       <c r="H35" s="5"/>
@@ -3512,7 +3563,7 @@
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="6"/>
       <c r="B36" s="9" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C36" s="5"/>
       <c r="D36" s="5"/>
@@ -3528,7 +3579,7 @@
       <c r="B37" s="9"/>
       <c r="C37" s="5"/>
       <c r="D37" s="9" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E37" s="5"/>
       <c r="F37" s="9"/>
@@ -3727,9 +3778,9 @@
   </sheetData>
   <mergeCells count="10">
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="B7:B26"/>
+    <mergeCell ref="B7:B32"/>
     <mergeCell ref="C7:C32"/>
-    <mergeCell ref="D7:D26"/>
+    <mergeCell ref="D7:D27"/>
     <mergeCell ref="E7:E26"/>
     <mergeCell ref="F7:F32"/>
     <mergeCell ref="E29:E30"/>
@@ -3766,7 +3817,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="19" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -3778,63 +3829,63 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="20" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B2" s="20" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C2" s="20" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D2" s="20" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F2" s="20" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G2" s="20" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="H2" s="20" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="21" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B3" s="22" t="s">
         <v>2</v>
       </c>
       <c r="C3" s="23" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D3" s="23" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E3" s="24" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F3" s="25" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G3" s="24" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H3" s="24"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="21" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B4" s="22" t="s">
         <v>2</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D4" s="23" t="s">
         <v>26</v>
@@ -3846,91 +3897,91 @@
         <v>52</v>
       </c>
       <c r="G4" s="24" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H4" s="24"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="21" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B5" s="22" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="23" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D5" s="23" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E5" s="24" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F5" s="27" t="s">
         <v>53</v>
       </c>
       <c r="G5" s="24" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H5" s="24"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="21" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B6" s="22" t="s">
         <v>2</v>
       </c>
       <c r="C6" s="23" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D6" s="23" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E6" s="24" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F6" s="28" t="s">
         <v>54</v>
       </c>
       <c r="G6" s="24" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H6" s="24"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="21" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B7" s="22" t="s">
         <v>3</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D7" s="23" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E7" s="24" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F7" s="25" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G7" s="24" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H7" s="24"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="21" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B8" s="22" t="s">
         <v>3</v>
       </c>
       <c r="C8" s="23" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D8" s="23" t="s">
         <v>26</v>
@@ -3942,13 +3993,13 @@
         <v>52</v>
       </c>
       <c r="G8" s="24" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H8" s="24"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="21" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B9" s="22" t="s">
         <v>3</v>
@@ -3960,19 +4011,19 @@
         <v>33</v>
       </c>
       <c r="E9" s="24" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F9" s="28" t="s">
         <v>54</v>
       </c>
       <c r="G9" s="24" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H9" s="24"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="21" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B10" s="22" t="s">
         <v>3</v>
@@ -3984,67 +4035,67 @@
         <v>40</v>
       </c>
       <c r="E10" s="24" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F10" s="28" t="s">
         <v>54</v>
       </c>
       <c r="G10" s="24" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="H10" s="24"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="21" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B11" s="22" t="s">
         <v>4</v>
       </c>
       <c r="C11" s="23" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D11" s="23" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E11" s="24" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F11" s="25" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G11" s="24" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H11" s="24"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="21" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B12" s="22" t="s">
         <v>4</v>
       </c>
       <c r="C12" s="23" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D12" s="23" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E12" s="24" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F12" s="26" t="s">
         <v>52</v>
       </c>
       <c r="G12" s="24" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H12" s="24"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="21" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B13" s="22" t="s">
         <v>4</v>
@@ -4056,49 +4107,49 @@
         <v>29</v>
       </c>
       <c r="E13" s="24" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F13" s="28" t="s">
         <v>54</v>
       </c>
       <c r="G13" s="24" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H13" s="24"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="21" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B14" s="22" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="23" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D14" s="23" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E14" s="24" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F14" s="25" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G14" s="24" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H14" s="24"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="21" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B15" s="22" t="s">
         <v>5</v>
       </c>
       <c r="C15" s="23" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D15" s="23" t="s">
         <v>26</v>
@@ -4110,157 +4161,157 @@
         <v>52</v>
       </c>
       <c r="G15" s="24" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H15" s="24"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="21" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B16" s="22" t="s">
         <v>5</v>
       </c>
       <c r="C16" s="23" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D16" s="23" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E16" s="24" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F16" s="27" t="s">
         <v>53</v>
       </c>
       <c r="G16" s="24" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H16" s="24"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="21" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B17" s="22" t="s">
         <v>5</v>
       </c>
       <c r="C17" s="23" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D17" s="23" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E17" s="24" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F17" s="28" t="s">
         <v>54</v>
       </c>
       <c r="G17" s="24" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H17" s="24"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="21" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B18" s="22" t="s">
         <v>6</v>
       </c>
       <c r="C18" s="23" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D18" s="23" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E18" s="24" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F18" s="25" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G18" s="24" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H18" s="24"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="21" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B19" s="22" t="s">
         <v>6</v>
       </c>
       <c r="C19" s="23" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D19" s="23" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E19" s="24" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F19" s="26" t="s">
         <v>52</v>
       </c>
       <c r="G19" s="24" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H19" s="24"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="21" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B20" s="22" t="s">
         <v>6</v>
       </c>
       <c r="C20" s="23" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D20" s="23" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E20" s="24" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F20" s="27" t="s">
         <v>53</v>
       </c>
       <c r="G20" s="24" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H20" s="24"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="21" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B21" s="22" t="s">
         <v>6</v>
       </c>
       <c r="C21" s="23" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D21" s="23" t="s">
         <v>37</v>
       </c>
       <c r="E21" s="24" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F21" s="28" t="s">
         <v>54</v>
       </c>
       <c r="G21" s="24" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="H21" s="24"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="21" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B22" s="22" t="s">
         <v>6</v>
@@ -4272,117 +4323,117 @@
         <v>41</v>
       </c>
       <c r="E22" s="24" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F22" s="28" t="s">
         <v>54</v>
       </c>
       <c r="G22" s="24" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H22" s="24" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="29" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B23" s="22" t="s">
         <v>2</v>
       </c>
       <c r="C23" s="23" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D23" s="23" t="s">
-        <v>82</v>
+        <v>35</v>
       </c>
       <c r="E23" s="24" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F23" s="26" t="s">
         <v>52</v>
       </c>
       <c r="G23" s="24" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="H23" s="24"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="29" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B24" s="22" t="s">
         <v>2</v>
       </c>
       <c r="C24" s="23" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D24" s="23" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E24" s="24" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F24" s="28" t="s">
         <v>54</v>
       </c>
       <c r="G24" s="24" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H24" s="24"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="29" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B25" s="22" t="s">
         <v>3</v>
       </c>
       <c r="C25" s="23" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D25" s="23" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E25" s="24" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F25" s="26" t="s">
         <v>52</v>
       </c>
       <c r="G25" s="24" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="H25" s="24"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="29" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B26" s="22" t="s">
         <v>4</v>
       </c>
       <c r="C26" s="23" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D26" s="23" t="s">
-        <v>82</v>
+        <v>112</v>
       </c>
       <c r="E26" s="24" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F26" s="26" t="s">
         <v>52</v>
       </c>
       <c r="G26" s="24" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="H26" s="24"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="29" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B27" s="22" t="s">
         <v>4</v>
@@ -4394,69 +4445,69 @@
         <v>41</v>
       </c>
       <c r="E27" s="24" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F27" s="28" t="s">
         <v>54</v>
       </c>
       <c r="G27" s="24" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H27" s="24"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="29" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B28" s="22" t="s">
         <v>5</v>
       </c>
       <c r="C28" s="23" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D28" s="23" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E28" s="24" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F28" s="26" t="s">
         <v>52</v>
       </c>
       <c r="G28" s="24" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="H28" s="24"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="29" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B29" s="22" t="s">
         <v>6</v>
       </c>
       <c r="C29" s="23" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D29" s="23" t="s">
         <v>35</v>
       </c>
       <c r="E29" s="24" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F29" s="26" t="s">
         <v>52</v>
       </c>
       <c r="G29" s="24" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="H29" s="24" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="29" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B30" s="22" t="s">
         <v>6</v>
@@ -4468,47 +4519,47 @@
         <v>41</v>
       </c>
       <c r="E30" s="24" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F30" s="28" t="s">
         <v>54</v>
       </c>
       <c r="G30" s="24" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H30" s="24" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="21" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B31" s="22" t="s">
         <v>4</v>
       </c>
       <c r="C31" s="23" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D31" s="23" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E31" s="24" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="F31" s="28" t="s">
         <v>54</v>
       </c>
       <c r="G31" s="24" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="H31" s="24" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="21" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B32" s="22" t="s">
         <v>7</v>
@@ -4520,21 +4571,21 @@
         <v>17</v>
       </c>
       <c r="E32" s="24" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="F32" s="28" t="s">
         <v>54</v>
       </c>
       <c r="G32" s="24" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="H32" s="24" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="21" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B33" s="22" t="s">
         <v>8</v>
@@ -4546,19 +4597,19 @@
         <v>37</v>
       </c>
       <c r="E33" s="24" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="F33" s="28" t="s">
         <v>54</v>
       </c>
       <c r="G33" s="24" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="H33" s="24"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="29" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B34" s="22" t="s">
         <v>5</v>
@@ -4570,19 +4621,19 @@
         <v>33</v>
       </c>
       <c r="E34" s="24" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="F34" s="28" t="s">
         <v>54</v>
       </c>
       <c r="G34" s="24" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="H34" s="24"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="21" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B35" s="22" t="s">
         <v>3</v>
@@ -4594,19 +4645,19 @@
         <v>47</v>
       </c>
       <c r="E35" s="24" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="F35" s="28" t="s">
         <v>54</v>
       </c>
       <c r="G35" s="24" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="H35" s="24"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="21" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B36" s="22" t="s">
         <v>6</v>
@@ -4618,13 +4669,13 @@
         <v>47</v>
       </c>
       <c r="E36" s="24" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="F36" s="28" t="s">
         <v>54</v>
       </c>
       <c r="G36" s="24" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="H36" s="24"/>
     </row>

--- a/시간표.xlsx
+++ b/시간표.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="첫째 주간표" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="둘째 주간표" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="일정(편집용)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="첫째 주간표" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="둘째 주간표" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="일정(편집용)" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'첫째 주간표'!$A$1:$H$52</definedName>
@@ -1383,13 +1383,7 @@
       </c>
       <c r="F39" s="5" t="n"/>
       <c r="G39" s="5" t="n"/>
-      <c r="H39" s="11" t="inlineStr">
-        <is>
-          <t>테스트수업
-17:00–17:30
-미정</t>
-        </is>
-      </c>
+      <c r="H39" s="5" t="n"/>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" s="6" t="inlineStr"/>
@@ -1399,7 +1393,7 @@
       <c r="E40" s="10" t="n"/>
       <c r="F40" s="5" t="n"/>
       <c r="G40" s="5" t="n"/>
-      <c r="H40" s="8" t="n"/>
+      <c r="H40" s="5" t="n"/>
     </row>
     <row r="41" ht="15" customHeight="1">
       <c r="A41" s="6" t="inlineStr">
@@ -1603,7 +1597,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="27">
+  <mergeCells count="26">
     <mergeCell ref="C4:C5"/>
     <mergeCell ref="B34:B36"/>
     <mergeCell ref="E4:E5"/>
@@ -1615,7 +1609,6 @@
     <mergeCell ref="H31:H34"/>
     <mergeCell ref="C35:C36"/>
     <mergeCell ref="F45:F46"/>
-    <mergeCell ref="H39:H40"/>
     <mergeCell ref="D4:D5"/>
     <mergeCell ref="C27:C30"/>
     <mergeCell ref="F35:F38"/>
@@ -2418,7 +2411,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H37"/>
+  <dimension ref="A1:H36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -3791,44 +3784,6 @@
         </is>
       </c>
       <c r="H36" s="25" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="23" t="inlineStr">
-        <is>
-          <t>첫째</t>
-        </is>
-      </c>
-      <c r="B37" s="24" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C37" s="24" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="D37" s="24" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
-      <c r="E37" s="25" t="inlineStr">
-        <is>
-          <t>테스트수업</t>
-        </is>
-      </c>
-      <c r="F37" s="29" t="inlineStr">
-        <is>
-          <t>학원</t>
-        </is>
-      </c>
-      <c r="G37" s="25" t="inlineStr">
-        <is>
-          <t>미정</t>
-        </is>
-      </c>
-      <c r="H37" s="25" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/시간표.xlsx
+++ b/시간표.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="첫째 주간표" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="둘째 주간표" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="일정(편집용)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="첫째 주간표" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="둘째 주간표" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="일정(편집용)" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'첫째 주간표'!$A$1:$H$52</definedName>
@@ -1831,7 +1831,12 @@
       <c r="D11" s="10" t="n"/>
       <c r="E11" s="10" t="n"/>
       <c r="F11" s="10" t="n"/>
-      <c r="G11" s="5" t="n"/>
+      <c r="G11" s="11" t="inlineStr">
+        <is>
+          <t>발레
+10:00–11:00</t>
+        </is>
+      </c>
       <c r="H11" s="5" t="n"/>
     </row>
     <row r="12" ht="15" customHeight="1">
@@ -1841,7 +1846,7 @@
       <c r="D12" s="10" t="n"/>
       <c r="E12" s="10" t="n"/>
       <c r="F12" s="10" t="n"/>
-      <c r="G12" s="5" t="n"/>
+      <c r="G12" s="10" t="n"/>
       <c r="H12" s="5" t="n"/>
     </row>
     <row r="13" ht="15" customHeight="1">
@@ -1855,7 +1860,7 @@
       <c r="D13" s="10" t="n"/>
       <c r="E13" s="10" t="n"/>
       <c r="F13" s="10" t="n"/>
-      <c r="G13" s="5" t="n"/>
+      <c r="G13" s="10" t="n"/>
       <c r="H13" s="5" t="n"/>
     </row>
     <row r="14" ht="15" customHeight="1">
@@ -1865,7 +1870,7 @@
       <c r="D14" s="10" t="n"/>
       <c r="E14" s="10" t="n"/>
       <c r="F14" s="10" t="n"/>
-      <c r="G14" s="5" t="n"/>
+      <c r="G14" s="8" t="n"/>
       <c r="H14" s="5" t="n"/>
     </row>
     <row r="15" ht="15" customHeight="1">
@@ -2388,7 +2393,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="E7:E26"/>
     <mergeCell ref="F7:F32"/>
@@ -2396,6 +2401,7 @@
     <mergeCell ref="E29:E30"/>
     <mergeCell ref="C7:C32"/>
     <mergeCell ref="D7:D27"/>
+    <mergeCell ref="G11:G14"/>
     <mergeCell ref="F35:F38"/>
     <mergeCell ref="B36:B38"/>
     <mergeCell ref="B7:B32"/>
@@ -2411,7 +2417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H36"/>
+  <dimension ref="A1:H37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -3784,6 +3790,40 @@
         </is>
       </c>
       <c r="H36" s="25" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="30" t="inlineStr">
+        <is>
+          <t>둘째</t>
+        </is>
+      </c>
+      <c r="B37" s="24" t="inlineStr">
+        <is>
+          <t>토</t>
+        </is>
+      </c>
+      <c r="C37" s="24" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="D37" s="24" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E37" s="25" t="inlineStr">
+        <is>
+          <t>발레</t>
+        </is>
+      </c>
+      <c r="F37" s="29" t="inlineStr">
+        <is>
+          <t>학원</t>
+        </is>
+      </c>
+      <c r="G37" s="25" t="inlineStr"/>
+      <c r="H37" s="25" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/시간표.xlsx
+++ b/시간표.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="첫째 주간표" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="둘째 주간표" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="일정(편집용)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="첫째 주간표" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="둘째 주간표" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="일정(편집용)" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'첫째 주간표'!$A$1:$H$52</definedName>
@@ -1831,12 +1831,7 @@
       <c r="D11" s="10" t="n"/>
       <c r="E11" s="10" t="n"/>
       <c r="F11" s="10" t="n"/>
-      <c r="G11" s="11" t="inlineStr">
-        <is>
-          <t>발레
-10:00–11:00</t>
-        </is>
-      </c>
+      <c r="G11" s="5" t="n"/>
       <c r="H11" s="5" t="n"/>
     </row>
     <row r="12" ht="15" customHeight="1">
@@ -1846,7 +1841,7 @@
       <c r="D12" s="10" t="n"/>
       <c r="E12" s="10" t="n"/>
       <c r="F12" s="10" t="n"/>
-      <c r="G12" s="10" t="n"/>
+      <c r="G12" s="5" t="n"/>
       <c r="H12" s="5" t="n"/>
     </row>
     <row r="13" ht="15" customHeight="1">
@@ -1860,7 +1855,7 @@
       <c r="D13" s="10" t="n"/>
       <c r="E13" s="10" t="n"/>
       <c r="F13" s="10" t="n"/>
-      <c r="G13" s="10" t="n"/>
+      <c r="G13" s="5" t="n"/>
       <c r="H13" s="5" t="n"/>
     </row>
     <row r="14" ht="15" customHeight="1">
@@ -1870,7 +1865,7 @@
       <c r="D14" s="10" t="n"/>
       <c r="E14" s="10" t="n"/>
       <c r="F14" s="10" t="n"/>
-      <c r="G14" s="8" t="n"/>
+      <c r="G14" s="5" t="n"/>
       <c r="H14" s="5" t="n"/>
     </row>
     <row r="15" ht="15" customHeight="1">
@@ -2393,7 +2388,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="E7:E26"/>
     <mergeCell ref="F7:F32"/>
@@ -2401,7 +2396,6 @@
     <mergeCell ref="E29:E30"/>
     <mergeCell ref="C7:C32"/>
     <mergeCell ref="D7:D27"/>
-    <mergeCell ref="G11:G14"/>
     <mergeCell ref="F35:F38"/>
     <mergeCell ref="B36:B38"/>
     <mergeCell ref="B7:B32"/>
@@ -2417,7 +2411,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H37"/>
+  <dimension ref="A1:H36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -3790,40 +3784,6 @@
         </is>
       </c>
       <c r="H36" s="25" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="30" t="inlineStr">
-        <is>
-          <t>둘째</t>
-        </is>
-      </c>
-      <c r="B37" s="24" t="inlineStr">
-        <is>
-          <t>토</t>
-        </is>
-      </c>
-      <c r="C37" s="24" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="D37" s="24" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="E37" s="25" t="inlineStr">
-        <is>
-          <t>발레</t>
-        </is>
-      </c>
-      <c r="F37" s="29" t="inlineStr">
-        <is>
-          <t>학원</t>
-        </is>
-      </c>
-      <c r="G37" s="25" t="inlineStr"/>
-      <c r="H37" s="25" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/시간표.xlsx
+++ b/시간표.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="첫째 주간표" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="둘째 주간표" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="일정(편집용)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="첫째 주간표" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="둘째 주간표" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="일정(편집용)" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'첫째 주간표'!$A$1:$H$52</definedName>
@@ -1761,7 +1761,7 @@
       <c r="C7" s="9" t="inlineStr">
         <is>
           <t>어린이집
-09:10–15:20</t>
+09:10–15:30</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="D25" s="24" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="E25" s="25" t="inlineStr">

--- a/시간표.xlsx
+++ b/시간표.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="첫째 주간표" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="둘째 주간표" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="일정(편집용)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="첫째 주간표" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="둘째 주간표" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="일정(편집용)" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'첫째 주간표'!$A$1:$H$52</definedName>
@@ -1761,7 +1761,7 @@
       <c r="C7" s="9" t="inlineStr">
         <is>
           <t>어린이집
-09:10–15:30</t>
+09:10–15:20</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="D25" s="24" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="E25" s="25" t="inlineStr">

--- a/시간표.xlsx
+++ b/시간표.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="첫째 주간표" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="둘째 주간표" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="일정(편집용)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="첫째 주간표" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="둘째 주간표" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="일정(편집용)" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'첫째 주간표'!$A$1:$H$52</definedName>

--- a/시간표.xlsx
+++ b/시간표.xlsx
@@ -926,7 +926,13 @@
       <c r="D7" s="10" t="n"/>
       <c r="E7" s="10" t="n"/>
       <c r="F7" s="10" t="n"/>
-      <c r="G7" s="5" t="n"/>
+      <c r="G7" s="11" t="inlineStr">
+        <is>
+          <t>댄스학원
+09:00–10:00*
+약 한 달 한시적·종료시간 추정</t>
+        </is>
+      </c>
       <c r="H7" s="5" t="n"/>
     </row>
     <row r="8" ht="15" customHeight="1">
@@ -936,7 +942,7 @@
       <c r="D8" s="10" t="n"/>
       <c r="E8" s="10" t="n"/>
       <c r="F8" s="10" t="n"/>
-      <c r="G8" s="5" t="n"/>
+      <c r="G8" s="10" t="n"/>
       <c r="H8" s="5" t="n"/>
     </row>
     <row r="9" ht="15" customHeight="1">
@@ -950,13 +956,7 @@
       <c r="D9" s="10" t="n"/>
       <c r="E9" s="10" t="n"/>
       <c r="F9" s="10" t="n"/>
-      <c r="G9" s="11" t="inlineStr">
-        <is>
-          <t>첼로
-09:30–10:00
-수/토 중 하나 (주말 일정에 따라 변동)</t>
-        </is>
-      </c>
+      <c r="G9" s="10" t="n"/>
       <c r="H9" s="5" t="n"/>
     </row>
     <row r="10" ht="15" customHeight="1">
@@ -1515,7 +1515,7 @@
         <is>
           <t>첼로
 19:40–20:10
-수/토 중 하나 (주말 일정에 따라 변동)</t>
+첼로교실</t>
         </is>
       </c>
       <c r="E49" s="5" t="n"/>
@@ -1606,6 +1606,7 @@
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="C6:C24"/>
     <mergeCell ref="F6:F22"/>
+    <mergeCell ref="G7:G10"/>
     <mergeCell ref="H31:H34"/>
     <mergeCell ref="C35:C36"/>
     <mergeCell ref="F45:F46"/>
@@ -1619,7 +1620,6 @@
     <mergeCell ref="D49:D51"/>
     <mergeCell ref="E6:E24"/>
     <mergeCell ref="B6:B24"/>
-    <mergeCell ref="G9:G10"/>
     <mergeCell ref="D23:D26"/>
     <mergeCell ref="B4:B5"/>
     <mergeCell ref="F4:F5"/>
@@ -3585,11 +3585,7 @@
           <t>첼로교실</t>
         </is>
       </c>
-      <c r="H31" s="25" t="inlineStr">
-        <is>
-          <t>수/토 중 하나 (주말 일정에 따라 변동)</t>
-        </is>
-      </c>
+      <c r="H31" s="25" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="23" t="inlineStr">
@@ -3599,22 +3595,22 @@
       </c>
       <c r="B32" s="24" t="inlineStr">
         <is>
-          <t>토</t>
+          <t>일</t>
         </is>
       </c>
       <c r="C32" s="24" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="D32" s="24" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="E32" s="25" t="inlineStr">
         <is>
-          <t>첼로</t>
+          <t>수영</t>
         </is>
       </c>
       <c r="F32" s="29" t="inlineStr">
@@ -3624,87 +3620,83 @@
       </c>
       <c r="G32" s="25" t="inlineStr">
         <is>
-          <t>첼로교실</t>
-        </is>
-      </c>
-      <c r="H32" s="25" t="inlineStr">
-        <is>
-          <t>수/토 중 하나 (주말 일정에 따라 변동)</t>
-        </is>
-      </c>
+          <t>수영장</t>
+        </is>
+      </c>
+      <c r="H32" s="25" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="23" t="inlineStr">
+      <c r="A33" s="30" t="inlineStr">
+        <is>
+          <t>둘째</t>
+        </is>
+      </c>
+      <c r="B33" s="24" t="inlineStr">
+        <is>
+          <t>목</t>
+        </is>
+      </c>
+      <c r="C33" s="24" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="D33" s="24" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E33" s="25" t="inlineStr">
+        <is>
+          <t>축구</t>
+        </is>
+      </c>
+      <c r="F33" s="29" t="inlineStr">
+        <is>
+          <t>학원</t>
+        </is>
+      </c>
+      <c r="G33" s="25" t="inlineStr">
+        <is>
+          <t>축구교실</t>
+        </is>
+      </c>
+      <c r="H33" s="25" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="23" t="inlineStr">
         <is>
           <t>첫째</t>
         </is>
       </c>
-      <c r="B33" s="24" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C33" s="24" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="D33" s="24" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="E33" s="25" t="inlineStr">
-        <is>
-          <t>수영</t>
-        </is>
-      </c>
-      <c r="F33" s="29" t="inlineStr">
+      <c r="B34" s="24" t="inlineStr">
+        <is>
+          <t>화</t>
+        </is>
+      </c>
+      <c r="C34" s="24" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="D34" s="24" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="E34" s="25" t="inlineStr">
+        <is>
+          <t>화상영어</t>
+        </is>
+      </c>
+      <c r="F34" s="29" t="inlineStr">
         <is>
           <t>학원</t>
         </is>
       </c>
-      <c r="G33" s="25" t="inlineStr">
-        <is>
-          <t>수영장</t>
-        </is>
-      </c>
-      <c r="H33" s="25" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="30" t="inlineStr">
-        <is>
-          <t>둘째</t>
-        </is>
-      </c>
-      <c r="B34" s="24" t="inlineStr">
-        <is>
-          <t>목</t>
-        </is>
-      </c>
-      <c r="C34" s="24" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="D34" s="24" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="E34" s="25" t="inlineStr">
-        <is>
-          <t>축구</t>
-        </is>
-      </c>
-      <c r="F34" s="29" t="inlineStr">
-        <is>
-          <t>학원</t>
-        </is>
-      </c>
       <c r="G34" s="25" t="inlineStr">
         <is>
-          <t>축구교실</t>
+          <t>온라인</t>
         </is>
       </c>
       <c r="H34" s="25" t="inlineStr"/>
@@ -3717,7 +3709,7 @@
       </c>
       <c r="B35" s="24" t="inlineStr">
         <is>
-          <t>화</t>
+          <t>금</t>
         </is>
       </c>
       <c r="C35" s="24" t="inlineStr">
@@ -3755,22 +3747,22 @@
       </c>
       <c r="B36" s="24" t="inlineStr">
         <is>
-          <t>금</t>
+          <t>토</t>
         </is>
       </c>
       <c r="C36" s="24" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="D36" s="24" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="E36" s="25" t="inlineStr">
         <is>
-          <t>화상영어</t>
+          <t>댄스학원</t>
         </is>
       </c>
       <c r="F36" s="29" t="inlineStr">
@@ -3780,10 +3772,14 @@
       </c>
       <c r="G36" s="25" t="inlineStr">
         <is>
-          <t>온라인</t>
-        </is>
-      </c>
-      <c r="H36" s="25" t="inlineStr"/>
+          <t>댄스학원</t>
+        </is>
+      </c>
+      <c r="H36" s="25" t="inlineStr">
+        <is>
+          <t>약 한 달 한시적·종료시간 추정 / ※ 종료시간 추정</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/시간표.xlsx
+++ b/시간표.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="첫째 주간표" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="둘째 주간표" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="일정(편집용)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="첫째 주간표" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="둘째 주간표" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="일정(편집용)" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'첫째 주간표'!$A$1:$H$52</definedName>
@@ -1793,7 +1793,13 @@
       <c r="D8" s="10" t="n"/>
       <c r="E8" s="10" t="n"/>
       <c r="F8" s="10" t="n"/>
-      <c r="G8" s="5" t="n"/>
+      <c r="G8" s="11" t="inlineStr">
+        <is>
+          <t>축구
+09:20–09:50*
+추정</t>
+        </is>
+      </c>
       <c r="H8" s="5" t="n"/>
     </row>
     <row r="9" ht="15" customHeight="1">
@@ -1807,7 +1813,7 @@
       <c r="D9" s="10" t="n"/>
       <c r="E9" s="10" t="n"/>
       <c r="F9" s="10" t="n"/>
-      <c r="G9" s="5" t="n"/>
+      <c r="G9" s="10" t="n"/>
       <c r="H9" s="5" t="n"/>
     </row>
     <row r="10" ht="15" customHeight="1">
@@ -1817,7 +1823,7 @@
       <c r="D10" s="10" t="n"/>
       <c r="E10" s="10" t="n"/>
       <c r="F10" s="10" t="n"/>
-      <c r="G10" s="5" t="n"/>
+      <c r="G10" s="8" t="n"/>
       <c r="H10" s="5" t="n"/>
     </row>
     <row r="11" ht="15" customHeight="1">
@@ -2045,13 +2051,7 @@
       <c r="B29" s="10" t="n"/>
       <c r="C29" s="10" t="n"/>
       <c r="D29" s="5" t="n"/>
-      <c r="E29" s="11" t="inlineStr">
-        <is>
-          <t>축구
-14:30–15:00
-축구교실</t>
-        </is>
-      </c>
+      <c r="E29" s="5" t="n"/>
       <c r="F29" s="10" t="n"/>
       <c r="G29" s="5" t="n"/>
       <c r="H29" s="5" t="n"/>
@@ -2061,7 +2061,7 @@
       <c r="B30" s="10" t="n"/>
       <c r="C30" s="10" t="n"/>
       <c r="D30" s="5" t="n"/>
-      <c r="E30" s="8" t="n"/>
+      <c r="E30" s="5" t="n"/>
       <c r="F30" s="10" t="n"/>
       <c r="G30" s="5" t="n"/>
       <c r="H30" s="5" t="n"/>
@@ -2393,9 +2393,9 @@
     <mergeCell ref="E7:E26"/>
     <mergeCell ref="F7:F32"/>
     <mergeCell ref="D37:D38"/>
-    <mergeCell ref="E29:E30"/>
     <mergeCell ref="C7:C32"/>
     <mergeCell ref="D7:D27"/>
+    <mergeCell ref="G8:G10"/>
     <mergeCell ref="F35:F38"/>
     <mergeCell ref="B36:B38"/>
     <mergeCell ref="B7:B32"/>
@@ -3626,29 +3626,29 @@
       <c r="H32" s="25" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="30" t="inlineStr">
-        <is>
-          <t>둘째</t>
+      <c r="A33" s="23" t="inlineStr">
+        <is>
+          <t>첫째</t>
         </is>
       </c>
       <c r="B33" s="24" t="inlineStr">
         <is>
-          <t>목</t>
+          <t>화</t>
         </is>
       </c>
       <c r="C33" s="24" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="D33" s="24" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="E33" s="25" t="inlineStr">
         <is>
-          <t>축구</t>
+          <t>화상영어</t>
         </is>
       </c>
       <c r="F33" s="29" t="inlineStr">
@@ -3658,7 +3658,7 @@
       </c>
       <c r="G33" s="25" t="inlineStr">
         <is>
-          <t>축구교실</t>
+          <t>온라인</t>
         </is>
       </c>
       <c r="H33" s="25" t="inlineStr"/>
@@ -3671,7 +3671,7 @@
       </c>
       <c r="B34" s="24" t="inlineStr">
         <is>
-          <t>화</t>
+          <t>금</t>
         </is>
       </c>
       <c r="C34" s="24" t="inlineStr">
@@ -3709,22 +3709,22 @@
       </c>
       <c r="B35" s="24" t="inlineStr">
         <is>
-          <t>금</t>
+          <t>토</t>
         </is>
       </c>
       <c r="C35" s="24" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="D35" s="24" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="E35" s="25" t="inlineStr">
         <is>
-          <t>화상영어</t>
+          <t>댄스학원</t>
         </is>
       </c>
       <c r="F35" s="29" t="inlineStr">
@@ -3734,15 +3734,19 @@
       </c>
       <c r="G35" s="25" t="inlineStr">
         <is>
-          <t>온라인</t>
-        </is>
-      </c>
-      <c r="H35" s="25" t="inlineStr"/>
+          <t>댄스학원</t>
+        </is>
+      </c>
+      <c r="H35" s="25" t="inlineStr">
+        <is>
+          <t>약 한 달 한시적·종료시간 추정 / ※ 종료시간 추정</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="23" t="inlineStr">
-        <is>
-          <t>첫째</t>
+      <c r="A36" s="30" t="inlineStr">
+        <is>
+          <t>둘째</t>
         </is>
       </c>
       <c r="B36" s="24" t="inlineStr">
@@ -3752,17 +3756,17 @@
       </c>
       <c r="C36" s="24" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="D36" s="24" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="E36" s="25" t="inlineStr">
         <is>
-          <t>댄스학원</t>
+          <t>축구</t>
         </is>
       </c>
       <c r="F36" s="29" t="inlineStr">
@@ -3772,12 +3776,12 @@
       </c>
       <c r="G36" s="25" t="inlineStr">
         <is>
-          <t>댄스학원</t>
+          <t>축구교실</t>
         </is>
       </c>
       <c r="H36" s="25" t="inlineStr">
         <is>
-          <t>약 한 달 한시적·종료시간 추정 / ※ 종료시간 추정</t>
+          <t>추정 / ※ 종료시간 추정</t>
         </is>
       </c>
     </row>

--- a/시간표.xlsx
+++ b/시간표.xlsx
@@ -1793,13 +1793,7 @@
       <c r="D8" s="10" t="n"/>
       <c r="E8" s="10" t="n"/>
       <c r="F8" s="10" t="n"/>
-      <c r="G8" s="11" t="inlineStr">
-        <is>
-          <t>축구
-09:20–09:50*
-추정</t>
-        </is>
-      </c>
+      <c r="G8" s="5" t="n"/>
       <c r="H8" s="5" t="n"/>
     </row>
     <row r="9" ht="15" customHeight="1">
@@ -1813,7 +1807,7 @@
       <c r="D9" s="10" t="n"/>
       <c r="E9" s="10" t="n"/>
       <c r="F9" s="10" t="n"/>
-      <c r="G9" s="10" t="n"/>
+      <c r="G9" s="5" t="n"/>
       <c r="H9" s="5" t="n"/>
     </row>
     <row r="10" ht="15" customHeight="1">
@@ -1823,7 +1817,7 @@
       <c r="D10" s="10" t="n"/>
       <c r="E10" s="10" t="n"/>
       <c r="F10" s="10" t="n"/>
-      <c r="G10" s="8" t="n"/>
+      <c r="G10" s="5" t="n"/>
       <c r="H10" s="5" t="n"/>
     </row>
     <row r="11" ht="15" customHeight="1">
@@ -2308,7 +2302,13 @@
       </c>
       <c r="B49" s="5" t="n"/>
       <c r="C49" s="5" t="n"/>
-      <c r="D49" s="5" t="n"/>
+      <c r="D49" s="11" t="inlineStr">
+        <is>
+          <t>축구
+19:30–20:00*
+추정</t>
+        </is>
+      </c>
       <c r="E49" s="5" t="n"/>
       <c r="F49" s="5" t="n"/>
       <c r="G49" s="5" t="n"/>
@@ -2318,7 +2318,7 @@
       <c r="A50" s="6" t="inlineStr"/>
       <c r="B50" s="5" t="n"/>
       <c r="C50" s="5" t="n"/>
-      <c r="D50" s="5" t="n"/>
+      <c r="D50" s="8" t="n"/>
       <c r="E50" s="5" t="n"/>
       <c r="F50" s="5" t="n"/>
       <c r="G50" s="5" t="n"/>
@@ -2390,12 +2390,12 @@
   </sheetData>
   <mergeCells count="10">
     <mergeCell ref="A1:H1"/>
+    <mergeCell ref="D49:D50"/>
     <mergeCell ref="E7:E26"/>
     <mergeCell ref="F7:F32"/>
     <mergeCell ref="D37:D38"/>
     <mergeCell ref="C7:C32"/>
     <mergeCell ref="D7:D27"/>
-    <mergeCell ref="G8:G10"/>
     <mergeCell ref="F35:F38"/>
     <mergeCell ref="B36:B38"/>
     <mergeCell ref="B7:B32"/>
@@ -3751,17 +3751,17 @@
       </c>
       <c r="B36" s="24" t="inlineStr">
         <is>
-          <t>토</t>
+          <t>수</t>
         </is>
       </c>
       <c r="C36" s="24" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="D36" s="24" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="E36" s="25" t="inlineStr">

--- a/시간표.xlsx
+++ b/시간표.xlsx
@@ -926,13 +926,7 @@
       <c r="D7" s="10" t="n"/>
       <c r="E7" s="10" t="n"/>
       <c r="F7" s="10" t="n"/>
-      <c r="G7" s="11" t="inlineStr">
-        <is>
-          <t>댄스학원
-09:00–10:00*
-약 한 달 한시적·종료시간 추정</t>
-        </is>
-      </c>
+      <c r="G7" s="5" t="n"/>
       <c r="H7" s="5" t="n"/>
     </row>
     <row r="8" ht="15" customHeight="1">
@@ -942,7 +936,7 @@
       <c r="D8" s="10" t="n"/>
       <c r="E8" s="10" t="n"/>
       <c r="F8" s="10" t="n"/>
-      <c r="G8" s="10" t="n"/>
+      <c r="G8" s="5" t="n"/>
       <c r="H8" s="5" t="n"/>
     </row>
     <row r="9" ht="15" customHeight="1">
@@ -956,7 +950,7 @@
       <c r="D9" s="10" t="n"/>
       <c r="E9" s="10" t="n"/>
       <c r="F9" s="10" t="n"/>
-      <c r="G9" s="10" t="n"/>
+      <c r="G9" s="5" t="n"/>
       <c r="H9" s="5" t="n"/>
     </row>
     <row r="10" ht="15" customHeight="1">
@@ -966,7 +960,7 @@
       <c r="D10" s="10" t="n"/>
       <c r="E10" s="10" t="n"/>
       <c r="F10" s="10" t="n"/>
-      <c r="G10" s="8" t="n"/>
+      <c r="G10" s="5" t="n"/>
       <c r="H10" s="5" t="n"/>
     </row>
     <row r="11" ht="15" customHeight="1">
@@ -1597,7 +1591,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="26">
+  <mergeCells count="25">
     <mergeCell ref="C4:C5"/>
     <mergeCell ref="B34:B36"/>
     <mergeCell ref="E4:E5"/>
@@ -1606,7 +1600,6 @@
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="C6:C24"/>
     <mergeCell ref="F6:F22"/>
-    <mergeCell ref="G7:G10"/>
     <mergeCell ref="H31:H34"/>
     <mergeCell ref="C35:C36"/>
     <mergeCell ref="F45:F46"/>
@@ -2411,7 +2404,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H36"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -3702,29 +3695,29 @@
       <c r="H34" s="25" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="23" t="inlineStr">
-        <is>
-          <t>첫째</t>
+      <c r="A35" s="30" t="inlineStr">
+        <is>
+          <t>둘째</t>
         </is>
       </c>
       <c r="B35" s="24" t="inlineStr">
         <is>
-          <t>토</t>
+          <t>수</t>
         </is>
       </c>
       <c r="C35" s="24" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="D35" s="24" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="E35" s="25" t="inlineStr">
         <is>
-          <t>댄스학원</t>
+          <t>축구</t>
         </is>
       </c>
       <c r="F35" s="29" t="inlineStr">
@@ -3734,52 +3727,10 @@
       </c>
       <c r="G35" s="25" t="inlineStr">
         <is>
-          <t>댄스학원</t>
+          <t>축구교실</t>
         </is>
       </c>
       <c r="H35" s="25" t="inlineStr">
-        <is>
-          <t>약 한 달 한시적·종료시간 추정 / ※ 종료시간 추정</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="30" t="inlineStr">
-        <is>
-          <t>둘째</t>
-        </is>
-      </c>
-      <c r="B36" s="24" t="inlineStr">
-        <is>
-          <t>수</t>
-        </is>
-      </c>
-      <c r="C36" s="24" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="D36" s="24" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="E36" s="25" t="inlineStr">
-        <is>
-          <t>축구</t>
-        </is>
-      </c>
-      <c r="F36" s="29" t="inlineStr">
-        <is>
-          <t>학원</t>
-        </is>
-      </c>
-      <c r="G36" s="25" t="inlineStr">
-        <is>
-          <t>축구교실</t>
-        </is>
-      </c>
-      <c r="H36" s="25" t="inlineStr">
         <is>
           <t>추정 / ※ 종료시간 추정</t>
         </is>

--- a/시간표.xlsx
+++ b/시간표.xlsx
@@ -1747,32 +1747,32 @@
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>어린이집
-09:10–15:30</t>
+          <t>유치원
+09:10–15:10</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>어린이집
-09:10–15:30</t>
+          <t>유치원
+09:10–15:10</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>어린이집
-09:10–14:10</t>
+          <t>유치원
+09:10–15:10</t>
         </is>
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
-          <t>어린이집
-09:10–13:50</t>
+          <t>유치원
+09:10–15:10</t>
         </is>
       </c>
       <c r="F7" s="9" t="inlineStr">
         <is>
-          <t>어린이집
-09:10–15:30
+          <t>유치원
+09:10–15:10
 하원 시간 늘림</t>
         </is>
       </c>
@@ -2000,7 +2000,7 @@
       <c r="B26" s="10" t="n"/>
       <c r="C26" s="10" t="n"/>
       <c r="D26" s="10" t="n"/>
-      <c r="E26" s="8" t="n"/>
+      <c r="E26" s="10" t="n"/>
       <c r="F26" s="10" t="n"/>
       <c r="G26" s="5" t="n"/>
       <c r="H26" s="5" t="n"/>
@@ -2013,8 +2013,8 @@
       </c>
       <c r="B27" s="10" t="n"/>
       <c r="C27" s="10" t="n"/>
-      <c r="D27" s="8" t="n"/>
-      <c r="E27" s="5" t="n"/>
+      <c r="D27" s="10" t="n"/>
+      <c r="E27" s="10" t="n"/>
       <c r="F27" s="10" t="n"/>
       <c r="G27" s="5" t="n"/>
       <c r="H27" s="5" t="n"/>
@@ -2023,8 +2023,8 @@
       <c r="A28" s="6" t="inlineStr"/>
       <c r="B28" s="10" t="n"/>
       <c r="C28" s="10" t="n"/>
-      <c r="D28" s="5" t="n"/>
-      <c r="E28" s="5" t="n"/>
+      <c r="D28" s="10" t="n"/>
+      <c r="E28" s="10" t="n"/>
       <c r="F28" s="10" t="n"/>
       <c r="G28" s="5" t="n"/>
       <c r="H28" s="5" t="n"/>
@@ -2037,8 +2037,8 @@
       </c>
       <c r="B29" s="10" t="n"/>
       <c r="C29" s="10" t="n"/>
-      <c r="D29" s="5" t="n"/>
-      <c r="E29" s="5" t="n"/>
+      <c r="D29" s="10" t="n"/>
+      <c r="E29" s="10" t="n"/>
       <c r="F29" s="10" t="n"/>
       <c r="G29" s="5" t="n"/>
       <c r="H29" s="5" t="n"/>
@@ -2047,8 +2047,8 @@
       <c r="A30" s="6" t="inlineStr"/>
       <c r="B30" s="10" t="n"/>
       <c r="C30" s="10" t="n"/>
-      <c r="D30" s="5" t="n"/>
-      <c r="E30" s="5" t="n"/>
+      <c r="D30" s="10" t="n"/>
+      <c r="E30" s="10" t="n"/>
       <c r="F30" s="10" t="n"/>
       <c r="G30" s="5" t="n"/>
       <c r="H30" s="5" t="n"/>
@@ -2059,21 +2059,21 @@
           <t>15:00</t>
         </is>
       </c>
-      <c r="B31" s="10" t="n"/>
-      <c r="C31" s="10" t="n"/>
-      <c r="D31" s="5" t="n"/>
-      <c r="E31" s="5" t="n"/>
-      <c r="F31" s="10" t="n"/>
+      <c r="B31" s="8" t="n"/>
+      <c r="C31" s="8" t="n"/>
+      <c r="D31" s="8" t="n"/>
+      <c r="E31" s="8" t="n"/>
+      <c r="F31" s="8" t="n"/>
       <c r="G31" s="5" t="n"/>
       <c r="H31" s="5" t="n"/>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" s="6" t="inlineStr"/>
-      <c r="B32" s="8" t="n"/>
-      <c r="C32" s="8" t="n"/>
+      <c r="B32" s="5" t="n"/>
+      <c r="C32" s="5" t="n"/>
       <c r="D32" s="5" t="n"/>
       <c r="E32" s="5" t="n"/>
-      <c r="F32" s="8" t="n"/>
+      <c r="F32" s="5" t="n"/>
       <c r="G32" s="5" t="n"/>
       <c r="H32" s="5" t="n"/>
     </row>
@@ -2382,16 +2382,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="D49:D50"/>
+    <mergeCell ref="F7:F31"/>
+    <mergeCell ref="D37:D38"/>
+    <mergeCell ref="C7:C31"/>
+    <mergeCell ref="B7:B31"/>
+    <mergeCell ref="D7:D31"/>
+    <mergeCell ref="E7:E31"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="D49:D50"/>
-    <mergeCell ref="E7:E26"/>
-    <mergeCell ref="F7:F32"/>
-    <mergeCell ref="D37:D38"/>
-    <mergeCell ref="C7:C32"/>
-    <mergeCell ref="D7:D27"/>
     <mergeCell ref="F35:F38"/>
     <mergeCell ref="B36:B38"/>
-    <mergeCell ref="B7:B32"/>
   </mergeCells>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="1" fitToWidth="1"/>
@@ -3248,12 +3248,12 @@
       </c>
       <c r="D23" s="24" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="E23" s="25" t="inlineStr">
         <is>
-          <t>어린이집</t>
+          <t>유치원</t>
         </is>
       </c>
       <c r="F23" s="27" t="inlineStr">
@@ -3263,7 +3263,7 @@
       </c>
       <c r="G23" s="25" t="inlineStr">
         <is>
-          <t>어린이집</t>
+          <t>유치원</t>
         </is>
       </c>
       <c r="H23" s="25" t="inlineStr"/>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="D25" s="24" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="E25" s="25" t="inlineStr">
         <is>
-          <t>어린이집</t>
+          <t>유치원</t>
         </is>
       </c>
       <c r="F25" s="27" t="inlineStr">
@@ -3339,7 +3339,7 @@
       </c>
       <c r="G25" s="25" t="inlineStr">
         <is>
-          <t>어린이집</t>
+          <t>유치원</t>
         </is>
       </c>
       <c r="H25" s="25" t="inlineStr"/>
@@ -3362,12 +3362,12 @@
       </c>
       <c r="D26" s="24" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="E26" s="25" t="inlineStr">
         <is>
-          <t>어린이집</t>
+          <t>유치원</t>
         </is>
       </c>
       <c r="F26" s="27" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="G26" s="25" t="inlineStr">
         <is>
-          <t>어린이집</t>
+          <t>유치원</t>
         </is>
       </c>
       <c r="H26" s="25" t="inlineStr"/>
@@ -3438,12 +3438,12 @@
       </c>
       <c r="D28" s="24" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="E28" s="25" t="inlineStr">
         <is>
-          <t>어린이집</t>
+          <t>유치원</t>
         </is>
       </c>
       <c r="F28" s="27" t="inlineStr">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="G28" s="25" t="inlineStr">
         <is>
-          <t>어린이집</t>
+          <t>유치원</t>
         </is>
       </c>
       <c r="H28" s="25" t="inlineStr"/>
@@ -3476,12 +3476,12 @@
       </c>
       <c r="D29" s="24" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="E29" s="25" t="inlineStr">
         <is>
-          <t>어린이집</t>
+          <t>유치원</t>
         </is>
       </c>
       <c r="F29" s="27" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="G29" s="25" t="inlineStr">
         <is>
-          <t>어린이집</t>
+          <t>유치원</t>
         </is>
       </c>
       <c r="H29" s="25" t="inlineStr">

--- a/시간표.xlsx
+++ b/시간표.xlsx
@@ -1370,7 +1370,7 @@
       <c r="D39" s="5" t="n"/>
       <c r="E39" s="11" t="inlineStr">
         <is>
-          <t>한글수업
+          <t>영어수업
 17:10–17:40
 한글교실</t>
         </is>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="E17" s="25" t="inlineStr">
         <is>
-          <t>한글수업</t>
+          <t>영어수업</t>
         </is>
       </c>
       <c r="F17" s="29" t="inlineStr">

--- a/시간표.xlsx
+++ b/시간표.xlsx
@@ -1508,7 +1508,7 @@
       <c r="D49" s="11" t="inlineStr">
         <is>
           <t>첼로
-19:40–20:10
+19:30–20:10
 첼로교실</t>
         </is>
       </c>
@@ -3555,7 +3555,7 @@
       </c>
       <c r="C31" s="24" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="D31" s="24" t="inlineStr">

--- a/시간표.xlsx
+++ b/시간표.xlsx
@@ -1367,7 +1367,13 @@
       </c>
       <c r="B39" s="5" t="n"/>
       <c r="C39" s="5" t="n"/>
-      <c r="D39" s="5" t="n"/>
+      <c r="D39" s="11" t="inlineStr">
+        <is>
+          <t>한글수업
+17:10–17:40*
+추정</t>
+        </is>
+      </c>
       <c r="E39" s="11" t="inlineStr">
         <is>
           <t>영어수업
@@ -1383,7 +1389,7 @@
       <c r="A40" s="6" t="inlineStr"/>
       <c r="B40" s="5" t="n"/>
       <c r="C40" s="5" t="n"/>
-      <c r="D40" s="5" t="n"/>
+      <c r="D40" s="10" t="n"/>
       <c r="E40" s="10" t="n"/>
       <c r="F40" s="5" t="n"/>
       <c r="G40" s="5" t="n"/>
@@ -1397,7 +1403,7 @@
       </c>
       <c r="B41" s="5" t="n"/>
       <c r="C41" s="5" t="n"/>
-      <c r="D41" s="5" t="n"/>
+      <c r="D41" s="8" t="n"/>
       <c r="E41" s="8" t="n"/>
       <c r="F41" s="5" t="n"/>
       <c r="G41" s="5" t="n"/>
@@ -1591,7 +1597,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="25">
+  <mergeCells count="26">
     <mergeCell ref="C4:C5"/>
     <mergeCell ref="B34:B36"/>
     <mergeCell ref="E4:E5"/>
@@ -1603,6 +1609,7 @@
     <mergeCell ref="H31:H34"/>
     <mergeCell ref="C35:C36"/>
     <mergeCell ref="F45:F46"/>
+    <mergeCell ref="D39:D41"/>
     <mergeCell ref="D4:D5"/>
     <mergeCell ref="C27:C30"/>
     <mergeCell ref="F35:F38"/>
@@ -2404,7 +2411,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H35"/>
+  <dimension ref="A1:H36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -3731,6 +3738,48 @@
         </is>
       </c>
       <c r="H35" s="25" t="inlineStr">
+        <is>
+          <t>추정 / ※ 종료시간 추정</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="23" t="inlineStr">
+        <is>
+          <t>첫째</t>
+        </is>
+      </c>
+      <c r="B36" s="24" t="inlineStr">
+        <is>
+          <t>수</t>
+        </is>
+      </c>
+      <c r="C36" s="24" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="D36" s="24" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="E36" s="25" t="inlineStr">
+        <is>
+          <t>한글수업</t>
+        </is>
+      </c>
+      <c r="F36" s="29" t="inlineStr">
+        <is>
+          <t>학원</t>
+        </is>
+      </c>
+      <c r="G36" s="25" t="inlineStr">
+        <is>
+          <t>한글교실</t>
+        </is>
+      </c>
+      <c r="H36" s="25" t="inlineStr">
         <is>
           <t>추정 / ※ 종료시간 추정</t>
         </is>

--- a/시간표.xlsx
+++ b/시간표.xlsx
@@ -1450,32 +1450,20 @@
         </is>
       </c>
       <c r="B45" s="5" t="n"/>
-      <c r="C45" s="11" t="inlineStr">
-        <is>
-          <t>화상영어
-18:30–19:00
-온라인</t>
-        </is>
-      </c>
+      <c r="C45" s="5" t="n"/>
       <c r="D45" s="5" t="n"/>
       <c r="E45" s="5" t="n"/>
-      <c r="F45" s="11" t="inlineStr">
-        <is>
-          <t>화상영어
-18:30–19:00
-온라인</t>
-        </is>
-      </c>
+      <c r="F45" s="5" t="n"/>
       <c r="G45" s="5" t="n"/>
       <c r="H45" s="5" t="n"/>
     </row>
     <row r="46" ht="15" customHeight="1">
       <c r="A46" s="6" t="inlineStr"/>
       <c r="B46" s="5" t="n"/>
-      <c r="C46" s="8" t="n"/>
+      <c r="C46" s="5" t="n"/>
       <c r="D46" s="5" t="n"/>
       <c r="E46" s="5" t="n"/>
-      <c r="F46" s="8" t="n"/>
+      <c r="F46" s="5" t="n"/>
       <c r="G46" s="5" t="n"/>
       <c r="H46" s="5" t="n"/>
     </row>
@@ -1486,20 +1474,32 @@
         </is>
       </c>
       <c r="B47" s="5" t="n"/>
-      <c r="C47" s="5" t="n"/>
+      <c r="C47" s="11" t="inlineStr">
+        <is>
+          <t>화상영어
+19:00–19:30
+온라인</t>
+        </is>
+      </c>
       <c r="D47" s="5" t="n"/>
       <c r="E47" s="5" t="n"/>
-      <c r="F47" s="5" t="n"/>
+      <c r="F47" s="11" t="inlineStr">
+        <is>
+          <t>화상영어
+19:00–19:30
+온라인</t>
+        </is>
+      </c>
       <c r="G47" s="5" t="n"/>
       <c r="H47" s="5" t="n"/>
     </row>
     <row r="48" ht="15" customHeight="1">
       <c r="A48" s="6" t="inlineStr"/>
       <c r="B48" s="5" t="n"/>
-      <c r="C48" s="5" t="n"/>
+      <c r="C48" s="8" t="n"/>
       <c r="D48" s="5" t="n"/>
       <c r="E48" s="5" t="n"/>
-      <c r="F48" s="5" t="n"/>
+      <c r="F48" s="8" t="n"/>
       <c r="G48" s="5" t="n"/>
       <c r="H48" s="5" t="n"/>
     </row>
@@ -1601,16 +1601,16 @@
     <mergeCell ref="C4:C5"/>
     <mergeCell ref="B34:B36"/>
     <mergeCell ref="E4:E5"/>
-    <mergeCell ref="C45:C46"/>
     <mergeCell ref="D6:D22"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="C6:C24"/>
     <mergeCell ref="F6:F22"/>
     <mergeCell ref="H31:H34"/>
     <mergeCell ref="C35:C36"/>
-    <mergeCell ref="F45:F46"/>
     <mergeCell ref="D39:D41"/>
+    <mergeCell ref="C47:C48"/>
     <mergeCell ref="D4:D5"/>
+    <mergeCell ref="F47:F48"/>
     <mergeCell ref="C27:C30"/>
     <mergeCell ref="F35:F38"/>
     <mergeCell ref="F23:F28"/>
@@ -3638,12 +3638,12 @@
       </c>
       <c r="C33" s="24" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D33" s="24" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="E33" s="25" t="inlineStr">
@@ -3676,12 +3676,12 @@
       </c>
       <c r="C34" s="24" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D34" s="24" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="E34" s="25" t="inlineStr">

--- a/시간표.xlsx
+++ b/시간표.xlsx
@@ -1125,9 +1125,9 @@
       <c r="E23" s="10" t="n"/>
       <c r="F23" s="12" t="inlineStr">
         <is>
-          <t>방과후 종이접기
+          <t>맞춤형 종이접기
 12:50–14:20
-학교</t>
+무료</t>
         </is>
       </c>
       <c r="G23" s="5" t="n"/>
@@ -1154,9 +1154,9 @@
       <c r="D25" s="10" t="n"/>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>방과후 메이키메이커
+          <t>맞춤형 메이키메이커
 13:40–15:10
-학교</t>
+무료</t>
         </is>
       </c>
       <c r="F25" s="10" t="n"/>
@@ -1169,7 +1169,7 @@
         <is>
           <t>방과후 회화미술
 13:50–15:20
-학교</t>
+유료</t>
         </is>
       </c>
       <c r="C26" s="5" t="n"/>
@@ -2585,7 +2585,11 @@
           <t>학교</t>
         </is>
       </c>
-      <c r="H5" s="25" t="inlineStr"/>
+      <c r="H5" s="25" t="inlineStr">
+        <is>
+          <t>유료</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="23" t="inlineStr">
@@ -2990,7 +2994,7 @@
       </c>
       <c r="E16" s="25" t="inlineStr">
         <is>
-          <t>방과후 메이키메이커</t>
+          <t>맞춤형 메이키메이커</t>
         </is>
       </c>
       <c r="F16" s="28" t="inlineStr">
@@ -3003,7 +3007,11 @@
           <t>학교</t>
         </is>
       </c>
-      <c r="H16" s="25" t="inlineStr"/>
+      <c r="H16" s="25" t="inlineStr">
+        <is>
+          <t>무료</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="23" t="inlineStr">
@@ -3142,7 +3150,7 @@
       </c>
       <c r="E20" s="25" t="inlineStr">
         <is>
-          <t>방과후 종이접기</t>
+          <t>맞춤형 종이접기</t>
         </is>
       </c>
       <c r="F20" s="28" t="inlineStr">
@@ -3155,7 +3163,11 @@
           <t>학교</t>
         </is>
       </c>
-      <c r="H20" s="25" t="inlineStr"/>
+      <c r="H20" s="25" t="inlineStr">
+        <is>
+          <t>무료</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="23" t="inlineStr">

--- a/시간표.xlsx
+++ b/시간표.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="첫째 주간표" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="둘째 주간표" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="일정(편집용)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="첫째 주간표" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="둘째 주간표" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="일정(편집용)" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'첫째 주간표'!$A$1:$H$52</definedName>

--- a/시간표.xlsx
+++ b/시간표.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="첫째 주간표" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="둘째 주간표" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="일정(편집용)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="첫째 주간표" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="둘째 주간표" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="일정(편집용)" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'첫째 주간표'!$A$1:$H$52</definedName>
@@ -336,10 +336,10 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1117,13 +1117,13 @@
       <c r="C23" s="10" t="n"/>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>태권도
-13:00–14:00
-태권도장</t>
+          <t>방과후 아나운서
+12:50–14:20
+유료</t>
         </is>
       </c>
       <c r="E23" s="10" t="n"/>
-      <c r="F23" s="12" t="inlineStr">
+      <c r="F23" s="11" t="inlineStr">
         <is>
           <t>맞춤형 종이접기
 12:50–14:20
@@ -1152,11 +1152,11 @@
       <c r="B25" s="5" t="n"/>
       <c r="C25" s="5" t="n"/>
       <c r="D25" s="10" t="n"/>
-      <c r="E25" s="12" t="inlineStr">
-        <is>
-          <t>맞춤형 메이키메이커
+      <c r="E25" s="11" t="inlineStr">
+        <is>
+          <t>방과후 큐보로봇
 13:40–15:10
-무료</t>
+유료</t>
         </is>
       </c>
       <c r="F25" s="10" t="n"/>
@@ -1165,7 +1165,7 @@
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" s="6" t="inlineStr"/>
-      <c r="B26" s="12" t="inlineStr">
+      <c r="B26" s="11" t="inlineStr">
         <is>
           <t>방과후 회화미술
 13:50–15:20
@@ -1173,7 +1173,7 @@
         </is>
       </c>
       <c r="C26" s="5" t="n"/>
-      <c r="D26" s="8" t="n"/>
+      <c r="D26" s="10" t="n"/>
       <c r="E26" s="10" t="n"/>
       <c r="F26" s="10" t="n"/>
       <c r="G26" s="5" t="n"/>
@@ -1186,14 +1186,14 @@
         </is>
       </c>
       <c r="B27" s="10" t="n"/>
-      <c r="C27" s="11" t="inlineStr">
+      <c r="C27" s="12" t="inlineStr">
         <is>
           <t>태권도
 14:00–15:00
 태권도장</t>
         </is>
       </c>
-      <c r="D27" s="5" t="n"/>
+      <c r="D27" s="10" t="n"/>
       <c r="E27" s="10" t="n"/>
       <c r="F27" s="10" t="n"/>
       <c r="G27" s="5" t="n"/>
@@ -1203,7 +1203,7 @@
       <c r="A28" s="6" t="inlineStr"/>
       <c r="B28" s="10" t="n"/>
       <c r="C28" s="10" t="n"/>
-      <c r="D28" s="5" t="n"/>
+      <c r="D28" s="8" t="n"/>
       <c r="E28" s="10" t="n"/>
       <c r="F28" s="8" t="n"/>
       <c r="G28" s="5" t="n"/>
@@ -1219,7 +1219,7 @@
       <c r="C29" s="10" t="n"/>
       <c r="D29" s="5" t="n"/>
       <c r="E29" s="10" t="n"/>
-      <c r="F29" s="11" t="inlineStr">
+      <c r="F29" s="12" t="inlineStr">
         <is>
           <t>미술학원
 14:40–16:00
@@ -1251,7 +1251,7 @@
       <c r="E31" s="8" t="n"/>
       <c r="F31" s="10" t="n"/>
       <c r="G31" s="5" t="n"/>
-      <c r="H31" s="11" t="inlineStr">
+      <c r="H31" s="12" t="inlineStr">
         <is>
           <t>수영
 15:00–16:00
@@ -1275,7 +1275,13 @@
           <t>15:30</t>
         </is>
       </c>
-      <c r="B33" s="5" t="n"/>
+      <c r="B33" s="12" t="inlineStr">
+        <is>
+          <t>한글수업
+15:20–15:50
+한글교실</t>
+        </is>
+      </c>
       <c r="C33" s="5" t="n"/>
       <c r="D33" s="5" t="n"/>
       <c r="E33" s="5" t="n"/>
@@ -1285,13 +1291,7 @@
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" s="6" t="inlineStr"/>
-      <c r="B34" s="11" t="inlineStr">
-        <is>
-          <t>한글수업
-15:50–16:20
-한글교실</t>
-        </is>
-      </c>
+      <c r="B34" s="8" t="n"/>
       <c r="C34" s="5" t="n"/>
       <c r="D34" s="5" t="n"/>
       <c r="E34" s="5" t="n"/>
@@ -1305,8 +1305,8 @@
           <t>16:00</t>
         </is>
       </c>
-      <c r="B35" s="10" t="n"/>
-      <c r="C35" s="11" t="inlineStr">
+      <c r="B35" s="5" t="n"/>
+      <c r="C35" s="12" t="inlineStr">
         <is>
           <t>피아노
 16:00–16:30
@@ -1315,7 +1315,7 @@
       </c>
       <c r="D35" s="5" t="n"/>
       <c r="E35" s="5" t="n"/>
-      <c r="F35" s="11" t="inlineStr">
+      <c r="F35" s="12" t="inlineStr">
         <is>
           <t>태권도
 16:00–17:00
@@ -1327,7 +1327,7 @@
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" s="6" t="inlineStr"/>
-      <c r="B36" s="8" t="n"/>
+      <c r="B36" s="5" t="n"/>
       <c r="C36" s="8" t="n"/>
       <c r="D36" s="5" t="n"/>
       <c r="E36" s="5" t="n"/>
@@ -1353,7 +1353,13 @@
       <c r="A38" s="6" t="inlineStr"/>
       <c r="B38" s="5" t="n"/>
       <c r="C38" s="5" t="n"/>
-      <c r="D38" s="5" t="n"/>
+      <c r="D38" s="12" t="inlineStr">
+        <is>
+          <t>한글수업
+16:50–17:20*
+추정</t>
+        </is>
+      </c>
       <c r="E38" s="5" t="n"/>
       <c r="F38" s="8" t="n"/>
       <c r="G38" s="5" t="n"/>
@@ -1367,14 +1373,8 @@
       </c>
       <c r="B39" s="5" t="n"/>
       <c r="C39" s="5" t="n"/>
-      <c r="D39" s="11" t="inlineStr">
-        <is>
-          <t>한글수업
-17:10–17:40*
-추정</t>
-        </is>
-      </c>
-      <c r="E39" s="11" t="inlineStr">
+      <c r="D39" s="10" t="n"/>
+      <c r="E39" s="12" t="inlineStr">
         <is>
           <t>영어수업
 17:10–17:40
@@ -1389,7 +1389,7 @@
       <c r="A40" s="6" t="inlineStr"/>
       <c r="B40" s="5" t="n"/>
       <c r="C40" s="5" t="n"/>
-      <c r="D40" s="10" t="n"/>
+      <c r="D40" s="8" t="n"/>
       <c r="E40" s="10" t="n"/>
       <c r="F40" s="5" t="n"/>
       <c r="G40" s="5" t="n"/>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="B41" s="5" t="n"/>
       <c r="C41" s="5" t="n"/>
-      <c r="D41" s="8" t="n"/>
+      <c r="D41" s="5" t="n"/>
       <c r="E41" s="8" t="n"/>
       <c r="F41" s="5" t="n"/>
       <c r="G41" s="5" t="n"/>
@@ -1474,7 +1474,7 @@
         </is>
       </c>
       <c r="B47" s="5" t="n"/>
-      <c r="C47" s="11" t="inlineStr">
+      <c r="C47" s="12" t="inlineStr">
         <is>
           <t>화상영어
 19:00–19:30
@@ -1483,7 +1483,7 @@
       </c>
       <c r="D47" s="5" t="n"/>
       <c r="E47" s="5" t="n"/>
-      <c r="F47" s="11" t="inlineStr">
+      <c r="F47" s="12" t="inlineStr">
         <is>
           <t>화상영어
 19:00–19:30
@@ -1511,7 +1511,7 @@
       </c>
       <c r="B49" s="5" t="n"/>
       <c r="C49" s="5" t="n"/>
-      <c r="D49" s="11" t="inlineStr">
+      <c r="D49" s="12" t="inlineStr">
         <is>
           <t>첼로
 19:30–20:10
@@ -1597,9 +1597,8 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="26">
+  <mergeCells count="27">
     <mergeCell ref="C4:C5"/>
-    <mergeCell ref="B34:B36"/>
     <mergeCell ref="E4:E5"/>
     <mergeCell ref="D6:D22"/>
     <mergeCell ref="A1:H1"/>
@@ -1607,9 +1606,10 @@
     <mergeCell ref="F6:F22"/>
     <mergeCell ref="H31:H34"/>
     <mergeCell ref="C35:C36"/>
-    <mergeCell ref="D39:D41"/>
     <mergeCell ref="C47:C48"/>
     <mergeCell ref="D4:D5"/>
+    <mergeCell ref="D38:D40"/>
+    <mergeCell ref="D23:D28"/>
     <mergeCell ref="F47:F48"/>
     <mergeCell ref="C27:C30"/>
     <mergeCell ref="F35:F38"/>
@@ -1618,6 +1618,7 @@
     <mergeCell ref="B26:B32"/>
     <mergeCell ref="E39:E41"/>
     <mergeCell ref="D49:D51"/>
+    <mergeCell ref="B33:B34"/>
     <mergeCell ref="E6:E24"/>
     <mergeCell ref="B6:B24"/>
     <mergeCell ref="D23:D26"/>
@@ -2116,9 +2117,15 @@
       </c>
       <c r="B35" s="5" t="n"/>
       <c r="C35" s="5" t="n"/>
-      <c r="D35" s="5" t="n"/>
+      <c r="D35" s="12" t="inlineStr">
+        <is>
+          <t>한글수업
+16:10–16:40
+한글교실</t>
+        </is>
+      </c>
       <c r="E35" s="5" t="n"/>
-      <c r="F35" s="11" t="inlineStr">
+      <c r="F35" s="12" t="inlineStr">
         <is>
           <t>태권도
 16:00–17:00
@@ -2130,7 +2137,7 @@
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" s="6" t="inlineStr"/>
-      <c r="B36" s="11" t="inlineStr">
+      <c r="B36" s="12" t="inlineStr">
         <is>
           <t>한글수업
 16:20–16:50
@@ -2138,7 +2145,7 @@
         </is>
       </c>
       <c r="C36" s="5" t="n"/>
-      <c r="D36" s="5" t="n"/>
+      <c r="D36" s="10" t="n"/>
       <c r="E36" s="5" t="n"/>
       <c r="F36" s="10" t="n"/>
       <c r="G36" s="5" t="n"/>
@@ -2152,13 +2159,7 @@
       </c>
       <c r="B37" s="10" t="n"/>
       <c r="C37" s="5" t="n"/>
-      <c r="D37" s="11" t="inlineStr">
-        <is>
-          <t>한글수업
-16:30–17:00
-한글교실</t>
-        </is>
-      </c>
+      <c r="D37" s="8" t="n"/>
       <c r="E37" s="5" t="n"/>
       <c r="F37" s="10" t="n"/>
       <c r="G37" s="5" t="n"/>
@@ -2168,7 +2169,7 @@
       <c r="A38" s="6" t="inlineStr"/>
       <c r="B38" s="8" t="n"/>
       <c r="C38" s="5" t="n"/>
-      <c r="D38" s="8" t="n"/>
+      <c r="D38" s="5" t="n"/>
       <c r="E38" s="5" t="n"/>
       <c r="F38" s="8" t="n"/>
       <c r="G38" s="5" t="n"/>
@@ -2302,7 +2303,7 @@
       </c>
       <c r="B49" s="5" t="n"/>
       <c r="C49" s="5" t="n"/>
-      <c r="D49" s="11" t="inlineStr">
+      <c r="D49" s="12" t="inlineStr">
         <is>
           <t>축구
 19:30–20:00*
@@ -2390,8 +2391,8 @@
   </sheetData>
   <mergeCells count="10">
     <mergeCell ref="D49:D50"/>
+    <mergeCell ref="D35:D37"/>
     <mergeCell ref="F7:F31"/>
-    <mergeCell ref="D37:D38"/>
     <mergeCell ref="C7:C31"/>
     <mergeCell ref="B7:B31"/>
     <mergeCell ref="D7:D31"/>
@@ -2411,7 +2412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H36"/>
+  <dimension ref="A1:H37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2604,12 +2605,12 @@
       </c>
       <c r="C6" s="24" t="inlineStr">
         <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="D6" s="24" t="inlineStr">
+        <is>
           <t>15:50</t>
-        </is>
-      </c>
-      <c r="D6" s="24" t="inlineStr">
-        <is>
-          <t>16:20</t>
         </is>
       </c>
       <c r="E6" s="25" t="inlineStr">
@@ -2994,7 +2995,7 @@
       </c>
       <c r="E16" s="25" t="inlineStr">
         <is>
-          <t>맞춤형 메이키메이커</t>
+          <t>방과후 큐보로봇</t>
         </is>
       </c>
       <c r="F16" s="28" t="inlineStr">
@@ -3009,7 +3010,7 @@
       </c>
       <c r="H16" s="25" t="inlineStr">
         <is>
-          <t>무료</t>
+          <t>유료</t>
         </is>
       </c>
     </row>
@@ -3414,12 +3415,12 @@
       </c>
       <c r="C27" s="24" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="D27" s="24" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="E27" s="25" t="inlineStr">
@@ -3768,12 +3769,12 @@
       </c>
       <c r="C36" s="24" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="D36" s="24" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="E36" s="25" t="inlineStr">
@@ -3794,6 +3795,48 @@
       <c r="H36" s="25" t="inlineStr">
         <is>
           <t>추정 / ※ 종료시간 추정</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="23" t="inlineStr">
+        <is>
+          <t>첫째</t>
+        </is>
+      </c>
+      <c r="B37" s="24" t="inlineStr">
+        <is>
+          <t>수</t>
+        </is>
+      </c>
+      <c r="C37" s="24" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="D37" s="24" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="E37" s="25" t="inlineStr">
+        <is>
+          <t>방과후 아나운서</t>
+        </is>
+      </c>
+      <c r="F37" s="28" t="inlineStr">
+        <is>
+          <t>방과후</t>
+        </is>
+      </c>
+      <c r="G37" s="25" t="inlineStr">
+        <is>
+          <t>학교</t>
+        </is>
+      </c>
+      <c r="H37" s="25" t="inlineStr">
+        <is>
+          <t>유료</t>
         </is>
       </c>
     </row>

--- a/시간표.xlsx
+++ b/시간표.xlsx
@@ -73,13 +73,13 @@
     <font>
       <name val="맑은 고딕"/>
       <b val="1"/>
-      <color rgb="002E6B1F"/>
+      <color rgb="009C4A16"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
       <b val="1"/>
-      <color rgb="009C4A16"/>
+      <color rgb="002E6B1F"/>
       <sz val="10"/>
     </font>
     <font>
@@ -185,12 +185,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9EAD3"/>
+        <fgColor rgb="00FCE5CD"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE5CD"/>
+        <fgColor rgb="00D9EAD3"/>
       </patternFill>
     </fill>
     <fill>
@@ -336,20 +336,20 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1165,13 +1165,7 @@
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" s="6" t="inlineStr"/>
-      <c r="B26" s="11" t="inlineStr">
-        <is>
-          <t>방과후 회화미술
-13:50–15:20
-유료</t>
-        </is>
-      </c>
+      <c r="B26" s="5" t="n"/>
       <c r="C26" s="5" t="n"/>
       <c r="D26" s="10" t="n"/>
       <c r="E26" s="10" t="n"/>
@@ -1185,7 +1179,7 @@
           <t>14:00</t>
         </is>
       </c>
-      <c r="B27" s="10" t="n"/>
+      <c r="B27" s="5" t="n"/>
       <c r="C27" s="12" t="inlineStr">
         <is>
           <t>태권도
@@ -1201,7 +1195,7 @@
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" s="6" t="inlineStr"/>
-      <c r="B28" s="10" t="n"/>
+      <c r="B28" s="5" t="n"/>
       <c r="C28" s="10" t="n"/>
       <c r="D28" s="8" t="n"/>
       <c r="E28" s="10" t="n"/>
@@ -1215,7 +1209,7 @@
           <t>14:30</t>
         </is>
       </c>
-      <c r="B29" s="10" t="n"/>
+      <c r="B29" s="5" t="n"/>
       <c r="C29" s="10" t="n"/>
       <c r="D29" s="5" t="n"/>
       <c r="E29" s="10" t="n"/>
@@ -1231,7 +1225,7 @@
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" s="6" t="inlineStr"/>
-      <c r="B30" s="10" t="n"/>
+      <c r="B30" s="5" t="n"/>
       <c r="C30" s="8" t="n"/>
       <c r="D30" s="5" t="n"/>
       <c r="E30" s="10" t="n"/>
@@ -1245,7 +1239,7 @@
           <t>15:00</t>
         </is>
       </c>
-      <c r="B31" s="10" t="n"/>
+      <c r="B31" s="5" t="n"/>
       <c r="C31" s="5" t="n"/>
       <c r="D31" s="5" t="n"/>
       <c r="E31" s="8" t="n"/>
@@ -1261,7 +1255,13 @@
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" s="6" t="inlineStr"/>
-      <c r="B32" s="8" t="n"/>
+      <c r="B32" s="12" t="inlineStr">
+        <is>
+          <t>한글수업
+15:20–15:50
+한글교실</t>
+        </is>
+      </c>
       <c r="C32" s="5" t="n"/>
       <c r="D32" s="5" t="n"/>
       <c r="E32" s="5" t="n"/>
@@ -1275,13 +1275,7 @@
           <t>15:30</t>
         </is>
       </c>
-      <c r="B33" s="12" t="inlineStr">
-        <is>
-          <t>한글수업
-15:20–15:50
-한글교실</t>
-        </is>
-      </c>
+      <c r="B33" s="10" t="n"/>
       <c r="C33" s="5" t="n"/>
       <c r="D33" s="5" t="n"/>
       <c r="E33" s="5" t="n"/>
@@ -1597,7 +1591,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="27">
+  <mergeCells count="25">
     <mergeCell ref="C4:C5"/>
     <mergeCell ref="E4:E5"/>
     <mergeCell ref="D6:D22"/>
@@ -1611,17 +1605,15 @@
     <mergeCell ref="D38:D40"/>
     <mergeCell ref="D23:D28"/>
     <mergeCell ref="F47:F48"/>
+    <mergeCell ref="B32:B34"/>
     <mergeCell ref="C27:C30"/>
     <mergeCell ref="F35:F38"/>
     <mergeCell ref="F23:F28"/>
     <mergeCell ref="E25:E31"/>
-    <mergeCell ref="B26:B32"/>
+    <mergeCell ref="D49:D51"/>
     <mergeCell ref="E39:E41"/>
-    <mergeCell ref="D49:D51"/>
-    <mergeCell ref="B33:B34"/>
     <mergeCell ref="E6:E24"/>
     <mergeCell ref="B6:B24"/>
-    <mergeCell ref="D23:D26"/>
     <mergeCell ref="B4:B5"/>
     <mergeCell ref="F4:F5"/>
     <mergeCell ref="F29:F34"/>
@@ -2412,7 +2404,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H37"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2563,34 +2555,30 @@
       </c>
       <c r="C5" s="24" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="D5" s="24" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="E5" s="25" t="inlineStr">
         <is>
-          <t>방과후 회화미술</t>
+          <t>한글수업</t>
         </is>
       </c>
       <c r="F5" s="28" t="inlineStr">
         <is>
-          <t>방과후</t>
+          <t>학원</t>
         </is>
       </c>
       <c r="G5" s="25" t="inlineStr">
         <is>
-          <t>학교</t>
-        </is>
-      </c>
-      <c r="H5" s="25" t="inlineStr">
-        <is>
-          <t>유료</t>
-        </is>
-      </c>
+          <t>한글교실</t>
+        </is>
+      </c>
+      <c r="H5" s="25" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="23" t="inlineStr">
@@ -2600,32 +2588,32 @@
       </c>
       <c r="B6" s="24" t="inlineStr">
         <is>
-          <t>월</t>
+          <t>화</t>
         </is>
       </c>
       <c r="C6" s="24" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="D6" s="24" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="E6" s="25" t="inlineStr">
         <is>
-          <t>한글수업</t>
-        </is>
-      </c>
-      <c r="F6" s="29" t="inlineStr">
-        <is>
-          <t>학원</t>
+          <t>등교</t>
+        </is>
+      </c>
+      <c r="F6" s="26" t="inlineStr">
+        <is>
+          <t>돌봄/픽업</t>
         </is>
       </c>
       <c r="G6" s="25" t="inlineStr">
         <is>
-          <t>한글교실</t>
+          <t>집→학교</t>
         </is>
       </c>
       <c r="H6" s="25" t="inlineStr"/>
@@ -2643,27 +2631,27 @@
       </c>
       <c r="C7" s="24" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="D7" s="24" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="E7" s="25" t="inlineStr">
         <is>
-          <t>등교</t>
-        </is>
-      </c>
-      <c r="F7" s="26" t="inlineStr">
-        <is>
-          <t>돌봄/픽업</t>
+          <t>정규수업</t>
+        </is>
+      </c>
+      <c r="F7" s="27" t="inlineStr">
+        <is>
+          <t>정규수업</t>
         </is>
       </c>
       <c r="G7" s="25" t="inlineStr">
         <is>
-          <t>집→학교</t>
+          <t>○○초</t>
         </is>
       </c>
       <c r="H7" s="25" t="inlineStr"/>
@@ -2681,27 +2669,27 @@
       </c>
       <c r="C8" s="24" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="D8" s="24" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="E8" s="25" t="inlineStr">
         <is>
-          <t>정규수업</t>
-        </is>
-      </c>
-      <c r="F8" s="27" t="inlineStr">
-        <is>
-          <t>정규수업</t>
+          <t>태권도</t>
+        </is>
+      </c>
+      <c r="F8" s="28" t="inlineStr">
+        <is>
+          <t>학원</t>
         </is>
       </c>
       <c r="G8" s="25" t="inlineStr">
         <is>
-          <t>○○초</t>
+          <t>태권도장</t>
         </is>
       </c>
       <c r="H8" s="25" t="inlineStr"/>
@@ -2719,27 +2707,27 @@
       </c>
       <c r="C9" s="24" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="D9" s="24" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="E9" s="25" t="inlineStr">
         <is>
-          <t>태권도</t>
-        </is>
-      </c>
-      <c r="F9" s="29" t="inlineStr">
+          <t>피아노</t>
+        </is>
+      </c>
+      <c r="F9" s="28" t="inlineStr">
         <is>
           <t>학원</t>
         </is>
       </c>
       <c r="G9" s="25" t="inlineStr">
         <is>
-          <t>태권도장</t>
+          <t>피아노학원</t>
         </is>
       </c>
       <c r="H9" s="25" t="inlineStr"/>
@@ -2752,32 +2740,32 @@
       </c>
       <c r="B10" s="24" t="inlineStr">
         <is>
-          <t>화</t>
+          <t>수</t>
         </is>
       </c>
       <c r="C10" s="24" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="D10" s="24" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="E10" s="25" t="inlineStr">
         <is>
-          <t>피아노</t>
-        </is>
-      </c>
-      <c r="F10" s="29" t="inlineStr">
-        <is>
-          <t>학원</t>
+          <t>등교</t>
+        </is>
+      </c>
+      <c r="F10" s="26" t="inlineStr">
+        <is>
+          <t>돌봄/픽업</t>
         </is>
       </c>
       <c r="G10" s="25" t="inlineStr">
         <is>
-          <t>피아노학원</t>
+          <t>집→학교</t>
         </is>
       </c>
       <c r="H10" s="25" t="inlineStr"/>
@@ -2795,27 +2783,27 @@
       </c>
       <c r="C11" s="24" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="D11" s="24" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="E11" s="25" t="inlineStr">
         <is>
-          <t>등교</t>
-        </is>
-      </c>
-      <c r="F11" s="26" t="inlineStr">
-        <is>
-          <t>돌봄/픽업</t>
+          <t>정규수업(단축)</t>
+        </is>
+      </c>
+      <c r="F11" s="27" t="inlineStr">
+        <is>
+          <t>정규수업</t>
         </is>
       </c>
       <c r="G11" s="25" t="inlineStr">
         <is>
-          <t>집→학교</t>
+          <t>○○초</t>
         </is>
       </c>
       <c r="H11" s="25" t="inlineStr"/>
@@ -2828,32 +2816,32 @@
       </c>
       <c r="B12" s="24" t="inlineStr">
         <is>
-          <t>수</t>
+          <t>목</t>
         </is>
       </c>
       <c r="C12" s="24" t="inlineStr">
         <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="D12" s="24" t="inlineStr">
+        <is>
           <t>08:45</t>
         </is>
       </c>
-      <c r="D12" s="24" t="inlineStr">
-        <is>
-          <t>12:50</t>
-        </is>
-      </c>
       <c r="E12" s="25" t="inlineStr">
         <is>
-          <t>정규수업(단축)</t>
-        </is>
-      </c>
-      <c r="F12" s="27" t="inlineStr">
-        <is>
-          <t>정규수업</t>
+          <t>등교</t>
+        </is>
+      </c>
+      <c r="F12" s="26" t="inlineStr">
+        <is>
+          <t>돌봄/픽업</t>
         </is>
       </c>
       <c r="G12" s="25" t="inlineStr">
         <is>
-          <t>○○초</t>
+          <t>집→학교</t>
         </is>
       </c>
       <c r="H12" s="25" t="inlineStr"/>
@@ -2866,32 +2854,32 @@
       </c>
       <c r="B13" s="24" t="inlineStr">
         <is>
-          <t>수</t>
+          <t>목</t>
         </is>
       </c>
       <c r="C13" s="24" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="D13" s="24" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="E13" s="25" t="inlineStr">
         <is>
-          <t>태권도</t>
-        </is>
-      </c>
-      <c r="F13" s="29" t="inlineStr">
-        <is>
-          <t>학원</t>
+          <t>정규수업</t>
+        </is>
+      </c>
+      <c r="F13" s="27" t="inlineStr">
+        <is>
+          <t>정규수업</t>
         </is>
       </c>
       <c r="G13" s="25" t="inlineStr">
         <is>
-          <t>태권도장</t>
+          <t>○○초</t>
         </is>
       </c>
       <c r="H13" s="25" t="inlineStr"/>
@@ -2909,30 +2897,34 @@
       </c>
       <c r="C14" s="24" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="D14" s="24" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="E14" s="25" t="inlineStr">
         <is>
-          <t>등교</t>
-        </is>
-      </c>
-      <c r="F14" s="26" t="inlineStr">
-        <is>
-          <t>돌봄/픽업</t>
+          <t>방과후 큐보로봇</t>
+        </is>
+      </c>
+      <c r="F14" s="29" t="inlineStr">
+        <is>
+          <t>방과후</t>
         </is>
       </c>
       <c r="G14" s="25" t="inlineStr">
         <is>
-          <t>집→학교</t>
-        </is>
-      </c>
-      <c r="H14" s="25" t="inlineStr"/>
+          <t>학교</t>
+        </is>
+      </c>
+      <c r="H14" s="25" t="inlineStr">
+        <is>
+          <t>유료</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="23" t="inlineStr">
@@ -2947,27 +2939,27 @@
       </c>
       <c r="C15" s="24" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="D15" s="24" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="E15" s="25" t="inlineStr">
         <is>
-          <t>정규수업</t>
-        </is>
-      </c>
-      <c r="F15" s="27" t="inlineStr">
-        <is>
-          <t>정규수업</t>
+          <t>영어수업</t>
+        </is>
+      </c>
+      <c r="F15" s="28" t="inlineStr">
+        <is>
+          <t>학원</t>
         </is>
       </c>
       <c r="G15" s="25" t="inlineStr">
         <is>
-          <t>○○초</t>
+          <t>한글교실</t>
         </is>
       </c>
       <c r="H15" s="25" t="inlineStr"/>
@@ -2980,39 +2972,35 @@
       </c>
       <c r="B16" s="24" t="inlineStr">
         <is>
-          <t>목</t>
+          <t>금</t>
         </is>
       </c>
       <c r="C16" s="24" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="D16" s="24" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="E16" s="25" t="inlineStr">
         <is>
-          <t>방과후 큐보로봇</t>
-        </is>
-      </c>
-      <c r="F16" s="28" t="inlineStr">
-        <is>
-          <t>방과후</t>
+          <t>등교</t>
+        </is>
+      </c>
+      <c r="F16" s="26" t="inlineStr">
+        <is>
+          <t>돌봄/픽업</t>
         </is>
       </c>
       <c r="G16" s="25" t="inlineStr">
         <is>
-          <t>학교</t>
-        </is>
-      </c>
-      <c r="H16" s="25" t="inlineStr">
-        <is>
-          <t>유료</t>
-        </is>
-      </c>
+          <t>집→학교</t>
+        </is>
+      </c>
+      <c r="H16" s="25" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="23" t="inlineStr">
@@ -3022,32 +3010,32 @@
       </c>
       <c r="B17" s="24" t="inlineStr">
         <is>
-          <t>목</t>
+          <t>금</t>
         </is>
       </c>
       <c r="C17" s="24" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="D17" s="24" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="E17" s="25" t="inlineStr">
         <is>
-          <t>영어수업</t>
-        </is>
-      </c>
-      <c r="F17" s="29" t="inlineStr">
-        <is>
-          <t>학원</t>
+          <t>정규수업(단축)</t>
+        </is>
+      </c>
+      <c r="F17" s="27" t="inlineStr">
+        <is>
+          <t>정규수업</t>
         </is>
       </c>
       <c r="G17" s="25" t="inlineStr">
         <is>
-          <t>한글교실</t>
+          <t>○○초</t>
         </is>
       </c>
       <c r="H17" s="25" t="inlineStr"/>
@@ -3065,30 +3053,34 @@
       </c>
       <c r="C18" s="24" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="D18" s="24" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="E18" s="25" t="inlineStr">
         <is>
-          <t>등교</t>
-        </is>
-      </c>
-      <c r="F18" s="26" t="inlineStr">
-        <is>
-          <t>돌봄/픽업</t>
+          <t>맞춤형 종이접기</t>
+        </is>
+      </c>
+      <c r="F18" s="29" t="inlineStr">
+        <is>
+          <t>방과후</t>
         </is>
       </c>
       <c r="G18" s="25" t="inlineStr">
         <is>
-          <t>집→학교</t>
-        </is>
-      </c>
-      <c r="H18" s="25" t="inlineStr"/>
+          <t>학교</t>
+        </is>
+      </c>
+      <c r="H18" s="25" t="inlineStr">
+        <is>
+          <t>무료</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="23" t="inlineStr">
@@ -3103,27 +3095,27 @@
       </c>
       <c r="C19" s="24" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="D19" s="24" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="E19" s="25" t="inlineStr">
         <is>
-          <t>정규수업(단축)</t>
-        </is>
-      </c>
-      <c r="F19" s="27" t="inlineStr">
-        <is>
-          <t>정규수업</t>
+          <t>미술학원</t>
+        </is>
+      </c>
+      <c r="F19" s="28" t="inlineStr">
+        <is>
+          <t>학원</t>
         </is>
       </c>
       <c r="G19" s="25" t="inlineStr">
         <is>
-          <t>○○초</t>
+          <t>미술학원</t>
         </is>
       </c>
       <c r="H19" s="25" t="inlineStr"/>
@@ -3141,114 +3133,110 @@
       </c>
       <c r="C20" s="24" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="D20" s="24" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E20" s="25" t="inlineStr">
         <is>
-          <t>맞춤형 종이접기</t>
+          <t>태권도</t>
         </is>
       </c>
       <c r="F20" s="28" t="inlineStr">
         <is>
-          <t>방과후</t>
+          <t>학원</t>
         </is>
       </c>
       <c r="G20" s="25" t="inlineStr">
         <is>
-          <t>학교</t>
+          <t>태권도장</t>
         </is>
       </c>
       <c r="H20" s="25" t="inlineStr">
         <is>
-          <t>무료</t>
+          <t>둘째와 함께 · 이모님 픽업</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="23" t="inlineStr">
-        <is>
-          <t>첫째</t>
+      <c r="A21" s="30" t="inlineStr">
+        <is>
+          <t>둘째</t>
         </is>
       </c>
       <c r="B21" s="24" t="inlineStr">
         <is>
-          <t>금</t>
+          <t>월</t>
         </is>
       </c>
       <c r="C21" s="24" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="D21" s="24" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="E21" s="25" t="inlineStr">
         <is>
-          <t>미술학원</t>
-        </is>
-      </c>
-      <c r="F21" s="29" t="inlineStr">
+          <t>유치원</t>
+        </is>
+      </c>
+      <c r="F21" s="27" t="inlineStr">
+        <is>
+          <t>정규수업</t>
+        </is>
+      </c>
+      <c r="G21" s="25" t="inlineStr">
+        <is>
+          <t>유치원</t>
+        </is>
+      </c>
+      <c r="H21" s="25" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="30" t="inlineStr">
+        <is>
+          <t>둘째</t>
+        </is>
+      </c>
+      <c r="B22" s="24" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C22" s="24" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="D22" s="24" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="E22" s="25" t="inlineStr">
+        <is>
+          <t>한글수업</t>
+        </is>
+      </c>
+      <c r="F22" s="28" t="inlineStr">
         <is>
           <t>학원</t>
         </is>
       </c>
-      <c r="G21" s="25" t="inlineStr">
-        <is>
-          <t>미술학원</t>
-        </is>
-      </c>
-      <c r="H21" s="25" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="23" t="inlineStr">
-        <is>
-          <t>첫째</t>
-        </is>
-      </c>
-      <c r="B22" s="24" t="inlineStr">
-        <is>
-          <t>금</t>
-        </is>
-      </c>
-      <c r="C22" s="24" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D22" s="24" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="E22" s="25" t="inlineStr">
-        <is>
-          <t>태권도</t>
-        </is>
-      </c>
-      <c r="F22" s="29" t="inlineStr">
-        <is>
-          <t>학원</t>
-        </is>
-      </c>
       <c r="G22" s="25" t="inlineStr">
         <is>
-          <t>태권도장</t>
-        </is>
-      </c>
-      <c r="H22" s="25" t="inlineStr">
-        <is>
-          <t>둘째와 함께 · 이모님 픽업</t>
-        </is>
-      </c>
+          <t>한글교실</t>
+        </is>
+      </c>
+      <c r="H22" s="25" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="30" t="inlineStr">
@@ -3258,7 +3246,7 @@
       </c>
       <c r="B23" s="24" t="inlineStr">
         <is>
-          <t>월</t>
+          <t>화</t>
         </is>
       </c>
       <c r="C23" s="24" t="inlineStr">
@@ -3296,32 +3284,32 @@
       </c>
       <c r="B24" s="24" t="inlineStr">
         <is>
-          <t>월</t>
+          <t>수</t>
         </is>
       </c>
       <c r="C24" s="24" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="D24" s="24" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="E24" s="25" t="inlineStr">
         <is>
-          <t>한글수업</t>
-        </is>
-      </c>
-      <c r="F24" s="29" t="inlineStr">
-        <is>
-          <t>학원</t>
+          <t>유치원</t>
+        </is>
+      </c>
+      <c r="F24" s="27" t="inlineStr">
+        <is>
+          <t>정규수업</t>
         </is>
       </c>
       <c r="G24" s="25" t="inlineStr">
         <is>
-          <t>한글교실</t>
+          <t>유치원</t>
         </is>
       </c>
       <c r="H24" s="25" t="inlineStr"/>
@@ -3334,32 +3322,32 @@
       </c>
       <c r="B25" s="24" t="inlineStr">
         <is>
-          <t>화</t>
+          <t>수</t>
         </is>
       </c>
       <c r="C25" s="24" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="D25" s="24" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="E25" s="25" t="inlineStr">
         <is>
-          <t>유치원</t>
-        </is>
-      </c>
-      <c r="F25" s="27" t="inlineStr">
-        <is>
-          <t>정규수업</t>
+          <t>한글수업</t>
+        </is>
+      </c>
+      <c r="F25" s="28" t="inlineStr">
+        <is>
+          <t>학원</t>
         </is>
       </c>
       <c r="G25" s="25" t="inlineStr">
         <is>
-          <t>유치원</t>
+          <t>한글교실</t>
         </is>
       </c>
       <c r="H25" s="25" t="inlineStr"/>
@@ -3372,7 +3360,7 @@
       </c>
       <c r="B26" s="24" t="inlineStr">
         <is>
-          <t>수</t>
+          <t>목</t>
         </is>
       </c>
       <c r="C26" s="24" t="inlineStr">
@@ -3410,35 +3398,39 @@
       </c>
       <c r="B27" s="24" t="inlineStr">
         <is>
-          <t>수</t>
+          <t>금</t>
         </is>
       </c>
       <c r="C27" s="24" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="D27" s="24" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="E27" s="25" t="inlineStr">
         <is>
-          <t>한글수업</t>
-        </is>
-      </c>
-      <c r="F27" s="29" t="inlineStr">
-        <is>
-          <t>학원</t>
+          <t>유치원</t>
+        </is>
+      </c>
+      <c r="F27" s="27" t="inlineStr">
+        <is>
+          <t>정규수업</t>
         </is>
       </c>
       <c r="G27" s="25" t="inlineStr">
         <is>
-          <t>한글교실</t>
-        </is>
-      </c>
-      <c r="H27" s="25" t="inlineStr"/>
+          <t>유치원</t>
+        </is>
+      </c>
+      <c r="H27" s="25" t="inlineStr">
+        <is>
+          <t>하원 시간 늘림</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="30" t="inlineStr">
@@ -3448,119 +3440,115 @@
       </c>
       <c r="B28" s="24" t="inlineStr">
         <is>
-          <t>목</t>
+          <t>금</t>
         </is>
       </c>
       <c r="C28" s="24" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="D28" s="24" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E28" s="25" t="inlineStr">
         <is>
-          <t>유치원</t>
-        </is>
-      </c>
-      <c r="F28" s="27" t="inlineStr">
-        <is>
-          <t>정규수업</t>
+          <t>태권도</t>
+        </is>
+      </c>
+      <c r="F28" s="28" t="inlineStr">
+        <is>
+          <t>학원</t>
         </is>
       </c>
       <c r="G28" s="25" t="inlineStr">
         <is>
-          <t>유치원</t>
-        </is>
-      </c>
-      <c r="H28" s="25" t="inlineStr"/>
+          <t>태권도장</t>
+        </is>
+      </c>
+      <c r="H28" s="25" t="inlineStr">
+        <is>
+          <t>첫째와 함께 · 이모님 픽업</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="30" t="inlineStr">
-        <is>
-          <t>둘째</t>
+      <c r="A29" s="23" t="inlineStr">
+        <is>
+          <t>첫째</t>
         </is>
       </c>
       <c r="B29" s="24" t="inlineStr">
         <is>
-          <t>금</t>
+          <t>수</t>
         </is>
       </c>
       <c r="C29" s="24" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="D29" s="24" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="E29" s="25" t="inlineStr">
         <is>
-          <t>유치원</t>
-        </is>
-      </c>
-      <c r="F29" s="27" t="inlineStr">
-        <is>
-          <t>정규수업</t>
+          <t>첼로</t>
+        </is>
+      </c>
+      <c r="F29" s="28" t="inlineStr">
+        <is>
+          <t>학원</t>
         </is>
       </c>
       <c r="G29" s="25" t="inlineStr">
         <is>
-          <t>유치원</t>
-        </is>
-      </c>
-      <c r="H29" s="25" t="inlineStr">
-        <is>
-          <t>하원 시간 늘림</t>
-        </is>
-      </c>
+          <t>첼로교실</t>
+        </is>
+      </c>
+      <c r="H29" s="25" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="30" t="inlineStr">
-        <is>
-          <t>둘째</t>
+      <c r="A30" s="23" t="inlineStr">
+        <is>
+          <t>첫째</t>
         </is>
       </c>
       <c r="B30" s="24" t="inlineStr">
         <is>
-          <t>금</t>
+          <t>일</t>
         </is>
       </c>
       <c r="C30" s="24" t="inlineStr">
         <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="D30" s="24" t="inlineStr">
+        <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="D30" s="24" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
       <c r="E30" s="25" t="inlineStr">
         <is>
-          <t>태권도</t>
-        </is>
-      </c>
-      <c r="F30" s="29" t="inlineStr">
+          <t>수영</t>
+        </is>
+      </c>
+      <c r="F30" s="28" t="inlineStr">
         <is>
           <t>학원</t>
         </is>
       </c>
       <c r="G30" s="25" t="inlineStr">
         <is>
-          <t>태권도장</t>
-        </is>
-      </c>
-      <c r="H30" s="25" t="inlineStr">
-        <is>
-          <t>첫째와 함께 · 이모님 픽업</t>
-        </is>
-      </c>
+          <t>수영장</t>
+        </is>
+      </c>
+      <c r="H30" s="25" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="23" t="inlineStr">
@@ -3570,32 +3558,32 @@
       </c>
       <c r="B31" s="24" t="inlineStr">
         <is>
-          <t>수</t>
+          <t>화</t>
         </is>
       </c>
       <c r="C31" s="24" t="inlineStr">
         <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="D31" s="24" t="inlineStr">
+        <is>
           <t>19:30</t>
         </is>
       </c>
-      <c r="D31" s="24" t="inlineStr">
-        <is>
-          <t>20:10</t>
-        </is>
-      </c>
       <c r="E31" s="25" t="inlineStr">
         <is>
-          <t>첼로</t>
-        </is>
-      </c>
-      <c r="F31" s="29" t="inlineStr">
+          <t>화상영어</t>
+        </is>
+      </c>
+      <c r="F31" s="28" t="inlineStr">
         <is>
           <t>학원</t>
         </is>
       </c>
       <c r="G31" s="25" t="inlineStr">
         <is>
-          <t>첼로교실</t>
+          <t>온라인</t>
         </is>
       </c>
       <c r="H31" s="25" t="inlineStr"/>
@@ -3608,73 +3596,77 @@
       </c>
       <c r="B32" s="24" t="inlineStr">
         <is>
-          <t>일</t>
+          <t>금</t>
         </is>
       </c>
       <c r="C32" s="24" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D32" s="24" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="E32" s="25" t="inlineStr">
         <is>
-          <t>수영</t>
-        </is>
-      </c>
-      <c r="F32" s="29" t="inlineStr">
+          <t>화상영어</t>
+        </is>
+      </c>
+      <c r="F32" s="28" t="inlineStr">
         <is>
           <t>학원</t>
         </is>
       </c>
       <c r="G32" s="25" t="inlineStr">
         <is>
-          <t>수영장</t>
+          <t>온라인</t>
         </is>
       </c>
       <c r="H32" s="25" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="23" t="inlineStr">
-        <is>
-          <t>첫째</t>
+      <c r="A33" s="30" t="inlineStr">
+        <is>
+          <t>둘째</t>
         </is>
       </c>
       <c r="B33" s="24" t="inlineStr">
         <is>
-          <t>화</t>
+          <t>수</t>
         </is>
       </c>
       <c r="C33" s="24" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="D33" s="24" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="E33" s="25" t="inlineStr">
         <is>
-          <t>화상영어</t>
-        </is>
-      </c>
-      <c r="F33" s="29" t="inlineStr">
+          <t>축구</t>
+        </is>
+      </c>
+      <c r="F33" s="28" t="inlineStr">
         <is>
           <t>학원</t>
         </is>
       </c>
       <c r="G33" s="25" t="inlineStr">
         <is>
-          <t>온라인</t>
-        </is>
-      </c>
-      <c r="H33" s="25" t="inlineStr"/>
+          <t>축구교실</t>
+        </is>
+      </c>
+      <c r="H33" s="25" t="inlineStr">
+        <is>
+          <t>추정 / ※ 종료시간 추정</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="23" t="inlineStr">
@@ -3684,40 +3676,44 @@
       </c>
       <c r="B34" s="24" t="inlineStr">
         <is>
-          <t>금</t>
+          <t>수</t>
         </is>
       </c>
       <c r="C34" s="24" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="D34" s="24" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="E34" s="25" t="inlineStr">
         <is>
-          <t>화상영어</t>
-        </is>
-      </c>
-      <c r="F34" s="29" t="inlineStr">
+          <t>한글수업</t>
+        </is>
+      </c>
+      <c r="F34" s="28" t="inlineStr">
         <is>
           <t>학원</t>
         </is>
       </c>
       <c r="G34" s="25" t="inlineStr">
         <is>
-          <t>온라인</t>
-        </is>
-      </c>
-      <c r="H34" s="25" t="inlineStr"/>
+          <t>한글교실</t>
+        </is>
+      </c>
+      <c r="H34" s="25" t="inlineStr">
+        <is>
+          <t>추정 / ※ 종료시간 추정</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="30" t="inlineStr">
-        <is>
-          <t>둘째</t>
+      <c r="A35" s="23" t="inlineStr">
+        <is>
+          <t>첫째</t>
         </is>
       </c>
       <c r="B35" s="24" t="inlineStr">
@@ -3727,114 +3723,30 @@
       </c>
       <c r="C35" s="24" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="D35" s="24" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="E35" s="25" t="inlineStr">
         <is>
-          <t>축구</t>
+          <t>방과후 아나운서</t>
         </is>
       </c>
       <c r="F35" s="29" t="inlineStr">
         <is>
-          <t>학원</t>
+          <t>방과후</t>
         </is>
       </c>
       <c r="G35" s="25" t="inlineStr">
         <is>
-          <t>축구교실</t>
+          <t>학교</t>
         </is>
       </c>
       <c r="H35" s="25" t="inlineStr">
-        <is>
-          <t>추정 / ※ 종료시간 추정</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="23" t="inlineStr">
-        <is>
-          <t>첫째</t>
-        </is>
-      </c>
-      <c r="B36" s="24" t="inlineStr">
-        <is>
-          <t>수</t>
-        </is>
-      </c>
-      <c r="C36" s="24" t="inlineStr">
-        <is>
-          <t>16:50</t>
-        </is>
-      </c>
-      <c r="D36" s="24" t="inlineStr">
-        <is>
-          <t>17:20</t>
-        </is>
-      </c>
-      <c r="E36" s="25" t="inlineStr">
-        <is>
-          <t>한글수업</t>
-        </is>
-      </c>
-      <c r="F36" s="29" t="inlineStr">
-        <is>
-          <t>학원</t>
-        </is>
-      </c>
-      <c r="G36" s="25" t="inlineStr">
-        <is>
-          <t>한글교실</t>
-        </is>
-      </c>
-      <c r="H36" s="25" t="inlineStr">
-        <is>
-          <t>추정 / ※ 종료시간 추정</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="23" t="inlineStr">
-        <is>
-          <t>첫째</t>
-        </is>
-      </c>
-      <c r="B37" s="24" t="inlineStr">
-        <is>
-          <t>수</t>
-        </is>
-      </c>
-      <c r="C37" s="24" t="inlineStr">
-        <is>
-          <t>12:50</t>
-        </is>
-      </c>
-      <c r="D37" s="24" t="inlineStr">
-        <is>
-          <t>14:20</t>
-        </is>
-      </c>
-      <c r="E37" s="25" t="inlineStr">
-        <is>
-          <t>방과후 아나운서</t>
-        </is>
-      </c>
-      <c r="F37" s="28" t="inlineStr">
-        <is>
-          <t>방과후</t>
-        </is>
-      </c>
-      <c r="G37" s="25" t="inlineStr">
-        <is>
-          <t>학교</t>
-        </is>
-      </c>
-      <c r="H37" s="25" t="inlineStr">
         <is>
           <t>유료</t>
         </is>

--- a/시간표.xlsx
+++ b/시간표.xlsx
@@ -1179,7 +1179,13 @@
           <t>14:00</t>
         </is>
       </c>
-      <c r="B27" s="5" t="n"/>
+      <c r="B27" s="12" t="inlineStr">
+        <is>
+          <t>태권도
+14:00–15:00
+태권도장</t>
+        </is>
+      </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
           <t>태권도
@@ -1195,7 +1201,7 @@
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" s="6" t="inlineStr"/>
-      <c r="B28" s="5" t="n"/>
+      <c r="B28" s="10" t="n"/>
       <c r="C28" s="10" t="n"/>
       <c r="D28" s="8" t="n"/>
       <c r="E28" s="10" t="n"/>
@@ -1209,7 +1215,7 @@
           <t>14:30</t>
         </is>
       </c>
-      <c r="B29" s="5" t="n"/>
+      <c r="B29" s="10" t="n"/>
       <c r="C29" s="10" t="n"/>
       <c r="D29" s="5" t="n"/>
       <c r="E29" s="10" t="n"/>
@@ -1225,7 +1231,7 @@
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" s="6" t="inlineStr"/>
-      <c r="B30" s="5" t="n"/>
+      <c r="B30" s="8" t="n"/>
       <c r="C30" s="8" t="n"/>
       <c r="D30" s="5" t="n"/>
       <c r="E30" s="10" t="n"/>
@@ -1591,13 +1597,14 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="25">
+  <mergeCells count="26">
     <mergeCell ref="C4:C5"/>
     <mergeCell ref="E4:E5"/>
     <mergeCell ref="D6:D22"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="C6:C24"/>
     <mergeCell ref="F6:F22"/>
+    <mergeCell ref="B27:B30"/>
     <mergeCell ref="H31:H34"/>
     <mergeCell ref="C35:C36"/>
     <mergeCell ref="C47:C48"/>
@@ -2404,7 +2411,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H35"/>
+  <dimension ref="A1:H36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -3751,6 +3758,44 @@
           <t>유료</t>
         </is>
       </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="23" t="inlineStr">
+        <is>
+          <t>첫째</t>
+        </is>
+      </c>
+      <c r="B36" s="24" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C36" s="24" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="D36" s="24" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E36" s="25" t="inlineStr">
+        <is>
+          <t>태권도</t>
+        </is>
+      </c>
+      <c r="F36" s="28" t="inlineStr">
+        <is>
+          <t>학원</t>
+        </is>
+      </c>
+      <c r="G36" s="25" t="inlineStr">
+        <is>
+          <t>태권도장</t>
+        </is>
+      </c>
+      <c r="H36" s="25" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/시간표.xlsx
+++ b/시간표.xlsx
@@ -1314,7 +1314,13 @@
         </is>
       </c>
       <c r="D35" s="5" t="n"/>
-      <c r="E35" s="5" t="n"/>
+      <c r="E35" s="12" t="inlineStr">
+        <is>
+          <t>태권도
+16:00–17:00
+태권도장</t>
+        </is>
+      </c>
       <c r="F35" s="12" t="inlineStr">
         <is>
           <t>태권도
@@ -1330,7 +1336,7 @@
       <c r="B36" s="5" t="n"/>
       <c r="C36" s="8" t="n"/>
       <c r="D36" s="5" t="n"/>
-      <c r="E36" s="5" t="n"/>
+      <c r="E36" s="10" t="n"/>
       <c r="F36" s="10" t="n"/>
       <c r="G36" s="5" t="n"/>
       <c r="H36" s="5" t="n"/>
@@ -1344,7 +1350,7 @@
       <c r="B37" s="5" t="n"/>
       <c r="C37" s="5" t="n"/>
       <c r="D37" s="5" t="n"/>
-      <c r="E37" s="5" t="n"/>
+      <c r="E37" s="10" t="n"/>
       <c r="F37" s="10" t="n"/>
       <c r="G37" s="5" t="n"/>
       <c r="H37" s="5" t="n"/>
@@ -1360,7 +1366,7 @@
 추정</t>
         </is>
       </c>
-      <c r="E38" s="5" t="n"/>
+      <c r="E38" s="8" t="n"/>
       <c r="F38" s="8" t="n"/>
       <c r="G38" s="5" t="n"/>
       <c r="H38" s="5" t="n"/>
@@ -1597,9 +1603,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="26">
+  <mergeCells count="27">
     <mergeCell ref="C4:C5"/>
     <mergeCell ref="E4:E5"/>
+    <mergeCell ref="E35:E38"/>
     <mergeCell ref="D6:D22"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="C6:C24"/>
@@ -2411,7 +2418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H36"/>
+  <dimension ref="A1:H37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -3796,6 +3803,44 @@
         </is>
       </c>
       <c r="H36" s="25" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="23" t="inlineStr">
+        <is>
+          <t>첫째</t>
+        </is>
+      </c>
+      <c r="B37" s="24" t="inlineStr">
+        <is>
+          <t>목</t>
+        </is>
+      </c>
+      <c r="C37" s="24" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="D37" s="24" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E37" s="25" t="inlineStr">
+        <is>
+          <t>태권도</t>
+        </is>
+      </c>
+      <c r="F37" s="28" t="inlineStr">
+        <is>
+          <t>학원</t>
+        </is>
+      </c>
+      <c r="G37" s="25" t="inlineStr">
+        <is>
+          <t>태권도장</t>
+        </is>
+      </c>
+      <c r="H37" s="25" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/시간표.xlsx
+++ b/시간표.xlsx
@@ -1251,13 +1251,7 @@
       <c r="E31" s="8" t="n"/>
       <c r="F31" s="10" t="n"/>
       <c r="G31" s="5" t="n"/>
-      <c r="H31" s="12" t="inlineStr">
-        <is>
-          <t>수영
-15:00–16:00
-수영장</t>
-        </is>
-      </c>
+      <c r="H31" s="5" t="n"/>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" s="6" t="inlineStr"/>
@@ -1273,7 +1267,7 @@
       <c r="E32" s="5" t="n"/>
       <c r="F32" s="10" t="n"/>
       <c r="G32" s="5" t="n"/>
-      <c r="H32" s="10" t="n"/>
+      <c r="H32" s="5" t="n"/>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" s="6" t="inlineStr">
@@ -1287,7 +1281,7 @@
       <c r="E33" s="5" t="n"/>
       <c r="F33" s="10" t="n"/>
       <c r="G33" s="5" t="n"/>
-      <c r="H33" s="10" t="n"/>
+      <c r="H33" s="5" t="n"/>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" s="6" t="inlineStr"/>
@@ -1297,7 +1291,7 @@
       <c r="E34" s="5" t="n"/>
       <c r="F34" s="8" t="n"/>
       <c r="G34" s="5" t="n"/>
-      <c r="H34" s="8" t="n"/>
+      <c r="H34" s="5" t="n"/>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" s="4" t="inlineStr">
@@ -1329,7 +1323,13 @@
         </is>
       </c>
       <c r="G35" s="5" t="n"/>
-      <c r="H35" s="5" t="n"/>
+      <c r="H35" s="12" t="inlineStr">
+        <is>
+          <t>수영
+16:10–17:10
+수영장</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" s="6" t="inlineStr"/>
@@ -1339,7 +1339,7 @@
       <c r="E36" s="10" t="n"/>
       <c r="F36" s="10" t="n"/>
       <c r="G36" s="5" t="n"/>
-      <c r="H36" s="5" t="n"/>
+      <c r="H36" s="10" t="n"/>
     </row>
     <row r="37" ht="15" customHeight="1">
       <c r="A37" s="6" t="inlineStr">
@@ -1353,7 +1353,7 @@
       <c r="E37" s="10" t="n"/>
       <c r="F37" s="10" t="n"/>
       <c r="G37" s="5" t="n"/>
-      <c r="H37" s="5" t="n"/>
+      <c r="H37" s="10" t="n"/>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="A38" s="6" t="inlineStr"/>
@@ -1369,7 +1369,7 @@
       <c r="E38" s="8" t="n"/>
       <c r="F38" s="8" t="n"/>
       <c r="G38" s="5" t="n"/>
-      <c r="H38" s="5" t="n"/>
+      <c r="H38" s="10" t="n"/>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" s="4" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="F39" s="5" t="n"/>
       <c r="G39" s="5" t="n"/>
-      <c r="H39" s="5" t="n"/>
+      <c r="H39" s="8" t="n"/>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" s="6" t="inlineStr"/>
@@ -1612,7 +1612,6 @@
     <mergeCell ref="C6:C24"/>
     <mergeCell ref="F6:F22"/>
     <mergeCell ref="B27:B30"/>
-    <mergeCell ref="H31:H34"/>
     <mergeCell ref="C35:C36"/>
     <mergeCell ref="C47:C48"/>
     <mergeCell ref="D4:D5"/>
@@ -1626,6 +1625,7 @@
     <mergeCell ref="E25:E31"/>
     <mergeCell ref="D49:D51"/>
     <mergeCell ref="E39:E41"/>
+    <mergeCell ref="H35:H39"/>
     <mergeCell ref="E6:E24"/>
     <mergeCell ref="B6:B24"/>
     <mergeCell ref="B4:B5"/>
@@ -3539,12 +3539,12 @@
       </c>
       <c r="C30" s="24" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="D30" s="24" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="E30" s="25" t="inlineStr">

--- a/시간표.xlsx
+++ b/시간표.xlsx
@@ -1308,13 +1308,7 @@
         </is>
       </c>
       <c r="D35" s="5" t="n"/>
-      <c r="E35" s="12" t="inlineStr">
-        <is>
-          <t>태권도
-16:00–17:00
-태권도장</t>
-        </is>
-      </c>
+      <c r="E35" s="5" t="n"/>
       <c r="F35" s="12" t="inlineStr">
         <is>
           <t>태권도
@@ -1336,7 +1330,7 @@
       <c r="B36" s="5" t="n"/>
       <c r="C36" s="8" t="n"/>
       <c r="D36" s="5" t="n"/>
-      <c r="E36" s="10" t="n"/>
+      <c r="E36" s="5" t="n"/>
       <c r="F36" s="10" t="n"/>
       <c r="G36" s="5" t="n"/>
       <c r="H36" s="10" t="n"/>
@@ -1350,7 +1344,7 @@
       <c r="B37" s="5" t="n"/>
       <c r="C37" s="5" t="n"/>
       <c r="D37" s="5" t="n"/>
-      <c r="E37" s="10" t="n"/>
+      <c r="E37" s="5" t="n"/>
       <c r="F37" s="10" t="n"/>
       <c r="G37" s="5" t="n"/>
       <c r="H37" s="10" t="n"/>
@@ -1366,7 +1360,7 @@
 추정</t>
         </is>
       </c>
-      <c r="E38" s="8" t="n"/>
+      <c r="E38" s="5" t="n"/>
       <c r="F38" s="8" t="n"/>
       <c r="G38" s="5" t="n"/>
       <c r="H38" s="10" t="n"/>
@@ -1603,10 +1597,9 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="27">
+  <mergeCells count="26">
     <mergeCell ref="C4:C5"/>
     <mergeCell ref="E4:E5"/>
-    <mergeCell ref="E35:E38"/>
     <mergeCell ref="D6:D22"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="C6:C24"/>
@@ -2130,7 +2123,13 @@
 한글교실</t>
         </is>
       </c>
-      <c r="E35" s="5" t="n"/>
+      <c r="E35" s="12" t="inlineStr">
+        <is>
+          <t>태권도
+16:00–17:00
+태권도장</t>
+        </is>
+      </c>
       <c r="F35" s="12" t="inlineStr">
         <is>
           <t>태권도
@@ -2152,7 +2151,7 @@
       </c>
       <c r="C36" s="5" t="n"/>
       <c r="D36" s="10" t="n"/>
-      <c r="E36" s="5" t="n"/>
+      <c r="E36" s="10" t="n"/>
       <c r="F36" s="10" t="n"/>
       <c r="G36" s="5" t="n"/>
       <c r="H36" s="5" t="n"/>
@@ -2166,7 +2165,7 @@
       <c r="B37" s="10" t="n"/>
       <c r="C37" s="5" t="n"/>
       <c r="D37" s="8" t="n"/>
-      <c r="E37" s="5" t="n"/>
+      <c r="E37" s="10" t="n"/>
       <c r="F37" s="10" t="n"/>
       <c r="G37" s="5" t="n"/>
       <c r="H37" s="5" t="n"/>
@@ -2176,7 +2175,7 @@
       <c r="B38" s="8" t="n"/>
       <c r="C38" s="5" t="n"/>
       <c r="D38" s="5" t="n"/>
-      <c r="E38" s="5" t="n"/>
+      <c r="E38" s="8" t="n"/>
       <c r="F38" s="8" t="n"/>
       <c r="G38" s="5" t="n"/>
       <c r="H38" s="5" t="n"/>
@@ -2395,10 +2394,11 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="D49:D50"/>
     <mergeCell ref="D35:D37"/>
     <mergeCell ref="F7:F31"/>
+    <mergeCell ref="E35:E38"/>
     <mergeCell ref="C7:C31"/>
     <mergeCell ref="B7:B31"/>
     <mergeCell ref="D7:D31"/>
@@ -3805,9 +3805,9 @@
       <c r="H36" s="25" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="23" t="inlineStr">
-        <is>
-          <t>첫째</t>
+      <c r="A37" s="30" t="inlineStr">
+        <is>
+          <t>둘째</t>
         </is>
       </c>
       <c r="B37" s="24" t="inlineStr">

--- a/시간표.xlsx
+++ b/시간표.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="첫째 주간표" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="둘째 주간표" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="일정(편집용)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="첫째 주간표" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="둘째 주간표" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="일정(편집용)" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'첫째 주간표'!$A$1:$H$52</definedName>
@@ -1258,7 +1258,7 @@
       <c r="B32" s="12" t="inlineStr">
         <is>
           <t>한글수업
-15:20–15:50
+15:20–16:10
 한글교실</t>
         </is>
       </c>
@@ -1285,7 +1285,7 @@
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" s="6" t="inlineStr"/>
-      <c r="B34" s="8" t="n"/>
+      <c r="B34" s="10" t="n"/>
       <c r="C34" s="5" t="n"/>
       <c r="D34" s="5" t="n"/>
       <c r="E34" s="5" t="n"/>
@@ -1299,7 +1299,7 @@
           <t>16:00</t>
         </is>
       </c>
-      <c r="B35" s="5" t="n"/>
+      <c r="B35" s="8" t="n"/>
       <c r="C35" s="12" t="inlineStr">
         <is>
           <t>피아노
@@ -1356,7 +1356,7 @@
       <c r="D38" s="12" t="inlineStr">
         <is>
           <t>한글수업
-16:50–17:20*
+16:50–17:40*
 추정</t>
         </is>
       </c>
@@ -1377,7 +1377,7 @@
       <c r="E39" s="12" t="inlineStr">
         <is>
           <t>영어수업
-17:10–17:40
+17:10–18:10
 한글교실</t>
         </is>
       </c>
@@ -1389,7 +1389,7 @@
       <c r="A40" s="6" t="inlineStr"/>
       <c r="B40" s="5" t="n"/>
       <c r="C40" s="5" t="n"/>
-      <c r="D40" s="8" t="n"/>
+      <c r="D40" s="10" t="n"/>
       <c r="E40" s="10" t="n"/>
       <c r="F40" s="5" t="n"/>
       <c r="G40" s="5" t="n"/>
@@ -1403,8 +1403,8 @@
       </c>
       <c r="B41" s="5" t="n"/>
       <c r="C41" s="5" t="n"/>
-      <c r="D41" s="5" t="n"/>
-      <c r="E41" s="8" t="n"/>
+      <c r="D41" s="8" t="n"/>
+      <c r="E41" s="10" t="n"/>
       <c r="F41" s="5" t="n"/>
       <c r="G41" s="5" t="n"/>
       <c r="H41" s="5" t="n"/>
@@ -1414,7 +1414,7 @@
       <c r="B42" s="5" t="n"/>
       <c r="C42" s="5" t="n"/>
       <c r="D42" s="5" t="n"/>
-      <c r="E42" s="5" t="n"/>
+      <c r="E42" s="10" t="n"/>
       <c r="F42" s="5" t="n"/>
       <c r="G42" s="5" t="n"/>
       <c r="H42" s="5" t="n"/>
@@ -1428,7 +1428,7 @@
       <c r="B43" s="5" t="n"/>
       <c r="C43" s="5" t="n"/>
       <c r="D43" s="5" t="n"/>
-      <c r="E43" s="5" t="n"/>
+      <c r="E43" s="8" t="n"/>
       <c r="F43" s="5" t="n"/>
       <c r="G43" s="5" t="n"/>
       <c r="H43" s="5" t="n"/>
@@ -1608,21 +1608,21 @@
     <mergeCell ref="C35:C36"/>
     <mergeCell ref="C47:C48"/>
     <mergeCell ref="D4:D5"/>
-    <mergeCell ref="D38:D40"/>
     <mergeCell ref="D23:D28"/>
     <mergeCell ref="F47:F48"/>
-    <mergeCell ref="B32:B34"/>
     <mergeCell ref="C27:C30"/>
     <mergeCell ref="F35:F38"/>
     <mergeCell ref="F23:F28"/>
     <mergeCell ref="E25:E31"/>
     <mergeCell ref="D49:D51"/>
-    <mergeCell ref="E39:E41"/>
     <mergeCell ref="H35:H39"/>
     <mergeCell ref="E6:E24"/>
     <mergeCell ref="B6:B24"/>
+    <mergeCell ref="E39:E43"/>
+    <mergeCell ref="B32:B35"/>
     <mergeCell ref="B4:B5"/>
     <mergeCell ref="F4:F5"/>
+    <mergeCell ref="D38:D41"/>
     <mergeCell ref="F29:F34"/>
   </mergeCells>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
@@ -2574,7 +2574,7 @@
       </c>
       <c r="D5" s="24" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="E5" s="25" t="inlineStr">
@@ -2958,7 +2958,7 @@
       </c>
       <c r="D15" s="24" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="E15" s="25" t="inlineStr">
@@ -3700,7 +3700,7 @@
       </c>
       <c r="D34" s="24" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="E34" s="25" t="inlineStr">

--- a/시간표.xlsx
+++ b/시간표.xlsx
@@ -1119,7 +1119,7 @@
         <is>
           <t>방과후 아나운서
 12:50–14:20
-유료</t>
+학교</t>
         </is>
       </c>
       <c r="E23" s="10" t="n"/>
@@ -1156,7 +1156,7 @@
         <is>
           <t>방과후 큐보로봇
 13:40–15:10
-유료</t>
+학교</t>
         </is>
       </c>
       <c r="F25" s="10" t="n"/>
@@ -2934,11 +2934,7 @@
           <t>학교</t>
         </is>
       </c>
-      <c r="H14" s="25" t="inlineStr">
-        <is>
-          <t>유료</t>
-        </is>
-      </c>
+      <c r="H14" s="25" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="23" t="inlineStr">
@@ -3760,11 +3756,7 @@
           <t>학교</t>
         </is>
       </c>
-      <c r="H35" s="25" t="inlineStr">
-        <is>
-          <t>유료</t>
-        </is>
-      </c>
+      <c r="H35" s="25" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="23" t="inlineStr">

--- a/시간표.xlsx
+++ b/시간표.xlsx
@@ -1223,7 +1223,7 @@
         <is>
           <t>미술학원
 14:40–16:00
-미술학원</t>
+봉쁘앙 미술학원</t>
         </is>
       </c>
       <c r="G29" s="5" t="n"/>
@@ -1259,7 +1259,7 @@
         <is>
           <t>한글수업
 15:20–16:10
-한글교실</t>
+집 (과외)</t>
         </is>
       </c>
       <c r="C32" s="5" t="n"/>
@@ -1304,7 +1304,7 @@
         <is>
           <t>피아노
 16:00–16:30
-피아노학원</t>
+집 (과외)</t>
         </is>
       </c>
       <c r="D35" s="5" t="n"/>
@@ -1378,7 +1378,7 @@
         <is>
           <t>영어수업
 17:10–18:10
-한글교실</t>
+집 (과외)</t>
         </is>
       </c>
       <c r="F39" s="5" t="n"/>
@@ -1515,7 +1515,7 @@
         <is>
           <t>첼로
 19:30–20:10
-첼로교실</t>
+보스턴음악학원</t>
         </is>
       </c>
       <c r="E49" s="5" t="n"/>
@@ -2120,7 +2120,7 @@
         <is>
           <t>한글수업
 16:10–16:40
-한글교실</t>
+집 (과외)</t>
         </is>
       </c>
       <c r="E35" s="12" t="inlineStr">
@@ -2146,7 +2146,7 @@
         <is>
           <t>한글수업
 16:20–16:50
-한글교실</t>
+집 (과외)</t>
         </is>
       </c>
       <c r="C36" s="5" t="n"/>
@@ -2589,7 +2589,7 @@
       </c>
       <c r="G5" s="25" t="inlineStr">
         <is>
-          <t>한글교실</t>
+          <t>집 (과외)</t>
         </is>
       </c>
       <c r="H5" s="25" t="inlineStr"/>
@@ -2741,7 +2741,7 @@
       </c>
       <c r="G9" s="25" t="inlineStr">
         <is>
-          <t>피아노학원</t>
+          <t>집 (과외)</t>
         </is>
       </c>
       <c r="H9" s="25" t="inlineStr"/>
@@ -2969,7 +2969,7 @@
       </c>
       <c r="G15" s="25" t="inlineStr">
         <is>
-          <t>한글교실</t>
+          <t>집 (과외)</t>
         </is>
       </c>
       <c r="H15" s="25" t="inlineStr"/>
@@ -3125,7 +3125,7 @@
       </c>
       <c r="G19" s="25" t="inlineStr">
         <is>
-          <t>미술학원</t>
+          <t>봉쁘앙 미술학원</t>
         </is>
       </c>
       <c r="H19" s="25" t="inlineStr"/>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="G22" s="25" t="inlineStr">
         <is>
-          <t>한글교실</t>
+          <t>집 (과외)</t>
         </is>
       </c>
       <c r="H22" s="25" t="inlineStr"/>
@@ -3357,7 +3357,7 @@
       </c>
       <c r="G25" s="25" t="inlineStr">
         <is>
-          <t>한글교실</t>
+          <t>집 (과외)</t>
         </is>
       </c>
       <c r="H25" s="25" t="inlineStr"/>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="G29" s="25" t="inlineStr">
         <is>
-          <t>첼로교실</t>
+          <t>보스턴음악학원</t>
         </is>
       </c>
       <c r="H29" s="25" t="inlineStr"/>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="G34" s="25" t="inlineStr">
         <is>
-          <t>한글교실</t>
+          <t>집 (과외)</t>
         </is>
       </c>
       <c r="H34" s="25" t="inlineStr">

--- a/시간표.xlsx
+++ b/시간표.xlsx
@@ -9,11 +9,13 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="첫째 주간표" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="둘째 주간표" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="일정(편집용)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="두 아이 주간표" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="일정(편집용)" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'첫째 주간표'!$A$1:$H$52</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'둘째 주간표'!$A$1:$H$52</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'두 아이 주간표'!$A$1:$O$53</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -22,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="21">
+  <fonts count="26">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -122,6 +124,36 @@
       <name val="맑은 고딕"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="007A5E00"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="001F4E79"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="009C4A16"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="002E6B1F"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
@@ -209,7 +241,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -306,11 +338,44 @@
         <color rgb="00C9C9C9"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00C9C9C9"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C9C9C9"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C9C9C9"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C9C9C9"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C9C9C9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C9C9C9"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -362,32 +427,55 @@
     <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2416,6 +2504,1338 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:O53"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="9.5" customWidth="1" min="2" max="2"/>
+    <col width="9.5" customWidth="1" min="3" max="3"/>
+    <col width="9.5" customWidth="1" min="4" max="4"/>
+    <col width="9.5" customWidth="1" min="5" max="5"/>
+    <col width="9.5" customWidth="1" min="6" max="6"/>
+    <col width="9.5" customWidth="1" min="7" max="7"/>
+    <col width="9.5" customWidth="1" min="8" max="8"/>
+    <col width="9.5" customWidth="1" min="9" max="9"/>
+    <col width="9.5" customWidth="1" min="10" max="10"/>
+    <col width="9.5" customWidth="1" min="11" max="11"/>
+    <col width="9.5" customWidth="1" min="12" max="12"/>
+    <col width="9.5" customWidth="1" min="13" max="13"/>
+    <col width="9.5" customWidth="1" min="14" max="14"/>
+    <col width="9.5" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="21" t="inlineStr">
+        <is>
+          <t>두 아이 주간 시간표  (서원 · 서준)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>시간</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C2" s="22" t="n"/>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>화</t>
+        </is>
+      </c>
+      <c r="E2" s="22" t="n"/>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>수</t>
+        </is>
+      </c>
+      <c r="G2" s="22" t="n"/>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>목</t>
+        </is>
+      </c>
+      <c r="I2" s="22" t="n"/>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>금</t>
+        </is>
+      </c>
+      <c r="K2" s="22" t="n"/>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>토</t>
+        </is>
+      </c>
+      <c r="M2" s="22" t="n"/>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="O2" s="22" t="n"/>
+    </row>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" s="23" t="n"/>
+      <c r="B3" s="24" t="inlineStr">
+        <is>
+          <t>서원</t>
+        </is>
+      </c>
+      <c r="C3" s="25" t="inlineStr">
+        <is>
+          <t>서준</t>
+        </is>
+      </c>
+      <c r="D3" s="24" t="inlineStr">
+        <is>
+          <t>서원</t>
+        </is>
+      </c>
+      <c r="E3" s="25" t="inlineStr">
+        <is>
+          <t>서준</t>
+        </is>
+      </c>
+      <c r="F3" s="24" t="inlineStr">
+        <is>
+          <t>서원</t>
+        </is>
+      </c>
+      <c r="G3" s="25" t="inlineStr">
+        <is>
+          <t>서준</t>
+        </is>
+      </c>
+      <c r="H3" s="24" t="inlineStr">
+        <is>
+          <t>서원</t>
+        </is>
+      </c>
+      <c r="I3" s="25" t="inlineStr">
+        <is>
+          <t>서준</t>
+        </is>
+      </c>
+      <c r="J3" s="24" t="inlineStr">
+        <is>
+          <t>서원</t>
+        </is>
+      </c>
+      <c r="K3" s="25" t="inlineStr">
+        <is>
+          <t>서준</t>
+        </is>
+      </c>
+      <c r="L3" s="24" t="inlineStr">
+        <is>
+          <t>서원</t>
+        </is>
+      </c>
+      <c r="M3" s="25" t="inlineStr">
+        <is>
+          <t>서준</t>
+        </is>
+      </c>
+      <c r="N3" s="24" t="inlineStr">
+        <is>
+          <t>서원</t>
+        </is>
+      </c>
+      <c r="O3" s="25" t="inlineStr">
+        <is>
+          <t>서준</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="5" t="n"/>
+      <c r="G4" s="5" t="n"/>
+      <c r="H4" s="5" t="n"/>
+      <c r="I4" s="5" t="n"/>
+      <c r="J4" s="5" t="n"/>
+      <c r="K4" s="5" t="n"/>
+      <c r="L4" s="5" t="n"/>
+      <c r="M4" s="5" t="n"/>
+      <c r="N4" s="5" t="n"/>
+      <c r="O4" s="5" t="n"/>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" s="6" t="inlineStr"/>
+      <c r="B5" s="26" t="inlineStr">
+        <is>
+          <t>등교
+08:20</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="26" t="inlineStr">
+        <is>
+          <t>등교
+08:20</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="26" t="inlineStr">
+        <is>
+          <t>등교
+08:20</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="n"/>
+      <c r="H5" s="26" t="inlineStr">
+        <is>
+          <t>등교
+08:20</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="n"/>
+      <c r="J5" s="26" t="inlineStr">
+        <is>
+          <t>등교
+08:20</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="n"/>
+      <c r="L5" s="5" t="n"/>
+      <c r="M5" s="5" t="n"/>
+      <c r="N5" s="5" t="n"/>
+      <c r="O5" s="5" t="n"/>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="n"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="8" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="8" t="n"/>
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="8" t="n"/>
+      <c r="I6" s="5" t="n"/>
+      <c r="J6" s="8" t="n"/>
+      <c r="K6" s="5" t="n"/>
+      <c r="L6" s="5" t="n"/>
+      <c r="M6" s="5" t="n"/>
+      <c r="N6" s="5" t="n"/>
+      <c r="O6" s="5" t="n"/>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" s="6" t="inlineStr"/>
+      <c r="B7" s="27" t="inlineStr">
+        <is>
+          <t>정규수업
+08:45</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="27" t="inlineStr">
+        <is>
+          <t>정규수업
+08:45</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="27" t="inlineStr">
+        <is>
+          <t>정규수업(단축)
+08:45</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="n"/>
+      <c r="H7" s="27" t="inlineStr">
+        <is>
+          <t>정규수업
+08:45</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="n"/>
+      <c r="J7" s="27" t="inlineStr">
+        <is>
+          <t>정규수업(단축)
+08:45</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="n"/>
+      <c r="L7" s="5" t="n"/>
+      <c r="M7" s="5" t="n"/>
+      <c r="N7" s="5" t="n"/>
+      <c r="O7" s="5" t="n"/>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="n"/>
+      <c r="C8" s="27" t="inlineStr">
+        <is>
+          <t>유치원
+09:10</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="n"/>
+      <c r="E8" s="27" t="inlineStr">
+        <is>
+          <t>유치원
+09:10</t>
+        </is>
+      </c>
+      <c r="F8" s="10" t="n"/>
+      <c r="G8" s="27" t="inlineStr">
+        <is>
+          <t>유치원
+09:10</t>
+        </is>
+      </c>
+      <c r="H8" s="10" t="n"/>
+      <c r="I8" s="27" t="inlineStr">
+        <is>
+          <t>유치원
+09:10</t>
+        </is>
+      </c>
+      <c r="J8" s="10" t="n"/>
+      <c r="K8" s="27" t="inlineStr">
+        <is>
+          <t>유치원
+09:10</t>
+        </is>
+      </c>
+      <c r="L8" s="5" t="n"/>
+      <c r="M8" s="5" t="n"/>
+      <c r="N8" s="5" t="n"/>
+      <c r="O8" s="5" t="n"/>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" s="6" t="inlineStr"/>
+      <c r="B9" s="10" t="n"/>
+      <c r="C9" s="10" t="n"/>
+      <c r="D9" s="10" t="n"/>
+      <c r="E9" s="10" t="n"/>
+      <c r="F9" s="10" t="n"/>
+      <c r="G9" s="10" t="n"/>
+      <c r="H9" s="10" t="n"/>
+      <c r="I9" s="10" t="n"/>
+      <c r="J9" s="10" t="n"/>
+      <c r="K9" s="10" t="n"/>
+      <c r="L9" s="5" t="n"/>
+      <c r="M9" s="5" t="n"/>
+      <c r="N9" s="5" t="n"/>
+      <c r="O9" s="5" t="n"/>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="n"/>
+      <c r="C10" s="10" t="n"/>
+      <c r="D10" s="10" t="n"/>
+      <c r="E10" s="10" t="n"/>
+      <c r="F10" s="10" t="n"/>
+      <c r="G10" s="10" t="n"/>
+      <c r="H10" s="10" t="n"/>
+      <c r="I10" s="10" t="n"/>
+      <c r="J10" s="10" t="n"/>
+      <c r="K10" s="10" t="n"/>
+      <c r="L10" s="5" t="n"/>
+      <c r="M10" s="5" t="n"/>
+      <c r="N10" s="5" t="n"/>
+      <c r="O10" s="5" t="n"/>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" s="6" t="inlineStr"/>
+      <c r="B11" s="10" t="n"/>
+      <c r="C11" s="10" t="n"/>
+      <c r="D11" s="10" t="n"/>
+      <c r="E11" s="10" t="n"/>
+      <c r="F11" s="10" t="n"/>
+      <c r="G11" s="10" t="n"/>
+      <c r="H11" s="10" t="n"/>
+      <c r="I11" s="10" t="n"/>
+      <c r="J11" s="10" t="n"/>
+      <c r="K11" s="10" t="n"/>
+      <c r="L11" s="5" t="n"/>
+      <c r="M11" s="5" t="n"/>
+      <c r="N11" s="5" t="n"/>
+      <c r="O11" s="5" t="n"/>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="n"/>
+      <c r="C12" s="10" t="n"/>
+      <c r="D12" s="10" t="n"/>
+      <c r="E12" s="10" t="n"/>
+      <c r="F12" s="10" t="n"/>
+      <c r="G12" s="10" t="n"/>
+      <c r="H12" s="10" t="n"/>
+      <c r="I12" s="10" t="n"/>
+      <c r="J12" s="10" t="n"/>
+      <c r="K12" s="10" t="n"/>
+      <c r="L12" s="5" t="n"/>
+      <c r="M12" s="5" t="n"/>
+      <c r="N12" s="5" t="n"/>
+      <c r="O12" s="5" t="n"/>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" s="6" t="inlineStr"/>
+      <c r="B13" s="10" t="n"/>
+      <c r="C13" s="10" t="n"/>
+      <c r="D13" s="10" t="n"/>
+      <c r="E13" s="10" t="n"/>
+      <c r="F13" s="10" t="n"/>
+      <c r="G13" s="10" t="n"/>
+      <c r="H13" s="10" t="n"/>
+      <c r="I13" s="10" t="n"/>
+      <c r="J13" s="10" t="n"/>
+      <c r="K13" s="10" t="n"/>
+      <c r="L13" s="5" t="n"/>
+      <c r="M13" s="5" t="n"/>
+      <c r="N13" s="5" t="n"/>
+      <c r="O13" s="5" t="n"/>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="n"/>
+      <c r="C14" s="10" t="n"/>
+      <c r="D14" s="10" t="n"/>
+      <c r="E14" s="10" t="n"/>
+      <c r="F14" s="10" t="n"/>
+      <c r="G14" s="10" t="n"/>
+      <c r="H14" s="10" t="n"/>
+      <c r="I14" s="10" t="n"/>
+      <c r="J14" s="10" t="n"/>
+      <c r="K14" s="10" t="n"/>
+      <c r="L14" s="5" t="n"/>
+      <c r="M14" s="5" t="n"/>
+      <c r="N14" s="5" t="n"/>
+      <c r="O14" s="5" t="n"/>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" s="6" t="inlineStr"/>
+      <c r="B15" s="10" t="n"/>
+      <c r="C15" s="10" t="n"/>
+      <c r="D15" s="10" t="n"/>
+      <c r="E15" s="10" t="n"/>
+      <c r="F15" s="10" t="n"/>
+      <c r="G15" s="10" t="n"/>
+      <c r="H15" s="10" t="n"/>
+      <c r="I15" s="10" t="n"/>
+      <c r="J15" s="10" t="n"/>
+      <c r="K15" s="10" t="n"/>
+      <c r="L15" s="5" t="n"/>
+      <c r="M15" s="5" t="n"/>
+      <c r="N15" s="5" t="n"/>
+      <c r="O15" s="5" t="n"/>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="n"/>
+      <c r="C16" s="10" t="n"/>
+      <c r="D16" s="10" t="n"/>
+      <c r="E16" s="10" t="n"/>
+      <c r="F16" s="10" t="n"/>
+      <c r="G16" s="10" t="n"/>
+      <c r="H16" s="10" t="n"/>
+      <c r="I16" s="10" t="n"/>
+      <c r="J16" s="10" t="n"/>
+      <c r="K16" s="10" t="n"/>
+      <c r="L16" s="5" t="n"/>
+      <c r="M16" s="5" t="n"/>
+      <c r="N16" s="5" t="n"/>
+      <c r="O16" s="5" t="n"/>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" s="6" t="inlineStr"/>
+      <c r="B17" s="10" t="n"/>
+      <c r="C17" s="10" t="n"/>
+      <c r="D17" s="10" t="n"/>
+      <c r="E17" s="10" t="n"/>
+      <c r="F17" s="10" t="n"/>
+      <c r="G17" s="10" t="n"/>
+      <c r="H17" s="10" t="n"/>
+      <c r="I17" s="10" t="n"/>
+      <c r="J17" s="10" t="n"/>
+      <c r="K17" s="10" t="n"/>
+      <c r="L17" s="5" t="n"/>
+      <c r="M17" s="5" t="n"/>
+      <c r="N17" s="5" t="n"/>
+      <c r="O17" s="5" t="n"/>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="n"/>
+      <c r="C18" s="10" t="n"/>
+      <c r="D18" s="10" t="n"/>
+      <c r="E18" s="10" t="n"/>
+      <c r="F18" s="10" t="n"/>
+      <c r="G18" s="10" t="n"/>
+      <c r="H18" s="10" t="n"/>
+      <c r="I18" s="10" t="n"/>
+      <c r="J18" s="10" t="n"/>
+      <c r="K18" s="10" t="n"/>
+      <c r="L18" s="5" t="n"/>
+      <c r="M18" s="5" t="n"/>
+      <c r="N18" s="5" t="n"/>
+      <c r="O18" s="5" t="n"/>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" s="6" t="inlineStr"/>
+      <c r="B19" s="10" t="n"/>
+      <c r="C19" s="10" t="n"/>
+      <c r="D19" s="10" t="n"/>
+      <c r="E19" s="10" t="n"/>
+      <c r="F19" s="10" t="n"/>
+      <c r="G19" s="10" t="n"/>
+      <c r="H19" s="10" t="n"/>
+      <c r="I19" s="10" t="n"/>
+      <c r="J19" s="10" t="n"/>
+      <c r="K19" s="10" t="n"/>
+      <c r="L19" s="5" t="n"/>
+      <c r="M19" s="5" t="n"/>
+      <c r="N19" s="5" t="n"/>
+      <c r="O19" s="5" t="n"/>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="n"/>
+      <c r="C20" s="10" t="n"/>
+      <c r="D20" s="10" t="n"/>
+      <c r="E20" s="10" t="n"/>
+      <c r="F20" s="10" t="n"/>
+      <c r="G20" s="10" t="n"/>
+      <c r="H20" s="10" t="n"/>
+      <c r="I20" s="10" t="n"/>
+      <c r="J20" s="10" t="n"/>
+      <c r="K20" s="10" t="n"/>
+      <c r="L20" s="5" t="n"/>
+      <c r="M20" s="5" t="n"/>
+      <c r="N20" s="5" t="n"/>
+      <c r="O20" s="5" t="n"/>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" s="6" t="inlineStr"/>
+      <c r="B21" s="10" t="n"/>
+      <c r="C21" s="10" t="n"/>
+      <c r="D21" s="10" t="n"/>
+      <c r="E21" s="10" t="n"/>
+      <c r="F21" s="10" t="n"/>
+      <c r="G21" s="10" t="n"/>
+      <c r="H21" s="10" t="n"/>
+      <c r="I21" s="10" t="n"/>
+      <c r="J21" s="10" t="n"/>
+      <c r="K21" s="10" t="n"/>
+      <c r="L21" s="5" t="n"/>
+      <c r="M21" s="5" t="n"/>
+      <c r="N21" s="5" t="n"/>
+      <c r="O21" s="5" t="n"/>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="n"/>
+      <c r="C22" s="10" t="n"/>
+      <c r="D22" s="10" t="n"/>
+      <c r="E22" s="10" t="n"/>
+      <c r="F22" s="10" t="n"/>
+      <c r="G22" s="10" t="n"/>
+      <c r="H22" s="10" t="n"/>
+      <c r="I22" s="10" t="n"/>
+      <c r="J22" s="10" t="n"/>
+      <c r="K22" s="10" t="n"/>
+      <c r="L22" s="5" t="n"/>
+      <c r="M22" s="5" t="n"/>
+      <c r="N22" s="5" t="n"/>
+      <c r="O22" s="5" t="n"/>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" s="6" t="inlineStr"/>
+      <c r="B23" s="10" t="n"/>
+      <c r="C23" s="10" t="n"/>
+      <c r="D23" s="10" t="n"/>
+      <c r="E23" s="10" t="n"/>
+      <c r="F23" s="8" t="n"/>
+      <c r="G23" s="10" t="n"/>
+      <c r="H23" s="10" t="n"/>
+      <c r="I23" s="10" t="n"/>
+      <c r="J23" s="8" t="n"/>
+      <c r="K23" s="10" t="n"/>
+      <c r="L23" s="5" t="n"/>
+      <c r="M23" s="5" t="n"/>
+      <c r="N23" s="5" t="n"/>
+      <c r="O23" s="5" t="n"/>
+    </row>
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="n"/>
+      <c r="C24" s="10" t="n"/>
+      <c r="D24" s="10" t="n"/>
+      <c r="E24" s="10" t="n"/>
+      <c r="F24" s="28" t="inlineStr">
+        <is>
+          <t>방과후 아나운서
+12:50</t>
+        </is>
+      </c>
+      <c r="G24" s="10" t="n"/>
+      <c r="H24" s="10" t="n"/>
+      <c r="I24" s="10" t="n"/>
+      <c r="J24" s="28" t="inlineStr">
+        <is>
+          <t>맞춤형 종이접기
+12:50</t>
+        </is>
+      </c>
+      <c r="K24" s="10" t="n"/>
+      <c r="L24" s="5" t="n"/>
+      <c r="M24" s="5" t="n"/>
+      <c r="N24" s="5" t="n"/>
+      <c r="O24" s="5" t="n"/>
+    </row>
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" s="6" t="inlineStr"/>
+      <c r="B25" s="8" t="n"/>
+      <c r="C25" s="10" t="n"/>
+      <c r="D25" s="8" t="n"/>
+      <c r="E25" s="10" t="n"/>
+      <c r="F25" s="10" t="n"/>
+      <c r="G25" s="10" t="n"/>
+      <c r="H25" s="8" t="n"/>
+      <c r="I25" s="10" t="n"/>
+      <c r="J25" s="10" t="n"/>
+      <c r="K25" s="10" t="n"/>
+      <c r="L25" s="5" t="n"/>
+      <c r="M25" s="5" t="n"/>
+      <c r="N25" s="5" t="n"/>
+      <c r="O25" s="5" t="n"/>
+    </row>
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n"/>
+      <c r="C26" s="10" t="n"/>
+      <c r="D26" s="5" t="n"/>
+      <c r="E26" s="10" t="n"/>
+      <c r="F26" s="10" t="n"/>
+      <c r="G26" s="10" t="n"/>
+      <c r="H26" s="28" t="inlineStr">
+        <is>
+          <t>방과후 큐보로봇
+13:40</t>
+        </is>
+      </c>
+      <c r="I26" s="10" t="n"/>
+      <c r="J26" s="10" t="n"/>
+      <c r="K26" s="10" t="n"/>
+      <c r="L26" s="5" t="n"/>
+      <c r="M26" s="5" t="n"/>
+      <c r="N26" s="5" t="n"/>
+      <c r="O26" s="5" t="n"/>
+    </row>
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" s="6" t="inlineStr"/>
+      <c r="B27" s="5" t="n"/>
+      <c r="C27" s="10" t="n"/>
+      <c r="D27" s="5" t="n"/>
+      <c r="E27" s="10" t="n"/>
+      <c r="F27" s="10" t="n"/>
+      <c r="G27" s="10" t="n"/>
+      <c r="H27" s="10" t="n"/>
+      <c r="I27" s="10" t="n"/>
+      <c r="J27" s="10" t="n"/>
+      <c r="K27" s="10" t="n"/>
+      <c r="L27" s="5" t="n"/>
+      <c r="M27" s="5" t="n"/>
+      <c r="N27" s="5" t="n"/>
+      <c r="O27" s="5" t="n"/>
+    </row>
+    <row r="28" ht="15" customHeight="1">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="B28" s="29" t="inlineStr">
+        <is>
+          <t>태권도
+14:00</t>
+        </is>
+      </c>
+      <c r="C28" s="10" t="n"/>
+      <c r="D28" s="29" t="inlineStr">
+        <is>
+          <t>태권도
+14:00</t>
+        </is>
+      </c>
+      <c r="E28" s="10" t="n"/>
+      <c r="F28" s="10" t="n"/>
+      <c r="G28" s="10" t="n"/>
+      <c r="H28" s="10" t="n"/>
+      <c r="I28" s="10" t="n"/>
+      <c r="J28" s="10" t="n"/>
+      <c r="K28" s="10" t="n"/>
+      <c r="L28" s="5" t="n"/>
+      <c r="M28" s="5" t="n"/>
+      <c r="N28" s="5" t="n"/>
+      <c r="O28" s="5" t="n"/>
+    </row>
+    <row r="29" ht="15" customHeight="1">
+      <c r="A29" s="6" t="inlineStr"/>
+      <c r="B29" s="10" t="n"/>
+      <c r="C29" s="10" t="n"/>
+      <c r="D29" s="10" t="n"/>
+      <c r="E29" s="10" t="n"/>
+      <c r="F29" s="8" t="n"/>
+      <c r="G29" s="10" t="n"/>
+      <c r="H29" s="10" t="n"/>
+      <c r="I29" s="10" t="n"/>
+      <c r="J29" s="8" t="n"/>
+      <c r="K29" s="10" t="n"/>
+      <c r="L29" s="5" t="n"/>
+      <c r="M29" s="5" t="n"/>
+      <c r="N29" s="5" t="n"/>
+      <c r="O29" s="5" t="n"/>
+    </row>
+    <row r="30" ht="15" customHeight="1">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="B30" s="10" t="n"/>
+      <c r="C30" s="10" t="n"/>
+      <c r="D30" s="10" t="n"/>
+      <c r="E30" s="10" t="n"/>
+      <c r="F30" s="5" t="n"/>
+      <c r="G30" s="10" t="n"/>
+      <c r="H30" s="10" t="n"/>
+      <c r="I30" s="10" t="n"/>
+      <c r="J30" s="29" t="inlineStr">
+        <is>
+          <t>미술학원
+14:40</t>
+        </is>
+      </c>
+      <c r="K30" s="10" t="n"/>
+      <c r="L30" s="5" t="n"/>
+      <c r="M30" s="5" t="n"/>
+      <c r="N30" s="5" t="n"/>
+      <c r="O30" s="5" t="n"/>
+    </row>
+    <row r="31" ht="15" customHeight="1">
+      <c r="A31" s="6" t="inlineStr"/>
+      <c r="B31" s="8" t="n"/>
+      <c r="C31" s="10" t="n"/>
+      <c r="D31" s="8" t="n"/>
+      <c r="E31" s="10" t="n"/>
+      <c r="F31" s="5" t="n"/>
+      <c r="G31" s="10" t="n"/>
+      <c r="H31" s="10" t="n"/>
+      <c r="I31" s="10" t="n"/>
+      <c r="J31" s="10" t="n"/>
+      <c r="K31" s="10" t="n"/>
+      <c r="L31" s="5" t="n"/>
+      <c r="M31" s="5" t="n"/>
+      <c r="N31" s="5" t="n"/>
+      <c r="O31" s="5" t="n"/>
+    </row>
+    <row r="32" ht="15" customHeight="1">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n"/>
+      <c r="C32" s="8" t="n"/>
+      <c r="D32" s="5" t="n"/>
+      <c r="E32" s="8" t="n"/>
+      <c r="F32" s="5" t="n"/>
+      <c r="G32" s="8" t="n"/>
+      <c r="H32" s="8" t="n"/>
+      <c r="I32" s="8" t="n"/>
+      <c r="J32" s="10" t="n"/>
+      <c r="K32" s="8" t="n"/>
+      <c r="L32" s="5" t="n"/>
+      <c r="M32" s="5" t="n"/>
+      <c r="N32" s="5" t="n"/>
+      <c r="O32" s="5" t="n"/>
+    </row>
+    <row r="33" ht="15" customHeight="1">
+      <c r="A33" s="6" t="inlineStr"/>
+      <c r="B33" s="29" t="inlineStr">
+        <is>
+          <t>한글수업
+15:20</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="n"/>
+      <c r="D33" s="5" t="n"/>
+      <c r="E33" s="5" t="n"/>
+      <c r="F33" s="5" t="n"/>
+      <c r="G33" s="5" t="n"/>
+      <c r="H33" s="5" t="n"/>
+      <c r="I33" s="5" t="n"/>
+      <c r="J33" s="10" t="n"/>
+      <c r="K33" s="5" t="n"/>
+      <c r="L33" s="5" t="n"/>
+      <c r="M33" s="5" t="n"/>
+      <c r="N33" s="5" t="n"/>
+      <c r="O33" s="5" t="n"/>
+    </row>
+    <row r="34" ht="15" customHeight="1">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="B34" s="10" t="n"/>
+      <c r="C34" s="5" t="n"/>
+      <c r="D34" s="5" t="n"/>
+      <c r="E34" s="5" t="n"/>
+      <c r="F34" s="5" t="n"/>
+      <c r="G34" s="5" t="n"/>
+      <c r="H34" s="5" t="n"/>
+      <c r="I34" s="5" t="n"/>
+      <c r="J34" s="10" t="n"/>
+      <c r="K34" s="5" t="n"/>
+      <c r="L34" s="5" t="n"/>
+      <c r="M34" s="5" t="n"/>
+      <c r="N34" s="5" t="n"/>
+      <c r="O34" s="5" t="n"/>
+    </row>
+    <row r="35" ht="15" customHeight="1">
+      <c r="A35" s="6" t="inlineStr"/>
+      <c r="B35" s="10" t="n"/>
+      <c r="C35" s="5" t="n"/>
+      <c r="D35" s="5" t="n"/>
+      <c r="E35" s="5" t="n"/>
+      <c r="F35" s="5" t="n"/>
+      <c r="G35" s="5" t="n"/>
+      <c r="H35" s="5" t="n"/>
+      <c r="I35" s="5" t="n"/>
+      <c r="J35" s="8" t="n"/>
+      <c r="K35" s="5" t="n"/>
+      <c r="L35" s="5" t="n"/>
+      <c r="M35" s="5" t="n"/>
+      <c r="N35" s="5" t="n"/>
+      <c r="O35" s="5" t="n"/>
+    </row>
+    <row r="36" ht="15" customHeight="1">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="B36" s="8" t="n"/>
+      <c r="C36" s="5" t="n"/>
+      <c r="D36" s="29" t="inlineStr">
+        <is>
+          <t>피아노
+16:00</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="n"/>
+      <c r="F36" s="5" t="n"/>
+      <c r="G36" s="29" t="inlineStr">
+        <is>
+          <t>한글수업
+16:10</t>
+        </is>
+      </c>
+      <c r="H36" s="5" t="n"/>
+      <c r="I36" s="29" t="inlineStr">
+        <is>
+          <t>태권도
+16:00</t>
+        </is>
+      </c>
+      <c r="J36" s="29" t="inlineStr">
+        <is>
+          <t>태권도
+16:00</t>
+        </is>
+      </c>
+      <c r="K36" s="29" t="inlineStr">
+        <is>
+          <t>태권도
+16:00</t>
+        </is>
+      </c>
+      <c r="L36" s="5" t="n"/>
+      <c r="M36" s="5" t="n"/>
+      <c r="N36" s="29" t="inlineStr">
+        <is>
+          <t>수영
+16:10</t>
+        </is>
+      </c>
+      <c r="O36" s="5" t="n"/>
+    </row>
+    <row r="37" ht="15" customHeight="1">
+      <c r="A37" s="6" t="inlineStr"/>
+      <c r="B37" s="5" t="n"/>
+      <c r="C37" s="29" t="inlineStr">
+        <is>
+          <t>한글수업
+16:20</t>
+        </is>
+      </c>
+      <c r="D37" s="8" t="n"/>
+      <c r="E37" s="5" t="n"/>
+      <c r="F37" s="5" t="n"/>
+      <c r="G37" s="10" t="n"/>
+      <c r="H37" s="5" t="n"/>
+      <c r="I37" s="10" t="n"/>
+      <c r="J37" s="10" t="n"/>
+      <c r="K37" s="10" t="n"/>
+      <c r="L37" s="5" t="n"/>
+      <c r="M37" s="5" t="n"/>
+      <c r="N37" s="10" t="n"/>
+      <c r="O37" s="5" t="n"/>
+    </row>
+    <row r="38" ht="15" customHeight="1">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n"/>
+      <c r="C38" s="10" t="n"/>
+      <c r="D38" s="5" t="n"/>
+      <c r="E38" s="5" t="n"/>
+      <c r="F38" s="5" t="n"/>
+      <c r="G38" s="8" t="n"/>
+      <c r="H38" s="5" t="n"/>
+      <c r="I38" s="10" t="n"/>
+      <c r="J38" s="10" t="n"/>
+      <c r="K38" s="10" t="n"/>
+      <c r="L38" s="5" t="n"/>
+      <c r="M38" s="5" t="n"/>
+      <c r="N38" s="10" t="n"/>
+      <c r="O38" s="5" t="n"/>
+    </row>
+    <row r="39" ht="15" customHeight="1">
+      <c r="A39" s="6" t="inlineStr"/>
+      <c r="B39" s="5" t="n"/>
+      <c r="C39" s="8" t="n"/>
+      <c r="D39" s="5" t="n"/>
+      <c r="E39" s="5" t="n"/>
+      <c r="F39" s="29" t="inlineStr">
+        <is>
+          <t>한글수업
+16:50</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="n"/>
+      <c r="H39" s="5" t="n"/>
+      <c r="I39" s="8" t="n"/>
+      <c r="J39" s="8" t="n"/>
+      <c r="K39" s="8" t="n"/>
+      <c r="L39" s="5" t="n"/>
+      <c r="M39" s="5" t="n"/>
+      <c r="N39" s="10" t="n"/>
+      <c r="O39" s="5" t="n"/>
+    </row>
+    <row r="40" ht="15" customHeight="1">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n"/>
+      <c r="C40" s="5" t="n"/>
+      <c r="D40" s="5" t="n"/>
+      <c r="E40" s="5" t="n"/>
+      <c r="F40" s="10" t="n"/>
+      <c r="G40" s="5" t="n"/>
+      <c r="H40" s="29" t="inlineStr">
+        <is>
+          <t>영어수업
+17:10</t>
+        </is>
+      </c>
+      <c r="I40" s="5" t="n"/>
+      <c r="J40" s="5" t="n"/>
+      <c r="K40" s="5" t="n"/>
+      <c r="L40" s="5" t="n"/>
+      <c r="M40" s="5" t="n"/>
+      <c r="N40" s="8" t="n"/>
+      <c r="O40" s="5" t="n"/>
+    </row>
+    <row r="41" ht="15" customHeight="1">
+      <c r="A41" s="6" t="inlineStr"/>
+      <c r="B41" s="5" t="n"/>
+      <c r="C41" s="5" t="n"/>
+      <c r="D41" s="5" t="n"/>
+      <c r="E41" s="5" t="n"/>
+      <c r="F41" s="10" t="n"/>
+      <c r="G41" s="5" t="n"/>
+      <c r="H41" s="10" t="n"/>
+      <c r="I41" s="5" t="n"/>
+      <c r="J41" s="5" t="n"/>
+      <c r="K41" s="5" t="n"/>
+      <c r="L41" s="5" t="n"/>
+      <c r="M41" s="5" t="n"/>
+      <c r="N41" s="5" t="n"/>
+      <c r="O41" s="5" t="n"/>
+    </row>
+    <row r="42" ht="15" customHeight="1">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n"/>
+      <c r="C42" s="5" t="n"/>
+      <c r="D42" s="5" t="n"/>
+      <c r="E42" s="5" t="n"/>
+      <c r="F42" s="8" t="n"/>
+      <c r="G42" s="5" t="n"/>
+      <c r="H42" s="10" t="n"/>
+      <c r="I42" s="5" t="n"/>
+      <c r="J42" s="5" t="n"/>
+      <c r="K42" s="5" t="n"/>
+      <c r="L42" s="5" t="n"/>
+      <c r="M42" s="5" t="n"/>
+      <c r="N42" s="5" t="n"/>
+      <c r="O42" s="5" t="n"/>
+    </row>
+    <row r="43" ht="15" customHeight="1">
+      <c r="A43" s="6" t="inlineStr"/>
+      <c r="B43" s="5" t="n"/>
+      <c r="C43" s="5" t="n"/>
+      <c r="D43" s="5" t="n"/>
+      <c r="E43" s="5" t="n"/>
+      <c r="F43" s="5" t="n"/>
+      <c r="G43" s="5" t="n"/>
+      <c r="H43" s="10" t="n"/>
+      <c r="I43" s="5" t="n"/>
+      <c r="J43" s="5" t="n"/>
+      <c r="K43" s="5" t="n"/>
+      <c r="L43" s="5" t="n"/>
+      <c r="M43" s="5" t="n"/>
+      <c r="N43" s="5" t="n"/>
+      <c r="O43" s="5" t="n"/>
+    </row>
+    <row r="44" ht="15" customHeight="1">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n"/>
+      <c r="C44" s="5" t="n"/>
+      <c r="D44" s="5" t="n"/>
+      <c r="E44" s="5" t="n"/>
+      <c r="F44" s="5" t="n"/>
+      <c r="G44" s="5" t="n"/>
+      <c r="H44" s="8" t="n"/>
+      <c r="I44" s="5" t="n"/>
+      <c r="J44" s="5" t="n"/>
+      <c r="K44" s="5" t="n"/>
+      <c r="L44" s="5" t="n"/>
+      <c r="M44" s="5" t="n"/>
+      <c r="N44" s="5" t="n"/>
+      <c r="O44" s="5" t="n"/>
+    </row>
+    <row r="45" ht="15" customHeight="1">
+      <c r="A45" s="6" t="inlineStr"/>
+      <c r="B45" s="5" t="n"/>
+      <c r="C45" s="5" t="n"/>
+      <c r="D45" s="5" t="n"/>
+      <c r="E45" s="5" t="n"/>
+      <c r="F45" s="5" t="n"/>
+      <c r="G45" s="5" t="n"/>
+      <c r="H45" s="5" t="n"/>
+      <c r="I45" s="5" t="n"/>
+      <c r="J45" s="5" t="n"/>
+      <c r="K45" s="5" t="n"/>
+      <c r="L45" s="5" t="n"/>
+      <c r="M45" s="5" t="n"/>
+      <c r="N45" s="5" t="n"/>
+      <c r="O45" s="5" t="n"/>
+    </row>
+    <row r="46" ht="15" customHeight="1">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n"/>
+      <c r="C46" s="5" t="n"/>
+      <c r="D46" s="5" t="n"/>
+      <c r="E46" s="5" t="n"/>
+      <c r="F46" s="5" t="n"/>
+      <c r="G46" s="5" t="n"/>
+      <c r="H46" s="5" t="n"/>
+      <c r="I46" s="5" t="n"/>
+      <c r="J46" s="5" t="n"/>
+      <c r="K46" s="5" t="n"/>
+      <c r="L46" s="5" t="n"/>
+      <c r="M46" s="5" t="n"/>
+      <c r="N46" s="5" t="n"/>
+      <c r="O46" s="5" t="n"/>
+    </row>
+    <row r="47" ht="15" customHeight="1">
+      <c r="A47" s="6" t="inlineStr"/>
+      <c r="B47" s="5" t="n"/>
+      <c r="C47" s="5" t="n"/>
+      <c r="D47" s="5" t="n"/>
+      <c r="E47" s="5" t="n"/>
+      <c r="F47" s="5" t="n"/>
+      <c r="G47" s="5" t="n"/>
+      <c r="H47" s="5" t="n"/>
+      <c r="I47" s="5" t="n"/>
+      <c r="J47" s="5" t="n"/>
+      <c r="K47" s="5" t="n"/>
+      <c r="L47" s="5" t="n"/>
+      <c r="M47" s="5" t="n"/>
+      <c r="N47" s="5" t="n"/>
+      <c r="O47" s="5" t="n"/>
+    </row>
+    <row r="48" ht="15" customHeight="1">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n"/>
+      <c r="C48" s="5" t="n"/>
+      <c r="D48" s="29" t="inlineStr">
+        <is>
+          <t>화상영어
+19:00</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="n"/>
+      <c r="F48" s="5" t="n"/>
+      <c r="G48" s="5" t="n"/>
+      <c r="H48" s="5" t="n"/>
+      <c r="I48" s="5" t="n"/>
+      <c r="J48" s="29" t="inlineStr">
+        <is>
+          <t>화상영어
+19:00</t>
+        </is>
+      </c>
+      <c r="K48" s="5" t="n"/>
+      <c r="L48" s="5" t="n"/>
+      <c r="M48" s="5" t="n"/>
+      <c r="N48" s="5" t="n"/>
+      <c r="O48" s="5" t="n"/>
+    </row>
+    <row r="49" ht="15" customHeight="1">
+      <c r="A49" s="6" t="inlineStr"/>
+      <c r="B49" s="5" t="n"/>
+      <c r="C49" s="5" t="n"/>
+      <c r="D49" s="8" t="n"/>
+      <c r="E49" s="5" t="n"/>
+      <c r="F49" s="5" t="n"/>
+      <c r="G49" s="5" t="n"/>
+      <c r="H49" s="5" t="n"/>
+      <c r="I49" s="5" t="n"/>
+      <c r="J49" s="8" t="n"/>
+      <c r="K49" s="5" t="n"/>
+      <c r="L49" s="5" t="n"/>
+      <c r="M49" s="5" t="n"/>
+      <c r="N49" s="5" t="n"/>
+      <c r="O49" s="5" t="n"/>
+    </row>
+    <row r="50" ht="15" customHeight="1">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n"/>
+      <c r="C50" s="5" t="n"/>
+      <c r="D50" s="5" t="n"/>
+      <c r="E50" s="5" t="n"/>
+      <c r="F50" s="29" t="inlineStr">
+        <is>
+          <t>첼로
+19:30</t>
+        </is>
+      </c>
+      <c r="G50" s="29" t="inlineStr">
+        <is>
+          <t>축구
+19:30</t>
+        </is>
+      </c>
+      <c r="H50" s="5" t="n"/>
+      <c r="I50" s="5" t="n"/>
+      <c r="J50" s="5" t="n"/>
+      <c r="K50" s="5" t="n"/>
+      <c r="L50" s="5" t="n"/>
+      <c r="M50" s="5" t="n"/>
+      <c r="N50" s="5" t="n"/>
+      <c r="O50" s="5" t="n"/>
+    </row>
+    <row r="51" ht="15" customHeight="1">
+      <c r="A51" s="6" t="inlineStr"/>
+      <c r="B51" s="5" t="n"/>
+      <c r="C51" s="5" t="n"/>
+      <c r="D51" s="5" t="n"/>
+      <c r="E51" s="5" t="n"/>
+      <c r="F51" s="10" t="n"/>
+      <c r="G51" s="8" t="n"/>
+      <c r="H51" s="5" t="n"/>
+      <c r="I51" s="5" t="n"/>
+      <c r="J51" s="5" t="n"/>
+      <c r="K51" s="5" t="n"/>
+      <c r="L51" s="5" t="n"/>
+      <c r="M51" s="5" t="n"/>
+      <c r="N51" s="5" t="n"/>
+      <c r="O51" s="5" t="n"/>
+    </row>
+    <row r="52" ht="15" customHeight="1">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n"/>
+      <c r="C52" s="5" t="n"/>
+      <c r="D52" s="5" t="n"/>
+      <c r="E52" s="5" t="n"/>
+      <c r="F52" s="8" t="n"/>
+      <c r="G52" s="5" t="n"/>
+      <c r="H52" s="5" t="n"/>
+      <c r="I52" s="5" t="n"/>
+      <c r="J52" s="5" t="n"/>
+      <c r="K52" s="5" t="n"/>
+      <c r="L52" s="5" t="n"/>
+      <c r="M52" s="5" t="n"/>
+      <c r="N52" s="5" t="n"/>
+      <c r="O52" s="5" t="n"/>
+    </row>
+    <row r="53" ht="15" customHeight="1">
+      <c r="A53" s="6" t="inlineStr"/>
+      <c r="B53" s="5" t="n"/>
+      <c r="C53" s="5" t="n"/>
+      <c r="D53" s="5" t="n"/>
+      <c r="E53" s="5" t="n"/>
+      <c r="F53" s="5" t="n"/>
+      <c r="G53" s="5" t="n"/>
+      <c r="H53" s="5" t="n"/>
+      <c r="I53" s="5" t="n"/>
+      <c r="J53" s="5" t="n"/>
+      <c r="K53" s="5" t="n"/>
+      <c r="L53" s="5" t="n"/>
+      <c r="M53" s="5" t="n"/>
+      <c r="N53" s="5" t="n"/>
+      <c r="O53" s="5" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="44">
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="I36:I39"/>
+    <mergeCell ref="K36:K39"/>
+    <mergeCell ref="C8:C32"/>
+    <mergeCell ref="I8:I32"/>
+    <mergeCell ref="K8:K32"/>
+    <mergeCell ref="B7:B25"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="F24:F29"/>
+    <mergeCell ref="D36:D37"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="F7:F23"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="J36:J39"/>
+    <mergeCell ref="D48:D49"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="J30:J35"/>
+    <mergeCell ref="C37:C39"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="J24:J29"/>
+    <mergeCell ref="N36:N40"/>
+    <mergeCell ref="G36:G38"/>
+    <mergeCell ref="B28:B31"/>
+    <mergeCell ref="D28:D31"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="E8:E32"/>
+    <mergeCell ref="G8:G32"/>
+    <mergeCell ref="D7:D25"/>
+    <mergeCell ref="J7:J23"/>
+    <mergeCell ref="B33:B36"/>
+    <mergeCell ref="H7:H25"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="G50:G51"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="H26:H32"/>
+    <mergeCell ref="H5:H6"/>
+    <mergeCell ref="H40:H44"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="F39:F42"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="F50:F52"/>
+    <mergeCell ref="J48:J49"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.35" bottom="0.35" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H37"/>
@@ -2432,1407 +3852,1407 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="21" t="inlineStr">
+      <c r="A1" s="30" t="inlineStr">
         <is>
           <t>일정 편집용 — 여기 고친 뒤 '주간표 갱신' 요청하면 위 시간표가 다시 그려집니다</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="22" t="inlineStr">
+      <c r="A2" s="31" t="inlineStr">
         <is>
           <t>구분</t>
         </is>
       </c>
-      <c r="B2" s="22" t="inlineStr">
+      <c r="B2" s="31" t="inlineStr">
         <is>
           <t>요일</t>
         </is>
       </c>
-      <c r="C2" s="22" t="inlineStr">
+      <c r="C2" s="31" t="inlineStr">
         <is>
           <t>시작</t>
         </is>
       </c>
-      <c r="D2" s="22" t="inlineStr">
+      <c r="D2" s="31" t="inlineStr">
         <is>
           <t>종료</t>
         </is>
       </c>
-      <c r="E2" s="22" t="inlineStr">
+      <c r="E2" s="31" t="inlineStr">
         <is>
           <t>활동</t>
         </is>
       </c>
-      <c r="F2" s="22" t="inlineStr">
+      <c r="F2" s="31" t="inlineStr">
         <is>
           <t>분류</t>
         </is>
       </c>
-      <c r="G2" s="22" t="inlineStr">
+      <c r="G2" s="31" t="inlineStr">
         <is>
           <t>장소</t>
         </is>
       </c>
-      <c r="H2" s="22" t="inlineStr">
+      <c r="H2" s="31" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="23" t="inlineStr">
+      <c r="A3" s="32" t="inlineStr">
         <is>
           <t>첫째</t>
         </is>
       </c>
-      <c r="B3" s="24" t="inlineStr">
+      <c r="B3" s="33" t="inlineStr">
         <is>
           <t>월</t>
         </is>
       </c>
-      <c r="C3" s="24" t="inlineStr">
+      <c r="C3" s="33" t="inlineStr">
         <is>
           <t>08:20</t>
         </is>
       </c>
-      <c r="D3" s="24" t="inlineStr">
+      <c r="D3" s="33" t="inlineStr">
         <is>
           <t>08:45</t>
         </is>
       </c>
-      <c r="E3" s="25" t="inlineStr">
+      <c r="E3" s="34" t="inlineStr">
         <is>
           <t>등교</t>
         </is>
       </c>
-      <c r="F3" s="26" t="inlineStr">
+      <c r="F3" s="35" t="inlineStr">
         <is>
           <t>돌봄/픽업</t>
         </is>
       </c>
-      <c r="G3" s="25" t="inlineStr">
+      <c r="G3" s="34" t="inlineStr">
         <is>
           <t>집→학교</t>
         </is>
       </c>
-      <c r="H3" s="25" t="inlineStr"/>
+      <c r="H3" s="34" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="23" t="inlineStr">
+      <c r="A4" s="32" t="inlineStr">
         <is>
           <t>첫째</t>
         </is>
       </c>
-      <c r="B4" s="24" t="inlineStr">
+      <c r="B4" s="33" t="inlineStr">
         <is>
           <t>월</t>
         </is>
       </c>
-      <c r="C4" s="24" t="inlineStr">
+      <c r="C4" s="33" t="inlineStr">
         <is>
           <t>08:45</t>
         </is>
       </c>
-      <c r="D4" s="24" t="inlineStr">
+      <c r="D4" s="33" t="inlineStr">
         <is>
           <t>13:30</t>
         </is>
       </c>
-      <c r="E4" s="25" t="inlineStr">
+      <c r="E4" s="34" t="inlineStr">
         <is>
           <t>정규수업</t>
         </is>
       </c>
-      <c r="F4" s="27" t="inlineStr">
+      <c r="F4" s="36" t="inlineStr">
         <is>
           <t>정규수업</t>
         </is>
       </c>
-      <c r="G4" s="25" t="inlineStr">
+      <c r="G4" s="34" t="inlineStr">
         <is>
           <t>○○초</t>
         </is>
       </c>
-      <c r="H4" s="25" t="inlineStr"/>
+      <c r="H4" s="34" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="23" t="inlineStr">
+      <c r="A5" s="32" t="inlineStr">
         <is>
           <t>첫째</t>
         </is>
       </c>
-      <c r="B5" s="24" t="inlineStr">
+      <c r="B5" s="33" t="inlineStr">
         <is>
           <t>월</t>
         </is>
       </c>
-      <c r="C5" s="24" t="inlineStr">
+      <c r="C5" s="33" t="inlineStr">
         <is>
           <t>15:20</t>
         </is>
       </c>
-      <c r="D5" s="24" t="inlineStr">
+      <c r="D5" s="33" t="inlineStr">
         <is>
           <t>16:10</t>
         </is>
       </c>
-      <c r="E5" s="25" t="inlineStr">
+      <c r="E5" s="34" t="inlineStr">
         <is>
           <t>한글수업</t>
         </is>
       </c>
-      <c r="F5" s="28" t="inlineStr">
+      <c r="F5" s="37" t="inlineStr">
         <is>
           <t>학원</t>
         </is>
       </c>
-      <c r="G5" s="25" t="inlineStr">
+      <c r="G5" s="34" t="inlineStr">
         <is>
           <t>집 (과외)</t>
         </is>
       </c>
-      <c r="H5" s="25" t="inlineStr"/>
+      <c r="H5" s="34" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="23" t="inlineStr">
+      <c r="A6" s="32" t="inlineStr">
         <is>
           <t>첫째</t>
         </is>
       </c>
-      <c r="B6" s="24" t="inlineStr">
+      <c r="B6" s="33" t="inlineStr">
         <is>
           <t>화</t>
         </is>
       </c>
-      <c r="C6" s="24" t="inlineStr">
+      <c r="C6" s="33" t="inlineStr">
         <is>
           <t>08:20</t>
         </is>
       </c>
-      <c r="D6" s="24" t="inlineStr">
+      <c r="D6" s="33" t="inlineStr">
         <is>
           <t>08:45</t>
         </is>
       </c>
-      <c r="E6" s="25" t="inlineStr">
+      <c r="E6" s="34" t="inlineStr">
         <is>
           <t>등교</t>
         </is>
       </c>
-      <c r="F6" s="26" t="inlineStr">
+      <c r="F6" s="35" t="inlineStr">
         <is>
           <t>돌봄/픽업</t>
         </is>
       </c>
-      <c r="G6" s="25" t="inlineStr">
+      <c r="G6" s="34" t="inlineStr">
         <is>
           <t>집→학교</t>
         </is>
       </c>
-      <c r="H6" s="25" t="inlineStr"/>
+      <c r="H6" s="34" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="23" t="inlineStr">
+      <c r="A7" s="32" t="inlineStr">
         <is>
           <t>첫째</t>
         </is>
       </c>
-      <c r="B7" s="24" t="inlineStr">
+      <c r="B7" s="33" t="inlineStr">
         <is>
           <t>화</t>
         </is>
       </c>
-      <c r="C7" s="24" t="inlineStr">
+      <c r="C7" s="33" t="inlineStr">
         <is>
           <t>08:45</t>
         </is>
       </c>
-      <c r="D7" s="24" t="inlineStr">
+      <c r="D7" s="33" t="inlineStr">
         <is>
           <t>13:30</t>
         </is>
       </c>
-      <c r="E7" s="25" t="inlineStr">
+      <c r="E7" s="34" t="inlineStr">
         <is>
           <t>정규수업</t>
         </is>
       </c>
-      <c r="F7" s="27" t="inlineStr">
+      <c r="F7" s="36" t="inlineStr">
         <is>
           <t>정규수업</t>
         </is>
       </c>
-      <c r="G7" s="25" t="inlineStr">
+      <c r="G7" s="34" t="inlineStr">
         <is>
           <t>○○초</t>
         </is>
       </c>
-      <c r="H7" s="25" t="inlineStr"/>
+      <c r="H7" s="34" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="23" t="inlineStr">
+      <c r="A8" s="32" t="inlineStr">
         <is>
           <t>첫째</t>
         </is>
       </c>
-      <c r="B8" s="24" t="inlineStr">
+      <c r="B8" s="33" t="inlineStr">
         <is>
           <t>화</t>
         </is>
       </c>
-      <c r="C8" s="24" t="inlineStr">
+      <c r="C8" s="33" t="inlineStr">
         <is>
           <t>14:00</t>
         </is>
       </c>
-      <c r="D8" s="24" t="inlineStr">
+      <c r="D8" s="33" t="inlineStr">
         <is>
           <t>15:00</t>
         </is>
       </c>
-      <c r="E8" s="25" t="inlineStr">
+      <c r="E8" s="34" t="inlineStr">
         <is>
           <t>태권도</t>
         </is>
       </c>
-      <c r="F8" s="28" t="inlineStr">
+      <c r="F8" s="37" t="inlineStr">
         <is>
           <t>학원</t>
         </is>
       </c>
-      <c r="G8" s="25" t="inlineStr">
+      <c r="G8" s="34" t="inlineStr">
         <is>
           <t>태권도장</t>
         </is>
       </c>
-      <c r="H8" s="25" t="inlineStr"/>
+      <c r="H8" s="34" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="23" t="inlineStr">
+      <c r="A9" s="32" t="inlineStr">
         <is>
           <t>첫째</t>
         </is>
       </c>
-      <c r="B9" s="24" t="inlineStr">
+      <c r="B9" s="33" t="inlineStr">
         <is>
           <t>화</t>
         </is>
       </c>
-      <c r="C9" s="24" t="inlineStr">
+      <c r="C9" s="33" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="D9" s="24" t="inlineStr">
+      <c r="D9" s="33" t="inlineStr">
         <is>
           <t>16:30</t>
         </is>
       </c>
-      <c r="E9" s="25" t="inlineStr">
+      <c r="E9" s="34" t="inlineStr">
         <is>
           <t>피아노</t>
         </is>
       </c>
-      <c r="F9" s="28" t="inlineStr">
+      <c r="F9" s="37" t="inlineStr">
         <is>
           <t>학원</t>
         </is>
       </c>
-      <c r="G9" s="25" t="inlineStr">
+      <c r="G9" s="34" t="inlineStr">
         <is>
           <t>집 (과외)</t>
         </is>
       </c>
-      <c r="H9" s="25" t="inlineStr"/>
+      <c r="H9" s="34" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="23" t="inlineStr">
+      <c r="A10" s="32" t="inlineStr">
         <is>
           <t>첫째</t>
         </is>
       </c>
-      <c r="B10" s="24" t="inlineStr">
+      <c r="B10" s="33" t="inlineStr">
         <is>
           <t>수</t>
         </is>
       </c>
-      <c r="C10" s="24" t="inlineStr">
+      <c r="C10" s="33" t="inlineStr">
         <is>
           <t>08:20</t>
         </is>
       </c>
-      <c r="D10" s="24" t="inlineStr">
+      <c r="D10" s="33" t="inlineStr">
         <is>
           <t>08:45</t>
         </is>
       </c>
-      <c r="E10" s="25" t="inlineStr">
+      <c r="E10" s="34" t="inlineStr">
         <is>
           <t>등교</t>
         </is>
       </c>
-      <c r="F10" s="26" t="inlineStr">
+      <c r="F10" s="35" t="inlineStr">
         <is>
           <t>돌봄/픽업</t>
         </is>
       </c>
-      <c r="G10" s="25" t="inlineStr">
+      <c r="G10" s="34" t="inlineStr">
         <is>
           <t>집→학교</t>
         </is>
       </c>
-      <c r="H10" s="25" t="inlineStr"/>
+      <c r="H10" s="34" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="23" t="inlineStr">
+      <c r="A11" s="32" t="inlineStr">
         <is>
           <t>첫째</t>
         </is>
       </c>
-      <c r="B11" s="24" t="inlineStr">
+      <c r="B11" s="33" t="inlineStr">
         <is>
           <t>수</t>
         </is>
       </c>
-      <c r="C11" s="24" t="inlineStr">
+      <c r="C11" s="33" t="inlineStr">
         <is>
           <t>08:45</t>
         </is>
       </c>
-      <c r="D11" s="24" t="inlineStr">
+      <c r="D11" s="33" t="inlineStr">
         <is>
           <t>12:50</t>
         </is>
       </c>
-      <c r="E11" s="25" t="inlineStr">
+      <c r="E11" s="34" t="inlineStr">
         <is>
           <t>정규수업(단축)</t>
         </is>
       </c>
-      <c r="F11" s="27" t="inlineStr">
+      <c r="F11" s="36" t="inlineStr">
         <is>
           <t>정규수업</t>
         </is>
       </c>
-      <c r="G11" s="25" t="inlineStr">
+      <c r="G11" s="34" t="inlineStr">
         <is>
           <t>○○초</t>
         </is>
       </c>
-      <c r="H11" s="25" t="inlineStr"/>
+      <c r="H11" s="34" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="23" t="inlineStr">
+      <c r="A12" s="32" t="inlineStr">
         <is>
           <t>첫째</t>
         </is>
       </c>
-      <c r="B12" s="24" t="inlineStr">
+      <c r="B12" s="33" t="inlineStr">
         <is>
           <t>목</t>
         </is>
       </c>
-      <c r="C12" s="24" t="inlineStr">
+      <c r="C12" s="33" t="inlineStr">
         <is>
           <t>08:20</t>
         </is>
       </c>
-      <c r="D12" s="24" t="inlineStr">
+      <c r="D12" s="33" t="inlineStr">
         <is>
           <t>08:45</t>
         </is>
       </c>
-      <c r="E12" s="25" t="inlineStr">
+      <c r="E12" s="34" t="inlineStr">
         <is>
           <t>등교</t>
         </is>
       </c>
-      <c r="F12" s="26" t="inlineStr">
+      <c r="F12" s="35" t="inlineStr">
         <is>
           <t>돌봄/픽업</t>
         </is>
       </c>
-      <c r="G12" s="25" t="inlineStr">
+      <c r="G12" s="34" t="inlineStr">
         <is>
           <t>집→학교</t>
         </is>
       </c>
-      <c r="H12" s="25" t="inlineStr"/>
+      <c r="H12" s="34" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="23" t="inlineStr">
+      <c r="A13" s="32" t="inlineStr">
         <is>
           <t>첫째</t>
         </is>
       </c>
-      <c r="B13" s="24" t="inlineStr">
+      <c r="B13" s="33" t="inlineStr">
         <is>
           <t>목</t>
         </is>
       </c>
-      <c r="C13" s="24" t="inlineStr">
+      <c r="C13" s="33" t="inlineStr">
         <is>
           <t>08:45</t>
         </is>
       </c>
-      <c r="D13" s="24" t="inlineStr">
+      <c r="D13" s="33" t="inlineStr">
         <is>
           <t>13:30</t>
         </is>
       </c>
-      <c r="E13" s="25" t="inlineStr">
+      <c r="E13" s="34" t="inlineStr">
         <is>
           <t>정규수업</t>
         </is>
       </c>
-      <c r="F13" s="27" t="inlineStr">
+      <c r="F13" s="36" t="inlineStr">
         <is>
           <t>정규수업</t>
         </is>
       </c>
-      <c r="G13" s="25" t="inlineStr">
+      <c r="G13" s="34" t="inlineStr">
         <is>
           <t>○○초</t>
         </is>
       </c>
-      <c r="H13" s="25" t="inlineStr"/>
+      <c r="H13" s="34" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="23" t="inlineStr">
+      <c r="A14" s="32" t="inlineStr">
         <is>
           <t>첫째</t>
         </is>
       </c>
-      <c r="B14" s="24" t="inlineStr">
+      <c r="B14" s="33" t="inlineStr">
         <is>
           <t>목</t>
         </is>
       </c>
-      <c r="C14" s="24" t="inlineStr">
+      <c r="C14" s="33" t="inlineStr">
         <is>
           <t>13:40</t>
         </is>
       </c>
-      <c r="D14" s="24" t="inlineStr">
+      <c r="D14" s="33" t="inlineStr">
         <is>
           <t>15:10</t>
         </is>
       </c>
-      <c r="E14" s="25" t="inlineStr">
+      <c r="E14" s="34" t="inlineStr">
         <is>
           <t>방과후 큐보로봇</t>
         </is>
       </c>
-      <c r="F14" s="29" t="inlineStr">
+      <c r="F14" s="38" t="inlineStr">
         <is>
           <t>방과후</t>
         </is>
       </c>
-      <c r="G14" s="25" t="inlineStr">
+      <c r="G14" s="34" t="inlineStr">
         <is>
           <t>학교</t>
         </is>
       </c>
-      <c r="H14" s="25" t="inlineStr"/>
+      <c r="H14" s="34" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="23" t="inlineStr">
+      <c r="A15" s="32" t="inlineStr">
         <is>
           <t>첫째</t>
         </is>
       </c>
-      <c r="B15" s="24" t="inlineStr">
+      <c r="B15" s="33" t="inlineStr">
         <is>
           <t>목</t>
         </is>
       </c>
-      <c r="C15" s="24" t="inlineStr">
+      <c r="C15" s="33" t="inlineStr">
         <is>
           <t>17:10</t>
         </is>
       </c>
-      <c r="D15" s="24" t="inlineStr">
+      <c r="D15" s="33" t="inlineStr">
         <is>
           <t>18:10</t>
         </is>
       </c>
-      <c r="E15" s="25" t="inlineStr">
+      <c r="E15" s="34" t="inlineStr">
         <is>
           <t>영어수업</t>
         </is>
       </c>
-      <c r="F15" s="28" t="inlineStr">
+      <c r="F15" s="37" t="inlineStr">
         <is>
           <t>학원</t>
         </is>
       </c>
-      <c r="G15" s="25" t="inlineStr">
+      <c r="G15" s="34" t="inlineStr">
         <is>
           <t>집 (과외)</t>
         </is>
       </c>
-      <c r="H15" s="25" t="inlineStr"/>
+      <c r="H15" s="34" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="23" t="inlineStr">
+      <c r="A16" s="32" t="inlineStr">
         <is>
           <t>첫째</t>
         </is>
       </c>
-      <c r="B16" s="24" t="inlineStr">
+      <c r="B16" s="33" t="inlineStr">
         <is>
           <t>금</t>
         </is>
       </c>
-      <c r="C16" s="24" t="inlineStr">
+      <c r="C16" s="33" t="inlineStr">
         <is>
           <t>08:20</t>
         </is>
       </c>
-      <c r="D16" s="24" t="inlineStr">
+      <c r="D16" s="33" t="inlineStr">
         <is>
           <t>08:45</t>
         </is>
       </c>
-      <c r="E16" s="25" t="inlineStr">
+      <c r="E16" s="34" t="inlineStr">
         <is>
           <t>등교</t>
         </is>
       </c>
-      <c r="F16" s="26" t="inlineStr">
+      <c r="F16" s="35" t="inlineStr">
         <is>
           <t>돌봄/픽업</t>
         </is>
       </c>
-      <c r="G16" s="25" t="inlineStr">
+      <c r="G16" s="34" t="inlineStr">
         <is>
           <t>집→학교</t>
         </is>
       </c>
-      <c r="H16" s="25" t="inlineStr"/>
+      <c r="H16" s="34" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="23" t="inlineStr">
+      <c r="A17" s="32" t="inlineStr">
         <is>
           <t>첫째</t>
         </is>
       </c>
-      <c r="B17" s="24" t="inlineStr">
+      <c r="B17" s="33" t="inlineStr">
         <is>
           <t>금</t>
         </is>
       </c>
-      <c r="C17" s="24" t="inlineStr">
+      <c r="C17" s="33" t="inlineStr">
         <is>
           <t>08:45</t>
         </is>
       </c>
-      <c r="D17" s="24" t="inlineStr">
+      <c r="D17" s="33" t="inlineStr">
         <is>
           <t>12:50</t>
         </is>
       </c>
-      <c r="E17" s="25" t="inlineStr">
+      <c r="E17" s="34" t="inlineStr">
         <is>
           <t>정규수업(단축)</t>
         </is>
       </c>
-      <c r="F17" s="27" t="inlineStr">
+      <c r="F17" s="36" t="inlineStr">
         <is>
           <t>정규수업</t>
         </is>
       </c>
-      <c r="G17" s="25" t="inlineStr">
+      <c r="G17" s="34" t="inlineStr">
         <is>
           <t>○○초</t>
         </is>
       </c>
-      <c r="H17" s="25" t="inlineStr"/>
+      <c r="H17" s="34" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="23" t="inlineStr">
+      <c r="A18" s="32" t="inlineStr">
         <is>
           <t>첫째</t>
         </is>
       </c>
-      <c r="B18" s="24" t="inlineStr">
+      <c r="B18" s="33" t="inlineStr">
         <is>
           <t>금</t>
         </is>
       </c>
-      <c r="C18" s="24" t="inlineStr">
+      <c r="C18" s="33" t="inlineStr">
         <is>
           <t>12:50</t>
         </is>
       </c>
-      <c r="D18" s="24" t="inlineStr">
+      <c r="D18" s="33" t="inlineStr">
         <is>
           <t>14:20</t>
         </is>
       </c>
-      <c r="E18" s="25" t="inlineStr">
+      <c r="E18" s="34" t="inlineStr">
         <is>
           <t>맞춤형 종이접기</t>
         </is>
       </c>
-      <c r="F18" s="29" t="inlineStr">
+      <c r="F18" s="38" t="inlineStr">
         <is>
           <t>방과후</t>
         </is>
       </c>
-      <c r="G18" s="25" t="inlineStr">
+      <c r="G18" s="34" t="inlineStr">
         <is>
           <t>학교</t>
         </is>
       </c>
-      <c r="H18" s="25" t="inlineStr">
+      <c r="H18" s="34" t="inlineStr">
         <is>
           <t>무료</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="23" t="inlineStr">
+      <c r="A19" s="32" t="inlineStr">
         <is>
           <t>첫째</t>
         </is>
       </c>
-      <c r="B19" s="24" t="inlineStr">
+      <c r="B19" s="33" t="inlineStr">
         <is>
           <t>금</t>
         </is>
       </c>
-      <c r="C19" s="24" t="inlineStr">
+      <c r="C19" s="33" t="inlineStr">
         <is>
           <t>14:40</t>
         </is>
       </c>
-      <c r="D19" s="24" t="inlineStr">
+      <c r="D19" s="33" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="E19" s="25" t="inlineStr">
+      <c r="E19" s="34" t="inlineStr">
         <is>
           <t>미술학원</t>
         </is>
       </c>
-      <c r="F19" s="28" t="inlineStr">
+      <c r="F19" s="37" t="inlineStr">
         <is>
           <t>학원</t>
         </is>
       </c>
-      <c r="G19" s="25" t="inlineStr">
+      <c r="G19" s="34" t="inlineStr">
         <is>
           <t>봉쁘앙 미술학원</t>
         </is>
       </c>
-      <c r="H19" s="25" t="inlineStr"/>
+      <c r="H19" s="34" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="23" t="inlineStr">
+      <c r="A20" s="32" t="inlineStr">
         <is>
           <t>첫째</t>
         </is>
       </c>
-      <c r="B20" s="24" t="inlineStr">
+      <c r="B20" s="33" t="inlineStr">
         <is>
           <t>금</t>
         </is>
       </c>
-      <c r="C20" s="24" t="inlineStr">
+      <c r="C20" s="33" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="D20" s="24" t="inlineStr">
+      <c r="D20" s="33" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="E20" s="25" t="inlineStr">
+      <c r="E20" s="34" t="inlineStr">
         <is>
           <t>태권도</t>
         </is>
       </c>
-      <c r="F20" s="28" t="inlineStr">
+      <c r="F20" s="37" t="inlineStr">
         <is>
           <t>학원</t>
         </is>
       </c>
-      <c r="G20" s="25" t="inlineStr">
+      <c r="G20" s="34" t="inlineStr">
         <is>
           <t>태권도장</t>
         </is>
       </c>
-      <c r="H20" s="25" t="inlineStr">
+      <c r="H20" s="34" t="inlineStr">
         <is>
           <t>둘째와 함께 · 이모님 픽업</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="30" t="inlineStr">
+      <c r="A21" s="39" t="inlineStr">
         <is>
           <t>둘째</t>
         </is>
       </c>
-      <c r="B21" s="24" t="inlineStr">
+      <c r="B21" s="33" t="inlineStr">
         <is>
           <t>월</t>
         </is>
       </c>
-      <c r="C21" s="24" t="inlineStr">
+      <c r="C21" s="33" t="inlineStr">
         <is>
           <t>09:10</t>
         </is>
       </c>
-      <c r="D21" s="24" t="inlineStr">
+      <c r="D21" s="33" t="inlineStr">
         <is>
           <t>15:10</t>
         </is>
       </c>
-      <c r="E21" s="25" t="inlineStr">
+      <c r="E21" s="34" t="inlineStr">
         <is>
           <t>유치원</t>
         </is>
       </c>
-      <c r="F21" s="27" t="inlineStr">
+      <c r="F21" s="36" t="inlineStr">
         <is>
           <t>정규수업</t>
         </is>
       </c>
-      <c r="G21" s="25" t="inlineStr">
+      <c r="G21" s="34" t="inlineStr">
         <is>
           <t>유치원</t>
         </is>
       </c>
-      <c r="H21" s="25" t="inlineStr"/>
+      <c r="H21" s="34" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="30" t="inlineStr">
+      <c r="A22" s="39" t="inlineStr">
         <is>
           <t>둘째</t>
         </is>
       </c>
-      <c r="B22" s="24" t="inlineStr">
+      <c r="B22" s="33" t="inlineStr">
         <is>
           <t>월</t>
         </is>
       </c>
-      <c r="C22" s="24" t="inlineStr">
+      <c r="C22" s="33" t="inlineStr">
         <is>
           <t>16:20</t>
         </is>
       </c>
-      <c r="D22" s="24" t="inlineStr">
+      <c r="D22" s="33" t="inlineStr">
         <is>
           <t>16:50</t>
         </is>
       </c>
-      <c r="E22" s="25" t="inlineStr">
+      <c r="E22" s="34" t="inlineStr">
         <is>
           <t>한글수업</t>
         </is>
       </c>
-      <c r="F22" s="28" t="inlineStr">
+      <c r="F22" s="37" t="inlineStr">
         <is>
           <t>학원</t>
         </is>
       </c>
-      <c r="G22" s="25" t="inlineStr">
+      <c r="G22" s="34" t="inlineStr">
         <is>
           <t>집 (과외)</t>
         </is>
       </c>
-      <c r="H22" s="25" t="inlineStr"/>
+      <c r="H22" s="34" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="30" t="inlineStr">
+      <c r="A23" s="39" t="inlineStr">
         <is>
           <t>둘째</t>
         </is>
       </c>
-      <c r="B23" s="24" t="inlineStr">
+      <c r="B23" s="33" t="inlineStr">
         <is>
           <t>화</t>
         </is>
       </c>
-      <c r="C23" s="24" t="inlineStr">
+      <c r="C23" s="33" t="inlineStr">
         <is>
           <t>09:10</t>
         </is>
       </c>
-      <c r="D23" s="24" t="inlineStr">
+      <c r="D23" s="33" t="inlineStr">
         <is>
           <t>15:10</t>
         </is>
       </c>
-      <c r="E23" s="25" t="inlineStr">
+      <c r="E23" s="34" t="inlineStr">
         <is>
           <t>유치원</t>
         </is>
       </c>
-      <c r="F23" s="27" t="inlineStr">
+      <c r="F23" s="36" t="inlineStr">
         <is>
           <t>정규수업</t>
         </is>
       </c>
-      <c r="G23" s="25" t="inlineStr">
+      <c r="G23" s="34" t="inlineStr">
         <is>
           <t>유치원</t>
         </is>
       </c>
-      <c r="H23" s="25" t="inlineStr"/>
+      <c r="H23" s="34" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="30" t="inlineStr">
+      <c r="A24" s="39" t="inlineStr">
         <is>
           <t>둘째</t>
         </is>
       </c>
-      <c r="B24" s="24" t="inlineStr">
+      <c r="B24" s="33" t="inlineStr">
         <is>
           <t>수</t>
         </is>
       </c>
-      <c r="C24" s="24" t="inlineStr">
+      <c r="C24" s="33" t="inlineStr">
         <is>
           <t>09:10</t>
         </is>
       </c>
-      <c r="D24" s="24" t="inlineStr">
+      <c r="D24" s="33" t="inlineStr">
         <is>
           <t>15:10</t>
         </is>
       </c>
-      <c r="E24" s="25" t="inlineStr">
+      <c r="E24" s="34" t="inlineStr">
         <is>
           <t>유치원</t>
         </is>
       </c>
-      <c r="F24" s="27" t="inlineStr">
+      <c r="F24" s="36" t="inlineStr">
         <is>
           <t>정규수업</t>
         </is>
       </c>
-      <c r="G24" s="25" t="inlineStr">
+      <c r="G24" s="34" t="inlineStr">
         <is>
           <t>유치원</t>
         </is>
       </c>
-      <c r="H24" s="25" t="inlineStr"/>
+      <c r="H24" s="34" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="30" t="inlineStr">
+      <c r="A25" s="39" t="inlineStr">
         <is>
           <t>둘째</t>
         </is>
       </c>
-      <c r="B25" s="24" t="inlineStr">
+      <c r="B25" s="33" t="inlineStr">
         <is>
           <t>수</t>
         </is>
       </c>
-      <c r="C25" s="24" t="inlineStr">
+      <c r="C25" s="33" t="inlineStr">
         <is>
           <t>16:10</t>
         </is>
       </c>
-      <c r="D25" s="24" t="inlineStr">
+      <c r="D25" s="33" t="inlineStr">
         <is>
           <t>16:40</t>
         </is>
       </c>
-      <c r="E25" s="25" t="inlineStr">
+      <c r="E25" s="34" t="inlineStr">
         <is>
           <t>한글수업</t>
         </is>
       </c>
-      <c r="F25" s="28" t="inlineStr">
+      <c r="F25" s="37" t="inlineStr">
         <is>
           <t>학원</t>
         </is>
       </c>
-      <c r="G25" s="25" t="inlineStr">
+      <c r="G25" s="34" t="inlineStr">
         <is>
           <t>집 (과외)</t>
         </is>
       </c>
-      <c r="H25" s="25" t="inlineStr"/>
+      <c r="H25" s="34" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="30" t="inlineStr">
+      <c r="A26" s="39" t="inlineStr">
         <is>
           <t>둘째</t>
         </is>
       </c>
-      <c r="B26" s="24" t="inlineStr">
+      <c r="B26" s="33" t="inlineStr">
         <is>
           <t>목</t>
         </is>
       </c>
-      <c r="C26" s="24" t="inlineStr">
+      <c r="C26" s="33" t="inlineStr">
         <is>
           <t>09:10</t>
         </is>
       </c>
-      <c r="D26" s="24" t="inlineStr">
+      <c r="D26" s="33" t="inlineStr">
         <is>
           <t>15:10</t>
         </is>
       </c>
-      <c r="E26" s="25" t="inlineStr">
+      <c r="E26" s="34" t="inlineStr">
         <is>
           <t>유치원</t>
         </is>
       </c>
-      <c r="F26" s="27" t="inlineStr">
+      <c r="F26" s="36" t="inlineStr">
         <is>
           <t>정규수업</t>
         </is>
       </c>
-      <c r="G26" s="25" t="inlineStr">
+      <c r="G26" s="34" t="inlineStr">
         <is>
           <t>유치원</t>
         </is>
       </c>
-      <c r="H26" s="25" t="inlineStr"/>
+      <c r="H26" s="34" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="30" t="inlineStr">
+      <c r="A27" s="39" t="inlineStr">
         <is>
           <t>둘째</t>
         </is>
       </c>
-      <c r="B27" s="24" t="inlineStr">
+      <c r="B27" s="33" t="inlineStr">
         <is>
           <t>금</t>
         </is>
       </c>
-      <c r="C27" s="24" t="inlineStr">
+      <c r="C27" s="33" t="inlineStr">
         <is>
           <t>09:10</t>
         </is>
       </c>
-      <c r="D27" s="24" t="inlineStr">
+      <c r="D27" s="33" t="inlineStr">
         <is>
           <t>15:10</t>
         </is>
       </c>
-      <c r="E27" s="25" t="inlineStr">
+      <c r="E27" s="34" t="inlineStr">
         <is>
           <t>유치원</t>
         </is>
       </c>
-      <c r="F27" s="27" t="inlineStr">
+      <c r="F27" s="36" t="inlineStr">
         <is>
           <t>정규수업</t>
         </is>
       </c>
-      <c r="G27" s="25" t="inlineStr">
+      <c r="G27" s="34" t="inlineStr">
         <is>
           <t>유치원</t>
         </is>
       </c>
-      <c r="H27" s="25" t="inlineStr">
+      <c r="H27" s="34" t="inlineStr">
         <is>
           <t>하원 시간 늘림</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="30" t="inlineStr">
+      <c r="A28" s="39" t="inlineStr">
         <is>
           <t>둘째</t>
         </is>
       </c>
-      <c r="B28" s="24" t="inlineStr">
+      <c r="B28" s="33" t="inlineStr">
         <is>
           <t>금</t>
         </is>
       </c>
-      <c r="C28" s="24" t="inlineStr">
+      <c r="C28" s="33" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="D28" s="24" t="inlineStr">
+      <c r="D28" s="33" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="E28" s="25" t="inlineStr">
+      <c r="E28" s="34" t="inlineStr">
         <is>
           <t>태권도</t>
         </is>
       </c>
-      <c r="F28" s="28" t="inlineStr">
+      <c r="F28" s="37" t="inlineStr">
         <is>
           <t>학원</t>
         </is>
       </c>
-      <c r="G28" s="25" t="inlineStr">
+      <c r="G28" s="34" t="inlineStr">
         <is>
           <t>태권도장</t>
         </is>
       </c>
-      <c r="H28" s="25" t="inlineStr">
+      <c r="H28" s="34" t="inlineStr">
         <is>
           <t>첫째와 함께 · 이모님 픽업</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="23" t="inlineStr">
+      <c r="A29" s="32" t="inlineStr">
         <is>
           <t>첫째</t>
         </is>
       </c>
-      <c r="B29" s="24" t="inlineStr">
+      <c r="B29" s="33" t="inlineStr">
         <is>
           <t>수</t>
         </is>
       </c>
-      <c r="C29" s="24" t="inlineStr">
+      <c r="C29" s="33" t="inlineStr">
         <is>
           <t>19:30</t>
         </is>
       </c>
-      <c r="D29" s="24" t="inlineStr">
+      <c r="D29" s="33" t="inlineStr">
         <is>
           <t>20:10</t>
         </is>
       </c>
-      <c r="E29" s="25" t="inlineStr">
+      <c r="E29" s="34" t="inlineStr">
         <is>
           <t>첼로</t>
         </is>
       </c>
-      <c r="F29" s="28" t="inlineStr">
+      <c r="F29" s="37" t="inlineStr">
         <is>
           <t>학원</t>
         </is>
       </c>
-      <c r="G29" s="25" t="inlineStr">
+      <c r="G29" s="34" t="inlineStr">
         <is>
           <t>보스턴음악학원</t>
         </is>
       </c>
-      <c r="H29" s="25" t="inlineStr"/>
+      <c r="H29" s="34" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="23" t="inlineStr">
+      <c r="A30" s="32" t="inlineStr">
         <is>
           <t>첫째</t>
         </is>
       </c>
-      <c r="B30" s="24" t="inlineStr">
+      <c r="B30" s="33" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C30" s="24" t="inlineStr">
+      <c r="C30" s="33" t="inlineStr">
         <is>
           <t>16:10</t>
         </is>
       </c>
-      <c r="D30" s="24" t="inlineStr">
+      <c r="D30" s="33" t="inlineStr">
         <is>
           <t>17:10</t>
         </is>
       </c>
-      <c r="E30" s="25" t="inlineStr">
+      <c r="E30" s="34" t="inlineStr">
         <is>
           <t>수영</t>
         </is>
       </c>
-      <c r="F30" s="28" t="inlineStr">
+      <c r="F30" s="37" t="inlineStr">
         <is>
           <t>학원</t>
         </is>
       </c>
-      <c r="G30" s="25" t="inlineStr">
+      <c r="G30" s="34" t="inlineStr">
         <is>
           <t>수영장</t>
         </is>
       </c>
-      <c r="H30" s="25" t="inlineStr"/>
+      <c r="H30" s="34" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="23" t="inlineStr">
+      <c r="A31" s="32" t="inlineStr">
         <is>
           <t>첫째</t>
         </is>
       </c>
-      <c r="B31" s="24" t="inlineStr">
+      <c r="B31" s="33" t="inlineStr">
         <is>
           <t>화</t>
         </is>
       </c>
-      <c r="C31" s="24" t="inlineStr">
+      <c r="C31" s="33" t="inlineStr">
         <is>
           <t>19:00</t>
         </is>
       </c>
-      <c r="D31" s="24" t="inlineStr">
+      <c r="D31" s="33" t="inlineStr">
         <is>
           <t>19:30</t>
         </is>
       </c>
-      <c r="E31" s="25" t="inlineStr">
+      <c r="E31" s="34" t="inlineStr">
         <is>
           <t>화상영어</t>
         </is>
       </c>
-      <c r="F31" s="28" t="inlineStr">
+      <c r="F31" s="37" t="inlineStr">
         <is>
           <t>학원</t>
         </is>
       </c>
-      <c r="G31" s="25" t="inlineStr">
+      <c r="G31" s="34" t="inlineStr">
         <is>
           <t>온라인</t>
         </is>
       </c>
-      <c r="H31" s="25" t="inlineStr"/>
+      <c r="H31" s="34" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="23" t="inlineStr">
+      <c r="A32" s="32" t="inlineStr">
         <is>
           <t>첫째</t>
         </is>
       </c>
-      <c r="B32" s="24" t="inlineStr">
+      <c r="B32" s="33" t="inlineStr">
         <is>
           <t>금</t>
         </is>
       </c>
-      <c r="C32" s="24" t="inlineStr">
+      <c r="C32" s="33" t="inlineStr">
         <is>
           <t>19:00</t>
         </is>
       </c>
-      <c r="D32" s="24" t="inlineStr">
+      <c r="D32" s="33" t="inlineStr">
         <is>
           <t>19:30</t>
         </is>
       </c>
-      <c r="E32" s="25" t="inlineStr">
+      <c r="E32" s="34" t="inlineStr">
         <is>
           <t>화상영어</t>
         </is>
       </c>
-      <c r="F32" s="28" t="inlineStr">
+      <c r="F32" s="37" t="inlineStr">
         <is>
           <t>학원</t>
         </is>
       </c>
-      <c r="G32" s="25" t="inlineStr">
+      <c r="G32" s="34" t="inlineStr">
         <is>
           <t>온라인</t>
         </is>
       </c>
-      <c r="H32" s="25" t="inlineStr"/>
+      <c r="H32" s="34" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="30" t="inlineStr">
+      <c r="A33" s="39" t="inlineStr">
         <is>
           <t>둘째</t>
         </is>
       </c>
-      <c r="B33" s="24" t="inlineStr">
+      <c r="B33" s="33" t="inlineStr">
         <is>
           <t>수</t>
         </is>
       </c>
-      <c r="C33" s="24" t="inlineStr">
+      <c r="C33" s="33" t="inlineStr">
         <is>
           <t>19:30</t>
         </is>
       </c>
-      <c r="D33" s="24" t="inlineStr">
+      <c r="D33" s="33" t="inlineStr">
         <is>
           <t>20:00</t>
         </is>
       </c>
-      <c r="E33" s="25" t="inlineStr">
+      <c r="E33" s="34" t="inlineStr">
         <is>
           <t>축구</t>
         </is>
       </c>
-      <c r="F33" s="28" t="inlineStr">
+      <c r="F33" s="37" t="inlineStr">
         <is>
           <t>학원</t>
         </is>
       </c>
-      <c r="G33" s="25" t="inlineStr">
+      <c r="G33" s="34" t="inlineStr">
         <is>
           <t>축구교실</t>
         </is>
       </c>
-      <c r="H33" s="25" t="inlineStr">
+      <c r="H33" s="34" t="inlineStr">
         <is>
           <t>추정 / ※ 종료시간 추정</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="23" t="inlineStr">
+      <c r="A34" s="32" t="inlineStr">
         <is>
           <t>첫째</t>
         </is>
       </c>
-      <c r="B34" s="24" t="inlineStr">
+      <c r="B34" s="33" t="inlineStr">
         <is>
           <t>수</t>
         </is>
       </c>
-      <c r="C34" s="24" t="inlineStr">
+      <c r="C34" s="33" t="inlineStr">
         <is>
           <t>16:50</t>
         </is>
       </c>
-      <c r="D34" s="24" t="inlineStr">
+      <c r="D34" s="33" t="inlineStr">
         <is>
           <t>17:40</t>
         </is>
       </c>
-      <c r="E34" s="25" t="inlineStr">
+      <c r="E34" s="34" t="inlineStr">
         <is>
           <t>한글수업</t>
         </is>
       </c>
-      <c r="F34" s="28" t="inlineStr">
+      <c r="F34" s="37" t="inlineStr">
         <is>
           <t>학원</t>
         </is>
       </c>
-      <c r="G34" s="25" t="inlineStr">
+      <c r="G34" s="34" t="inlineStr">
         <is>
           <t>집 (과외)</t>
         </is>
       </c>
-      <c r="H34" s="25" t="inlineStr">
+      <c r="H34" s="34" t="inlineStr">
         <is>
           <t>추정 / ※ 종료시간 추정</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="23" t="inlineStr">
+      <c r="A35" s="32" t="inlineStr">
         <is>
           <t>첫째</t>
         </is>
       </c>
-      <c r="B35" s="24" t="inlineStr">
+      <c r="B35" s="33" t="inlineStr">
         <is>
           <t>수</t>
         </is>
       </c>
-      <c r="C35" s="24" t="inlineStr">
+      <c r="C35" s="33" t="inlineStr">
         <is>
           <t>12:50</t>
         </is>
       </c>
-      <c r="D35" s="24" t="inlineStr">
+      <c r="D35" s="33" t="inlineStr">
         <is>
           <t>14:20</t>
         </is>
       </c>
-      <c r="E35" s="25" t="inlineStr">
+      <c r="E35" s="34" t="inlineStr">
         <is>
           <t>방과후 아나운서</t>
         </is>
       </c>
-      <c r="F35" s="29" t="inlineStr">
+      <c r="F35" s="38" t="inlineStr">
         <is>
           <t>방과후</t>
         </is>
       </c>
-      <c r="G35" s="25" t="inlineStr">
+      <c r="G35" s="34" t="inlineStr">
         <is>
           <t>학교</t>
         </is>
       </c>
-      <c r="H35" s="25" t="inlineStr"/>
+      <c r="H35" s="34" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="23" t="inlineStr">
+      <c r="A36" s="32" t="inlineStr">
         <is>
           <t>첫째</t>
         </is>
       </c>
-      <c r="B36" s="24" t="inlineStr">
+      <c r="B36" s="33" t="inlineStr">
         <is>
           <t>월</t>
         </is>
       </c>
-      <c r="C36" s="24" t="inlineStr">
+      <c r="C36" s="33" t="inlineStr">
         <is>
           <t>14:00</t>
         </is>
       </c>
-      <c r="D36" s="24" t="inlineStr">
+      <c r="D36" s="33" t="inlineStr">
         <is>
           <t>15:00</t>
         </is>
       </c>
-      <c r="E36" s="25" t="inlineStr">
+      <c r="E36" s="34" t="inlineStr">
         <is>
           <t>태권도</t>
         </is>
       </c>
-      <c r="F36" s="28" t="inlineStr">
+      <c r="F36" s="37" t="inlineStr">
         <is>
           <t>학원</t>
         </is>
       </c>
-      <c r="G36" s="25" t="inlineStr">
+      <c r="G36" s="34" t="inlineStr">
         <is>
           <t>태권도장</t>
         </is>
       </c>
-      <c r="H36" s="25" t="inlineStr"/>
+      <c r="H36" s="34" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="30" t="inlineStr">
+      <c r="A37" s="39" t="inlineStr">
         <is>
           <t>둘째</t>
         </is>
       </c>
-      <c r="B37" s="24" t="inlineStr">
+      <c r="B37" s="33" t="inlineStr">
         <is>
           <t>목</t>
         </is>
       </c>
-      <c r="C37" s="24" t="inlineStr">
+      <c r="C37" s="33" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="D37" s="24" t="inlineStr">
+      <c r="D37" s="33" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="E37" s="25" t="inlineStr">
+      <c r="E37" s="34" t="inlineStr">
         <is>
           <t>태권도</t>
         </is>
       </c>
-      <c r="F37" s="28" t="inlineStr">
+      <c r="F37" s="37" t="inlineStr">
         <is>
           <t>학원</t>
         </is>
       </c>
-      <c r="G37" s="25" t="inlineStr">
+      <c r="G37" s="34" t="inlineStr">
         <is>
           <t>태권도장</t>
         </is>
       </c>
-      <c r="H37" s="25" t="inlineStr"/>
+      <c r="H37" s="34" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/시간표.xlsx
+++ b/시간표.xlsx
@@ -24,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="26">
+  <fonts count="29">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -129,26 +129,43 @@
     <font>
       <name val="맑은 고딕"/>
       <b val="1"/>
+      <color rgb="00555555"/>
+      <sz val="6.5"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="00555555"/>
+      <sz val="6.5"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
       <color rgb="007A5E00"/>
-      <sz val="8"/>
+      <sz val="6.5"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
       <b val="1"/>
       <color rgb="001F4E79"/>
-      <sz val="8"/>
+      <sz val="7.5"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
       <b val="1"/>
       <color rgb="009C4A16"/>
-      <sz val="8"/>
+      <sz val="7.5"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="009C4A16"/>
+      <sz val="6.5"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
       <b val="1"/>
       <color rgb="002E6B1F"/>
-      <sz val="8"/>
+      <sz val="7.5"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
@@ -375,7 +392,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -438,44 +455,53 @@
     <xf numFmtId="0" fontId="17" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="26" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="26" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="26" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1444,8 +1470,8 @@
       <c r="D38" s="12" t="inlineStr">
         <is>
           <t>한글수업
-16:50–17:40*
-추정</t>
+16:50–17:40
+집 (과외)</t>
         </is>
       </c>
       <c r="E38" s="5" t="n"/>
@@ -1714,7 +1740,7 @@
     <mergeCell ref="F29:F34"/>
   </mergeCells>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="1" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -2496,7 +2522,7 @@
     <mergeCell ref="B36:B38"/>
   </mergeCells>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="1" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -2509,31 +2535,31 @@
   <dimension ref="A1:O53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="9.5" customWidth="1" min="2" max="2"/>
-    <col width="9.5" customWidth="1" min="3" max="3"/>
-    <col width="9.5" customWidth="1" min="4" max="4"/>
-    <col width="9.5" customWidth="1" min="5" max="5"/>
-    <col width="9.5" customWidth="1" min="6" max="6"/>
-    <col width="9.5" customWidth="1" min="7" max="7"/>
-    <col width="9.5" customWidth="1" min="8" max="8"/>
-    <col width="9.5" customWidth="1" min="9" max="9"/>
-    <col width="9.5" customWidth="1" min="10" max="10"/>
-    <col width="9.5" customWidth="1" min="11" max="11"/>
-    <col width="9.5" customWidth="1" min="12" max="12"/>
-    <col width="9.5" customWidth="1" min="13" max="13"/>
-    <col width="9.5" customWidth="1" min="14" max="14"/>
-    <col width="9.5" customWidth="1" min="15" max="15"/>
+    <col width="5.5" customWidth="1" min="1" max="1"/>
+    <col width="9.800000000000001" customWidth="1" min="2" max="2"/>
+    <col width="9.800000000000001" customWidth="1" min="3" max="3"/>
+    <col width="9.800000000000001" customWidth="1" min="4" max="4"/>
+    <col width="9.800000000000001" customWidth="1" min="5" max="5"/>
+    <col width="9.800000000000001" customWidth="1" min="6" max="6"/>
+    <col width="9.800000000000001" customWidth="1" min="7" max="7"/>
+    <col width="9.800000000000001" customWidth="1" min="8" max="8"/>
+    <col width="9.800000000000001" customWidth="1" min="9" max="9"/>
+    <col width="9.800000000000001" customWidth="1" min="10" max="10"/>
+    <col width="9.800000000000001" customWidth="1" min="11" max="11"/>
+    <col width="9.800000000000001" customWidth="1" min="12" max="12"/>
+    <col width="9.800000000000001" customWidth="1" min="13" max="13"/>
+    <col width="9.800000000000001" customWidth="1" min="14" max="14"/>
+    <col width="9.800000000000001" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
+    <row r="1" ht="22" customHeight="1">
       <c r="A1" s="21" t="inlineStr">
         <is>
           <t>두 아이 주간 시간표  (서원 · 서준)</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="18" customHeight="1">
+    <row r="2" ht="15" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>시간</t>
@@ -2582,7 +2608,7 @@
       </c>
       <c r="O2" s="22" t="n"/>
     </row>
-    <row r="3" ht="15" customHeight="1">
+    <row r="3" ht="13" customHeight="1">
       <c r="A3" s="23" t="n"/>
       <c r="B3" s="24" t="inlineStr">
         <is>
@@ -2655,8 +2681,8 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+    <row r="4" ht="11.5" customHeight="1">
+      <c r="A4" s="26" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
@@ -2676,40 +2702,40 @@
       <c r="N4" s="5" t="n"/>
       <c r="O4" s="5" t="n"/>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="6" t="inlineStr"/>
-      <c r="B5" s="26" t="inlineStr">
+    <row r="5" ht="11.5" customHeight="1">
+      <c r="A5" s="27" t="inlineStr"/>
+      <c r="B5" s="28" t="inlineStr">
         <is>
           <t>등교
-08:20</t>
+08:20–08:45</t>
         </is>
       </c>
       <c r="C5" s="5" t="n"/>
-      <c r="D5" s="26" t="inlineStr">
+      <c r="D5" s="28" t="inlineStr">
         <is>
           <t>등교
-08:20</t>
+08:20–08:45</t>
         </is>
       </c>
       <c r="E5" s="5" t="n"/>
-      <c r="F5" s="26" t="inlineStr">
+      <c r="F5" s="28" t="inlineStr">
         <is>
           <t>등교
-08:20</t>
+08:20–08:45</t>
         </is>
       </c>
       <c r="G5" s="5" t="n"/>
-      <c r="H5" s="26" t="inlineStr">
+      <c r="H5" s="28" t="inlineStr">
         <is>
           <t>등교
-08:20</t>
+08:20–08:45</t>
         </is>
       </c>
       <c r="I5" s="5" t="n"/>
-      <c r="J5" s="26" t="inlineStr">
+      <c r="J5" s="28" t="inlineStr">
         <is>
           <t>등교
-08:20</t>
+08:20–08:45</t>
         </is>
       </c>
       <c r="K5" s="5" t="n"/>
@@ -2718,8 +2744,8 @@
       <c r="N5" s="5" t="n"/>
       <c r="O5" s="5" t="n"/>
     </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
+    <row r="6" ht="11.5" customHeight="1">
+      <c r="A6" s="27" t="inlineStr">
         <is>
           <t>08:30</t>
         </is>
@@ -2739,40 +2765,40 @@
       <c r="N6" s="5" t="n"/>
       <c r="O6" s="5" t="n"/>
     </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" s="6" t="inlineStr"/>
-      <c r="B7" s="27" t="inlineStr">
+    <row r="7" ht="11.5" customHeight="1">
+      <c r="A7" s="27" t="inlineStr"/>
+      <c r="B7" s="29" t="inlineStr">
         <is>
           <t>정규수업
-08:45</t>
+08:45–13:30</t>
         </is>
       </c>
       <c r="C7" s="5" t="n"/>
-      <c r="D7" s="27" t="inlineStr">
+      <c r="D7" s="29" t="inlineStr">
         <is>
           <t>정규수업
-08:45</t>
+08:45–13:30</t>
         </is>
       </c>
       <c r="E7" s="5" t="n"/>
-      <c r="F7" s="27" t="inlineStr">
+      <c r="F7" s="29" t="inlineStr">
         <is>
           <t>정규수업(단축)
-08:45</t>
+08:45–12:50</t>
         </is>
       </c>
       <c r="G7" s="5" t="n"/>
-      <c r="H7" s="27" t="inlineStr">
+      <c r="H7" s="29" t="inlineStr">
         <is>
           <t>정규수업
-08:45</t>
+08:45–13:30</t>
         </is>
       </c>
       <c r="I7" s="5" t="n"/>
-      <c r="J7" s="27" t="inlineStr">
+      <c r="J7" s="29" t="inlineStr">
         <is>
           <t>정규수업(단축)
-08:45</t>
+08:45–12:50</t>
         </is>
       </c>
       <c r="K7" s="5" t="n"/>
@@ -2781,45 +2807,45 @@
       <c r="N7" s="5" t="n"/>
       <c r="O7" s="5" t="n"/>
     </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
+    <row r="8" ht="11.5" customHeight="1">
+      <c r="A8" s="26" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
       <c r="B8" s="10" t="n"/>
-      <c r="C8" s="27" t="inlineStr">
+      <c r="C8" s="29" t="inlineStr">
         <is>
           <t>유치원
-09:10</t>
+09:10–15:10</t>
         </is>
       </c>
       <c r="D8" s="10" t="n"/>
-      <c r="E8" s="27" t="inlineStr">
+      <c r="E8" s="29" t="inlineStr">
         <is>
           <t>유치원
-09:10</t>
+09:10–15:10</t>
         </is>
       </c>
       <c r="F8" s="10" t="n"/>
-      <c r="G8" s="27" t="inlineStr">
+      <c r="G8" s="29" t="inlineStr">
         <is>
           <t>유치원
-09:10</t>
+09:10–15:10</t>
         </is>
       </c>
       <c r="H8" s="10" t="n"/>
-      <c r="I8" s="27" t="inlineStr">
+      <c r="I8" s="29" t="inlineStr">
         <is>
           <t>유치원
-09:10</t>
+09:10–15:10</t>
         </is>
       </c>
       <c r="J8" s="10" t="n"/>
-      <c r="K8" s="27" t="inlineStr">
+      <c r="K8" s="29" t="inlineStr">
         <is>
           <t>유치원
-09:10</t>
+09:10–15:10</t>
         </is>
       </c>
       <c r="L8" s="5" t="n"/>
@@ -2827,8 +2853,8 @@
       <c r="N8" s="5" t="n"/>
       <c r="O8" s="5" t="n"/>
     </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" s="6" t="inlineStr"/>
+    <row r="9" ht="11.5" customHeight="1">
+      <c r="A9" s="27" t="inlineStr"/>
       <c r="B9" s="10" t="n"/>
       <c r="C9" s="10" t="n"/>
       <c r="D9" s="10" t="n"/>
@@ -2844,8 +2870,8 @@
       <c r="N9" s="5" t="n"/>
       <c r="O9" s="5" t="n"/>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
+    <row r="10" ht="11.5" customHeight="1">
+      <c r="A10" s="27" t="inlineStr">
         <is>
           <t>09:30</t>
         </is>
@@ -2865,8 +2891,8 @@
       <c r="N10" s="5" t="n"/>
       <c r="O10" s="5" t="n"/>
     </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" s="6" t="inlineStr"/>
+    <row r="11" ht="11.5" customHeight="1">
+      <c r="A11" s="27" t="inlineStr"/>
       <c r="B11" s="10" t="n"/>
       <c r="C11" s="10" t="n"/>
       <c r="D11" s="10" t="n"/>
@@ -2882,8 +2908,8 @@
       <c r="N11" s="5" t="n"/>
       <c r="O11" s="5" t="n"/>
     </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
+    <row r="12" ht="11.5" customHeight="1">
+      <c r="A12" s="26" t="inlineStr">
         <is>
           <t>10:00</t>
         </is>
@@ -2903,8 +2929,8 @@
       <c r="N12" s="5" t="n"/>
       <c r="O12" s="5" t="n"/>
     </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" s="6" t="inlineStr"/>
+    <row r="13" ht="11.5" customHeight="1">
+      <c r="A13" s="27" t="inlineStr"/>
       <c r="B13" s="10" t="n"/>
       <c r="C13" s="10" t="n"/>
       <c r="D13" s="10" t="n"/>
@@ -2920,8 +2946,8 @@
       <c r="N13" s="5" t="n"/>
       <c r="O13" s="5" t="n"/>
     </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" s="6" t="inlineStr">
+    <row r="14" ht="11.5" customHeight="1">
+      <c r="A14" s="27" t="inlineStr">
         <is>
           <t>10:30</t>
         </is>
@@ -2941,8 +2967,8 @@
       <c r="N14" s="5" t="n"/>
       <c r="O14" s="5" t="n"/>
     </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" s="6" t="inlineStr"/>
+    <row r="15" ht="11.5" customHeight="1">
+      <c r="A15" s="27" t="inlineStr"/>
       <c r="B15" s="10" t="n"/>
       <c r="C15" s="10" t="n"/>
       <c r="D15" s="10" t="n"/>
@@ -2958,8 +2984,8 @@
       <c r="N15" s="5" t="n"/>
       <c r="O15" s="5" t="n"/>
     </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" s="4" t="inlineStr">
+    <row r="16" ht="11.5" customHeight="1">
+      <c r="A16" s="26" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
@@ -2979,8 +3005,8 @@
       <c r="N16" s="5" t="n"/>
       <c r="O16" s="5" t="n"/>
     </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" s="6" t="inlineStr"/>
+    <row r="17" ht="11.5" customHeight="1">
+      <c r="A17" s="27" t="inlineStr"/>
       <c r="B17" s="10" t="n"/>
       <c r="C17" s="10" t="n"/>
       <c r="D17" s="10" t="n"/>
@@ -2996,8 +3022,8 @@
       <c r="N17" s="5" t="n"/>
       <c r="O17" s="5" t="n"/>
     </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" s="6" t="inlineStr">
+    <row r="18" ht="11.5" customHeight="1">
+      <c r="A18" s="27" t="inlineStr">
         <is>
           <t>11:30</t>
         </is>
@@ -3017,8 +3043,8 @@
       <c r="N18" s="5" t="n"/>
       <c r="O18" s="5" t="n"/>
     </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" s="6" t="inlineStr"/>
+    <row r="19" ht="11.5" customHeight="1">
+      <c r="A19" s="27" t="inlineStr"/>
       <c r="B19" s="10" t="n"/>
       <c r="C19" s="10" t="n"/>
       <c r="D19" s="10" t="n"/>
@@ -3034,8 +3060,8 @@
       <c r="N19" s="5" t="n"/>
       <c r="O19" s="5" t="n"/>
     </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" s="4" t="inlineStr">
+    <row r="20" ht="11.5" customHeight="1">
+      <c r="A20" s="26" t="inlineStr">
         <is>
           <t>12:00</t>
         </is>
@@ -3055,8 +3081,8 @@
       <c r="N20" s="5" t="n"/>
       <c r="O20" s="5" t="n"/>
     </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" s="6" t="inlineStr"/>
+    <row r="21" ht="11.5" customHeight="1">
+      <c r="A21" s="27" t="inlineStr"/>
       <c r="B21" s="10" t="n"/>
       <c r="C21" s="10" t="n"/>
       <c r="D21" s="10" t="n"/>
@@ -3072,8 +3098,8 @@
       <c r="N21" s="5" t="n"/>
       <c r="O21" s="5" t="n"/>
     </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" s="6" t="inlineStr">
+    <row r="22" ht="11.5" customHeight="1">
+      <c r="A22" s="27" t="inlineStr">
         <is>
           <t>12:30</t>
         </is>
@@ -3093,8 +3119,8 @@
       <c r="N22" s="5" t="n"/>
       <c r="O22" s="5" t="n"/>
     </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" s="6" t="inlineStr"/>
+    <row r="23" ht="11.5" customHeight="1">
+      <c r="A23" s="27" t="inlineStr"/>
       <c r="B23" s="10" t="n"/>
       <c r="C23" s="10" t="n"/>
       <c r="D23" s="10" t="n"/>
@@ -3110,8 +3136,8 @@
       <c r="N23" s="5" t="n"/>
       <c r="O23" s="5" t="n"/>
     </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" s="4" t="inlineStr">
+    <row r="24" ht="11.5" customHeight="1">
+      <c r="A24" s="26" t="inlineStr">
         <is>
           <t>13:00</t>
         </is>
@@ -3120,19 +3146,19 @@
       <c r="C24" s="10" t="n"/>
       <c r="D24" s="10" t="n"/>
       <c r="E24" s="10" t="n"/>
-      <c r="F24" s="28" t="inlineStr">
+      <c r="F24" s="30" t="inlineStr">
         <is>
           <t>방과후 아나운서
-12:50</t>
+12:50–14:20</t>
         </is>
       </c>
       <c r="G24" s="10" t="n"/>
       <c r="H24" s="10" t="n"/>
       <c r="I24" s="10" t="n"/>
-      <c r="J24" s="28" t="inlineStr">
+      <c r="J24" s="30" t="inlineStr">
         <is>
           <t>맞춤형 종이접기
-12:50</t>
+12:50–14:20</t>
         </is>
       </c>
       <c r="K24" s="10" t="n"/>
@@ -3141,8 +3167,8 @@
       <c r="N24" s="5" t="n"/>
       <c r="O24" s="5" t="n"/>
     </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" s="6" t="inlineStr"/>
+    <row r="25" ht="11.5" customHeight="1">
+      <c r="A25" s="27" t="inlineStr"/>
       <c r="B25" s="8" t="n"/>
       <c r="C25" s="10" t="n"/>
       <c r="D25" s="8" t="n"/>
@@ -3158,8 +3184,8 @@
       <c r="N25" s="5" t="n"/>
       <c r="O25" s="5" t="n"/>
     </row>
-    <row r="26" ht="15" customHeight="1">
-      <c r="A26" s="6" t="inlineStr">
+    <row r="26" ht="11.5" customHeight="1">
+      <c r="A26" s="27" t="inlineStr">
         <is>
           <t>13:30</t>
         </is>
@@ -3170,10 +3196,10 @@
       <c r="E26" s="10" t="n"/>
       <c r="F26" s="10" t="n"/>
       <c r="G26" s="10" t="n"/>
-      <c r="H26" s="28" t="inlineStr">
+      <c r="H26" s="30" t="inlineStr">
         <is>
           <t>방과후 큐보로봇
-13:40</t>
+13:40–15:10</t>
         </is>
       </c>
       <c r="I26" s="10" t="n"/>
@@ -3184,8 +3210,8 @@
       <c r="N26" s="5" t="n"/>
       <c r="O26" s="5" t="n"/>
     </row>
-    <row r="27" ht="15" customHeight="1">
-      <c r="A27" s="6" t="inlineStr"/>
+    <row r="27" ht="11.5" customHeight="1">
+      <c r="A27" s="27" t="inlineStr"/>
       <c r="B27" s="5" t="n"/>
       <c r="C27" s="10" t="n"/>
       <c r="D27" s="5" t="n"/>
@@ -3201,23 +3227,23 @@
       <c r="N27" s="5" t="n"/>
       <c r="O27" s="5" t="n"/>
     </row>
-    <row r="28" ht="15" customHeight="1">
-      <c r="A28" s="4" t="inlineStr">
+    <row r="28" ht="11.5" customHeight="1">
+      <c r="A28" s="26" t="inlineStr">
         <is>
           <t>14:00</t>
         </is>
       </c>
-      <c r="B28" s="29" t="inlineStr">
+      <c r="B28" s="31" t="inlineStr">
         <is>
           <t>태권도
-14:00</t>
+14:00–15:00</t>
         </is>
       </c>
       <c r="C28" s="10" t="n"/>
-      <c r="D28" s="29" t="inlineStr">
+      <c r="D28" s="31" t="inlineStr">
         <is>
           <t>태권도
-14:00</t>
+14:00–15:00</t>
         </is>
       </c>
       <c r="E28" s="10" t="n"/>
@@ -3232,8 +3258,8 @@
       <c r="N28" s="5" t="n"/>
       <c r="O28" s="5" t="n"/>
     </row>
-    <row r="29" ht="15" customHeight="1">
-      <c r="A29" s="6" t="inlineStr"/>
+    <row r="29" ht="11.5" customHeight="1">
+      <c r="A29" s="27" t="inlineStr"/>
       <c r="B29" s="10" t="n"/>
       <c r="C29" s="10" t="n"/>
       <c r="D29" s="10" t="n"/>
@@ -3249,8 +3275,8 @@
       <c r="N29" s="5" t="n"/>
       <c r="O29" s="5" t="n"/>
     </row>
-    <row r="30" ht="15" customHeight="1">
-      <c r="A30" s="6" t="inlineStr">
+    <row r="30" ht="11.5" customHeight="1">
+      <c r="A30" s="27" t="inlineStr">
         <is>
           <t>14:30</t>
         </is>
@@ -3263,10 +3289,10 @@
       <c r="G30" s="10" t="n"/>
       <c r="H30" s="10" t="n"/>
       <c r="I30" s="10" t="n"/>
-      <c r="J30" s="29" t="inlineStr">
+      <c r="J30" s="31" t="inlineStr">
         <is>
           <t>미술학원
-14:40</t>
+14:40–16:00</t>
         </is>
       </c>
       <c r="K30" s="10" t="n"/>
@@ -3275,8 +3301,8 @@
       <c r="N30" s="5" t="n"/>
       <c r="O30" s="5" t="n"/>
     </row>
-    <row r="31" ht="15" customHeight="1">
-      <c r="A31" s="6" t="inlineStr"/>
+    <row r="31" ht="11.5" customHeight="1">
+      <c r="A31" s="27" t="inlineStr"/>
       <c r="B31" s="8" t="n"/>
       <c r="C31" s="10" t="n"/>
       <c r="D31" s="8" t="n"/>
@@ -3292,8 +3318,8 @@
       <c r="N31" s="5" t="n"/>
       <c r="O31" s="5" t="n"/>
     </row>
-    <row r="32" ht="15" customHeight="1">
-      <c r="A32" s="4" t="inlineStr">
+    <row r="32" ht="11.5" customHeight="1">
+      <c r="A32" s="26" t="inlineStr">
         <is>
           <t>15:00</t>
         </is>
@@ -3313,12 +3339,12 @@
       <c r="N32" s="5" t="n"/>
       <c r="O32" s="5" t="n"/>
     </row>
-    <row r="33" ht="15" customHeight="1">
-      <c r="A33" s="6" t="inlineStr"/>
-      <c r="B33" s="29" t="inlineStr">
+    <row r="33" ht="11.5" customHeight="1">
+      <c r="A33" s="27" t="inlineStr"/>
+      <c r="B33" s="31" t="inlineStr">
         <is>
           <t>한글수업
-15:20</t>
+15:20–16:10</t>
         </is>
       </c>
       <c r="C33" s="5" t="n"/>
@@ -3335,8 +3361,8 @@
       <c r="N33" s="5" t="n"/>
       <c r="O33" s="5" t="n"/>
     </row>
-    <row r="34" ht="15" customHeight="1">
-      <c r="A34" s="6" t="inlineStr">
+    <row r="34" ht="11.5" customHeight="1">
+      <c r="A34" s="27" t="inlineStr">
         <is>
           <t>15:30</t>
         </is>
@@ -3356,8 +3382,8 @@
       <c r="N34" s="5" t="n"/>
       <c r="O34" s="5" t="n"/>
     </row>
-    <row r="35" ht="15" customHeight="1">
-      <c r="A35" s="6" t="inlineStr"/>
+    <row r="35" ht="11.5" customHeight="1">
+      <c r="A35" s="27" t="inlineStr"/>
       <c r="B35" s="10" t="n"/>
       <c r="C35" s="5" t="n"/>
       <c r="D35" s="5" t="n"/>
@@ -3373,64 +3399,64 @@
       <c r="N35" s="5" t="n"/>
       <c r="O35" s="5" t="n"/>
     </row>
-    <row r="36" ht="15" customHeight="1">
-      <c r="A36" s="4" t="inlineStr">
+    <row r="36" ht="11.5" customHeight="1">
+      <c r="A36" s="26" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
       <c r="B36" s="8" t="n"/>
       <c r="C36" s="5" t="n"/>
-      <c r="D36" s="29" t="inlineStr">
+      <c r="D36" s="32" t="inlineStr">
         <is>
           <t>피아노
-16:00</t>
+16:00–16:30</t>
         </is>
       </c>
       <c r="E36" s="5" t="n"/>
       <c r="F36" s="5" t="n"/>
-      <c r="G36" s="29" t="inlineStr">
+      <c r="G36" s="32" t="inlineStr">
         <is>
           <t>한글수업
-16:10</t>
+16:10–16:40</t>
         </is>
       </c>
       <c r="H36" s="5" t="n"/>
-      <c r="I36" s="29" t="inlineStr">
+      <c r="I36" s="31" t="inlineStr">
         <is>
           <t>태권도
-16:00</t>
-        </is>
-      </c>
-      <c r="J36" s="29" t="inlineStr">
+16:00–17:00</t>
+        </is>
+      </c>
+      <c r="J36" s="31" t="inlineStr">
         <is>
           <t>태권도
-16:00</t>
-        </is>
-      </c>
-      <c r="K36" s="29" t="inlineStr">
+16:00–17:00</t>
+        </is>
+      </c>
+      <c r="K36" s="31" t="inlineStr">
         <is>
           <t>태권도
-16:00</t>
+16:00–17:00</t>
         </is>
       </c>
       <c r="L36" s="5" t="n"/>
       <c r="M36" s="5" t="n"/>
-      <c r="N36" s="29" t="inlineStr">
+      <c r="N36" s="31" t="inlineStr">
         <is>
           <t>수영
-16:10</t>
+16:10–17:10</t>
         </is>
       </c>
       <c r="O36" s="5" t="n"/>
     </row>
-    <row r="37" ht="15" customHeight="1">
-      <c r="A37" s="6" t="inlineStr"/>
+    <row r="37" ht="11.5" customHeight="1">
+      <c r="A37" s="27" t="inlineStr"/>
       <c r="B37" s="5" t="n"/>
-      <c r="C37" s="29" t="inlineStr">
+      <c r="C37" s="32" t="inlineStr">
         <is>
           <t>한글수업
-16:20</t>
+16:20–16:50</t>
         </is>
       </c>
       <c r="D37" s="8" t="n"/>
@@ -3446,8 +3472,8 @@
       <c r="N37" s="10" t="n"/>
       <c r="O37" s="5" t="n"/>
     </row>
-    <row r="38" ht="15" customHeight="1">
-      <c r="A38" s="6" t="inlineStr">
+    <row r="38" ht="11.5" customHeight="1">
+      <c r="A38" s="27" t="inlineStr">
         <is>
           <t>16:30</t>
         </is>
@@ -3467,16 +3493,16 @@
       <c r="N38" s="10" t="n"/>
       <c r="O38" s="5" t="n"/>
     </row>
-    <row r="39" ht="15" customHeight="1">
-      <c r="A39" s="6" t="inlineStr"/>
+    <row r="39" ht="11.5" customHeight="1">
+      <c r="A39" s="27" t="inlineStr"/>
       <c r="B39" s="5" t="n"/>
       <c r="C39" s="8" t="n"/>
       <c r="D39" s="5" t="n"/>
       <c r="E39" s="5" t="n"/>
-      <c r="F39" s="29" t="inlineStr">
+      <c r="F39" s="31" t="inlineStr">
         <is>
           <t>한글수업
-16:50</t>
+16:50–17:40</t>
         </is>
       </c>
       <c r="G39" s="5" t="n"/>
@@ -3489,8 +3515,8 @@
       <c r="N39" s="10" t="n"/>
       <c r="O39" s="5" t="n"/>
     </row>
-    <row r="40" ht="15" customHeight="1">
-      <c r="A40" s="4" t="inlineStr">
+    <row r="40" ht="11.5" customHeight="1">
+      <c r="A40" s="26" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
@@ -3501,10 +3527,10 @@
       <c r="E40" s="5" t="n"/>
       <c r="F40" s="10" t="n"/>
       <c r="G40" s="5" t="n"/>
-      <c r="H40" s="29" t="inlineStr">
+      <c r="H40" s="31" t="inlineStr">
         <is>
           <t>영어수업
-17:10</t>
+17:10–18:10</t>
         </is>
       </c>
       <c r="I40" s="5" t="n"/>
@@ -3515,8 +3541,8 @@
       <c r="N40" s="8" t="n"/>
       <c r="O40" s="5" t="n"/>
     </row>
-    <row r="41" ht="15" customHeight="1">
-      <c r="A41" s="6" t="inlineStr"/>
+    <row r="41" ht="11.5" customHeight="1">
+      <c r="A41" s="27" t="inlineStr"/>
       <c r="B41" s="5" t="n"/>
       <c r="C41" s="5" t="n"/>
       <c r="D41" s="5" t="n"/>
@@ -3532,8 +3558,8 @@
       <c r="N41" s="5" t="n"/>
       <c r="O41" s="5" t="n"/>
     </row>
-    <row r="42" ht="15" customHeight="1">
-      <c r="A42" s="6" t="inlineStr">
+    <row r="42" ht="11.5" customHeight="1">
+      <c r="A42" s="27" t="inlineStr">
         <is>
           <t>17:30</t>
         </is>
@@ -3553,8 +3579,8 @@
       <c r="N42" s="5" t="n"/>
       <c r="O42" s="5" t="n"/>
     </row>
-    <row r="43" ht="15" customHeight="1">
-      <c r="A43" s="6" t="inlineStr"/>
+    <row r="43" ht="11.5" customHeight="1">
+      <c r="A43" s="27" t="inlineStr"/>
       <c r="B43" s="5" t="n"/>
       <c r="C43" s="5" t="n"/>
       <c r="D43" s="5" t="n"/>
@@ -3570,8 +3596,8 @@
       <c r="N43" s="5" t="n"/>
       <c r="O43" s="5" t="n"/>
     </row>
-    <row r="44" ht="15" customHeight="1">
-      <c r="A44" s="4" t="inlineStr">
+    <row r="44" ht="11.5" customHeight="1">
+      <c r="A44" s="26" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
@@ -3591,8 +3617,8 @@
       <c r="N44" s="5" t="n"/>
       <c r="O44" s="5" t="n"/>
     </row>
-    <row r="45" ht="15" customHeight="1">
-      <c r="A45" s="6" t="inlineStr"/>
+    <row r="45" ht="11.5" customHeight="1">
+      <c r="A45" s="27" t="inlineStr"/>
       <c r="B45" s="5" t="n"/>
       <c r="C45" s="5" t="n"/>
       <c r="D45" s="5" t="n"/>
@@ -3608,8 +3634,8 @@
       <c r="N45" s="5" t="n"/>
       <c r="O45" s="5" t="n"/>
     </row>
-    <row r="46" ht="15" customHeight="1">
-      <c r="A46" s="6" t="inlineStr">
+    <row r="46" ht="11.5" customHeight="1">
+      <c r="A46" s="27" t="inlineStr">
         <is>
           <t>18:30</t>
         </is>
@@ -3629,8 +3655,8 @@
       <c r="N46" s="5" t="n"/>
       <c r="O46" s="5" t="n"/>
     </row>
-    <row r="47" ht="15" customHeight="1">
-      <c r="A47" s="6" t="inlineStr"/>
+    <row r="47" ht="11.5" customHeight="1">
+      <c r="A47" s="27" t="inlineStr"/>
       <c r="B47" s="5" t="n"/>
       <c r="C47" s="5" t="n"/>
       <c r="D47" s="5" t="n"/>
@@ -3646,18 +3672,18 @@
       <c r="N47" s="5" t="n"/>
       <c r="O47" s="5" t="n"/>
     </row>
-    <row r="48" ht="15" customHeight="1">
-      <c r="A48" s="4" t="inlineStr">
+    <row r="48" ht="11.5" customHeight="1">
+      <c r="A48" s="26" t="inlineStr">
         <is>
           <t>19:00</t>
         </is>
       </c>
       <c r="B48" s="5" t="n"/>
       <c r="C48" s="5" t="n"/>
-      <c r="D48" s="29" t="inlineStr">
+      <c r="D48" s="32" t="inlineStr">
         <is>
           <t>화상영어
-19:00</t>
+19:00–19:30</t>
         </is>
       </c>
       <c r="E48" s="5" t="n"/>
@@ -3665,10 +3691,10 @@
       <c r="G48" s="5" t="n"/>
       <c r="H48" s="5" t="n"/>
       <c r="I48" s="5" t="n"/>
-      <c r="J48" s="29" t="inlineStr">
+      <c r="J48" s="32" t="inlineStr">
         <is>
           <t>화상영어
-19:00</t>
+19:00–19:30</t>
         </is>
       </c>
       <c r="K48" s="5" t="n"/>
@@ -3677,8 +3703,8 @@
       <c r="N48" s="5" t="n"/>
       <c r="O48" s="5" t="n"/>
     </row>
-    <row r="49" ht="15" customHeight="1">
-      <c r="A49" s="6" t="inlineStr"/>
+    <row r="49" ht="11.5" customHeight="1">
+      <c r="A49" s="27" t="inlineStr"/>
       <c r="B49" s="5" t="n"/>
       <c r="C49" s="5" t="n"/>
       <c r="D49" s="8" t="n"/>
@@ -3694,8 +3720,8 @@
       <c r="N49" s="5" t="n"/>
       <c r="O49" s="5" t="n"/>
     </row>
-    <row r="50" ht="15" customHeight="1">
-      <c r="A50" s="6" t="inlineStr">
+    <row r="50" ht="11.5" customHeight="1">
+      <c r="A50" s="27" t="inlineStr">
         <is>
           <t>19:30</t>
         </is>
@@ -3704,16 +3730,16 @@
       <c r="C50" s="5" t="n"/>
       <c r="D50" s="5" t="n"/>
       <c r="E50" s="5" t="n"/>
-      <c r="F50" s="29" t="inlineStr">
+      <c r="F50" s="31" t="inlineStr">
         <is>
           <t>첼로
-19:30</t>
-        </is>
-      </c>
-      <c r="G50" s="29" t="inlineStr">
+19:30–20:10</t>
+        </is>
+      </c>
+      <c r="G50" s="32" t="inlineStr">
         <is>
           <t>축구
-19:30</t>
+19:30–20:00</t>
         </is>
       </c>
       <c r="H50" s="5" t="n"/>
@@ -3725,8 +3751,8 @@
       <c r="N50" s="5" t="n"/>
       <c r="O50" s="5" t="n"/>
     </row>
-    <row r="51" ht="15" customHeight="1">
-      <c r="A51" s="6" t="inlineStr"/>
+    <row r="51" ht="11.5" customHeight="1">
+      <c r="A51" s="27" t="inlineStr"/>
       <c r="B51" s="5" t="n"/>
       <c r="C51" s="5" t="n"/>
       <c r="D51" s="5" t="n"/>
@@ -3742,8 +3768,8 @@
       <c r="N51" s="5" t="n"/>
       <c r="O51" s="5" t="n"/>
     </row>
-    <row r="52" ht="15" customHeight="1">
-      <c r="A52" s="4" t="inlineStr">
+    <row r="52" ht="11.5" customHeight="1">
+      <c r="A52" s="26" t="inlineStr">
         <is>
           <t>20:00</t>
         </is>
@@ -3763,8 +3789,8 @@
       <c r="N52" s="5" t="n"/>
       <c r="O52" s="5" t="n"/>
     </row>
-    <row r="53" ht="15" customHeight="1">
-      <c r="A53" s="6" t="inlineStr"/>
+    <row r="53" ht="11.5" customHeight="1">
+      <c r="A53" s="27" t="inlineStr"/>
       <c r="B53" s="5" t="n"/>
       <c r="C53" s="5" t="n"/>
       <c r="D53" s="5" t="n"/>
@@ -3827,8 +3853,8 @@
     <mergeCell ref="F50:F52"/>
     <mergeCell ref="J48:J49"/>
   </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.35" bottom="0.35" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="1" fitToWidth="1"/>
+  <pageMargins left="0.18" right="0.18" top="0.22" bottom="0.22" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -3852,1407 +3878,1403 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="30" t="inlineStr">
+      <c r="A1" s="33" t="inlineStr">
         <is>
           <t>일정 편집용 — 여기 고친 뒤 '주간표 갱신' 요청하면 위 시간표가 다시 그려집니다</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="31" t="inlineStr">
+      <c r="A2" s="34" t="inlineStr">
         <is>
           <t>구분</t>
         </is>
       </c>
-      <c r="B2" s="31" t="inlineStr">
+      <c r="B2" s="34" t="inlineStr">
         <is>
           <t>요일</t>
         </is>
       </c>
-      <c r="C2" s="31" t="inlineStr">
+      <c r="C2" s="34" t="inlineStr">
         <is>
           <t>시작</t>
         </is>
       </c>
-      <c r="D2" s="31" t="inlineStr">
+      <c r="D2" s="34" t="inlineStr">
         <is>
           <t>종료</t>
         </is>
       </c>
-      <c r="E2" s="31" t="inlineStr">
+      <c r="E2" s="34" t="inlineStr">
         <is>
           <t>활동</t>
         </is>
       </c>
-      <c r="F2" s="31" t="inlineStr">
+      <c r="F2" s="34" t="inlineStr">
         <is>
           <t>분류</t>
         </is>
       </c>
-      <c r="G2" s="31" t="inlineStr">
+      <c r="G2" s="34" t="inlineStr">
         <is>
           <t>장소</t>
         </is>
       </c>
-      <c r="H2" s="31" t="inlineStr">
+      <c r="H2" s="34" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="32" t="inlineStr">
+      <c r="A3" s="35" t="inlineStr">
         <is>
           <t>첫째</t>
         </is>
       </c>
-      <c r="B3" s="33" t="inlineStr">
+      <c r="B3" s="36" t="inlineStr">
         <is>
           <t>월</t>
         </is>
       </c>
-      <c r="C3" s="33" t="inlineStr">
+      <c r="C3" s="36" t="inlineStr">
         <is>
           <t>08:20</t>
         </is>
       </c>
-      <c r="D3" s="33" t="inlineStr">
+      <c r="D3" s="36" t="inlineStr">
         <is>
           <t>08:45</t>
         </is>
       </c>
-      <c r="E3" s="34" t="inlineStr">
+      <c r="E3" s="37" t="inlineStr">
         <is>
           <t>등교</t>
         </is>
       </c>
-      <c r="F3" s="35" t="inlineStr">
+      <c r="F3" s="38" t="inlineStr">
         <is>
           <t>돌봄/픽업</t>
         </is>
       </c>
-      <c r="G3" s="34" t="inlineStr">
+      <c r="G3" s="37" t="inlineStr">
         <is>
           <t>집→학교</t>
         </is>
       </c>
-      <c r="H3" s="34" t="inlineStr"/>
+      <c r="H3" s="37" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="32" t="inlineStr">
+      <c r="A4" s="35" t="inlineStr">
         <is>
           <t>첫째</t>
         </is>
       </c>
-      <c r="B4" s="33" t="inlineStr">
+      <c r="B4" s="36" t="inlineStr">
         <is>
           <t>월</t>
         </is>
       </c>
-      <c r="C4" s="33" t="inlineStr">
+      <c r="C4" s="36" t="inlineStr">
         <is>
           <t>08:45</t>
         </is>
       </c>
-      <c r="D4" s="33" t="inlineStr">
+      <c r="D4" s="36" t="inlineStr">
         <is>
           <t>13:30</t>
         </is>
       </c>
-      <c r="E4" s="34" t="inlineStr">
+      <c r="E4" s="37" t="inlineStr">
         <is>
           <t>정규수업</t>
         </is>
       </c>
-      <c r="F4" s="36" t="inlineStr">
+      <c r="F4" s="39" t="inlineStr">
         <is>
           <t>정규수업</t>
         </is>
       </c>
-      <c r="G4" s="34" t="inlineStr">
+      <c r="G4" s="37" t="inlineStr">
         <is>
           <t>○○초</t>
         </is>
       </c>
-      <c r="H4" s="34" t="inlineStr"/>
+      <c r="H4" s="37" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="32" t="inlineStr">
+      <c r="A5" s="35" t="inlineStr">
         <is>
           <t>첫째</t>
         </is>
       </c>
-      <c r="B5" s="33" t="inlineStr">
+      <c r="B5" s="36" t="inlineStr">
         <is>
           <t>월</t>
         </is>
       </c>
-      <c r="C5" s="33" t="inlineStr">
+      <c r="C5" s="36" t="inlineStr">
         <is>
           <t>15:20</t>
         </is>
       </c>
-      <c r="D5" s="33" t="inlineStr">
+      <c r="D5" s="36" t="inlineStr">
         <is>
           <t>16:10</t>
         </is>
       </c>
-      <c r="E5" s="34" t="inlineStr">
+      <c r="E5" s="37" t="inlineStr">
         <is>
           <t>한글수업</t>
         </is>
       </c>
-      <c r="F5" s="37" t="inlineStr">
+      <c r="F5" s="40" t="inlineStr">
         <is>
           <t>학원</t>
         </is>
       </c>
-      <c r="G5" s="34" t="inlineStr">
+      <c r="G5" s="37" t="inlineStr">
         <is>
           <t>집 (과외)</t>
         </is>
       </c>
-      <c r="H5" s="34" t="inlineStr"/>
+      <c r="H5" s="37" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="32" t="inlineStr">
+      <c r="A6" s="35" t="inlineStr">
         <is>
           <t>첫째</t>
         </is>
       </c>
-      <c r="B6" s="33" t="inlineStr">
+      <c r="B6" s="36" t="inlineStr">
         <is>
           <t>화</t>
         </is>
       </c>
-      <c r="C6" s="33" t="inlineStr">
+      <c r="C6" s="36" t="inlineStr">
         <is>
           <t>08:20</t>
         </is>
       </c>
-      <c r="D6" s="33" t="inlineStr">
+      <c r="D6" s="36" t="inlineStr">
         <is>
           <t>08:45</t>
         </is>
       </c>
-      <c r="E6" s="34" t="inlineStr">
+      <c r="E6" s="37" t="inlineStr">
         <is>
           <t>등교</t>
         </is>
       </c>
-      <c r="F6" s="35" t="inlineStr">
+      <c r="F6" s="38" t="inlineStr">
         <is>
           <t>돌봄/픽업</t>
         </is>
       </c>
-      <c r="G6" s="34" t="inlineStr">
+      <c r="G6" s="37" t="inlineStr">
         <is>
           <t>집→학교</t>
         </is>
       </c>
-      <c r="H6" s="34" t="inlineStr"/>
+      <c r="H6" s="37" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="32" t="inlineStr">
+      <c r="A7" s="35" t="inlineStr">
         <is>
           <t>첫째</t>
         </is>
       </c>
-      <c r="B7" s="33" t="inlineStr">
+      <c r="B7" s="36" t="inlineStr">
         <is>
           <t>화</t>
         </is>
       </c>
-      <c r="C7" s="33" t="inlineStr">
+      <c r="C7" s="36" t="inlineStr">
         <is>
           <t>08:45</t>
         </is>
       </c>
-      <c r="D7" s="33" t="inlineStr">
+      <c r="D7" s="36" t="inlineStr">
         <is>
           <t>13:30</t>
         </is>
       </c>
-      <c r="E7" s="34" t="inlineStr">
+      <c r="E7" s="37" t="inlineStr">
         <is>
           <t>정규수업</t>
         </is>
       </c>
-      <c r="F7" s="36" t="inlineStr">
+      <c r="F7" s="39" t="inlineStr">
         <is>
           <t>정규수업</t>
         </is>
       </c>
-      <c r="G7" s="34" t="inlineStr">
+      <c r="G7" s="37" t="inlineStr">
         <is>
           <t>○○초</t>
         </is>
       </c>
-      <c r="H7" s="34" t="inlineStr"/>
+      <c r="H7" s="37" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="32" t="inlineStr">
+      <c r="A8" s="35" t="inlineStr">
         <is>
           <t>첫째</t>
         </is>
       </c>
-      <c r="B8" s="33" t="inlineStr">
+      <c r="B8" s="36" t="inlineStr">
         <is>
           <t>화</t>
         </is>
       </c>
-      <c r="C8" s="33" t="inlineStr">
+      <c r="C8" s="36" t="inlineStr">
         <is>
           <t>14:00</t>
         </is>
       </c>
-      <c r="D8" s="33" t="inlineStr">
+      <c r="D8" s="36" t="inlineStr">
         <is>
           <t>15:00</t>
         </is>
       </c>
-      <c r="E8" s="34" t="inlineStr">
+      <c r="E8" s="37" t="inlineStr">
         <is>
           <t>태권도</t>
         </is>
       </c>
-      <c r="F8" s="37" t="inlineStr">
+      <c r="F8" s="40" t="inlineStr">
         <is>
           <t>학원</t>
         </is>
       </c>
-      <c r="G8" s="34" t="inlineStr">
+      <c r="G8" s="37" t="inlineStr">
         <is>
           <t>태권도장</t>
         </is>
       </c>
-      <c r="H8" s="34" t="inlineStr"/>
+      <c r="H8" s="37" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="32" t="inlineStr">
+      <c r="A9" s="35" t="inlineStr">
         <is>
           <t>첫째</t>
         </is>
       </c>
-      <c r="B9" s="33" t="inlineStr">
+      <c r="B9" s="36" t="inlineStr">
         <is>
           <t>화</t>
         </is>
       </c>
-      <c r="C9" s="33" t="inlineStr">
+      <c r="C9" s="36" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="D9" s="33" t="inlineStr">
+      <c r="D9" s="36" t="inlineStr">
         <is>
           <t>16:30</t>
         </is>
       </c>
-      <c r="E9" s="34" t="inlineStr">
+      <c r="E9" s="37" t="inlineStr">
         <is>
           <t>피아노</t>
         </is>
       </c>
-      <c r="F9" s="37" t="inlineStr">
+      <c r="F9" s="40" t="inlineStr">
         <is>
           <t>학원</t>
         </is>
       </c>
-      <c r="G9" s="34" t="inlineStr">
+      <c r="G9" s="37" t="inlineStr">
         <is>
           <t>집 (과외)</t>
         </is>
       </c>
-      <c r="H9" s="34" t="inlineStr"/>
+      <c r="H9" s="37" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="32" t="inlineStr">
+      <c r="A10" s="35" t="inlineStr">
         <is>
           <t>첫째</t>
         </is>
       </c>
-      <c r="B10" s="33" t="inlineStr">
+      <c r="B10" s="36" t="inlineStr">
         <is>
           <t>수</t>
         </is>
       </c>
-      <c r="C10" s="33" t="inlineStr">
+      <c r="C10" s="36" t="inlineStr">
         <is>
           <t>08:20</t>
         </is>
       </c>
-      <c r="D10" s="33" t="inlineStr">
+      <c r="D10" s="36" t="inlineStr">
         <is>
           <t>08:45</t>
         </is>
       </c>
-      <c r="E10" s="34" t="inlineStr">
+      <c r="E10" s="37" t="inlineStr">
         <is>
           <t>등교</t>
         </is>
       </c>
-      <c r="F10" s="35" t="inlineStr">
+      <c r="F10" s="38" t="inlineStr">
         <is>
           <t>돌봄/픽업</t>
         </is>
       </c>
-      <c r="G10" s="34" t="inlineStr">
+      <c r="G10" s="37" t="inlineStr">
         <is>
           <t>집→학교</t>
         </is>
       </c>
-      <c r="H10" s="34" t="inlineStr"/>
+      <c r="H10" s="37" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="32" t="inlineStr">
+      <c r="A11" s="35" t="inlineStr">
         <is>
           <t>첫째</t>
         </is>
       </c>
-      <c r="B11" s="33" t="inlineStr">
+      <c r="B11" s="36" t="inlineStr">
         <is>
           <t>수</t>
         </is>
       </c>
-      <c r="C11" s="33" t="inlineStr">
+      <c r="C11" s="36" t="inlineStr">
         <is>
           <t>08:45</t>
         </is>
       </c>
-      <c r="D11" s="33" t="inlineStr">
+      <c r="D11" s="36" t="inlineStr">
         <is>
           <t>12:50</t>
         </is>
       </c>
-      <c r="E11" s="34" t="inlineStr">
+      <c r="E11" s="37" t="inlineStr">
         <is>
           <t>정규수업(단축)</t>
         </is>
       </c>
-      <c r="F11" s="36" t="inlineStr">
+      <c r="F11" s="39" t="inlineStr">
         <is>
           <t>정규수업</t>
         </is>
       </c>
-      <c r="G11" s="34" t="inlineStr">
+      <c r="G11" s="37" t="inlineStr">
         <is>
           <t>○○초</t>
         </is>
       </c>
-      <c r="H11" s="34" t="inlineStr"/>
+      <c r="H11" s="37" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="32" t="inlineStr">
+      <c r="A12" s="35" t="inlineStr">
         <is>
           <t>첫째</t>
         </is>
       </c>
-      <c r="B12" s="33" t="inlineStr">
+      <c r="B12" s="36" t="inlineStr">
         <is>
           <t>목</t>
         </is>
       </c>
-      <c r="C12" s="33" t="inlineStr">
+      <c r="C12" s="36" t="inlineStr">
         <is>
           <t>08:20</t>
         </is>
       </c>
-      <c r="D12" s="33" t="inlineStr">
+      <c r="D12" s="36" t="inlineStr">
         <is>
           <t>08:45</t>
         </is>
       </c>
-      <c r="E12" s="34" t="inlineStr">
+      <c r="E12" s="37" t="inlineStr">
         <is>
           <t>등교</t>
         </is>
       </c>
-      <c r="F12" s="35" t="inlineStr">
+      <c r="F12" s="38" t="inlineStr">
         <is>
           <t>돌봄/픽업</t>
         </is>
       </c>
-      <c r="G12" s="34" t="inlineStr">
+      <c r="G12" s="37" t="inlineStr">
         <is>
           <t>집→학교</t>
         </is>
       </c>
-      <c r="H12" s="34" t="inlineStr"/>
+      <c r="H12" s="37" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="32" t="inlineStr">
+      <c r="A13" s="35" t="inlineStr">
         <is>
           <t>첫째</t>
         </is>
       </c>
-      <c r="B13" s="33" t="inlineStr">
+      <c r="B13" s="36" t="inlineStr">
         <is>
           <t>목</t>
         </is>
       </c>
-      <c r="C13" s="33" t="inlineStr">
+      <c r="C13" s="36" t="inlineStr">
         <is>
           <t>08:45</t>
         </is>
       </c>
-      <c r="D13" s="33" t="inlineStr">
+      <c r="D13" s="36" t="inlineStr">
         <is>
           <t>13:30</t>
         </is>
       </c>
-      <c r="E13" s="34" t="inlineStr">
+      <c r="E13" s="37" t="inlineStr">
         <is>
           <t>정규수업</t>
         </is>
       </c>
-      <c r="F13" s="36" t="inlineStr">
+      <c r="F13" s="39" t="inlineStr">
         <is>
           <t>정규수업</t>
         </is>
       </c>
-      <c r="G13" s="34" t="inlineStr">
+      <c r="G13" s="37" t="inlineStr">
         <is>
           <t>○○초</t>
         </is>
       </c>
-      <c r="H13" s="34" t="inlineStr"/>
+      <c r="H13" s="37" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="32" t="inlineStr">
+      <c r="A14" s="35" t="inlineStr">
         <is>
           <t>첫째</t>
         </is>
       </c>
-      <c r="B14" s="33" t="inlineStr">
+      <c r="B14" s="36" t="inlineStr">
         <is>
           <t>목</t>
         </is>
       </c>
-      <c r="C14" s="33" t="inlineStr">
+      <c r="C14" s="36" t="inlineStr">
         <is>
           <t>13:40</t>
         </is>
       </c>
-      <c r="D14" s="33" t="inlineStr">
+      <c r="D14" s="36" t="inlineStr">
         <is>
           <t>15:10</t>
         </is>
       </c>
-      <c r="E14" s="34" t="inlineStr">
+      <c r="E14" s="37" t="inlineStr">
         <is>
           <t>방과후 큐보로봇</t>
         </is>
       </c>
-      <c r="F14" s="38" t="inlineStr">
+      <c r="F14" s="41" t="inlineStr">
         <is>
           <t>방과후</t>
         </is>
       </c>
-      <c r="G14" s="34" t="inlineStr">
+      <c r="G14" s="37" t="inlineStr">
         <is>
           <t>학교</t>
         </is>
       </c>
-      <c r="H14" s="34" t="inlineStr"/>
+      <c r="H14" s="37" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="32" t="inlineStr">
+      <c r="A15" s="35" t="inlineStr">
         <is>
           <t>첫째</t>
         </is>
       </c>
-      <c r="B15" s="33" t="inlineStr">
+      <c r="B15" s="36" t="inlineStr">
         <is>
           <t>목</t>
         </is>
       </c>
-      <c r="C15" s="33" t="inlineStr">
+      <c r="C15" s="36" t="inlineStr">
         <is>
           <t>17:10</t>
         </is>
       </c>
-      <c r="D15" s="33" t="inlineStr">
+      <c r="D15" s="36" t="inlineStr">
         <is>
           <t>18:10</t>
         </is>
       </c>
-      <c r="E15" s="34" t="inlineStr">
+      <c r="E15" s="37" t="inlineStr">
         <is>
           <t>영어수업</t>
         </is>
       </c>
-      <c r="F15" s="37" t="inlineStr">
+      <c r="F15" s="40" t="inlineStr">
         <is>
           <t>학원</t>
         </is>
       </c>
-      <c r="G15" s="34" t="inlineStr">
+      <c r="G15" s="37" t="inlineStr">
         <is>
           <t>집 (과외)</t>
         </is>
       </c>
-      <c r="H15" s="34" t="inlineStr"/>
+      <c r="H15" s="37" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="32" t="inlineStr">
+      <c r="A16" s="35" t="inlineStr">
         <is>
           <t>첫째</t>
         </is>
       </c>
-      <c r="B16" s="33" t="inlineStr">
+      <c r="B16" s="36" t="inlineStr">
         <is>
           <t>금</t>
         </is>
       </c>
-      <c r="C16" s="33" t="inlineStr">
+      <c r="C16" s="36" t="inlineStr">
         <is>
           <t>08:20</t>
         </is>
       </c>
-      <c r="D16" s="33" t="inlineStr">
+      <c r="D16" s="36" t="inlineStr">
         <is>
           <t>08:45</t>
         </is>
       </c>
-      <c r="E16" s="34" t="inlineStr">
+      <c r="E16" s="37" t="inlineStr">
         <is>
           <t>등교</t>
         </is>
       </c>
-      <c r="F16" s="35" t="inlineStr">
+      <c r="F16" s="38" t="inlineStr">
         <is>
           <t>돌봄/픽업</t>
         </is>
       </c>
-      <c r="G16" s="34" t="inlineStr">
+      <c r="G16" s="37" t="inlineStr">
         <is>
           <t>집→학교</t>
         </is>
       </c>
-      <c r="H16" s="34" t="inlineStr"/>
+      <c r="H16" s="37" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="32" t="inlineStr">
+      <c r="A17" s="35" t="inlineStr">
         <is>
           <t>첫째</t>
         </is>
       </c>
-      <c r="B17" s="33" t="inlineStr">
+      <c r="B17" s="36" t="inlineStr">
         <is>
           <t>금</t>
         </is>
       </c>
-      <c r="C17" s="33" t="inlineStr">
+      <c r="C17" s="36" t="inlineStr">
         <is>
           <t>08:45</t>
         </is>
       </c>
-      <c r="D17" s="33" t="inlineStr">
+      <c r="D17" s="36" t="inlineStr">
         <is>
           <t>12:50</t>
         </is>
       </c>
-      <c r="E17" s="34" t="inlineStr">
+      <c r="E17" s="37" t="inlineStr">
         <is>
           <t>정규수업(단축)</t>
         </is>
       </c>
-      <c r="F17" s="36" t="inlineStr">
+      <c r="F17" s="39" t="inlineStr">
         <is>
           <t>정규수업</t>
         </is>
       </c>
-      <c r="G17" s="34" t="inlineStr">
+      <c r="G17" s="37" t="inlineStr">
         <is>
           <t>○○초</t>
         </is>
       </c>
-      <c r="H17" s="34" t="inlineStr"/>
+      <c r="H17" s="37" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="32" t="inlineStr">
+      <c r="A18" s="35" t="inlineStr">
         <is>
           <t>첫째</t>
         </is>
       </c>
-      <c r="B18" s="33" t="inlineStr">
+      <c r="B18" s="36" t="inlineStr">
         <is>
           <t>금</t>
         </is>
       </c>
-      <c r="C18" s="33" t="inlineStr">
+      <c r="C18" s="36" t="inlineStr">
         <is>
           <t>12:50</t>
         </is>
       </c>
-      <c r="D18" s="33" t="inlineStr">
+      <c r="D18" s="36" t="inlineStr">
         <is>
           <t>14:20</t>
         </is>
       </c>
-      <c r="E18" s="34" t="inlineStr">
+      <c r="E18" s="37" t="inlineStr">
         <is>
           <t>맞춤형 종이접기</t>
         </is>
       </c>
-      <c r="F18" s="38" t="inlineStr">
+      <c r="F18" s="41" t="inlineStr">
         <is>
           <t>방과후</t>
         </is>
       </c>
-      <c r="G18" s="34" t="inlineStr">
+      <c r="G18" s="37" t="inlineStr">
         <is>
           <t>학교</t>
         </is>
       </c>
-      <c r="H18" s="34" t="inlineStr">
+      <c r="H18" s="37" t="inlineStr">
         <is>
           <t>무료</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="32" t="inlineStr">
+      <c r="A19" s="35" t="inlineStr">
         <is>
           <t>첫째</t>
         </is>
       </c>
-      <c r="B19" s="33" t="inlineStr">
+      <c r="B19" s="36" t="inlineStr">
         <is>
           <t>금</t>
         </is>
       </c>
-      <c r="C19" s="33" t="inlineStr">
+      <c r="C19" s="36" t="inlineStr">
         <is>
           <t>14:40</t>
         </is>
       </c>
-      <c r="D19" s="33" t="inlineStr">
+      <c r="D19" s="36" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="E19" s="34" t="inlineStr">
+      <c r="E19" s="37" t="inlineStr">
         <is>
           <t>미술학원</t>
         </is>
       </c>
-      <c r="F19" s="37" t="inlineStr">
+      <c r="F19" s="40" t="inlineStr">
         <is>
           <t>학원</t>
         </is>
       </c>
-      <c r="G19" s="34" t="inlineStr">
+      <c r="G19" s="37" t="inlineStr">
         <is>
           <t>봉쁘앙 미술학원</t>
         </is>
       </c>
-      <c r="H19" s="34" t="inlineStr"/>
+      <c r="H19" s="37" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="32" t="inlineStr">
+      <c r="A20" s="35" t="inlineStr">
         <is>
           <t>첫째</t>
         </is>
       </c>
-      <c r="B20" s="33" t="inlineStr">
+      <c r="B20" s="36" t="inlineStr">
         <is>
           <t>금</t>
         </is>
       </c>
-      <c r="C20" s="33" t="inlineStr">
+      <c r="C20" s="36" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="D20" s="33" t="inlineStr">
+      <c r="D20" s="36" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="E20" s="34" t="inlineStr">
+      <c r="E20" s="37" t="inlineStr">
         <is>
           <t>태권도</t>
         </is>
       </c>
-      <c r="F20" s="37" t="inlineStr">
+      <c r="F20" s="40" t="inlineStr">
         <is>
           <t>학원</t>
         </is>
       </c>
-      <c r="G20" s="34" t="inlineStr">
+      <c r="G20" s="37" t="inlineStr">
         <is>
           <t>태권도장</t>
         </is>
       </c>
-      <c r="H20" s="34" t="inlineStr">
+      <c r="H20" s="37" t="inlineStr">
         <is>
           <t>둘째와 함께 · 이모님 픽업</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="39" t="inlineStr">
+      <c r="A21" s="42" t="inlineStr">
         <is>
           <t>둘째</t>
         </is>
       </c>
-      <c r="B21" s="33" t="inlineStr">
+      <c r="B21" s="36" t="inlineStr">
         <is>
           <t>월</t>
         </is>
       </c>
-      <c r="C21" s="33" t="inlineStr">
+      <c r="C21" s="36" t="inlineStr">
         <is>
           <t>09:10</t>
         </is>
       </c>
-      <c r="D21" s="33" t="inlineStr">
+      <c r="D21" s="36" t="inlineStr">
         <is>
           <t>15:10</t>
         </is>
       </c>
-      <c r="E21" s="34" t="inlineStr">
+      <c r="E21" s="37" t="inlineStr">
         <is>
           <t>유치원</t>
         </is>
       </c>
-      <c r="F21" s="36" t="inlineStr">
+      <c r="F21" s="39" t="inlineStr">
         <is>
           <t>정규수업</t>
         </is>
       </c>
-      <c r="G21" s="34" t="inlineStr">
+      <c r="G21" s="37" t="inlineStr">
         <is>
           <t>유치원</t>
         </is>
       </c>
-      <c r="H21" s="34" t="inlineStr"/>
+      <c r="H21" s="37" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="39" t="inlineStr">
+      <c r="A22" s="42" t="inlineStr">
         <is>
           <t>둘째</t>
         </is>
       </c>
-      <c r="B22" s="33" t="inlineStr">
+      <c r="B22" s="36" t="inlineStr">
         <is>
           <t>월</t>
         </is>
       </c>
-      <c r="C22" s="33" t="inlineStr">
+      <c r="C22" s="36" t="inlineStr">
         <is>
           <t>16:20</t>
         </is>
       </c>
-      <c r="D22" s="33" t="inlineStr">
+      <c r="D22" s="36" t="inlineStr">
         <is>
           <t>16:50</t>
         </is>
       </c>
-      <c r="E22" s="34" t="inlineStr">
+      <c r="E22" s="37" t="inlineStr">
         <is>
           <t>한글수업</t>
         </is>
       </c>
-      <c r="F22" s="37" t="inlineStr">
+      <c r="F22" s="40" t="inlineStr">
         <is>
           <t>학원</t>
         </is>
       </c>
-      <c r="G22" s="34" t="inlineStr">
+      <c r="G22" s="37" t="inlineStr">
         <is>
           <t>집 (과외)</t>
         </is>
       </c>
-      <c r="H22" s="34" t="inlineStr"/>
+      <c r="H22" s="37" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="39" t="inlineStr">
+      <c r="A23" s="42" t="inlineStr">
         <is>
           <t>둘째</t>
         </is>
       </c>
-      <c r="B23" s="33" t="inlineStr">
+      <c r="B23" s="36" t="inlineStr">
         <is>
           <t>화</t>
         </is>
       </c>
-      <c r="C23" s="33" t="inlineStr">
+      <c r="C23" s="36" t="inlineStr">
         <is>
           <t>09:10</t>
         </is>
       </c>
-      <c r="D23" s="33" t="inlineStr">
+      <c r="D23" s="36" t="inlineStr">
         <is>
           <t>15:10</t>
         </is>
       </c>
-      <c r="E23" s="34" t="inlineStr">
+      <c r="E23" s="37" t="inlineStr">
         <is>
           <t>유치원</t>
         </is>
       </c>
-      <c r="F23" s="36" t="inlineStr">
+      <c r="F23" s="39" t="inlineStr">
         <is>
           <t>정규수업</t>
         </is>
       </c>
-      <c r="G23" s="34" t="inlineStr">
+      <c r="G23" s="37" t="inlineStr">
         <is>
           <t>유치원</t>
         </is>
       </c>
-      <c r="H23" s="34" t="inlineStr"/>
+      <c r="H23" s="37" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="39" t="inlineStr">
+      <c r="A24" s="42" t="inlineStr">
         <is>
           <t>둘째</t>
         </is>
       </c>
-      <c r="B24" s="33" t="inlineStr">
+      <c r="B24" s="36" t="inlineStr">
         <is>
           <t>수</t>
         </is>
       </c>
-      <c r="C24" s="33" t="inlineStr">
+      <c r="C24" s="36" t="inlineStr">
         <is>
           <t>09:10</t>
         </is>
       </c>
-      <c r="D24" s="33" t="inlineStr">
+      <c r="D24" s="36" t="inlineStr">
         <is>
           <t>15:10</t>
         </is>
       </c>
-      <c r="E24" s="34" t="inlineStr">
+      <c r="E24" s="37" t="inlineStr">
         <is>
           <t>유치원</t>
         </is>
       </c>
-      <c r="F24" s="36" t="inlineStr">
+      <c r="F24" s="39" t="inlineStr">
         <is>
           <t>정규수업</t>
         </is>
       </c>
-      <c r="G24" s="34" t="inlineStr">
+      <c r="G24" s="37" t="inlineStr">
         <is>
           <t>유치원</t>
         </is>
       </c>
-      <c r="H24" s="34" t="inlineStr"/>
+      <c r="H24" s="37" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="39" t="inlineStr">
+      <c r="A25" s="42" t="inlineStr">
         <is>
           <t>둘째</t>
         </is>
       </c>
-      <c r="B25" s="33" t="inlineStr">
+      <c r="B25" s="36" t="inlineStr">
         <is>
           <t>수</t>
         </is>
       </c>
-      <c r="C25" s="33" t="inlineStr">
+      <c r="C25" s="36" t="inlineStr">
         <is>
           <t>16:10</t>
         </is>
       </c>
-      <c r="D25" s="33" t="inlineStr">
+      <c r="D25" s="36" t="inlineStr">
         <is>
           <t>16:40</t>
         </is>
       </c>
-      <c r="E25" s="34" t="inlineStr">
+      <c r="E25" s="37" t="inlineStr">
         <is>
           <t>한글수업</t>
         </is>
       </c>
-      <c r="F25" s="37" t="inlineStr">
+      <c r="F25" s="40" t="inlineStr">
         <is>
           <t>학원</t>
         </is>
       </c>
-      <c r="G25" s="34" t="inlineStr">
+      <c r="G25" s="37" t="inlineStr">
         <is>
           <t>집 (과외)</t>
         </is>
       </c>
-      <c r="H25" s="34" t="inlineStr"/>
+      <c r="H25" s="37" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="39" t="inlineStr">
+      <c r="A26" s="42" t="inlineStr">
         <is>
           <t>둘째</t>
         </is>
       </c>
-      <c r="B26" s="33" t="inlineStr">
+      <c r="B26" s="36" t="inlineStr">
         <is>
           <t>목</t>
         </is>
       </c>
-      <c r="C26" s="33" t="inlineStr">
+      <c r="C26" s="36" t="inlineStr">
         <is>
           <t>09:10</t>
         </is>
       </c>
-      <c r="D26" s="33" t="inlineStr">
+      <c r="D26" s="36" t="inlineStr">
         <is>
           <t>15:10</t>
         </is>
       </c>
-      <c r="E26" s="34" t="inlineStr">
+      <c r="E26" s="37" t="inlineStr">
         <is>
           <t>유치원</t>
         </is>
       </c>
-      <c r="F26" s="36" t="inlineStr">
+      <c r="F26" s="39" t="inlineStr">
         <is>
           <t>정규수업</t>
         </is>
       </c>
-      <c r="G26" s="34" t="inlineStr">
+      <c r="G26" s="37" t="inlineStr">
         <is>
           <t>유치원</t>
         </is>
       </c>
-      <c r="H26" s="34" t="inlineStr"/>
+      <c r="H26" s="37" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="39" t="inlineStr">
+      <c r="A27" s="42" t="inlineStr">
         <is>
           <t>둘째</t>
         </is>
       </c>
-      <c r="B27" s="33" t="inlineStr">
+      <c r="B27" s="36" t="inlineStr">
         <is>
           <t>금</t>
         </is>
       </c>
-      <c r="C27" s="33" t="inlineStr">
+      <c r="C27" s="36" t="inlineStr">
         <is>
           <t>09:10</t>
         </is>
       </c>
-      <c r="D27" s="33" t="inlineStr">
+      <c r="D27" s="36" t="inlineStr">
         <is>
           <t>15:10</t>
         </is>
       </c>
-      <c r="E27" s="34" t="inlineStr">
+      <c r="E27" s="37" t="inlineStr">
         <is>
           <t>유치원</t>
         </is>
       </c>
-      <c r="F27" s="36" t="inlineStr">
+      <c r="F27" s="39" t="inlineStr">
         <is>
           <t>정규수업</t>
         </is>
       </c>
-      <c r="G27" s="34" t="inlineStr">
+      <c r="G27" s="37" t="inlineStr">
         <is>
           <t>유치원</t>
         </is>
       </c>
-      <c r="H27" s="34" t="inlineStr">
+      <c r="H27" s="37" t="inlineStr">
         <is>
           <t>하원 시간 늘림</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="39" t="inlineStr">
+      <c r="A28" s="42" t="inlineStr">
         <is>
           <t>둘째</t>
         </is>
       </c>
-      <c r="B28" s="33" t="inlineStr">
+      <c r="B28" s="36" t="inlineStr">
         <is>
           <t>금</t>
         </is>
       </c>
-      <c r="C28" s="33" t="inlineStr">
+      <c r="C28" s="36" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="D28" s="33" t="inlineStr">
+      <c r="D28" s="36" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="E28" s="34" t="inlineStr">
+      <c r="E28" s="37" t="inlineStr">
         <is>
           <t>태권도</t>
         </is>
       </c>
-      <c r="F28" s="37" t="inlineStr">
+      <c r="F28" s="40" t="inlineStr">
         <is>
           <t>학원</t>
         </is>
       </c>
-      <c r="G28" s="34" t="inlineStr">
+      <c r="G28" s="37" t="inlineStr">
         <is>
           <t>태권도장</t>
         </is>
       </c>
-      <c r="H28" s="34" t="inlineStr">
+      <c r="H28" s="37" t="inlineStr">
         <is>
           <t>첫째와 함께 · 이모님 픽업</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="32" t="inlineStr">
+      <c r="A29" s="35" t="inlineStr">
         <is>
           <t>첫째</t>
         </is>
       </c>
-      <c r="B29" s="33" t="inlineStr">
+      <c r="B29" s="36" t="inlineStr">
         <is>
           <t>수</t>
         </is>
       </c>
-      <c r="C29" s="33" t="inlineStr">
+      <c r="C29" s="36" t="inlineStr">
         <is>
           <t>19:30</t>
         </is>
       </c>
-      <c r="D29" s="33" t="inlineStr">
+      <c r="D29" s="36" t="inlineStr">
         <is>
           <t>20:10</t>
         </is>
       </c>
-      <c r="E29" s="34" t="inlineStr">
+      <c r="E29" s="37" t="inlineStr">
         <is>
           <t>첼로</t>
         </is>
       </c>
-      <c r="F29" s="37" t="inlineStr">
+      <c r="F29" s="40" t="inlineStr">
         <is>
           <t>학원</t>
         </is>
       </c>
-      <c r="G29" s="34" t="inlineStr">
+      <c r="G29" s="37" t="inlineStr">
         <is>
           <t>보스턴음악학원</t>
         </is>
       </c>
-      <c r="H29" s="34" t="inlineStr"/>
+      <c r="H29" s="37" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="32" t="inlineStr">
+      <c r="A30" s="35" t="inlineStr">
         <is>
           <t>첫째</t>
         </is>
       </c>
-      <c r="B30" s="33" t="inlineStr">
+      <c r="B30" s="36" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C30" s="33" t="inlineStr">
+      <c r="C30" s="36" t="inlineStr">
         <is>
           <t>16:10</t>
         </is>
       </c>
-      <c r="D30" s="33" t="inlineStr">
+      <c r="D30" s="36" t="inlineStr">
         <is>
           <t>17:10</t>
         </is>
       </c>
-      <c r="E30" s="34" t="inlineStr">
+      <c r="E30" s="37" t="inlineStr">
         <is>
           <t>수영</t>
         </is>
       </c>
-      <c r="F30" s="37" t="inlineStr">
+      <c r="F30" s="40" t="inlineStr">
         <is>
           <t>학원</t>
         </is>
       </c>
-      <c r="G30" s="34" t="inlineStr">
+      <c r="G30" s="37" t="inlineStr">
         <is>
           <t>수영장</t>
         </is>
       </c>
-      <c r="H30" s="34" t="inlineStr"/>
+      <c r="H30" s="37" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="32" t="inlineStr">
+      <c r="A31" s="35" t="inlineStr">
         <is>
           <t>첫째</t>
         </is>
       </c>
-      <c r="B31" s="33" t="inlineStr">
+      <c r="B31" s="36" t="inlineStr">
         <is>
           <t>화</t>
         </is>
       </c>
-      <c r="C31" s="33" t="inlineStr">
+      <c r="C31" s="36" t="inlineStr">
         <is>
           <t>19:00</t>
         </is>
       </c>
-      <c r="D31" s="33" t="inlineStr">
+      <c r="D31" s="36" t="inlineStr">
         <is>
           <t>19:30</t>
         </is>
       </c>
-      <c r="E31" s="34" t="inlineStr">
+      <c r="E31" s="37" t="inlineStr">
         <is>
           <t>화상영어</t>
         </is>
       </c>
-      <c r="F31" s="37" t="inlineStr">
+      <c r="F31" s="40" t="inlineStr">
         <is>
           <t>학원</t>
         </is>
       </c>
-      <c r="G31" s="34" t="inlineStr">
+      <c r="G31" s="37" t="inlineStr">
         <is>
           <t>온라인</t>
         </is>
       </c>
-      <c r="H31" s="34" t="inlineStr"/>
+      <c r="H31" s="37" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="32" t="inlineStr">
+      <c r="A32" s="35" t="inlineStr">
         <is>
           <t>첫째</t>
         </is>
       </c>
-      <c r="B32" s="33" t="inlineStr">
+      <c r="B32" s="36" t="inlineStr">
         <is>
           <t>금</t>
         </is>
       </c>
-      <c r="C32" s="33" t="inlineStr">
+      <c r="C32" s="36" t="inlineStr">
         <is>
           <t>19:00</t>
         </is>
       </c>
-      <c r="D32" s="33" t="inlineStr">
+      <c r="D32" s="36" t="inlineStr">
         <is>
           <t>19:30</t>
         </is>
       </c>
-      <c r="E32" s="34" t="inlineStr">
+      <c r="E32" s="37" t="inlineStr">
         <is>
           <t>화상영어</t>
         </is>
       </c>
-      <c r="F32" s="37" t="inlineStr">
+      <c r="F32" s="40" t="inlineStr">
         <is>
           <t>학원</t>
         </is>
       </c>
-      <c r="G32" s="34" t="inlineStr">
+      <c r="G32" s="37" t="inlineStr">
         <is>
           <t>온라인</t>
         </is>
       </c>
-      <c r="H32" s="34" t="inlineStr"/>
+      <c r="H32" s="37" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="39" t="inlineStr">
+      <c r="A33" s="42" t="inlineStr">
         <is>
           <t>둘째</t>
         </is>
       </c>
-      <c r="B33" s="33" t="inlineStr">
+      <c r="B33" s="36" t="inlineStr">
         <is>
           <t>수</t>
         </is>
       </c>
-      <c r="C33" s="33" t="inlineStr">
+      <c r="C33" s="36" t="inlineStr">
         <is>
           <t>19:30</t>
         </is>
       </c>
-      <c r="D33" s="33" t="inlineStr">
+      <c r="D33" s="36" t="inlineStr">
         <is>
           <t>20:00</t>
         </is>
       </c>
-      <c r="E33" s="34" t="inlineStr">
+      <c r="E33" s="37" t="inlineStr">
         <is>
           <t>축구</t>
         </is>
       </c>
-      <c r="F33" s="37" t="inlineStr">
+      <c r="F33" s="40" t="inlineStr">
         <is>
           <t>학원</t>
         </is>
       </c>
-      <c r="G33" s="34" t="inlineStr">
+      <c r="G33" s="37" t="inlineStr">
         <is>
           <t>축구교실</t>
         </is>
       </c>
-      <c r="H33" s="34" t="inlineStr">
+      <c r="H33" s="37" t="inlineStr">
         <is>
           <t>추정 / ※ 종료시간 추정</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="32" t="inlineStr">
+      <c r="A34" s="35" t="inlineStr">
         <is>
           <t>첫째</t>
         </is>
       </c>
-      <c r="B34" s="33" t="inlineStr">
+      <c r="B34" s="36" t="inlineStr">
         <is>
           <t>수</t>
         </is>
       </c>
-      <c r="C34" s="33" t="inlineStr">
+      <c r="C34" s="36" t="inlineStr">
         <is>
           <t>16:50</t>
         </is>
       </c>
-      <c r="D34" s="33" t="inlineStr">
+      <c r="D34" s="36" t="inlineStr">
         <is>
           <t>17:40</t>
         </is>
       </c>
-      <c r="E34" s="34" t="inlineStr">
+      <c r="E34" s="37" t="inlineStr">
         <is>
           <t>한글수업</t>
         </is>
       </c>
-      <c r="F34" s="37" t="inlineStr">
+      <c r="F34" s="40" t="inlineStr">
         <is>
           <t>학원</t>
         </is>
       </c>
-      <c r="G34" s="34" t="inlineStr">
+      <c r="G34" s="37" t="inlineStr">
         <is>
           <t>집 (과외)</t>
         </is>
       </c>
-      <c r="H34" s="34" t="inlineStr">
-        <is>
-          <t>추정 / ※ 종료시간 추정</t>
-        </is>
-      </c>
+      <c r="H34" s="37" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="32" t="inlineStr">
+      <c r="A35" s="35" t="inlineStr">
         <is>
           <t>첫째</t>
         </is>
       </c>
-      <c r="B35" s="33" t="inlineStr">
+      <c r="B35" s="36" t="inlineStr">
         <is>
           <t>수</t>
         </is>
       </c>
-      <c r="C35" s="33" t="inlineStr">
+      <c r="C35" s="36" t="inlineStr">
         <is>
           <t>12:50</t>
         </is>
       </c>
-      <c r="D35" s="33" t="inlineStr">
+      <c r="D35" s="36" t="inlineStr">
         <is>
           <t>14:20</t>
         </is>
       </c>
-      <c r="E35" s="34" t="inlineStr">
+      <c r="E35" s="37" t="inlineStr">
         <is>
           <t>방과후 아나운서</t>
         </is>
       </c>
-      <c r="F35" s="38" t="inlineStr">
+      <c r="F35" s="41" t="inlineStr">
         <is>
           <t>방과후</t>
         </is>
       </c>
-      <c r="G35" s="34" t="inlineStr">
+      <c r="G35" s="37" t="inlineStr">
         <is>
           <t>학교</t>
         </is>
       </c>
-      <c r="H35" s="34" t="inlineStr"/>
+      <c r="H35" s="37" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="32" t="inlineStr">
+      <c r="A36" s="35" t="inlineStr">
         <is>
           <t>첫째</t>
         </is>
       </c>
-      <c r="B36" s="33" t="inlineStr">
+      <c r="B36" s="36" t="inlineStr">
         <is>
           <t>월</t>
         </is>
       </c>
-      <c r="C36" s="33" t="inlineStr">
+      <c r="C36" s="36" t="inlineStr">
         <is>
           <t>14:00</t>
         </is>
       </c>
-      <c r="D36" s="33" t="inlineStr">
+      <c r="D36" s="36" t="inlineStr">
         <is>
           <t>15:00</t>
         </is>
       </c>
-      <c r="E36" s="34" t="inlineStr">
+      <c r="E36" s="37" t="inlineStr">
         <is>
           <t>태권도</t>
         </is>
       </c>
-      <c r="F36" s="37" t="inlineStr">
+      <c r="F36" s="40" t="inlineStr">
         <is>
           <t>학원</t>
         </is>
       </c>
-      <c r="G36" s="34" t="inlineStr">
+      <c r="G36" s="37" t="inlineStr">
         <is>
           <t>태권도장</t>
         </is>
       </c>
-      <c r="H36" s="34" t="inlineStr"/>
+      <c r="H36" s="37" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="39" t="inlineStr">
+      <c r="A37" s="42" t="inlineStr">
         <is>
           <t>둘째</t>
         </is>
       </c>
-      <c r="B37" s="33" t="inlineStr">
+      <c r="B37" s="36" t="inlineStr">
         <is>
           <t>목</t>
         </is>
       </c>
-      <c r="C37" s="33" t="inlineStr">
+      <c r="C37" s="36" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="D37" s="33" t="inlineStr">
+      <c r="D37" s="36" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="E37" s="34" t="inlineStr">
+      <c r="E37" s="37" t="inlineStr">
         <is>
           <t>태권도</t>
         </is>
       </c>
-      <c r="F37" s="37" t="inlineStr">
+      <c r="F37" s="40" t="inlineStr">
         <is>
           <t>학원</t>
         </is>
       </c>
-      <c r="G37" s="34" t="inlineStr">
+      <c r="G37" s="37" t="inlineStr">
         <is>
           <t>태권도장</t>
         </is>
       </c>
-      <c r="H37" s="34" t="inlineStr"/>
+      <c r="H37" s="37" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/시간표.xlsx
+++ b/시간표.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'첫째 주간표'!$A$1:$H$52</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'둘째 주간표'!$A$1:$H$52</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'두 아이 주간표'!$A$1:$O$53</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'두 아이 주간표'!$A$1:$O$55</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -24,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="29">
+  <fonts count="31">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -140,32 +140,43 @@
     <font>
       <name val="맑은 고딕"/>
       <b val="1"/>
-      <color rgb="007A5E00"/>
+      <color rgb="0020388C"/>
       <sz val="6.5"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
       <b val="1"/>
-      <color rgb="001F4E79"/>
+      <color rgb="0020388C"/>
       <sz val="7.5"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
       <b val="1"/>
-      <color rgb="009C4A16"/>
+      <color rgb="008A4520"/>
       <sz val="7.5"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
       <b val="1"/>
-      <color rgb="009C4A16"/>
+      <color rgb="008A4520"/>
       <sz val="6.5"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
       <b val="1"/>
-      <color rgb="002E6B1F"/>
-      <sz val="7.5"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="0020388C"/>
+      <sz val="7"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="008A4520"/>
+      <sz val="7"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
@@ -190,7 +201,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="23">
     <fill>
       <patternFill/>
     </fill>
@@ -250,6 +261,51 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="002F6FC0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="003B4CB8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C4661F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EFF3FD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDE5F9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9BAEB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C3D0F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FBE6D8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EFB894"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5D0B4"/>
       </patternFill>
     </fill>
     <fill>
@@ -392,7 +448,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -449,10 +505,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -461,47 +517,75 @@
     <xf numFmtId="0" fontId="19" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2532,7 +2616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O53"/>
+  <dimension ref="A1:O55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5.5" customWidth="1" min="1" max="1"/>
@@ -2814,35 +2898,35 @@
         </is>
       </c>
       <c r="B8" s="10" t="n"/>
-      <c r="C8" s="29" t="inlineStr">
+      <c r="C8" s="30" t="inlineStr">
         <is>
           <t>유치원
 09:10–15:10</t>
         </is>
       </c>
       <c r="D8" s="10" t="n"/>
-      <c r="E8" s="29" t="inlineStr">
+      <c r="E8" s="30" t="inlineStr">
         <is>
           <t>유치원
 09:10–15:10</t>
         </is>
       </c>
       <c r="F8" s="10" t="n"/>
-      <c r="G8" s="29" t="inlineStr">
+      <c r="G8" s="30" t="inlineStr">
         <is>
           <t>유치원
 09:10–15:10</t>
         </is>
       </c>
       <c r="H8" s="10" t="n"/>
-      <c r="I8" s="29" t="inlineStr">
+      <c r="I8" s="30" t="inlineStr">
         <is>
           <t>유치원
 09:10–15:10</t>
         </is>
       </c>
       <c r="J8" s="10" t="n"/>
-      <c r="K8" s="29" t="inlineStr">
+      <c r="K8" s="30" t="inlineStr">
         <is>
           <t>유치원
 09:10–15:10</t>
@@ -3146,7 +3230,7 @@
       <c r="C24" s="10" t="n"/>
       <c r="D24" s="10" t="n"/>
       <c r="E24" s="10" t="n"/>
-      <c r="F24" s="30" t="inlineStr">
+      <c r="F24" s="31" t="inlineStr">
         <is>
           <t>방과후 아나운서
 12:50–14:20</t>
@@ -3155,7 +3239,7 @@
       <c r="G24" s="10" t="n"/>
       <c r="H24" s="10" t="n"/>
       <c r="I24" s="10" t="n"/>
-      <c r="J24" s="30" t="inlineStr">
+      <c r="J24" s="31" t="inlineStr">
         <is>
           <t>맞춤형 종이접기
 12:50–14:20</t>
@@ -3196,7 +3280,7 @@
       <c r="E26" s="10" t="n"/>
       <c r="F26" s="10" t="n"/>
       <c r="G26" s="10" t="n"/>
-      <c r="H26" s="30" t="inlineStr">
+      <c r="H26" s="31" t="inlineStr">
         <is>
           <t>방과후 큐보로봇
 13:40–15:10</t>
@@ -3233,14 +3317,14 @@
           <t>14:00</t>
         </is>
       </c>
-      <c r="B28" s="31" t="inlineStr">
+      <c r="B28" s="32" t="inlineStr">
         <is>
           <t>태권도
 14:00–15:00</t>
         </is>
       </c>
       <c r="C28" s="10" t="n"/>
-      <c r="D28" s="31" t="inlineStr">
+      <c r="D28" s="32" t="inlineStr">
         <is>
           <t>태권도
 14:00–15:00</t>
@@ -3289,7 +3373,7 @@
       <c r="G30" s="10" t="n"/>
       <c r="H30" s="10" t="n"/>
       <c r="I30" s="10" t="n"/>
-      <c r="J30" s="31" t="inlineStr">
+      <c r="J30" s="32" t="inlineStr">
         <is>
           <t>미술학원
 14:40–16:00</t>
@@ -3341,7 +3425,7 @@
     </row>
     <row r="33" ht="11.5" customHeight="1">
       <c r="A33" s="27" t="inlineStr"/>
-      <c r="B33" s="31" t="inlineStr">
+      <c r="B33" s="32" t="inlineStr">
         <is>
           <t>한글수업
 15:20–16:10</t>
@@ -3407,7 +3491,7 @@
       </c>
       <c r="B36" s="8" t="n"/>
       <c r="C36" s="5" t="n"/>
-      <c r="D36" s="32" t="inlineStr">
+      <c r="D36" s="33" t="inlineStr">
         <is>
           <t>피아노
 16:00–16:30</t>
@@ -3415,26 +3499,26 @@
       </c>
       <c r="E36" s="5" t="n"/>
       <c r="F36" s="5" t="n"/>
-      <c r="G36" s="32" t="inlineStr">
+      <c r="G36" s="34" t="inlineStr">
         <is>
           <t>한글수업
 16:10–16:40</t>
         </is>
       </c>
       <c r="H36" s="5" t="n"/>
-      <c r="I36" s="31" t="inlineStr">
+      <c r="I36" s="35" t="inlineStr">
         <is>
           <t>태권도
 16:00–17:00</t>
         </is>
       </c>
-      <c r="J36" s="31" t="inlineStr">
+      <c r="J36" s="32" t="inlineStr">
         <is>
           <t>태권도
 16:00–17:00</t>
         </is>
       </c>
-      <c r="K36" s="31" t="inlineStr">
+      <c r="K36" s="35" t="inlineStr">
         <is>
           <t>태권도
 16:00–17:00</t>
@@ -3442,7 +3526,7 @@
       </c>
       <c r="L36" s="5" t="n"/>
       <c r="M36" s="5" t="n"/>
-      <c r="N36" s="31" t="inlineStr">
+      <c r="N36" s="32" t="inlineStr">
         <is>
           <t>수영
 16:10–17:10</t>
@@ -3453,7 +3537,7 @@
     <row r="37" ht="11.5" customHeight="1">
       <c r="A37" s="27" t="inlineStr"/>
       <c r="B37" s="5" t="n"/>
-      <c r="C37" s="32" t="inlineStr">
+      <c r="C37" s="34" t="inlineStr">
         <is>
           <t>한글수업
 16:20–16:50</t>
@@ -3499,7 +3583,7 @@
       <c r="C39" s="8" t="n"/>
       <c r="D39" s="5" t="n"/>
       <c r="E39" s="5" t="n"/>
-      <c r="F39" s="31" t="inlineStr">
+      <c r="F39" s="32" t="inlineStr">
         <is>
           <t>한글수업
 16:50–17:40</t>
@@ -3527,7 +3611,7 @@
       <c r="E40" s="5" t="n"/>
       <c r="F40" s="10" t="n"/>
       <c r="G40" s="5" t="n"/>
-      <c r="H40" s="31" t="inlineStr">
+      <c r="H40" s="32" t="inlineStr">
         <is>
           <t>영어수업
 17:10–18:10</t>
@@ -3680,7 +3764,7 @@
       </c>
       <c r="B48" s="5" t="n"/>
       <c r="C48" s="5" t="n"/>
-      <c r="D48" s="32" t="inlineStr">
+      <c r="D48" s="33" t="inlineStr">
         <is>
           <t>화상영어
 19:00–19:30</t>
@@ -3691,7 +3775,7 @@
       <c r="G48" s="5" t="n"/>
       <c r="H48" s="5" t="n"/>
       <c r="I48" s="5" t="n"/>
-      <c r="J48" s="32" t="inlineStr">
+      <c r="J48" s="33" t="inlineStr">
         <is>
           <t>화상영어
 19:00–19:30</t>
@@ -3730,13 +3814,13 @@
       <c r="C50" s="5" t="n"/>
       <c r="D50" s="5" t="n"/>
       <c r="E50" s="5" t="n"/>
-      <c r="F50" s="31" t="inlineStr">
+      <c r="F50" s="32" t="inlineStr">
         <is>
           <t>첼로
 19:30–20:10</t>
         </is>
       </c>
-      <c r="G50" s="32" t="inlineStr">
+      <c r="G50" s="34" t="inlineStr">
         <is>
           <t>축구
 19:30–20:00</t>
@@ -3806,8 +3890,51 @@
       <c r="N53" s="5" t="n"/>
       <c r="O53" s="5" t="n"/>
     </row>
+    <row r="55" ht="13" customHeight="1">
+      <c r="A55" s="36" t="inlineStr">
+        <is>
+          <t>색상 구분</t>
+        </is>
+      </c>
+      <c r="B55" s="37" t="inlineStr">
+        <is>
+          <t>서원 정규수업</t>
+        </is>
+      </c>
+      <c r="C55" s="22" t="n"/>
+      <c r="D55" s="38" t="inlineStr">
+        <is>
+          <t>서원 방과후</t>
+        </is>
+      </c>
+      <c r="E55" s="22" t="n"/>
+      <c r="F55" s="39" t="inlineStr">
+        <is>
+          <t>서원 학원</t>
+        </is>
+      </c>
+      <c r="G55" s="22" t="n"/>
+      <c r="H55" s="40" t="inlineStr">
+        <is>
+          <t>서준 정규수업</t>
+        </is>
+      </c>
+      <c r="I55" s="22" t="n"/>
+      <c r="J55" s="41" t="inlineStr">
+        <is>
+          <t>서준 방과후</t>
+        </is>
+      </c>
+      <c r="K55" s="22" t="n"/>
+      <c r="L55" s="42" t="inlineStr">
+        <is>
+          <t>서준 학원</t>
+        </is>
+      </c>
+      <c r="M55" s="22" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="44">
+  <mergeCells count="50">
     <mergeCell ref="L2:M2"/>
     <mergeCell ref="I36:I39"/>
     <mergeCell ref="K36:K39"/>
@@ -3815,9 +3942,11 @@
     <mergeCell ref="I8:I32"/>
     <mergeCell ref="K8:K32"/>
     <mergeCell ref="B7:B25"/>
+    <mergeCell ref="H55:I55"/>
     <mergeCell ref="F5:F6"/>
     <mergeCell ref="F24:F29"/>
     <mergeCell ref="D36:D37"/>
+    <mergeCell ref="F55:G55"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="F7:F23"/>
     <mergeCell ref="D2:E2"/>
@@ -3828,6 +3957,8 @@
     <mergeCell ref="C37:C39"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="J24:J29"/>
+    <mergeCell ref="J55:K55"/>
+    <mergeCell ref="L55:M55"/>
     <mergeCell ref="N36:N40"/>
     <mergeCell ref="G36:G38"/>
     <mergeCell ref="B28:B31"/>
@@ -3844,8 +3975,10 @@
     <mergeCell ref="G50:G51"/>
     <mergeCell ref="D5:D6"/>
     <mergeCell ref="H26:H32"/>
+    <mergeCell ref="B55:C55"/>
     <mergeCell ref="H5:H6"/>
     <mergeCell ref="H40:H44"/>
+    <mergeCell ref="D55:E55"/>
     <mergeCell ref="J5:J6"/>
     <mergeCell ref="F39:F42"/>
     <mergeCell ref="J2:K2"/>
@@ -3878,1403 +4011,1403 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="33" t="inlineStr">
+      <c r="A1" s="43" t="inlineStr">
         <is>
           <t>일정 편집용 — 여기 고친 뒤 '주간표 갱신' 요청하면 위 시간표가 다시 그려집니다</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="34" t="inlineStr">
+      <c r="A2" s="44" t="inlineStr">
         <is>
           <t>구분</t>
         </is>
       </c>
-      <c r="B2" s="34" t="inlineStr">
+      <c r="B2" s="44" t="inlineStr">
         <is>
           <t>요일</t>
         </is>
       </c>
-      <c r="C2" s="34" t="inlineStr">
+      <c r="C2" s="44" t="inlineStr">
         <is>
           <t>시작</t>
         </is>
       </c>
-      <c r="D2" s="34" t="inlineStr">
+      <c r="D2" s="44" t="inlineStr">
         <is>
           <t>종료</t>
         </is>
       </c>
-      <c r="E2" s="34" t="inlineStr">
+      <c r="E2" s="44" t="inlineStr">
         <is>
           <t>활동</t>
         </is>
       </c>
-      <c r="F2" s="34" t="inlineStr">
+      <c r="F2" s="44" t="inlineStr">
         <is>
           <t>분류</t>
         </is>
       </c>
-      <c r="G2" s="34" t="inlineStr">
+      <c r="G2" s="44" t="inlineStr">
         <is>
           <t>장소</t>
         </is>
       </c>
-      <c r="H2" s="34" t="inlineStr">
+      <c r="H2" s="44" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="35" t="inlineStr">
+      <c r="A3" s="45" t="inlineStr">
         <is>
           <t>첫째</t>
         </is>
       </c>
-      <c r="B3" s="36" t="inlineStr">
+      <c r="B3" s="46" t="inlineStr">
         <is>
           <t>월</t>
         </is>
       </c>
-      <c r="C3" s="36" t="inlineStr">
+      <c r="C3" s="46" t="inlineStr">
         <is>
           <t>08:20</t>
         </is>
       </c>
-      <c r="D3" s="36" t="inlineStr">
+      <c r="D3" s="46" t="inlineStr">
         <is>
           <t>08:45</t>
         </is>
       </c>
-      <c r="E3" s="37" t="inlineStr">
+      <c r="E3" s="47" t="inlineStr">
         <is>
           <t>등교</t>
         </is>
       </c>
-      <c r="F3" s="38" t="inlineStr">
+      <c r="F3" s="48" t="inlineStr">
         <is>
           <t>돌봄/픽업</t>
         </is>
       </c>
-      <c r="G3" s="37" t="inlineStr">
+      <c r="G3" s="47" t="inlineStr">
         <is>
           <t>집→학교</t>
         </is>
       </c>
-      <c r="H3" s="37" t="inlineStr"/>
+      <c r="H3" s="47" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="35" t="inlineStr">
+      <c r="A4" s="45" t="inlineStr">
         <is>
           <t>첫째</t>
         </is>
       </c>
-      <c r="B4" s="36" t="inlineStr">
+      <c r="B4" s="46" t="inlineStr">
         <is>
           <t>월</t>
         </is>
       </c>
-      <c r="C4" s="36" t="inlineStr">
+      <c r="C4" s="46" t="inlineStr">
         <is>
           <t>08:45</t>
         </is>
       </c>
-      <c r="D4" s="36" t="inlineStr">
+      <c r="D4" s="46" t="inlineStr">
         <is>
           <t>13:30</t>
         </is>
       </c>
-      <c r="E4" s="37" t="inlineStr">
+      <c r="E4" s="47" t="inlineStr">
         <is>
           <t>정규수업</t>
         </is>
       </c>
-      <c r="F4" s="39" t="inlineStr">
+      <c r="F4" s="49" t="inlineStr">
         <is>
           <t>정규수업</t>
         </is>
       </c>
-      <c r="G4" s="37" t="inlineStr">
+      <c r="G4" s="47" t="inlineStr">
         <is>
           <t>○○초</t>
         </is>
       </c>
-      <c r="H4" s="37" t="inlineStr"/>
+      <c r="H4" s="47" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="35" t="inlineStr">
+      <c r="A5" s="45" t="inlineStr">
         <is>
           <t>첫째</t>
         </is>
       </c>
-      <c r="B5" s="36" t="inlineStr">
+      <c r="B5" s="46" t="inlineStr">
         <is>
           <t>월</t>
         </is>
       </c>
-      <c r="C5" s="36" t="inlineStr">
+      <c r="C5" s="46" t="inlineStr">
         <is>
           <t>15:20</t>
         </is>
       </c>
-      <c r="D5" s="36" t="inlineStr">
+      <c r="D5" s="46" t="inlineStr">
         <is>
           <t>16:10</t>
         </is>
       </c>
-      <c r="E5" s="37" t="inlineStr">
+      <c r="E5" s="47" t="inlineStr">
         <is>
           <t>한글수업</t>
         </is>
       </c>
-      <c r="F5" s="40" t="inlineStr">
+      <c r="F5" s="50" t="inlineStr">
         <is>
           <t>학원</t>
         </is>
       </c>
-      <c r="G5" s="37" t="inlineStr">
+      <c r="G5" s="47" t="inlineStr">
         <is>
           <t>집 (과외)</t>
         </is>
       </c>
-      <c r="H5" s="37" t="inlineStr"/>
+      <c r="H5" s="47" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="35" t="inlineStr">
+      <c r="A6" s="45" t="inlineStr">
         <is>
           <t>첫째</t>
         </is>
       </c>
-      <c r="B6" s="36" t="inlineStr">
+      <c r="B6" s="46" t="inlineStr">
         <is>
           <t>화</t>
         </is>
       </c>
-      <c r="C6" s="36" t="inlineStr">
+      <c r="C6" s="46" t="inlineStr">
         <is>
           <t>08:20</t>
         </is>
       </c>
-      <c r="D6" s="36" t="inlineStr">
+      <c r="D6" s="46" t="inlineStr">
         <is>
           <t>08:45</t>
         </is>
       </c>
-      <c r="E6" s="37" t="inlineStr">
+      <c r="E6" s="47" t="inlineStr">
         <is>
           <t>등교</t>
         </is>
       </c>
-      <c r="F6" s="38" t="inlineStr">
+      <c r="F6" s="48" t="inlineStr">
         <is>
           <t>돌봄/픽업</t>
         </is>
       </c>
-      <c r="G6" s="37" t="inlineStr">
+      <c r="G6" s="47" t="inlineStr">
         <is>
           <t>집→학교</t>
         </is>
       </c>
-      <c r="H6" s="37" t="inlineStr"/>
+      <c r="H6" s="47" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="35" t="inlineStr">
+      <c r="A7" s="45" t="inlineStr">
         <is>
           <t>첫째</t>
         </is>
       </c>
-      <c r="B7" s="36" t="inlineStr">
+      <c r="B7" s="46" t="inlineStr">
         <is>
           <t>화</t>
         </is>
       </c>
-      <c r="C7" s="36" t="inlineStr">
+      <c r="C7" s="46" t="inlineStr">
         <is>
           <t>08:45</t>
         </is>
       </c>
-      <c r="D7" s="36" t="inlineStr">
+      <c r="D7" s="46" t="inlineStr">
         <is>
           <t>13:30</t>
         </is>
       </c>
-      <c r="E7" s="37" t="inlineStr">
+      <c r="E7" s="47" t="inlineStr">
         <is>
           <t>정규수업</t>
         </is>
       </c>
-      <c r="F7" s="39" t="inlineStr">
+      <c r="F7" s="49" t="inlineStr">
         <is>
           <t>정규수업</t>
         </is>
       </c>
-      <c r="G7" s="37" t="inlineStr">
+      <c r="G7" s="47" t="inlineStr">
         <is>
           <t>○○초</t>
         </is>
       </c>
-      <c r="H7" s="37" t="inlineStr"/>
+      <c r="H7" s="47" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="35" t="inlineStr">
+      <c r="A8" s="45" t="inlineStr">
         <is>
           <t>첫째</t>
         </is>
       </c>
-      <c r="B8" s="36" t="inlineStr">
+      <c r="B8" s="46" t="inlineStr">
         <is>
           <t>화</t>
         </is>
       </c>
-      <c r="C8" s="36" t="inlineStr">
+      <c r="C8" s="46" t="inlineStr">
         <is>
           <t>14:00</t>
         </is>
       </c>
-      <c r="D8" s="36" t="inlineStr">
+      <c r="D8" s="46" t="inlineStr">
         <is>
           <t>15:00</t>
         </is>
       </c>
-      <c r="E8" s="37" t="inlineStr">
+      <c r="E8" s="47" t="inlineStr">
         <is>
           <t>태권도</t>
         </is>
       </c>
-      <c r="F8" s="40" t="inlineStr">
+      <c r="F8" s="50" t="inlineStr">
         <is>
           <t>학원</t>
         </is>
       </c>
-      <c r="G8" s="37" t="inlineStr">
+      <c r="G8" s="47" t="inlineStr">
         <is>
           <t>태권도장</t>
         </is>
       </c>
-      <c r="H8" s="37" t="inlineStr"/>
+      <c r="H8" s="47" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="35" t="inlineStr">
+      <c r="A9" s="45" t="inlineStr">
         <is>
           <t>첫째</t>
         </is>
       </c>
-      <c r="B9" s="36" t="inlineStr">
+      <c r="B9" s="46" t="inlineStr">
         <is>
           <t>화</t>
         </is>
       </c>
-      <c r="C9" s="36" t="inlineStr">
+      <c r="C9" s="46" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="D9" s="36" t="inlineStr">
+      <c r="D9" s="46" t="inlineStr">
         <is>
           <t>16:30</t>
         </is>
       </c>
-      <c r="E9" s="37" t="inlineStr">
+      <c r="E9" s="47" t="inlineStr">
         <is>
           <t>피아노</t>
         </is>
       </c>
-      <c r="F9" s="40" t="inlineStr">
+      <c r="F9" s="50" t="inlineStr">
         <is>
           <t>학원</t>
         </is>
       </c>
-      <c r="G9" s="37" t="inlineStr">
+      <c r="G9" s="47" t="inlineStr">
         <is>
           <t>집 (과외)</t>
         </is>
       </c>
-      <c r="H9" s="37" t="inlineStr"/>
+      <c r="H9" s="47" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="35" t="inlineStr">
+      <c r="A10" s="45" t="inlineStr">
         <is>
           <t>첫째</t>
         </is>
       </c>
-      <c r="B10" s="36" t="inlineStr">
+      <c r="B10" s="46" t="inlineStr">
         <is>
           <t>수</t>
         </is>
       </c>
-      <c r="C10" s="36" t="inlineStr">
+      <c r="C10" s="46" t="inlineStr">
         <is>
           <t>08:20</t>
         </is>
       </c>
-      <c r="D10" s="36" t="inlineStr">
+      <c r="D10" s="46" t="inlineStr">
         <is>
           <t>08:45</t>
         </is>
       </c>
-      <c r="E10" s="37" t="inlineStr">
+      <c r="E10" s="47" t="inlineStr">
         <is>
           <t>등교</t>
         </is>
       </c>
-      <c r="F10" s="38" t="inlineStr">
+      <c r="F10" s="48" t="inlineStr">
         <is>
           <t>돌봄/픽업</t>
         </is>
       </c>
-      <c r="G10" s="37" t="inlineStr">
+      <c r="G10" s="47" t="inlineStr">
         <is>
           <t>집→학교</t>
         </is>
       </c>
-      <c r="H10" s="37" t="inlineStr"/>
+      <c r="H10" s="47" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="35" t="inlineStr">
+      <c r="A11" s="45" t="inlineStr">
         <is>
           <t>첫째</t>
         </is>
       </c>
-      <c r="B11" s="36" t="inlineStr">
+      <c r="B11" s="46" t="inlineStr">
         <is>
           <t>수</t>
         </is>
       </c>
-      <c r="C11" s="36" t="inlineStr">
+      <c r="C11" s="46" t="inlineStr">
         <is>
           <t>08:45</t>
         </is>
       </c>
-      <c r="D11" s="36" t="inlineStr">
+      <c r="D11" s="46" t="inlineStr">
         <is>
           <t>12:50</t>
         </is>
       </c>
-      <c r="E11" s="37" t="inlineStr">
+      <c r="E11" s="47" t="inlineStr">
         <is>
           <t>정규수업(단축)</t>
         </is>
       </c>
-      <c r="F11" s="39" t="inlineStr">
+      <c r="F11" s="49" t="inlineStr">
         <is>
           <t>정규수업</t>
         </is>
       </c>
-      <c r="G11" s="37" t="inlineStr">
+      <c r="G11" s="47" t="inlineStr">
         <is>
           <t>○○초</t>
         </is>
       </c>
-      <c r="H11" s="37" t="inlineStr"/>
+      <c r="H11" s="47" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="35" t="inlineStr">
+      <c r="A12" s="45" t="inlineStr">
         <is>
           <t>첫째</t>
         </is>
       </c>
-      <c r="B12" s="36" t="inlineStr">
+      <c r="B12" s="46" t="inlineStr">
         <is>
           <t>목</t>
         </is>
       </c>
-      <c r="C12" s="36" t="inlineStr">
+      <c r="C12" s="46" t="inlineStr">
         <is>
           <t>08:20</t>
         </is>
       </c>
-      <c r="D12" s="36" t="inlineStr">
+      <c r="D12" s="46" t="inlineStr">
         <is>
           <t>08:45</t>
         </is>
       </c>
-      <c r="E12" s="37" t="inlineStr">
+      <c r="E12" s="47" t="inlineStr">
         <is>
           <t>등교</t>
         </is>
       </c>
-      <c r="F12" s="38" t="inlineStr">
+      <c r="F12" s="48" t="inlineStr">
         <is>
           <t>돌봄/픽업</t>
         </is>
       </c>
-      <c r="G12" s="37" t="inlineStr">
+      <c r="G12" s="47" t="inlineStr">
         <is>
           <t>집→학교</t>
         </is>
       </c>
-      <c r="H12" s="37" t="inlineStr"/>
+      <c r="H12" s="47" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="35" t="inlineStr">
+      <c r="A13" s="45" t="inlineStr">
         <is>
           <t>첫째</t>
         </is>
       </c>
-      <c r="B13" s="36" t="inlineStr">
+      <c r="B13" s="46" t="inlineStr">
         <is>
           <t>목</t>
         </is>
       </c>
-      <c r="C13" s="36" t="inlineStr">
+      <c r="C13" s="46" t="inlineStr">
         <is>
           <t>08:45</t>
         </is>
       </c>
-      <c r="D13" s="36" t="inlineStr">
+      <c r="D13" s="46" t="inlineStr">
         <is>
           <t>13:30</t>
         </is>
       </c>
-      <c r="E13" s="37" t="inlineStr">
+      <c r="E13" s="47" t="inlineStr">
         <is>
           <t>정규수업</t>
         </is>
       </c>
-      <c r="F13" s="39" t="inlineStr">
+      <c r="F13" s="49" t="inlineStr">
         <is>
           <t>정규수업</t>
         </is>
       </c>
-      <c r="G13" s="37" t="inlineStr">
+      <c r="G13" s="47" t="inlineStr">
         <is>
           <t>○○초</t>
         </is>
       </c>
-      <c r="H13" s="37" t="inlineStr"/>
+      <c r="H13" s="47" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="35" t="inlineStr">
+      <c r="A14" s="45" t="inlineStr">
         <is>
           <t>첫째</t>
         </is>
       </c>
-      <c r="B14" s="36" t="inlineStr">
+      <c r="B14" s="46" t="inlineStr">
         <is>
           <t>목</t>
         </is>
       </c>
-      <c r="C14" s="36" t="inlineStr">
+      <c r="C14" s="46" t="inlineStr">
         <is>
           <t>13:40</t>
         </is>
       </c>
-      <c r="D14" s="36" t="inlineStr">
+      <c r="D14" s="46" t="inlineStr">
         <is>
           <t>15:10</t>
         </is>
       </c>
-      <c r="E14" s="37" t="inlineStr">
+      <c r="E14" s="47" t="inlineStr">
         <is>
           <t>방과후 큐보로봇</t>
         </is>
       </c>
-      <c r="F14" s="41" t="inlineStr">
+      <c r="F14" s="51" t="inlineStr">
         <is>
           <t>방과후</t>
         </is>
       </c>
-      <c r="G14" s="37" t="inlineStr">
+      <c r="G14" s="47" t="inlineStr">
         <is>
           <t>학교</t>
         </is>
       </c>
-      <c r="H14" s="37" t="inlineStr"/>
+      <c r="H14" s="47" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="35" t="inlineStr">
+      <c r="A15" s="45" t="inlineStr">
         <is>
           <t>첫째</t>
         </is>
       </c>
-      <c r="B15" s="36" t="inlineStr">
+      <c r="B15" s="46" t="inlineStr">
         <is>
           <t>목</t>
         </is>
       </c>
-      <c r="C15" s="36" t="inlineStr">
+      <c r="C15" s="46" t="inlineStr">
         <is>
           <t>17:10</t>
         </is>
       </c>
-      <c r="D15" s="36" t="inlineStr">
+      <c r="D15" s="46" t="inlineStr">
         <is>
           <t>18:10</t>
         </is>
       </c>
-      <c r="E15" s="37" t="inlineStr">
+      <c r="E15" s="47" t="inlineStr">
         <is>
           <t>영어수업</t>
         </is>
       </c>
-      <c r="F15" s="40" t="inlineStr">
+      <c r="F15" s="50" t="inlineStr">
         <is>
           <t>학원</t>
         </is>
       </c>
-      <c r="G15" s="37" t="inlineStr">
+      <c r="G15" s="47" t="inlineStr">
         <is>
           <t>집 (과외)</t>
         </is>
       </c>
-      <c r="H15" s="37" t="inlineStr"/>
+      <c r="H15" s="47" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="35" t="inlineStr">
+      <c r="A16" s="45" t="inlineStr">
         <is>
           <t>첫째</t>
         </is>
       </c>
-      <c r="B16" s="36" t="inlineStr">
+      <c r="B16" s="46" t="inlineStr">
         <is>
           <t>금</t>
         </is>
       </c>
-      <c r="C16" s="36" t="inlineStr">
+      <c r="C16" s="46" t="inlineStr">
         <is>
           <t>08:20</t>
         </is>
       </c>
-      <c r="D16" s="36" t="inlineStr">
+      <c r="D16" s="46" t="inlineStr">
         <is>
           <t>08:45</t>
         </is>
       </c>
-      <c r="E16" s="37" t="inlineStr">
+      <c r="E16" s="47" t="inlineStr">
         <is>
           <t>등교</t>
         </is>
       </c>
-      <c r="F16" s="38" t="inlineStr">
+      <c r="F16" s="48" t="inlineStr">
         <is>
           <t>돌봄/픽업</t>
         </is>
       </c>
-      <c r="G16" s="37" t="inlineStr">
+      <c r="G16" s="47" t="inlineStr">
         <is>
           <t>집→학교</t>
         </is>
       </c>
-      <c r="H16" s="37" t="inlineStr"/>
+      <c r="H16" s="47" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="35" t="inlineStr">
+      <c r="A17" s="45" t="inlineStr">
         <is>
           <t>첫째</t>
         </is>
       </c>
-      <c r="B17" s="36" t="inlineStr">
+      <c r="B17" s="46" t="inlineStr">
         <is>
           <t>금</t>
         </is>
       </c>
-      <c r="C17" s="36" t="inlineStr">
+      <c r="C17" s="46" t="inlineStr">
         <is>
           <t>08:45</t>
         </is>
       </c>
-      <c r="D17" s="36" t="inlineStr">
+      <c r="D17" s="46" t="inlineStr">
         <is>
           <t>12:50</t>
         </is>
       </c>
-      <c r="E17" s="37" t="inlineStr">
+      <c r="E17" s="47" t="inlineStr">
         <is>
           <t>정규수업(단축)</t>
         </is>
       </c>
-      <c r="F17" s="39" t="inlineStr">
+      <c r="F17" s="49" t="inlineStr">
         <is>
           <t>정규수업</t>
         </is>
       </c>
-      <c r="G17" s="37" t="inlineStr">
+      <c r="G17" s="47" t="inlineStr">
         <is>
           <t>○○초</t>
         </is>
       </c>
-      <c r="H17" s="37" t="inlineStr"/>
+      <c r="H17" s="47" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="35" t="inlineStr">
+      <c r="A18" s="45" t="inlineStr">
         <is>
           <t>첫째</t>
         </is>
       </c>
-      <c r="B18" s="36" t="inlineStr">
+      <c r="B18" s="46" t="inlineStr">
         <is>
           <t>금</t>
         </is>
       </c>
-      <c r="C18" s="36" t="inlineStr">
+      <c r="C18" s="46" t="inlineStr">
         <is>
           <t>12:50</t>
         </is>
       </c>
-      <c r="D18" s="36" t="inlineStr">
+      <c r="D18" s="46" t="inlineStr">
         <is>
           <t>14:20</t>
         </is>
       </c>
-      <c r="E18" s="37" t="inlineStr">
+      <c r="E18" s="47" t="inlineStr">
         <is>
           <t>맞춤형 종이접기</t>
         </is>
       </c>
-      <c r="F18" s="41" t="inlineStr">
+      <c r="F18" s="51" t="inlineStr">
         <is>
           <t>방과후</t>
         </is>
       </c>
-      <c r="G18" s="37" t="inlineStr">
+      <c r="G18" s="47" t="inlineStr">
         <is>
           <t>학교</t>
         </is>
       </c>
-      <c r="H18" s="37" t="inlineStr">
+      <c r="H18" s="47" t="inlineStr">
         <is>
           <t>무료</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="35" t="inlineStr">
+      <c r="A19" s="45" t="inlineStr">
         <is>
           <t>첫째</t>
         </is>
       </c>
-      <c r="B19" s="36" t="inlineStr">
+      <c r="B19" s="46" t="inlineStr">
         <is>
           <t>금</t>
         </is>
       </c>
-      <c r="C19" s="36" t="inlineStr">
+      <c r="C19" s="46" t="inlineStr">
         <is>
           <t>14:40</t>
         </is>
       </c>
-      <c r="D19" s="36" t="inlineStr">
+      <c r="D19" s="46" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="E19" s="37" t="inlineStr">
+      <c r="E19" s="47" t="inlineStr">
         <is>
           <t>미술학원</t>
         </is>
       </c>
-      <c r="F19" s="40" t="inlineStr">
+      <c r="F19" s="50" t="inlineStr">
         <is>
           <t>학원</t>
         </is>
       </c>
-      <c r="G19" s="37" t="inlineStr">
+      <c r="G19" s="47" t="inlineStr">
         <is>
           <t>봉쁘앙 미술학원</t>
         </is>
       </c>
-      <c r="H19" s="37" t="inlineStr"/>
+      <c r="H19" s="47" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="35" t="inlineStr">
+      <c r="A20" s="45" t="inlineStr">
         <is>
           <t>첫째</t>
         </is>
       </c>
-      <c r="B20" s="36" t="inlineStr">
+      <c r="B20" s="46" t="inlineStr">
         <is>
           <t>금</t>
         </is>
       </c>
-      <c r="C20" s="36" t="inlineStr">
+      <c r="C20" s="46" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="D20" s="36" t="inlineStr">
+      <c r="D20" s="46" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="E20" s="37" t="inlineStr">
+      <c r="E20" s="47" t="inlineStr">
         <is>
           <t>태권도</t>
         </is>
       </c>
-      <c r="F20" s="40" t="inlineStr">
+      <c r="F20" s="50" t="inlineStr">
         <is>
           <t>학원</t>
         </is>
       </c>
-      <c r="G20" s="37" t="inlineStr">
+      <c r="G20" s="47" t="inlineStr">
         <is>
           <t>태권도장</t>
         </is>
       </c>
-      <c r="H20" s="37" t="inlineStr">
+      <c r="H20" s="47" t="inlineStr">
         <is>
           <t>둘째와 함께 · 이모님 픽업</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="42" t="inlineStr">
+      <c r="A21" s="52" t="inlineStr">
         <is>
           <t>둘째</t>
         </is>
       </c>
-      <c r="B21" s="36" t="inlineStr">
+      <c r="B21" s="46" t="inlineStr">
         <is>
           <t>월</t>
         </is>
       </c>
-      <c r="C21" s="36" t="inlineStr">
+      <c r="C21" s="46" t="inlineStr">
         <is>
           <t>09:10</t>
         </is>
       </c>
-      <c r="D21" s="36" t="inlineStr">
+      <c r="D21" s="46" t="inlineStr">
         <is>
           <t>15:10</t>
         </is>
       </c>
-      <c r="E21" s="37" t="inlineStr">
+      <c r="E21" s="47" t="inlineStr">
         <is>
           <t>유치원</t>
         </is>
       </c>
-      <c r="F21" s="39" t="inlineStr">
+      <c r="F21" s="49" t="inlineStr">
         <is>
           <t>정규수업</t>
         </is>
       </c>
-      <c r="G21" s="37" t="inlineStr">
+      <c r="G21" s="47" t="inlineStr">
         <is>
           <t>유치원</t>
         </is>
       </c>
-      <c r="H21" s="37" t="inlineStr"/>
+      <c r="H21" s="47" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="42" t="inlineStr">
+      <c r="A22" s="52" t="inlineStr">
         <is>
           <t>둘째</t>
         </is>
       </c>
-      <c r="B22" s="36" t="inlineStr">
+      <c r="B22" s="46" t="inlineStr">
         <is>
           <t>월</t>
         </is>
       </c>
-      <c r="C22" s="36" t="inlineStr">
+      <c r="C22" s="46" t="inlineStr">
         <is>
           <t>16:20</t>
         </is>
       </c>
-      <c r="D22" s="36" t="inlineStr">
+      <c r="D22" s="46" t="inlineStr">
         <is>
           <t>16:50</t>
         </is>
       </c>
-      <c r="E22" s="37" t="inlineStr">
+      <c r="E22" s="47" t="inlineStr">
         <is>
           <t>한글수업</t>
         </is>
       </c>
-      <c r="F22" s="40" t="inlineStr">
+      <c r="F22" s="50" t="inlineStr">
         <is>
           <t>학원</t>
         </is>
       </c>
-      <c r="G22" s="37" t="inlineStr">
+      <c r="G22" s="47" t="inlineStr">
         <is>
           <t>집 (과외)</t>
         </is>
       </c>
-      <c r="H22" s="37" t="inlineStr"/>
+      <c r="H22" s="47" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="42" t="inlineStr">
+      <c r="A23" s="52" t="inlineStr">
         <is>
           <t>둘째</t>
         </is>
       </c>
-      <c r="B23" s="36" t="inlineStr">
+      <c r="B23" s="46" t="inlineStr">
         <is>
           <t>화</t>
         </is>
       </c>
-      <c r="C23" s="36" t="inlineStr">
+      <c r="C23" s="46" t="inlineStr">
         <is>
           <t>09:10</t>
         </is>
       </c>
-      <c r="D23" s="36" t="inlineStr">
+      <c r="D23" s="46" t="inlineStr">
         <is>
           <t>15:10</t>
         </is>
       </c>
-      <c r="E23" s="37" t="inlineStr">
+      <c r="E23" s="47" t="inlineStr">
         <is>
           <t>유치원</t>
         </is>
       </c>
-      <c r="F23" s="39" t="inlineStr">
+      <c r="F23" s="49" t="inlineStr">
         <is>
           <t>정규수업</t>
         </is>
       </c>
-      <c r="G23" s="37" t="inlineStr">
+      <c r="G23" s="47" t="inlineStr">
         <is>
           <t>유치원</t>
         </is>
       </c>
-      <c r="H23" s="37" t="inlineStr"/>
+      <c r="H23" s="47" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="42" t="inlineStr">
+      <c r="A24" s="52" t="inlineStr">
         <is>
           <t>둘째</t>
         </is>
       </c>
-      <c r="B24" s="36" t="inlineStr">
+      <c r="B24" s="46" t="inlineStr">
         <is>
           <t>수</t>
         </is>
       </c>
-      <c r="C24" s="36" t="inlineStr">
+      <c r="C24" s="46" t="inlineStr">
         <is>
           <t>09:10</t>
         </is>
       </c>
-      <c r="D24" s="36" t="inlineStr">
+      <c r="D24" s="46" t="inlineStr">
         <is>
           <t>15:10</t>
         </is>
       </c>
-      <c r="E24" s="37" t="inlineStr">
+      <c r="E24" s="47" t="inlineStr">
         <is>
           <t>유치원</t>
         </is>
       </c>
-      <c r="F24" s="39" t="inlineStr">
+      <c r="F24" s="49" t="inlineStr">
         <is>
           <t>정규수업</t>
         </is>
       </c>
-      <c r="G24" s="37" t="inlineStr">
+      <c r="G24" s="47" t="inlineStr">
         <is>
           <t>유치원</t>
         </is>
       </c>
-      <c r="H24" s="37" t="inlineStr"/>
+      <c r="H24" s="47" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="42" t="inlineStr">
+      <c r="A25" s="52" t="inlineStr">
         <is>
           <t>둘째</t>
         </is>
       </c>
-      <c r="B25" s="36" t="inlineStr">
+      <c r="B25" s="46" t="inlineStr">
         <is>
           <t>수</t>
         </is>
       </c>
-      <c r="C25" s="36" t="inlineStr">
+      <c r="C25" s="46" t="inlineStr">
         <is>
           <t>16:10</t>
         </is>
       </c>
-      <c r="D25" s="36" t="inlineStr">
+      <c r="D25" s="46" t="inlineStr">
         <is>
           <t>16:40</t>
         </is>
       </c>
-      <c r="E25" s="37" t="inlineStr">
+      <c r="E25" s="47" t="inlineStr">
         <is>
           <t>한글수업</t>
         </is>
       </c>
-      <c r="F25" s="40" t="inlineStr">
+      <c r="F25" s="50" t="inlineStr">
         <is>
           <t>학원</t>
         </is>
       </c>
-      <c r="G25" s="37" t="inlineStr">
+      <c r="G25" s="47" t="inlineStr">
         <is>
           <t>집 (과외)</t>
         </is>
       </c>
-      <c r="H25" s="37" t="inlineStr"/>
+      <c r="H25" s="47" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="42" t="inlineStr">
+      <c r="A26" s="52" t="inlineStr">
         <is>
           <t>둘째</t>
         </is>
       </c>
-      <c r="B26" s="36" t="inlineStr">
+      <c r="B26" s="46" t="inlineStr">
         <is>
           <t>목</t>
         </is>
       </c>
-      <c r="C26" s="36" t="inlineStr">
+      <c r="C26" s="46" t="inlineStr">
         <is>
           <t>09:10</t>
         </is>
       </c>
-      <c r="D26" s="36" t="inlineStr">
+      <c r="D26" s="46" t="inlineStr">
         <is>
           <t>15:10</t>
         </is>
       </c>
-      <c r="E26" s="37" t="inlineStr">
+      <c r="E26" s="47" t="inlineStr">
         <is>
           <t>유치원</t>
         </is>
       </c>
-      <c r="F26" s="39" t="inlineStr">
+      <c r="F26" s="49" t="inlineStr">
         <is>
           <t>정규수업</t>
         </is>
       </c>
-      <c r="G26" s="37" t="inlineStr">
+      <c r="G26" s="47" t="inlineStr">
         <is>
           <t>유치원</t>
         </is>
       </c>
-      <c r="H26" s="37" t="inlineStr"/>
+      <c r="H26" s="47" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="42" t="inlineStr">
+      <c r="A27" s="52" t="inlineStr">
         <is>
           <t>둘째</t>
         </is>
       </c>
-      <c r="B27" s="36" t="inlineStr">
+      <c r="B27" s="46" t="inlineStr">
         <is>
           <t>금</t>
         </is>
       </c>
-      <c r="C27" s="36" t="inlineStr">
+      <c r="C27" s="46" t="inlineStr">
         <is>
           <t>09:10</t>
         </is>
       </c>
-      <c r="D27" s="36" t="inlineStr">
+      <c r="D27" s="46" t="inlineStr">
         <is>
           <t>15:10</t>
         </is>
       </c>
-      <c r="E27" s="37" t="inlineStr">
+      <c r="E27" s="47" t="inlineStr">
         <is>
           <t>유치원</t>
         </is>
       </c>
-      <c r="F27" s="39" t="inlineStr">
+      <c r="F27" s="49" t="inlineStr">
         <is>
           <t>정규수업</t>
         </is>
       </c>
-      <c r="G27" s="37" t="inlineStr">
+      <c r="G27" s="47" t="inlineStr">
         <is>
           <t>유치원</t>
         </is>
       </c>
-      <c r="H27" s="37" t="inlineStr">
+      <c r="H27" s="47" t="inlineStr">
         <is>
           <t>하원 시간 늘림</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="42" t="inlineStr">
+      <c r="A28" s="52" t="inlineStr">
         <is>
           <t>둘째</t>
         </is>
       </c>
-      <c r="B28" s="36" t="inlineStr">
+      <c r="B28" s="46" t="inlineStr">
         <is>
           <t>금</t>
         </is>
       </c>
-      <c r="C28" s="36" t="inlineStr">
+      <c r="C28" s="46" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="D28" s="36" t="inlineStr">
+      <c r="D28" s="46" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="E28" s="37" t="inlineStr">
+      <c r="E28" s="47" t="inlineStr">
         <is>
           <t>태권도</t>
         </is>
       </c>
-      <c r="F28" s="40" t="inlineStr">
+      <c r="F28" s="50" t="inlineStr">
         <is>
           <t>학원</t>
         </is>
       </c>
-      <c r="G28" s="37" t="inlineStr">
+      <c r="G28" s="47" t="inlineStr">
         <is>
           <t>태권도장</t>
         </is>
       </c>
-      <c r="H28" s="37" t="inlineStr">
+      <c r="H28" s="47" t="inlineStr">
         <is>
           <t>첫째와 함께 · 이모님 픽업</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="35" t="inlineStr">
+      <c r="A29" s="45" t="inlineStr">
         <is>
           <t>첫째</t>
         </is>
       </c>
-      <c r="B29" s="36" t="inlineStr">
+      <c r="B29" s="46" t="inlineStr">
         <is>
           <t>수</t>
         </is>
       </c>
-      <c r="C29" s="36" t="inlineStr">
+      <c r="C29" s="46" t="inlineStr">
         <is>
           <t>19:30</t>
         </is>
       </c>
-      <c r="D29" s="36" t="inlineStr">
+      <c r="D29" s="46" t="inlineStr">
         <is>
           <t>20:10</t>
         </is>
       </c>
-      <c r="E29" s="37" t="inlineStr">
+      <c r="E29" s="47" t="inlineStr">
         <is>
           <t>첼로</t>
         </is>
       </c>
-      <c r="F29" s="40" t="inlineStr">
+      <c r="F29" s="50" t="inlineStr">
         <is>
           <t>학원</t>
         </is>
       </c>
-      <c r="G29" s="37" t="inlineStr">
+      <c r="G29" s="47" t="inlineStr">
         <is>
           <t>보스턴음악학원</t>
         </is>
       </c>
-      <c r="H29" s="37" t="inlineStr"/>
+      <c r="H29" s="47" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="35" t="inlineStr">
+      <c r="A30" s="45" t="inlineStr">
         <is>
           <t>첫째</t>
         </is>
       </c>
-      <c r="B30" s="36" t="inlineStr">
+      <c r="B30" s="46" t="inlineStr">
         <is>
           <t>일</t>
         </is>
       </c>
-      <c r="C30" s="36" t="inlineStr">
+      <c r="C30" s="46" t="inlineStr">
         <is>
           <t>16:10</t>
         </is>
       </c>
-      <c r="D30" s="36" t="inlineStr">
+      <c r="D30" s="46" t="inlineStr">
         <is>
           <t>17:10</t>
         </is>
       </c>
-      <c r="E30" s="37" t="inlineStr">
+      <c r="E30" s="47" t="inlineStr">
         <is>
           <t>수영</t>
         </is>
       </c>
-      <c r="F30" s="40" t="inlineStr">
+      <c r="F30" s="50" t="inlineStr">
         <is>
           <t>학원</t>
         </is>
       </c>
-      <c r="G30" s="37" t="inlineStr">
+      <c r="G30" s="47" t="inlineStr">
         <is>
           <t>수영장</t>
         </is>
       </c>
-      <c r="H30" s="37" t="inlineStr"/>
+      <c r="H30" s="47" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="35" t="inlineStr">
+      <c r="A31" s="45" t="inlineStr">
         <is>
           <t>첫째</t>
         </is>
       </c>
-      <c r="B31" s="36" t="inlineStr">
+      <c r="B31" s="46" t="inlineStr">
         <is>
           <t>화</t>
         </is>
       </c>
-      <c r="C31" s="36" t="inlineStr">
+      <c r="C31" s="46" t="inlineStr">
         <is>
           <t>19:00</t>
         </is>
       </c>
-      <c r="D31" s="36" t="inlineStr">
+      <c r="D31" s="46" t="inlineStr">
         <is>
           <t>19:30</t>
         </is>
       </c>
-      <c r="E31" s="37" t="inlineStr">
+      <c r="E31" s="47" t="inlineStr">
         <is>
           <t>화상영어</t>
         </is>
       </c>
-      <c r="F31" s="40" t="inlineStr">
+      <c r="F31" s="50" t="inlineStr">
         <is>
           <t>학원</t>
         </is>
       </c>
-      <c r="G31" s="37" t="inlineStr">
+      <c r="G31" s="47" t="inlineStr">
         <is>
           <t>온라인</t>
         </is>
       </c>
-      <c r="H31" s="37" t="inlineStr"/>
+      <c r="H31" s="47" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="35" t="inlineStr">
+      <c r="A32" s="45" t="inlineStr">
         <is>
           <t>첫째</t>
         </is>
       </c>
-      <c r="B32" s="36" t="inlineStr">
+      <c r="B32" s="46" t="inlineStr">
         <is>
           <t>금</t>
         </is>
       </c>
-      <c r="C32" s="36" t="inlineStr">
+      <c r="C32" s="46" t="inlineStr">
         <is>
           <t>19:00</t>
         </is>
       </c>
-      <c r="D32" s="36" t="inlineStr">
+      <c r="D32" s="46" t="inlineStr">
         <is>
           <t>19:30</t>
         </is>
       </c>
-      <c r="E32" s="37" t="inlineStr">
+      <c r="E32" s="47" t="inlineStr">
         <is>
           <t>화상영어</t>
         </is>
       </c>
-      <c r="F32" s="40" t="inlineStr">
+      <c r="F32" s="50" t="inlineStr">
         <is>
           <t>학원</t>
         </is>
       </c>
-      <c r="G32" s="37" t="inlineStr">
+      <c r="G32" s="47" t="inlineStr">
         <is>
           <t>온라인</t>
         </is>
       </c>
-      <c r="H32" s="37" t="inlineStr"/>
+      <c r="H32" s="47" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="42" t="inlineStr">
+      <c r="A33" s="52" t="inlineStr">
         <is>
           <t>둘째</t>
         </is>
       </c>
-      <c r="B33" s="36" t="inlineStr">
+      <c r="B33" s="46" t="inlineStr">
         <is>
           <t>수</t>
         </is>
       </c>
-      <c r="C33" s="36" t="inlineStr">
+      <c r="C33" s="46" t="inlineStr">
         <is>
           <t>19:30</t>
         </is>
       </c>
-      <c r="D33" s="36" t="inlineStr">
+      <c r="D33" s="46" t="inlineStr">
         <is>
           <t>20:00</t>
         </is>
       </c>
-      <c r="E33" s="37" t="inlineStr">
+      <c r="E33" s="47" t="inlineStr">
         <is>
           <t>축구</t>
         </is>
       </c>
-      <c r="F33" s="40" t="inlineStr">
+      <c r="F33" s="50" t="inlineStr">
         <is>
           <t>학원</t>
         </is>
       </c>
-      <c r="G33" s="37" t="inlineStr">
+      <c r="G33" s="47" t="inlineStr">
         <is>
           <t>축구교실</t>
         </is>
       </c>
-      <c r="H33" s="37" t="inlineStr">
+      <c r="H33" s="47" t="inlineStr">
         <is>
           <t>추정 / ※ 종료시간 추정</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="35" t="inlineStr">
+      <c r="A34" s="45" t="inlineStr">
         <is>
           <t>첫째</t>
         </is>
       </c>
-      <c r="B34" s="36" t="inlineStr">
+      <c r="B34" s="46" t="inlineStr">
         <is>
           <t>수</t>
         </is>
       </c>
-      <c r="C34" s="36" t="inlineStr">
+      <c r="C34" s="46" t="inlineStr">
         <is>
           <t>16:50</t>
         </is>
       </c>
-      <c r="D34" s="36" t="inlineStr">
+      <c r="D34" s="46" t="inlineStr">
         <is>
           <t>17:40</t>
         </is>
       </c>
-      <c r="E34" s="37" t="inlineStr">
+      <c r="E34" s="47" t="inlineStr">
         <is>
           <t>한글수업</t>
         </is>
       </c>
-      <c r="F34" s="40" t="inlineStr">
+      <c r="F34" s="50" t="inlineStr">
         <is>
           <t>학원</t>
         </is>
       </c>
-      <c r="G34" s="37" t="inlineStr">
+      <c r="G34" s="47" t="inlineStr">
         <is>
           <t>집 (과외)</t>
         </is>
       </c>
-      <c r="H34" s="37" t="inlineStr"/>
+      <c r="H34" s="47" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="35" t="inlineStr">
+      <c r="A35" s="45" t="inlineStr">
         <is>
           <t>첫째</t>
         </is>
       </c>
-      <c r="B35" s="36" t="inlineStr">
+      <c r="B35" s="46" t="inlineStr">
         <is>
           <t>수</t>
         </is>
       </c>
-      <c r="C35" s="36" t="inlineStr">
+      <c r="C35" s="46" t="inlineStr">
         <is>
           <t>12:50</t>
         </is>
       </c>
-      <c r="D35" s="36" t="inlineStr">
+      <c r="D35" s="46" t="inlineStr">
         <is>
           <t>14:20</t>
         </is>
       </c>
-      <c r="E35" s="37" t="inlineStr">
+      <c r="E35" s="47" t="inlineStr">
         <is>
           <t>방과후 아나운서</t>
         </is>
       </c>
-      <c r="F35" s="41" t="inlineStr">
+      <c r="F35" s="51" t="inlineStr">
         <is>
           <t>방과후</t>
         </is>
       </c>
-      <c r="G35" s="37" t="inlineStr">
+      <c r="G35" s="47" t="inlineStr">
         <is>
           <t>학교</t>
         </is>
       </c>
-      <c r="H35" s="37" t="inlineStr"/>
+      <c r="H35" s="47" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="35" t="inlineStr">
+      <c r="A36" s="45" t="inlineStr">
         <is>
           <t>첫째</t>
         </is>
       </c>
-      <c r="B36" s="36" t="inlineStr">
+      <c r="B36" s="46" t="inlineStr">
         <is>
           <t>월</t>
         </is>
       </c>
-      <c r="C36" s="36" t="inlineStr">
+      <c r="C36" s="46" t="inlineStr">
         <is>
           <t>14:00</t>
         </is>
       </c>
-      <c r="D36" s="36" t="inlineStr">
+      <c r="D36" s="46" t="inlineStr">
         <is>
           <t>15:00</t>
         </is>
       </c>
-      <c r="E36" s="37" t="inlineStr">
+      <c r="E36" s="47" t="inlineStr">
         <is>
           <t>태권도</t>
         </is>
       </c>
-      <c r="F36" s="40" t="inlineStr">
+      <c r="F36" s="50" t="inlineStr">
         <is>
           <t>학원</t>
         </is>
       </c>
-      <c r="G36" s="37" t="inlineStr">
+      <c r="G36" s="47" t="inlineStr">
         <is>
           <t>태권도장</t>
         </is>
       </c>
-      <c r="H36" s="37" t="inlineStr"/>
+      <c r="H36" s="47" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="42" t="inlineStr">
+      <c r="A37" s="52" t="inlineStr">
         <is>
           <t>둘째</t>
         </is>
       </c>
-      <c r="B37" s="36" t="inlineStr">
+      <c r="B37" s="46" t="inlineStr">
         <is>
           <t>목</t>
         </is>
       </c>
-      <c r="C37" s="36" t="inlineStr">
+      <c r="C37" s="46" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="D37" s="36" t="inlineStr">
+      <c r="D37" s="46" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="E37" s="37" t="inlineStr">
+      <c r="E37" s="47" t="inlineStr">
         <is>
           <t>태권도</t>
         </is>
       </c>
-      <c r="F37" s="40" t="inlineStr">
+      <c r="F37" s="50" t="inlineStr">
         <is>
           <t>학원</t>
         </is>
       </c>
-      <c r="G37" s="37" t="inlineStr">
+      <c r="G37" s="47" t="inlineStr">
         <is>
           <t>태권도장</t>
         </is>
       </c>
-      <c r="H37" s="37" t="inlineStr"/>
+      <c r="H37" s="47" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/시간표.xlsx
+++ b/시간표.xlsx
@@ -1953,32 +1953,31 @@
       <c r="B7" s="9" t="inlineStr">
         <is>
           <t>유치원
-09:10–15:10</t>
+09:00–15:15</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
           <t>유치원
-09:10–15:10</t>
+09:00–15:15</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
           <t>유치원
-09:10–15:10</t>
+09:00–15:15</t>
         </is>
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
           <t>유치원
-09:10–15:10</t>
+09:00–15:15</t>
         </is>
       </c>
       <c r="F7" s="9" t="inlineStr">
         <is>
           <t>유치원
-09:10–15:10
-하원 시간 늘림</t>
+09:00–15:15</t>
         </is>
       </c>
       <c r="G7" s="5" t="n"/>
@@ -2901,35 +2900,35 @@
       <c r="C8" s="30" t="inlineStr">
         <is>
           <t>유치원
-09:10–15:10</t>
+09:00–15:15</t>
         </is>
       </c>
       <c r="D8" s="10" t="n"/>
       <c r="E8" s="30" t="inlineStr">
         <is>
           <t>유치원
-09:10–15:10</t>
+09:00–15:15</t>
         </is>
       </c>
       <c r="F8" s="10" t="n"/>
       <c r="G8" s="30" t="inlineStr">
         <is>
           <t>유치원
-09:10–15:10</t>
+09:00–15:15</t>
         </is>
       </c>
       <c r="H8" s="10" t="n"/>
       <c r="I8" s="30" t="inlineStr">
         <is>
           <t>유치원
-09:10–15:10</t>
+09:00–15:15</t>
         </is>
       </c>
       <c r="J8" s="10" t="n"/>
       <c r="K8" s="30" t="inlineStr">
         <is>
           <t>유치원
-09:10–15:10</t>
+09:00–15:15</t>
         </is>
       </c>
       <c r="L8" s="5" t="n"/>
@@ -4764,12 +4763,12 @@
       </c>
       <c r="C21" s="46" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="D21" s="46" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="E21" s="47" t="inlineStr">
@@ -4840,12 +4839,12 @@
       </c>
       <c r="C23" s="46" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="D23" s="46" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="E23" s="47" t="inlineStr">
@@ -4878,12 +4877,12 @@
       </c>
       <c r="C24" s="46" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="D24" s="46" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="E24" s="47" t="inlineStr">
@@ -4954,12 +4953,12 @@
       </c>
       <c r="C26" s="46" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="D26" s="46" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="E26" s="47" t="inlineStr">
@@ -4992,12 +4991,12 @@
       </c>
       <c r="C27" s="46" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="D27" s="46" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="E27" s="47" t="inlineStr">
@@ -5015,11 +5014,7 @@
           <t>유치원</t>
         </is>
       </c>
-      <c r="H27" s="47" t="inlineStr">
-        <is>
-          <t>하원 시간 늘림</t>
-        </is>
-      </c>
+      <c r="H27" s="47" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="52" t="inlineStr">

--- a/시간표.xlsx
+++ b/시간표.xlsx
@@ -1317,7 +1317,7 @@
         <is>
           <t>방과후 아나운서
 12:50–14:20
-학교</t>
+1-9</t>
         </is>
       </c>
       <c r="E23" s="10" t="n"/>
@@ -1354,7 +1354,7 @@
         <is>
           <t>방과후 큐보로봇
 13:40–15:10
-학교</t>
+과학실1</t>
         </is>
       </c>
       <c r="F25" s="10" t="n"/>
@@ -4509,7 +4509,7 @@
       </c>
       <c r="G14" s="47" t="inlineStr">
         <is>
-          <t>학교</t>
+          <t>과학실1</t>
         </is>
       </c>
       <c r="H14" s="47" t="inlineStr"/>
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G18" s="47" t="inlineStr">
         <is>
-          <t>학교</t>
+          <t>1-6</t>
         </is>
       </c>
       <c r="H18" s="47" t="inlineStr">
@@ -5323,7 +5323,7 @@
       </c>
       <c r="G35" s="47" t="inlineStr">
         <is>
-          <t>학교</t>
+          <t>1-9</t>
         </is>
       </c>
       <c r="H35" s="47" t="inlineStr"/>

--- a/시간표.xlsx
+++ b/시간표.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="첫째 주간표" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="둘째 주간표" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="두 아이 주간표" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="일정(편집용)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="첫째 주간표" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="둘째 주간표" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="두 아이 주간표" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="일정(편집용)" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'첫째 주간표'!$A$1:$H$52</definedName>
@@ -1316,7 +1316,7 @@
       <c r="D23" s="11" t="inlineStr">
         <is>
           <t>방과후 아나운서
-12:50–14:20
+12:50–13:30
 1-9</t>
         </is>
       </c>
@@ -1335,7 +1335,7 @@
       <c r="A24" s="6" t="inlineStr"/>
       <c r="B24" s="8" t="n"/>
       <c r="C24" s="8" t="n"/>
-      <c r="D24" s="10" t="n"/>
+      <c r="D24" s="8" t="n"/>
       <c r="E24" s="8" t="n"/>
       <c r="F24" s="10" t="n"/>
       <c r="G24" s="5" t="n"/>
@@ -1349,7 +1349,7 @@
       </c>
       <c r="B25" s="5" t="n"/>
       <c r="C25" s="5" t="n"/>
-      <c r="D25" s="10" t="n"/>
+      <c r="D25" s="5" t="n"/>
       <c r="E25" s="11" t="inlineStr">
         <is>
           <t>방과후 큐보로봇
@@ -1365,7 +1365,7 @@
       <c r="A26" s="6" t="inlineStr"/>
       <c r="B26" s="5" t="n"/>
       <c r="C26" s="5" t="n"/>
-      <c r="D26" s="10" t="n"/>
+      <c r="D26" s="5" t="n"/>
       <c r="E26" s="10" t="n"/>
       <c r="F26" s="10" t="n"/>
       <c r="G26" s="5" t="n"/>
@@ -1391,7 +1391,7 @@
 태권도장</t>
         </is>
       </c>
-      <c r="D27" s="10" t="n"/>
+      <c r="D27" s="5" t="n"/>
       <c r="E27" s="10" t="n"/>
       <c r="F27" s="10" t="n"/>
       <c r="G27" s="5" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="A28" s="6" t="inlineStr"/>
       <c r="B28" s="10" t="n"/>
       <c r="C28" s="10" t="n"/>
-      <c r="D28" s="8" t="n"/>
+      <c r="D28" s="5" t="n"/>
       <c r="E28" s="10" t="n"/>
       <c r="F28" s="8" t="n"/>
       <c r="G28" s="5" t="n"/>
@@ -1806,7 +1806,6 @@
     <mergeCell ref="C35:C36"/>
     <mergeCell ref="C47:C48"/>
     <mergeCell ref="D4:D5"/>
-    <mergeCell ref="D23:D28"/>
     <mergeCell ref="F47:F48"/>
     <mergeCell ref="C27:C30"/>
     <mergeCell ref="F35:F38"/>
@@ -1821,6 +1820,7 @@
     <mergeCell ref="B4:B5"/>
     <mergeCell ref="F4:F5"/>
     <mergeCell ref="D38:D41"/>
+    <mergeCell ref="D23:D24"/>
     <mergeCell ref="F29:F34"/>
   </mergeCells>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
@@ -3232,7 +3232,7 @@
       <c r="F24" s="31" t="inlineStr">
         <is>
           <t>방과후 아나운서
-12:50–14:20</t>
+12:50–13:30</t>
         </is>
       </c>
       <c r="G24" s="10" t="n"/>
@@ -3256,7 +3256,7 @@
       <c r="C25" s="10" t="n"/>
       <c r="D25" s="8" t="n"/>
       <c r="E25" s="10" t="n"/>
-      <c r="F25" s="10" t="n"/>
+      <c r="F25" s="8" t="n"/>
       <c r="G25" s="10" t="n"/>
       <c r="H25" s="8" t="n"/>
       <c r="I25" s="10" t="n"/>
@@ -3277,7 +3277,7 @@
       <c r="C26" s="10" t="n"/>
       <c r="D26" s="5" t="n"/>
       <c r="E26" s="10" t="n"/>
-      <c r="F26" s="10" t="n"/>
+      <c r="F26" s="5" t="n"/>
       <c r="G26" s="10" t="n"/>
       <c r="H26" s="31" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
       <c r="C27" s="10" t="n"/>
       <c r="D27" s="5" t="n"/>
       <c r="E27" s="10" t="n"/>
-      <c r="F27" s="10" t="n"/>
+      <c r="F27" s="5" t="n"/>
       <c r="G27" s="10" t="n"/>
       <c r="H27" s="10" t="n"/>
       <c r="I27" s="10" t="n"/>
@@ -3330,7 +3330,7 @@
         </is>
       </c>
       <c r="E28" s="10" t="n"/>
-      <c r="F28" s="10" t="n"/>
+      <c r="F28" s="5" t="n"/>
       <c r="G28" s="10" t="n"/>
       <c r="H28" s="10" t="n"/>
       <c r="I28" s="10" t="n"/>
@@ -3347,7 +3347,7 @@
       <c r="C29" s="10" t="n"/>
       <c r="D29" s="10" t="n"/>
       <c r="E29" s="10" t="n"/>
-      <c r="F29" s="8" t="n"/>
+      <c r="F29" s="5" t="n"/>
       <c r="G29" s="10" t="n"/>
       <c r="H29" s="10" t="n"/>
       <c r="I29" s="10" t="n"/>
@@ -3943,7 +3943,6 @@
     <mergeCell ref="B7:B25"/>
     <mergeCell ref="H55:I55"/>
     <mergeCell ref="F5:F6"/>
-    <mergeCell ref="F24:F29"/>
     <mergeCell ref="D36:D37"/>
     <mergeCell ref="F55:G55"/>
     <mergeCell ref="B2:C2"/>
@@ -3983,6 +3982,7 @@
     <mergeCell ref="J2:K2"/>
     <mergeCell ref="A1:O1"/>
     <mergeCell ref="F50:F52"/>
+    <mergeCell ref="F24:F25"/>
     <mergeCell ref="J48:J49"/>
   </mergeCells>
   <pageMargins left="0.18" right="0.18" top="0.22" bottom="0.22" header="0.5" footer="0.5"/>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="D35" s="46" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="E35" s="47" t="inlineStr">
